--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3692" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6096BA85-98AF-4A65-98DD-CC96308A0228}"/>
+  <xr:revisionPtr revIDLastSave="3751" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85046D33-AC8E-4594-A833-5284DF811392}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3311" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="237">
   <si>
     <t>Uke 01</t>
   </si>
@@ -757,6 +757,9 @@
   <si>
     <t>9 SF ADC</t>
   </si>
+  <si>
+    <t>Pilot BO</t>
+  </si>
 </sst>
 </file>
 
@@ -1035,7 +1038,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1285,12 +1288,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1307,6 +1304,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -11039,7 +11039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI60"/>
+  <dimension ref="A1:X60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -11489,22 +11489,22 @@
       </c>
       <c r="O9" s="77"/>
       <c r="P9" s="78"/>
-      <c r="Q9" s="87" t="s">
+      <c r="Q9" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="R9" s="88"/>
-      <c r="S9" s="87" t="s">
+      <c r="R9" s="86"/>
+      <c r="S9" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="T9" s="88"/>
-      <c r="U9" s="87" t="s">
+      <c r="T9" s="86"/>
+      <c r="U9" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="V9" s="88"/>
-      <c r="W9" s="87" t="s">
+      <c r="V9" s="86"/>
+      <c r="W9" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="X9" s="88"/>
+      <c r="X9" s="86"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
@@ -11673,22 +11673,22 @@
       </c>
       <c r="O13" s="77"/>
       <c r="P13" s="78"/>
-      <c r="Q13" s="87" t="s">
+      <c r="Q13" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="R13" s="88"/>
-      <c r="S13" s="87" t="s">
+      <c r="R13" s="86"/>
+      <c r="S13" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="T13" s="88"/>
-      <c r="U13" s="87" t="s">
+      <c r="T13" s="86"/>
+      <c r="U13" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="V13" s="88"/>
-      <c r="W13" s="87" t="s">
+      <c r="V13" s="86"/>
+      <c r="W13" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="X13" s="88"/>
+      <c r="X13" s="86"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -12102,26 +12102,26 @@
       <c r="N24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O24" s="87" t="s">
+      <c r="O24" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="P24" s="88"/>
-      <c r="Q24" s="87" t="s">
+      <c r="P24" s="86"/>
+      <c r="Q24" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="R24" s="88"/>
-      <c r="S24" s="87" t="s">
+      <c r="R24" s="86"/>
+      <c r="S24" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="T24" s="88"/>
-      <c r="U24" s="87" t="s">
+      <c r="T24" s="86"/>
+      <c r="U24" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="V24" s="88"/>
-      <c r="W24" s="87" t="s">
+      <c r="V24" s="86"/>
+      <c r="W24" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="X24" s="88"/>
+      <c r="X24" s="86"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -12240,26 +12240,26 @@
       <c r="N27" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O27" s="87" t="s">
+      <c r="O27" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="P27" s="88"/>
-      <c r="Q27" s="87" t="s">
+      <c r="P27" s="86"/>
+      <c r="Q27" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="R27" s="88"/>
-      <c r="S27" s="87" t="s">
+      <c r="R27" s="86"/>
+      <c r="S27" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="T27" s="88"/>
-      <c r="U27" s="87" t="s">
+      <c r="T27" s="86"/>
+      <c r="U27" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="V27" s="88"/>
-      <c r="W27" s="87" t="s">
+      <c r="V27" s="86"/>
+      <c r="W27" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="X27" s="88"/>
+      <c r="X27" s="86"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="X32" s="40"/>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>49</v>
       </c>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="X34" s="40"/>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="X35" s="18"/>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
       <c r="N36" s="4"/>
@@ -12641,7 +12641,7 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="4"/>
@@ -12649,7 +12649,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="4"/>
@@ -12657,7 +12657,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>182</v>
       </c>
@@ -12727,7 +12727,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="X40" s="46"/>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>10</v>
       </c>
@@ -12810,36 +12810,24 @@
         <v>8</v>
       </c>
       <c r="P41" s="38"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="43"/>
-      <c r="T41" s="44"/>
-      <c r="U41" s="17"/>
+      <c r="Q41" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="R41" s="18"/>
+      <c r="S41" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="T41" s="18"/>
+      <c r="U41" s="17" t="s">
+        <v>169</v>
+      </c>
       <c r="V41" s="18"/>
-      <c r="W41" s="17"/>
+      <c r="W41" s="17" t="s">
+        <v>169</v>
+      </c>
       <c r="X41" s="18"/>
-      <c r="Z41" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA41" s="38"/>
-      <c r="AB41" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="AC41" s="44"/>
-      <c r="AD41" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE41" s="44"/>
-      <c r="AF41" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG41" s="18"/>
-      <c r="AH41" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI41" s="18"/>
-    </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -12868,38 +12856,28 @@
       <c r="N42" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O42" s="69"/>
+      <c r="O42" s="69" t="s">
+        <v>149</v>
+      </c>
       <c r="P42" s="70"/>
-      <c r="Q42" s="69"/>
+      <c r="Q42" s="69" t="s">
+        <v>149</v>
+      </c>
       <c r="R42" s="70"/>
-      <c r="S42" s="69"/>
+      <c r="S42" s="69" t="s">
+        <v>149</v>
+      </c>
       <c r="T42" s="70"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="18"/>
-      <c r="Z42" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA42" s="70"/>
-      <c r="AB42" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="AC42" s="70"/>
-      <c r="AD42" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE42" s="70"/>
-      <c r="AF42" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG42" s="18"/>
-      <c r="AH42" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI42" s="18"/>
-    </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="U42" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="V42" s="34"/>
+      <c r="W42" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="X42" s="34"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
@@ -12926,38 +12904,28 @@
       <c r="N43" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O43" s="17"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="18"/>
-      <c r="S43" s="17"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="17"/>
-      <c r="V43" s="18"/>
-      <c r="W43" s="17"/>
-      <c r="X43" s="18"/>
-      <c r="Z43" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA43" s="18"/>
-      <c r="AB43" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC43" s="18"/>
-      <c r="AD43" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE43" s="18"/>
-      <c r="AF43" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG43" s="18"/>
-      <c r="AH43" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI43" s="18"/>
-    </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="O43" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="R43" s="40"/>
+      <c r="S43" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="T43" s="40"/>
+      <c r="U43" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="V43" s="40"/>
+      <c r="W43" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="X43" s="40"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
@@ -12965,14 +12933,14 @@
         <v>91</v>
       </c>
       <c r="C44" s="44"/>
-      <c r="D44" s="89" t="s">
+      <c r="D44" s="87" t="s">
         <v>185</v>
       </c>
-      <c r="E44" s="90"/>
-      <c r="F44" s="89" t="s">
+      <c r="E44" s="88"/>
+      <c r="F44" s="87" t="s">
         <v>184</v>
       </c>
-      <c r="G44" s="90"/>
+      <c r="G44" s="88"/>
       <c r="H44" s="43" t="s">
         <v>91</v>
       </c>
@@ -13004,86 +12972,56 @@
         <v>91</v>
       </c>
       <c r="X44" s="44"/>
-      <c r="Z44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA44" s="44"/>
-      <c r="AB44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC44" s="44"/>
-      <c r="AD44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE44" s="44"/>
-      <c r="AF44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG44" s="44"/>
-      <c r="AH44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI44" s="44"/>
-    </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="87" t="s">
+      <c r="B45" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="C45" s="88"/>
-      <c r="D45" s="87" t="s">
+      <c r="C45" s="86"/>
+      <c r="D45" s="85" t="s">
         <v>230</v>
       </c>
-      <c r="E45" s="88"/>
-      <c r="F45" s="87" t="s">
+      <c r="E45" s="86"/>
+      <c r="F45" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="G45" s="88"/>
-      <c r="H45" s="87" t="s">
+      <c r="G45" s="86"/>
+      <c r="H45" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="I45" s="88"/>
-      <c r="J45" s="87" t="s">
+      <c r="I45" s="86"/>
+      <c r="J45" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="K45" s="88"/>
+      <c r="K45" s="86"/>
       <c r="N45" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O45" s="17"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="39"/>
-      <c r="V45" s="40"/>
-      <c r="W45" s="39"/>
-      <c r="X45" s="40"/>
-      <c r="Z45" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA45" s="18"/>
-      <c r="AB45" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC45" s="18"/>
-      <c r="AD45" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE45" s="18"/>
-      <c r="AF45" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG45" s="40"/>
-      <c r="AH45" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI45" s="40"/>
-    </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="O45" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="P45" s="70"/>
+      <c r="Q45" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="R45" s="70"/>
+      <c r="S45" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="T45" s="70"/>
+      <c r="U45" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="V45" s="34"/>
+      <c r="W45" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="X45" s="34"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>28</v>
       </c>
@@ -13091,14 +13029,14 @@
         <v>165</v>
       </c>
       <c r="C46" s="40"/>
-      <c r="D46" s="89" t="s">
+      <c r="D46" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="E46" s="90"/>
-      <c r="F46" s="89" t="s">
+      <c r="E46" s="88"/>
+      <c r="F46" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="G46" s="90"/>
+      <c r="G46" s="88"/>
       <c r="H46" s="29" t="s">
         <v>9</v>
       </c>
@@ -13110,61 +13048,51 @@
       <c r="N46" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O46" s="39"/>
-      <c r="P46" s="40"/>
-      <c r="Q46" s="39"/>
-      <c r="R46" s="40"/>
-      <c r="S46" s="39"/>
-      <c r="T46" s="40"/>
-      <c r="U46" s="39"/>
-      <c r="V46" s="40"/>
-      <c r="W46" s="39"/>
-      <c r="X46" s="40"/>
-      <c r="Z46" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA46" s="40"/>
-      <c r="AB46" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC46" s="40"/>
-      <c r="AD46" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE46" s="40"/>
-      <c r="AF46" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG46" s="40"/>
-      <c r="AH46" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI46" s="40"/>
-    </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="O46" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="P46" s="24"/>
+      <c r="Q46" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="R46" s="24"/>
+      <c r="S46" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="T46" s="24"/>
+      <c r="U46" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="V46" s="24"/>
+      <c r="W46" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="X46" s="24"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="87" t="s">
+      <c r="B47" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="C47" s="88"/>
-      <c r="D47" s="87" t="s">
+      <c r="C47" s="86"/>
+      <c r="D47" s="85" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="88"/>
-      <c r="F47" s="87" t="s">
+      <c r="E47" s="86"/>
+      <c r="F47" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="G47" s="88"/>
-      <c r="H47" s="87" t="s">
+      <c r="G47" s="86"/>
+      <c r="H47" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="I47" s="88"/>
-      <c r="J47" s="87" t="s">
+      <c r="I47" s="86"/>
+      <c r="J47" s="85" t="s">
         <v>171</v>
       </c>
-      <c r="K47" s="88"/>
+      <c r="K47" s="86"/>
       <c r="N47" s="6" t="s">
         <v>32</v>
       </c>
@@ -13188,28 +13116,8 @@
         <v>8</v>
       </c>
       <c r="X47" s="38"/>
-      <c r="Z47" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA47" s="38"/>
-      <c r="AB47" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC47" s="38"/>
-      <c r="AD47" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE47" s="38"/>
-      <c r="AF47" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG47" s="38"/>
-      <c r="AH47" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI47" s="38"/>
-    </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>35</v>
       </c>
@@ -13236,38 +13144,28 @@
       <c r="N48" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O48" s="39"/>
+      <c r="O48" s="39" t="s">
+        <v>163</v>
+      </c>
       <c r="P48" s="40"/>
-      <c r="Q48" s="39"/>
+      <c r="Q48" s="39" t="s">
+        <v>163</v>
+      </c>
       <c r="R48" s="40"/>
-      <c r="S48" s="39"/>
+      <c r="S48" s="39" t="s">
+        <v>163</v>
+      </c>
       <c r="T48" s="40"/>
-      <c r="U48" s="23"/>
-      <c r="V48" s="24"/>
-      <c r="W48" s="23"/>
-      <c r="X48" s="24"/>
-      <c r="Z48" s="39" t="s">
+      <c r="U48" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="AA48" s="40"/>
-      <c r="AB48" s="39" t="s">
+      <c r="V48" s="40"/>
+      <c r="W48" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="AC48" s="40"/>
-      <c r="AD48" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE48" s="40"/>
-      <c r="AF48" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG48" s="24"/>
-      <c r="AH48" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI48" s="24"/>
-    </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="X48" s="40"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
@@ -13294,38 +13192,28 @@
       <c r="N49" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O49" s="39"/>
-      <c r="P49" s="40"/>
-      <c r="Q49" s="39"/>
-      <c r="R49" s="40"/>
-      <c r="S49" s="39"/>
-      <c r="T49" s="40"/>
-      <c r="U49" s="33"/>
+      <c r="O49" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="P49" s="44"/>
+      <c r="Q49" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="R49" s="44"/>
+      <c r="S49" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="T49" s="44"/>
+      <c r="U49" s="33" t="s">
+        <v>151</v>
+      </c>
       <c r="V49" s="34"/>
-      <c r="W49" s="33"/>
+      <c r="W49" s="33" t="s">
+        <v>151</v>
+      </c>
       <c r="X49" s="34"/>
-      <c r="Z49" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA49" s="40"/>
-      <c r="AB49" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC49" s="40"/>
-      <c r="AD49" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE49" s="40"/>
-      <c r="AF49" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="AG49" s="34"/>
-      <c r="AH49" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="AI49" s="34"/>
-    </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>40</v>
       </c>
@@ -13354,38 +13242,28 @@
       <c r="N50" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O50" s="23"/>
-      <c r="P50" s="24"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="24"/>
-      <c r="S50" s="23"/>
-      <c r="T50" s="24"/>
-      <c r="U50" s="33"/>
-      <c r="V50" s="34"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="34"/>
-      <c r="Z50" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA50" s="24"/>
-      <c r="AB50" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="AC50" s="24"/>
-      <c r="AD50" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE50" s="24"/>
-      <c r="AF50" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="AG50" s="34"/>
-      <c r="AH50" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="AI50" s="34"/>
-    </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="O50" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="R50" s="18"/>
+      <c r="S50" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="T50" s="18"/>
+      <c r="U50" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="V50" s="18"/>
+      <c r="W50" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="X50" s="18"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>45</v>
       </c>
@@ -13414,38 +13292,28 @@
       <c r="N51" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O51" s="23"/>
+      <c r="O51" s="23" t="s">
+        <v>136</v>
+      </c>
       <c r="P51" s="24"/>
-      <c r="Q51" s="23"/>
+      <c r="Q51" s="23" t="s">
+        <v>136</v>
+      </c>
       <c r="R51" s="24"/>
-      <c r="S51" s="23"/>
+      <c r="S51" s="23" t="s">
+        <v>136</v>
+      </c>
       <c r="T51" s="24"/>
-      <c r="U51" s="33"/>
-      <c r="V51" s="34"/>
-      <c r="W51" s="33"/>
-      <c r="X51" s="34"/>
-      <c r="Z51" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA51" s="24"/>
-      <c r="AB51" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC51" s="24"/>
-      <c r="AD51" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="AE51" s="24"/>
-      <c r="AF51" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="AG51" s="34"/>
-      <c r="AH51" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="AI51" s="34"/>
-    </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="U51" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="V51" s="18"/>
+      <c r="W51" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="X51" s="18"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
@@ -13474,34 +13342,28 @@
       <c r="N52" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O52" s="43"/>
-      <c r="P52" s="44"/>
-      <c r="Q52" s="43"/>
-      <c r="R52" s="44"/>
-      <c r="S52" s="43"/>
-      <c r="T52" s="44"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="30"/>
-      <c r="Z52" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA52" s="44"/>
-      <c r="AB52" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="AC52" s="44"/>
-      <c r="AD52" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE52" s="44"/>
-      <c r="AF52" s="29"/>
-      <c r="AG52" s="30"/>
-      <c r="AH52" s="29"/>
-      <c r="AI52" s="30"/>
-    </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="O52" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="P52" s="40"/>
+      <c r="Q52" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="R52" s="40"/>
+      <c r="S52" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="T52" s="40"/>
+      <c r="U52" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="V52" s="40"/>
+      <c r="W52" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="X52" s="40"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>49</v>
       </c>
@@ -13528,8 +13390,10 @@
       <c r="N53" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O53" s="43"/>
-      <c r="P53" s="44"/>
+      <c r="O53" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="P53" s="18"/>
       <c r="Q53" s="37" t="s">
         <v>8</v>
       </c>
@@ -13546,28 +13410,8 @@
         <v>8</v>
       </c>
       <c r="X53" s="38"/>
-      <c r="Z53" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA53" s="44"/>
-      <c r="AB53" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC53" s="38"/>
-      <c r="AD53" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE53" s="38"/>
-      <c r="AF53" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG53" s="38"/>
-      <c r="AH53" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI53" s="38"/>
-    </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
@@ -13592,34 +13436,24 @@
       <c r="N54" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O54" s="69"/>
-      <c r="P54" s="70"/>
-      <c r="Q54" s="69"/>
-      <c r="R54" s="70"/>
-      <c r="S54" s="69"/>
-      <c r="T54" s="70"/>
+      <c r="O54" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="R54" s="18"/>
+      <c r="S54" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="T54" s="18"/>
       <c r="U54" s="29"/>
       <c r="V54" s="30"/>
       <c r="W54" s="29"/>
       <c r="X54" s="30"/>
-      <c r="Z54" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA54" s="70"/>
-      <c r="AB54" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="AC54" s="70"/>
-      <c r="AD54" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE54" s="70"/>
-      <c r="AF54" s="29"/>
-      <c r="AG54" s="30"/>
-      <c r="AH54" s="29"/>
-      <c r="AI54" s="30"/>
-    </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="8"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -13631,38 +13465,27 @@
       <c r="K55" s="5"/>
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="18"/>
-      <c r="Q55" s="85"/>
-      <c r="R55" s="86"/>
-      <c r="S55" s="17"/>
-      <c r="T55" s="18"/>
-      <c r="U55" s="39"/>
-      <c r="V55" s="40"/>
-      <c r="W55" s="39"/>
-      <c r="X55" s="40"/>
-      <c r="Z55" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA55" s="18"/>
-      <c r="AB55" s="85" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC55" s="86"/>
-      <c r="AD55" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE55" s="18"/>
-      <c r="AF55" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG55" s="40"/>
-      <c r="AH55" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI55" s="40"/>
-    </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="N55" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="O55" s="91" t="s">
+        <v>181</v>
+      </c>
+      <c r="P55" s="91"/>
+      <c r="Q55" s="91" t="s">
+        <v>181</v>
+      </c>
+      <c r="R55" s="91"/>
+      <c r="S55" s="91" t="s">
+        <v>181</v>
+      </c>
+      <c r="T55" s="91"/>
+      <c r="U55" s="29"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="29"/>
+      <c r="X55" s="30"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -13675,7 +13498,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>1</v>
       </c>
@@ -13700,7 +13523,7 @@
       <c r="W57" s="4"/>
       <c r="X57" s="4"/>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>2</v>
       </c>
@@ -13714,7 +13537,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>3</v>
       </c>
@@ -13728,7 +13551,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>4</v>
       </c>
@@ -13737,82 +13560,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="535">
-    <mergeCell ref="Z55:AA55"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="AD55:AE55"/>
-    <mergeCell ref="AF55:AG55"/>
-    <mergeCell ref="AH55:AI55"/>
-    <mergeCell ref="Z54:AA54"/>
-    <mergeCell ref="AB54:AC54"/>
-    <mergeCell ref="AD54:AE54"/>
-    <mergeCell ref="AF54:AG54"/>
-    <mergeCell ref="AH54:AI54"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="AB52:AC52"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AF52:AG52"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="Z53:AA53"/>
-    <mergeCell ref="AB53:AC53"/>
-    <mergeCell ref="AD53:AE53"/>
-    <mergeCell ref="AF53:AG53"/>
-    <mergeCell ref="AH53:AI53"/>
-    <mergeCell ref="Z50:AA50"/>
-    <mergeCell ref="AB50:AC50"/>
-    <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="AF50:AG50"/>
-    <mergeCell ref="AH50:AI50"/>
-    <mergeCell ref="Z51:AA51"/>
-    <mergeCell ref="AB51:AC51"/>
-    <mergeCell ref="AD51:AE51"/>
-    <mergeCell ref="AF51:AG51"/>
-    <mergeCell ref="AH51:AI51"/>
-    <mergeCell ref="Z48:AA48"/>
-    <mergeCell ref="AB48:AC48"/>
-    <mergeCell ref="AD48:AE48"/>
-    <mergeCell ref="AF48:AG48"/>
-    <mergeCell ref="AH48:AI48"/>
-    <mergeCell ref="Z49:AA49"/>
-    <mergeCell ref="AB49:AC49"/>
-    <mergeCell ref="AD49:AE49"/>
-    <mergeCell ref="AF49:AG49"/>
-    <mergeCell ref="AH49:AI49"/>
-    <mergeCell ref="Z46:AA46"/>
-    <mergeCell ref="AB46:AC46"/>
-    <mergeCell ref="AD46:AE46"/>
-    <mergeCell ref="AF46:AG46"/>
-    <mergeCell ref="AH46:AI46"/>
-    <mergeCell ref="Z47:AA47"/>
-    <mergeCell ref="AB47:AC47"/>
-    <mergeCell ref="AD47:AE47"/>
-    <mergeCell ref="AF47:AG47"/>
-    <mergeCell ref="AH47:AI47"/>
-    <mergeCell ref="Z44:AA44"/>
-    <mergeCell ref="AB44:AC44"/>
-    <mergeCell ref="AD44:AE44"/>
-    <mergeCell ref="AF44:AG44"/>
-    <mergeCell ref="AH44:AI44"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="AB45:AC45"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="AF45:AG45"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="Z42:AA42"/>
-    <mergeCell ref="AB42:AC42"/>
-    <mergeCell ref="AD42:AE42"/>
-    <mergeCell ref="AF42:AG42"/>
-    <mergeCell ref="AH42:AI42"/>
-    <mergeCell ref="Z43:AA43"/>
-    <mergeCell ref="AB43:AC43"/>
-    <mergeCell ref="AD43:AE43"/>
-    <mergeCell ref="AF43:AG43"/>
-    <mergeCell ref="AH43:AI43"/>
-    <mergeCell ref="Z41:AA41"/>
-    <mergeCell ref="AB41:AC41"/>
-    <mergeCell ref="AD41:AE41"/>
-    <mergeCell ref="AF41:AG41"/>
-    <mergeCell ref="AH41:AI41"/>
+  <mergeCells count="460">
     <mergeCell ref="O54:P54"/>
     <mergeCell ref="Q54:R54"/>
     <mergeCell ref="S54:T54"/>
@@ -14276,7 +14024,7 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="74" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;22ARBEIDSPLAN SIMULATOROPERATØRER</oddHeader>
     <oddFooter>&amp;CUtarbeidet av Stein Mathisen
@@ -17072,10 +16820,10 @@
       </c>
       <c r="O7" s="29"/>
       <c r="P7" s="30"/>
-      <c r="Q7" s="91" t="s">
+      <c r="Q7" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="R7" s="92"/>
+      <c r="R7" s="90"/>
       <c r="S7" s="83"/>
       <c r="T7" s="84"/>
       <c r="U7" s="83"/>
@@ -17112,10 +16860,10 @@
       </c>
       <c r="O8" s="67"/>
       <c r="P8" s="68"/>
-      <c r="Q8" s="91" t="s">
+      <c r="Q8" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="R8" s="92"/>
+      <c r="R8" s="90"/>
       <c r="S8" s="67"/>
       <c r="T8" s="68"/>
       <c r="U8" s="29"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3751" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85046D33-AC8E-4594-A833-5284DF811392}"/>
+  <xr:revisionPtr revIDLastSave="3763" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D11F4E7-59E2-4641-91F5-797582CCA6E2}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="238">
   <si>
     <t>Uke 01</t>
   </si>
@@ -760,6 +760,9 @@
   <si>
     <t>Pilot BO</t>
   </si>
+  <si>
+    <t>A/tekn</t>
+  </si>
 </sst>
 </file>
 
@@ -1038,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1307,6 +1310,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -11039,7 +11046,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X60"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -12933,10 +12940,10 @@
         <v>91</v>
       </c>
       <c r="C44" s="44"/>
-      <c r="D44" s="87" t="s">
-        <v>185</v>
-      </c>
-      <c r="E44" s="88"/>
+      <c r="D44" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="E44" s="18"/>
       <c r="F44" s="87" t="s">
         <v>184</v>
       </c>
@@ -13121,10 +13128,10 @@
       <c r="A48" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="30"/>
+      <c r="B48" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" s="24"/>
       <c r="D48" s="21" t="s">
         <v>60</v>
       </c>
@@ -13217,10 +13224,10 @@
       <c r="A50" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C50" s="40"/>
+      <c r="B50" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" s="24"/>
       <c r="D50" s="21" t="s">
         <v>67</v>
       </c>
@@ -13415,12 +13422,12 @@
       <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="29"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="E54" s="18"/>
+      <c r="B54" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="C54" s="40"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="30"/>
       <c r="F54" s="17" t="s">
         <v>180</v>
       </c>
@@ -13457,8 +13464,10 @@
       <c r="A55" s="8"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
+      <c r="D55" s="87" t="s">
+        <v>185</v>
+      </c>
+      <c r="E55" s="88"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="J55" s="5"/>
@@ -13497,70 +13506,94 @@
       <c r="K56" s="5"/>
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
+      <c r="N56" s="92"/>
+      <c r="O56" s="93"/>
+      <c r="P56" s="93"/>
+      <c r="Q56" s="93"/>
+      <c r="R56" s="93"/>
+      <c r="S56" s="93"/>
+      <c r="T56" s="93"/>
+      <c r="U56" s="93"/>
+      <c r="V56" s="93"/>
+      <c r="W56" s="93"/>
+      <c r="X56" s="93"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A57" s="5">
-        <v>1</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G57" s="5">
-        <v>5</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="N57" s="7"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
+      <c r="A57" s="8"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
+        <v>1</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G58" s="5">
+        <v>5</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N58" s="7"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A59" s="5">
         <v>2</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G59" s="8">
         <v>6</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H59" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A59" s="8">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A60" s="8">
         <v>3</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G59" s="8">
+      <c r="G60" s="8">
         <v>9</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H60" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A60" s="5">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A61" s="5">
         <v>4</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B61" s="4" t="s">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="460">
+  <mergeCells count="461">
     <mergeCell ref="O54:P54"/>
     <mergeCell ref="Q54:R54"/>
     <mergeCell ref="S54:T54"/>
@@ -13999,6 +14032,7 @@
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="F42:G42"/>
+    <mergeCell ref="D55:E55"/>
     <mergeCell ref="O55:P55"/>
     <mergeCell ref="Q55:R55"/>
     <mergeCell ref="S55:T55"/>
@@ -14024,7 +14058,7 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="74" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="73" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;22ARBEIDSPLAN SIMULATOROPERATØRER</oddHeader>
     <oddFooter>&amp;CUtarbeidet av Stein Mathisen

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3763" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D11F4E7-59E2-4641-91F5-797582CCA6E2}"/>
+  <xr:revisionPtr revIDLastSave="3772" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43294624-4FAD-4EF7-B273-4471092D39FD}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3302" uniqueCount="242">
   <si>
     <t>Uke 01</t>
   </si>
@@ -762,6 +762,18 @@
   </si>
   <si>
     <t>A/tekn</t>
+  </si>
+  <si>
+    <t>9 SF OL 1 PA</t>
+  </si>
+  <si>
+    <t>SF OL 1 MVO</t>
+  </si>
+  <si>
+    <t>SF OL 1 KE</t>
+  </si>
+  <si>
+    <t>SF OL 1 BJG</t>
   </si>
 </sst>
 </file>
@@ -8133,7 +8145,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -8971,278 +8983,130 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="7"/>
+      <c r="O19" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="P19" s="62"/>
     </row>
     <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="7"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3">
-        <v>46111</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="3">
-        <v>46112</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3">
-        <v>46113</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3">
-        <v>46114</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
-        <v>46115</v>
-      </c>
+      <c r="O20" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="P20" s="62"/>
+    </row>
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
-      <c r="N21" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P21" s="3">
-        <v>46132</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R21" s="3">
-        <v>46133</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
-        <v>46134</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="V21" s="3">
-        <v>46135</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="46"/>
-      <c r="F22" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="36"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="P21" s="62"/>
+    </row>
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
-      <c r="N22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O22" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P22" s="46"/>
-      <c r="Q22" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="R22" s="44"/>
-      <c r="S22" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="T22" s="44"/>
-      <c r="U22" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="V22" s="44"/>
-      <c r="W22" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="X22" s="44"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="36"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="P22" s="62"/>
+    </row>
+    <row r="23" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
-      <c r="N23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O23" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="R23" s="38"/>
-      <c r="S23" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="T23" s="38"/>
-      <c r="U23" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="V23" s="38"/>
-      <c r="W23" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="X23" s="38"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="30"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="36"/>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
-      <c r="N24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O24" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="R24" s="24"/>
-      <c r="S24" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="T24" s="70"/>
-      <c r="U24" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="V24" s="22"/>
-      <c r="W24" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="X24" s="70"/>
+      <c r="N24" s="7"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="30"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="36"/>
+        <v>145</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3">
+        <v>46111</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3">
+        <v>46112</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G25" s="3">
+        <v>46113</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="3">
+        <v>46114</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K25" s="3">
+        <v>46115</v>
+      </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="R25" s="34"/>
-      <c r="S25" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="T25" s="24"/>
-      <c r="U25" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="V25" s="34"/>
-      <c r="W25" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="X25" s="22"/>
+        <v>146</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P25" s="3">
+        <v>46132</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R25" s="3">
+        <v>46133</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T25" s="3">
+        <v>46134</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="V25" s="3">
+        <v>46135</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="X25" s="3">
+        <v>46136</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="38"/>
+        <v>7</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="46"/>
+      <c r="D26" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="46"/>
       <c r="F26" s="37" t="s">
         <v>8</v>
       </c>
@@ -9254,12 +9118,12 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O26" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="P26" s="34"/>
+        <v>7</v>
+      </c>
+      <c r="O26" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="P26" s="46"/>
       <c r="Q26" s="43" t="s">
         <v>91</v>
       </c>
@@ -9278,61 +9142,61 @@
       <c r="X26" s="44"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="30"/>
-      <c r="D27" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="30"/>
+      <c r="A27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="38"/>
+      <c r="D27" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="38"/>
+      <c r="F27" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="38"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="35"/>
       <c r="K27" s="36"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O27" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="R27" s="34"/>
-      <c r="S27" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="T27" s="40"/>
-      <c r="U27" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="V27" s="40"/>
-      <c r="W27" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="X27" s="22"/>
+      <c r="N27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O27" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="R27" s="38"/>
+      <c r="S27" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="T27" s="38"/>
+      <c r="U27" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="V27" s="38"/>
+      <c r="W27" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="X27" s="38"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>28</v>
+      <c r="A28" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="29" t="s">
@@ -9345,75 +9209,79 @@
       <c r="K28" s="36"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="P28" s="24"/>
+      <c r="N28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O28" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="P28" s="34"/>
       <c r="Q28" s="23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="R28" s="24"/>
       <c r="S28" s="69" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="T28" s="70"/>
       <c r="U28" s="21" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="V28" s="22"/>
       <c r="W28" s="69" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="X28" s="70"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="30"/>
+      <c r="A29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="34"/>
+      <c r="D29" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="34"/>
       <c r="F29" s="29" t="s">
         <v>9</v>
       </c>
       <c r="G29" s="30"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="32"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="36"/>
       <c r="J29" s="35"/>
       <c r="K29" s="36"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O29" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="P29" s="34"/>
+      <c r="N29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="P29" s="22"/>
       <c r="Q29" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R29" s="34"/>
-      <c r="S29" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="T29" s="34"/>
+      <c r="S29" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="T29" s="24"/>
       <c r="U29" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="V29" s="34"/>
-      <c r="W29" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="X29" s="34"/>
+      <c r="W29" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="X29" s="22"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>35</v>
+      <c r="A30" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B30" s="37" t="s">
         <v>8</v>
@@ -9427,39 +9295,39 @@
         <v>8</v>
       </c>
       <c r="G30" s="38"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="36"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="32"/>
       <c r="J30" s="35"/>
       <c r="K30" s="36"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O30" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="R30" s="24"/>
-      <c r="S30" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="T30" s="40"/>
-      <c r="U30" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="V30" s="40"/>
-      <c r="W30" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="X30" s="34"/>
+      <c r="N30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O30" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="R30" s="44"/>
+      <c r="S30" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="T30" s="44"/>
+      <c r="U30" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="V30" s="44"/>
+      <c r="W30" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="X30" s="44"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
+      <c r="A31" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="B31" s="29" t="s">
         <v>9</v>
@@ -9473,48 +9341,48 @@
         <v>9</v>
       </c>
       <c r="G31" s="30"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="36"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="32"/>
       <c r="J31" s="35"/>
       <c r="K31" s="36"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
-      <c r="N31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O31" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="P31" s="70"/>
-      <c r="Q31" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="R31" s="24"/>
-      <c r="S31" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="T31" s="24"/>
-      <c r="U31" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="V31" s="24"/>
-      <c r="W31" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="X31" s="24"/>
+      <c r="N31" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="R31" s="34"/>
+      <c r="S31" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="T31" s="40"/>
+      <c r="U31" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="V31" s="40"/>
+      <c r="W31" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="X31" s="22"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="34"/>
+      <c r="A32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="18"/>
       <c r="F32" s="29" t="s">
         <v>9</v>
       </c>
@@ -9525,495 +9393,493 @@
       <c r="K32" s="36"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="1" t="s">
-        <v>40</v>
+      <c r="N32" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="O32" s="23" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="P32" s="24"/>
-      <c r="Q32" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="R32" s="22"/>
-      <c r="S32" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="T32" s="24"/>
-      <c r="U32" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="V32" s="24"/>
-      <c r="W32" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="X32" s="24"/>
+      <c r="Q32" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="R32" s="24"/>
+      <c r="S32" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="T32" s="70"/>
+      <c r="U32" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="V32" s="22"/>
+      <c r="W32" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="X32" s="70"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="36"/>
+      <c r="A33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="F33" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="32"/>
       <c r="J33" s="35"/>
       <c r="K33" s="36"/>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="O33" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="R33" s="24"/>
-      <c r="S33" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="T33" s="40"/>
-      <c r="U33" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="V33" s="24"/>
-      <c r="W33" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="X33" s="24"/>
+      <c r="N33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O33" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="R33" s="34"/>
+      <c r="S33" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="T33" s="34"/>
+      <c r="U33" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="V33" s="34"/>
+      <c r="W33" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="X33" s="34"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="30"/>
+      <c r="A34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="38"/>
+      <c r="D34" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="38"/>
+      <c r="F34" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="38"/>
       <c r="H34" s="35"/>
       <c r="I34" s="36"/>
       <c r="J34" s="35"/>
       <c r="K34" s="36"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
-      <c r="N34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O34" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="R34" s="22"/>
-      <c r="S34" s="23" t="s">
+      <c r="N34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O34" s="69" t="s">
+        <v>149</v>
+      </c>
+      <c r="P34" s="70"/>
+      <c r="Q34" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="T34" s="24"/>
+      <c r="R34" s="24"/>
+      <c r="S34" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="T34" s="40"/>
       <c r="U34" s="39" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="V34" s="40"/>
-      <c r="W34" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="X34" s="22"/>
+      <c r="W34" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="X34" s="34"/>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A35" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" s="34"/>
+      <c r="A35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="30"/>
       <c r="F35" s="29" t="s">
         <v>9</v>
       </c>
       <c r="G35" s="30"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="32"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="36"/>
       <c r="J35" s="35"/>
       <c r="K35" s="36"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-      <c r="N35" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="O35" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="81" t="s">
-        <v>139</v>
-      </c>
-      <c r="R35" s="82"/>
-      <c r="S35" s="79" t="s">
+      <c r="N35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="P35" s="70"/>
+      <c r="Q35" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="R35" s="24"/>
+      <c r="S35" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="T35" s="24"/>
+      <c r="U35" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="V35" s="24"/>
+      <c r="W35" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="X35" s="24"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="T35" s="80"/>
-      <c r="U35" s="79" t="s">
+      <c r="C36" s="34"/>
+      <c r="D36" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="V35" s="80"/>
-      <c r="W35" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="X35" s="34"/>
-    </row>
-    <row r="36" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="30"/>
+      <c r="E36" s="34"/>
       <c r="F36" s="29" t="s">
         <v>9</v>
       </c>
       <c r="G36" s="30"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="32"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="36"/>
       <c r="J36" s="35"/>
       <c r="K36" s="36"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O36" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="30"/>
-      <c r="S36" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="T36" s="34"/>
-      <c r="U36" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="V36" s="22"/>
-      <c r="W36" s="29"/>
-      <c r="X36" s="30"/>
-    </row>
-    <row r="37" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="O36" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="R36" s="22"/>
+      <c r="S36" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="T36" s="24"/>
+      <c r="U36" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="V36" s="24"/>
+      <c r="W36" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="X36" s="24"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A37" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="38"/>
+      <c r="D37" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="38"/>
+      <c r="F37" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" s="38"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="36"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-    </row>
-    <row r="38" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
+      <c r="N37" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O37" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="R37" s="24"/>
+      <c r="S37" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="T37" s="40"/>
+      <c r="U37" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="V37" s="24"/>
+      <c r="W37" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="X37" s="24"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="30"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="36"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-    </row>
-    <row r="39" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3">
-        <v>46118</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="3">
-        <v>46119</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G39" s="3">
-        <v>46120</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I39" s="3">
-        <v>46121</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K39" s="3">
-        <v>46122</v>
-      </c>
+      <c r="N38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O38" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="R38" s="22"/>
+      <c r="S38" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="T38" s="24"/>
+      <c r="U38" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="V38" s="40"/>
+      <c r="W38" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="X38" s="22"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A39" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="34"/>
+      <c r="D39" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="E39" s="34"/>
+      <c r="F39" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="36"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P39" s="3">
-        <v>46139</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R39" s="3">
-        <v>46140</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T39" s="3">
-        <v>46141</v>
-      </c>
-      <c r="U39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="V39" s="3">
-        <v>46142</v>
-      </c>
-      <c r="W39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="X39" s="3">
-        <v>46143</v>
-      </c>
+      <c r="N39" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O39" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="81" t="s">
+        <v>139</v>
+      </c>
+      <c r="R39" s="82"/>
+      <c r="S39" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="T39" s="80"/>
+      <c r="U39" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="V39" s="80"/>
+      <c r="W39" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="X39" s="34"/>
     </row>
     <row r="40" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="77"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="24"/>
-      <c r="F40" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="46"/>
-      <c r="H40" s="45" t="s">
+      <c r="E40" s="30"/>
+      <c r="F40" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="I40" s="46"/>
-      <c r="J40" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K40" s="46"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="36"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O40" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P40" s="46"/>
-      <c r="Q40" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R40" s="46"/>
-      <c r="S40" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="T40" s="46"/>
-      <c r="U40" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="V40" s="46"/>
-      <c r="W40" s="35"/>
-      <c r="X40" s="36"/>
+        <v>50</v>
+      </c>
+      <c r="O40" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="T40" s="34"/>
+      <c r="U40" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="V40" s="22"/>
+      <c r="W40" s="29"/>
+      <c r="X40" s="30"/>
     </row>
     <row r="41" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" s="77"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="24"/>
-      <c r="F41" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="30"/>
-      <c r="H41" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" s="30"/>
-      <c r="J41" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="K41" s="30"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O41" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="P41" s="22"/>
-      <c r="Q41" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="R41" s="18"/>
-      <c r="S41" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="T41" s="30"/>
-      <c r="U41" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="V41" s="22"/>
-      <c r="W41" s="35"/>
-      <c r="X41" s="36"/>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="77"/>
-      <c r="C42" s="78"/>
-      <c r="D42" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="E42" s="24"/>
-      <c r="F42" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="G42" s="70"/>
-      <c r="H42" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="I42" s="70"/>
-      <c r="J42" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="K42" s="70"/>
+    </row>
+    <row r="42" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O42" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="R42" s="40"/>
-      <c r="S42" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="T42" s="40"/>
-      <c r="U42" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="V42" s="18"/>
-      <c r="W42" s="35"/>
-      <c r="X42" s="36"/>
     </row>
     <row r="43" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="77"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="E43" s="24"/>
-      <c r="F43" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G43" s="62"/>
-      <c r="H43" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="I43" s="62"/>
-      <c r="J43" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="K43" s="62"/>
+        <v>160</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3">
+        <v>46118</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="3">
+        <v>46119</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
+        <v>46120</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
+        <v>46121</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
+        <v>46122</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
       <c r="N43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O43" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="R43" s="34"/>
-      <c r="S43" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="T43" s="34"/>
-      <c r="U43" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="V43" s="34"/>
-      <c r="W43" s="35"/>
-      <c r="X43" s="36"/>
+        <v>161</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P43" s="3">
+        <v>46139</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R43" s="3">
+        <v>46140</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3">
+        <v>46141</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="V43" s="3">
+        <v>46142</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
+        <v>46143</v>
+      </c>
     </row>
     <row r="44" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B44" s="77"/>
       <c r="C44" s="78"/>
@@ -10021,46 +9887,48 @@
         <v>56</v>
       </c>
       <c r="E44" s="24"/>
-      <c r="F44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="G44" s="44"/>
-      <c r="H44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="I44" s="44"/>
-      <c r="J44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="K44" s="44"/>
+      <c r="F44" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="46"/>
+      <c r="H44" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="46"/>
+      <c r="J44" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" s="46"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
       <c r="N44" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="P44" s="44"/>
-      <c r="Q44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="R44" s="44"/>
-      <c r="S44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="T44" s="44"/>
-      <c r="U44" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="V44" s="44"/>
+        <v>7</v>
+      </c>
+      <c r="O44" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="R44" s="46"/>
+      <c r="S44" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="T44" s="46"/>
+      <c r="U44" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="V44" s="46"/>
       <c r="W44" s="35"/>
       <c r="X44" s="36"/>
     </row>
     <row r="45" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" s="35"/>
-      <c r="C45" s="36"/>
+      <c r="A45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="77"/>
+      <c r="C45" s="78"/>
       <c r="D45" s="23" t="s">
         <v>56</v>
       </c>
@@ -10069,39 +9937,41 @@
         <v>9</v>
       </c>
       <c r="G45" s="30"/>
-      <c r="H45" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I45" s="22"/>
+      <c r="H45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="30"/>
       <c r="J45" s="29" t="s">
         <v>9</v>
       </c>
       <c r="K45" s="30"/>
-      <c r="N45" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O45" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="21" t="s">
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O45" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="R45" s="18"/>
+      <c r="S45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T45" s="30"/>
+      <c r="U45" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="R45" s="22"/>
-      <c r="S45" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="T45" s="18"/>
-      <c r="U45" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="V45" s="30"/>
+      <c r="V45" s="22"/>
       <c r="W45" s="35"/>
       <c r="X45" s="36"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>28</v>
+      <c r="A46" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B46" s="77"/>
       <c r="C46" s="78"/>
@@ -10110,42 +9980,44 @@
       </c>
       <c r="E46" s="24"/>
       <c r="F46" s="69" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G46" s="70"/>
       <c r="H46" s="69" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I46" s="70"/>
       <c r="J46" s="69" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="K46" s="70"/>
-      <c r="N46" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O46" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="R46" s="22"/>
-      <c r="S46" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T46" s="22"/>
-      <c r="U46" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="V46" s="22"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O46" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="P46" s="40"/>
+      <c r="Q46" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="R46" s="40"/>
+      <c r="S46" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="T46" s="40"/>
+      <c r="U46" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="V46" s="18"/>
       <c r="W46" s="35"/>
       <c r="X46" s="36"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>32</v>
+    <row r="47" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B47" s="77"/>
       <c r="C47" s="78"/>
@@ -10154,44 +10026,42 @@
       </c>
       <c r="E47" s="24"/>
       <c r="F47" s="61" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G47" s="62"/>
       <c r="H47" s="61" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="I47" s="62"/>
       <c r="J47" s="61" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K47" s="62"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="6" t="s">
-        <v>32</v>
+      <c r="N47" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="O47" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P47" s="34"/>
       <c r="Q47" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R47" s="34"/>
       <c r="S47" s="33" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="T47" s="34"/>
       <c r="U47" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="V47" s="34"/>
       <c r="W47" s="35"/>
       <c r="X47" s="36"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>35</v>
+    <row r="48" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B48" s="77"/>
       <c r="C48" s="78"/>
@@ -10199,45 +10069,43 @@
         <v>56</v>
       </c>
       <c r="E48" s="24"/>
-      <c r="F48" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="G48" s="24"/>
-      <c r="H48" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I48" s="22"/>
-      <c r="J48" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="K48" s="24"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O48" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="P48" s="22"/>
-      <c r="Q48" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="R48" s="22"/>
-      <c r="S48" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="T48" s="22"/>
-      <c r="U48" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="V48" s="22"/>
+      <c r="F48" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G48" s="44"/>
+      <c r="H48" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="I48" s="44"/>
+      <c r="J48" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="K48" s="44"/>
+      <c r="N48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O48" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="R48" s="44"/>
+      <c r="S48" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="T48" s="44"/>
+      <c r="U48" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="V48" s="44"/>
       <c r="W48" s="35"/>
       <c r="X48" s="36"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
-        <v>37</v>
+    <row r="49" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="B49" s="35"/>
       <c r="C49" s="36"/>
@@ -10245,91 +10113,87 @@
         <v>56</v>
       </c>
       <c r="E49" s="24"/>
-      <c r="F49" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="G49" s="50"/>
-      <c r="H49" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="I49" s="50"/>
-      <c r="J49" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="K49" s="22"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O49" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="P49" s="22"/>
+      <c r="F49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="30"/>
+      <c r="H49" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I49" s="22"/>
+      <c r="J49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K49" s="30"/>
+      <c r="N49" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O49" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="P49" s="18"/>
       <c r="Q49" s="21" t="s">
         <v>67</v>
       </c>
       <c r="R49" s="22"/>
-      <c r="S49" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="T49" s="22"/>
-      <c r="U49" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="V49" s="24"/>
+      <c r="S49" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="T49" s="18"/>
+      <c r="U49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="V49" s="30"/>
       <c r="W49" s="35"/>
       <c r="X49" s="36"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="35"/>
-      <c r="C50" s="36"/>
+      <c r="A50" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" s="77"/>
+      <c r="C50" s="78"/>
       <c r="D50" s="23" t="s">
         <v>56</v>
       </c>
       <c r="E50" s="24"/>
-      <c r="F50" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="G50" s="50"/>
-      <c r="H50" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="I50" s="50"/>
-      <c r="J50" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="K50" s="22"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O50" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="P50" s="40"/>
-      <c r="Q50" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="R50" s="40"/>
-      <c r="S50" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="T50" s="40"/>
-      <c r="U50" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="V50" s="24"/>
+      <c r="F50" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="G50" s="70"/>
+      <c r="H50" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="I50" s="70"/>
+      <c r="J50" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="K50" s="70"/>
+      <c r="N50" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O50" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="R50" s="22"/>
+      <c r="S50" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="T50" s="22"/>
+      <c r="U50" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="V50" s="22"/>
       <c r="W50" s="35"/>
       <c r="X50" s="36"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
-        <v>45</v>
+      <c r="A51" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="B51" s="77"/>
       <c r="C51" s="78"/>
@@ -10337,91 +10201,91 @@
         <v>56</v>
       </c>
       <c r="E51" s="24"/>
-      <c r="F51" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="G51" s="24"/>
-      <c r="H51" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="I51" s="24"/>
-      <c r="J51" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="K51" s="24"/>
+      <c r="F51" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="G51" s="62"/>
+      <c r="H51" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="I51" s="62"/>
+      <c r="J51" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="K51" s="62"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
-      <c r="N51" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="O51" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="P51" s="18"/>
-      <c r="Q51" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="R51" s="18"/>
-      <c r="S51" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="T51" s="18"/>
-      <c r="U51" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="V51" s="18"/>
+      <c r="N51" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O51" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="P51" s="34"/>
+      <c r="Q51" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="R51" s="34"/>
+      <c r="S51" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="T51" s="34"/>
+      <c r="U51" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="V51" s="34"/>
       <c r="W51" s="35"/>
       <c r="X51" s="36"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="36"/>
+      <c r="A52" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="77"/>
+      <c r="C52" s="78"/>
       <c r="D52" s="23" t="s">
         <v>56</v>
       </c>
       <c r="E52" s="24"/>
-      <c r="F52" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="G52" s="62"/>
-      <c r="H52" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="I52" s="62"/>
-      <c r="J52" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="K52" s="62"/>
+      <c r="F52" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="G52" s="24"/>
+      <c r="H52" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I52" s="22"/>
+      <c r="J52" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="K52" s="24"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O52" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="R52" s="34"/>
-      <c r="S52" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="T52" s="34"/>
-      <c r="U52" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="V52" s="34"/>
+      <c r="N52" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O52" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="R52" s="22"/>
+      <c r="S52" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="T52" s="22"/>
+      <c r="U52" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="V52" s="22"/>
       <c r="W52" s="35"/>
       <c r="X52" s="36"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A53" s="12" t="s">
-        <v>49</v>
+      <c r="A53" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B53" s="35"/>
       <c r="C53" s="36"/>
@@ -10429,45 +10293,45 @@
         <v>56</v>
       </c>
       <c r="E53" s="24"/>
-      <c r="F53" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="G53" s="62"/>
-      <c r="H53" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="I53" s="62"/>
-      <c r="J53" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="K53" s="62"/>
+      <c r="F53" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="G53" s="50"/>
+      <c r="H53" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="I53" s="50"/>
+      <c r="J53" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="K53" s="22"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
-      <c r="N53" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="O53" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="P53" s="18"/>
-      <c r="Q53" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="R53" s="18"/>
-      <c r="S53" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="T53" s="18"/>
-      <c r="U53" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="V53" s="18"/>
+      <c r="N53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="R53" s="22"/>
+      <c r="S53" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="T53" s="22"/>
+      <c r="U53" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="V53" s="24"/>
       <c r="W53" s="35"/>
       <c r="X53" s="36"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B54" s="35"/>
       <c r="C54" s="36"/>
@@ -10475,210 +10339,399 @@
         <v>56</v>
       </c>
       <c r="E54" s="24"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I54" s="22"/>
+      <c r="F54" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="G54" s="50"/>
+      <c r="H54" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="I54" s="50"/>
       <c r="J54" s="21" t="s">
         <v>67</v>
       </c>
       <c r="K54" s="22"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
       <c r="N54" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O54" s="39" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P54" s="40"/>
       <c r="Q54" s="39" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R54" s="40"/>
       <c r="S54" s="39" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="T54" s="40"/>
-      <c r="U54" s="83"/>
-      <c r="V54" s="84"/>
+      <c r="U54" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="V54" s="24"/>
       <c r="W54" s="35"/>
       <c r="X54" s="36"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
+      <c r="A55" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="77"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E55" s="24"/>
+      <c r="F55" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="G55" s="24"/>
+      <c r="H55" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="I55" s="24"/>
+      <c r="J55" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="K55" s="24"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O55" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="R55" s="18"/>
+      <c r="S55" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="T55" s="18"/>
+      <c r="U55" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="V55" s="18"/>
+      <c r="W55" s="35"/>
+      <c r="X55" s="36"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A56" s="5">
+      <c r="A56" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="35"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" s="24"/>
+      <c r="F56" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="G56" s="62"/>
+      <c r="H56" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="I56" s="62"/>
+      <c r="J56" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="K56" s="62"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O56" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="P56" s="34"/>
+      <c r="Q56" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="R56" s="34"/>
+      <c r="S56" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="T56" s="34"/>
+      <c r="U56" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="V56" s="34"/>
+      <c r="W56" s="35"/>
+      <c r="X56" s="36"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A57" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="35"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E57" s="24"/>
+      <c r="F57" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="G57" s="62"/>
+      <c r="H57" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="I57" s="62"/>
+      <c r="J57" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="K57" s="62"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O57" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="P57" s="18"/>
+      <c r="Q57" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="R57" s="18"/>
+      <c r="S57" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="T57" s="18"/>
+      <c r="U57" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="V57" s="18"/>
+      <c r="W57" s="35"/>
+      <c r="X57" s="36"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B58" s="35"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" s="24"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I58" s="22"/>
+      <c r="J58" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="K58" s="22"/>
+      <c r="N58" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O58" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="P58" s="40"/>
+      <c r="Q58" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="R58" s="40"/>
+      <c r="S58" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="T58" s="40"/>
+      <c r="U58" s="83"/>
+      <c r="V58" s="84"/>
+      <c r="W58" s="35"/>
+      <c r="X58" s="36"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A60" s="5">
         <v>1</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F60" s="5">
         <v>5</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G60" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A57" s="5">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A61" s="5">
         <v>2</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F61" s="8">
         <v>6</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A58" s="8">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
         <v>3</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B62" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F62" s="8">
         <v>9</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A59" s="5">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A63" s="5">
         <v>4</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B63" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-    </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-    </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="452">
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="U54:V54"/>
-    <mergeCell ref="W54:X54"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="S50:T50"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Xe524nFCx6bXV6lOIpMMS5jP996AfIafj6iK299GrdD7kpvf4IeSIycKfuLjwFGS4zSu2tB310/InEqNBds53A==" saltValue="0Bp3Y7SZUBqTdFnHoP6csQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="456">
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="W58:X58"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="S54:T54"/>
+    <mergeCell ref="S55:T55"/>
+    <mergeCell ref="S52:T52"/>
+    <mergeCell ref="W56:X56"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="Q57:R57"/>
+    <mergeCell ref="S57:T57"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="W57:X57"/>
+    <mergeCell ref="S56:T56"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:R56"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="U49:V49"/>
     <mergeCell ref="S51:T51"/>
-    <mergeCell ref="S48:T48"/>
-    <mergeCell ref="W52:X52"/>
-    <mergeCell ref="O53:P53"/>
-    <mergeCell ref="Q53:R53"/>
-    <mergeCell ref="S53:T53"/>
-    <mergeCell ref="U53:V53"/>
-    <mergeCell ref="W53:X53"/>
-    <mergeCell ref="S52:T52"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="Q52:R52"/>
-    <mergeCell ref="U52:V52"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="W51:X51"/>
+    <mergeCell ref="S49:T49"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W48:X48"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="Q48:R48"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="Q46:R46"/>
+    <mergeCell ref="W47:X47"/>
+    <mergeCell ref="W46:X46"/>
+    <mergeCell ref="S47:T47"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="W26:X26"/>
     <mergeCell ref="F30:G30"/>
-    <mergeCell ref="W27:X27"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="W46:X46"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="S47:T47"/>
-    <mergeCell ref="W47:X47"/>
-    <mergeCell ref="S45:T45"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="W45:X45"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W44:X44"/>
-    <mergeCell ref="U44:V44"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="W43:X43"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="S43:T43"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="O26:P26"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="H27:I27"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="O18:P18"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J26:K26"/>
     <mergeCell ref="H16:I16"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O22:P22"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="S13:T13"/>
     <mergeCell ref="J14:K14"/>
@@ -10704,13 +10757,13 @@
     <mergeCell ref="U5:V5"/>
     <mergeCell ref="U6:V6"/>
     <mergeCell ref="W2:X2"/>
-    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J36:K36"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="Q5:R5"/>
     <mergeCell ref="Q6:R6"/>
     <mergeCell ref="S5:T5"/>
     <mergeCell ref="S9:T9"/>
-    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="W28:X28"/>
     <mergeCell ref="S8:T8"/>
     <mergeCell ref="Q9:R9"/>
     <mergeCell ref="Q10:R10"/>
@@ -10718,14 +10771,14 @@
     <mergeCell ref="S11:T11"/>
     <mergeCell ref="U11:V11"/>
     <mergeCell ref="W11:X11"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="U35:V35"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="W12:X12"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="H2:I2"/>
@@ -10744,29 +10797,29 @@
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="J16:K16"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:I55"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J45:K45"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F14:G14"/>
@@ -10784,64 +10837,64 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="H47:I47"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="W51:X51"/>
-    <mergeCell ref="U50:V50"/>
-    <mergeCell ref="S49:T49"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="U48:V48"/>
-    <mergeCell ref="W48:X48"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
     <mergeCell ref="J51:K51"/>
-    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="W53:X53"/>
+    <mergeCell ref="W55:X55"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="W52:X52"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="W54:X54"/>
     <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="W29:X29"/>
     <mergeCell ref="Q15:R15"/>
     <mergeCell ref="S15:T15"/>
     <mergeCell ref="W15:X15"/>
-    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U28:V28"/>
     <mergeCell ref="W9:X9"/>
     <mergeCell ref="U9:V9"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="U32:V32"/>
     <mergeCell ref="U34:V34"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="W26:X26"/>
     <mergeCell ref="U15:V15"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:T26"/>
     <mergeCell ref="W3:X3"/>
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="W8:X8"/>
@@ -10888,146 +10941,146 @@
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="W45:X45"/>
+    <mergeCell ref="W40:X40"/>
+    <mergeCell ref="W44:X44"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="Q44:R44"/>
     <mergeCell ref="U40:V40"/>
-    <mergeCell ref="W41:X41"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W40:X40"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="Q45:R45"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="O45:P45"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="F40:G40"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="J44:K44"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="W16:X16"/>
     <mergeCell ref="S16:T16"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="F49:G49"/>
     <mergeCell ref="F47:G47"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="O51:P51"/>
+    <mergeCell ref="Q51:R51"/>
     <mergeCell ref="O47:P47"/>
-    <mergeCell ref="Q47:R47"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="S50:T50"/>
+    <mergeCell ref="S48:T48"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="S45:T45"/>
+    <mergeCell ref="O46:P46"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="S46:T46"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="S27:T27"/>
     <mergeCell ref="O29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="S46:T46"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="O45:P45"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="O38:P38"/>
     <mergeCell ref="O32:P32"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="O28:P28"/>
     <mergeCell ref="Q16:R16"/>
     <mergeCell ref="O16:P16"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="U29:V29"/>
     <mergeCell ref="S28:T28"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="U30:V30"/>
     <mergeCell ref="U17:V17"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="S54:T54"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="Q43:R43"/>
-    <mergeCell ref="O51:P51"/>
-    <mergeCell ref="Q51:R51"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="S58:T58"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="Q47:R47"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="Q55:R55"/>
+    <mergeCell ref="O54:P54"/>
+    <mergeCell ref="Q54:R54"/>
+    <mergeCell ref="O53:P53"/>
+    <mergeCell ref="Q53:R53"/>
+    <mergeCell ref="Q52:R52"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:R58"/>
+    <mergeCell ref="Q49:R49"/>
     <mergeCell ref="O50:P50"/>
     <mergeCell ref="Q50:R50"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="Q48:R48"/>
-    <mergeCell ref="O48:P48"/>
-    <mergeCell ref="O54:P54"/>
-    <mergeCell ref="Q54:R54"/>
-    <mergeCell ref="Q45:R45"/>
-    <mergeCell ref="O46:P46"/>
-    <mergeCell ref="Q46:R46"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3784" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E4D1262-1785-4BAF-A62D-58A8B16089DF}"/>
+  <xr:revisionPtr revIDLastSave="3798" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E193CF3-D573-44F3-AC64-F5ACFF0C1563}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3303" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3303" uniqueCount="244">
   <si>
     <t>Uke 01</t>
   </si>
@@ -774,6 +774,12 @@
   </si>
   <si>
     <t>SF OL 1 BJG</t>
+  </si>
+  <si>
+    <t>SF KUT SUR RTC</t>
+  </si>
+  <si>
+    <t>SF KUT SUR HF</t>
   </si>
 </sst>
 </file>
@@ -8162,8 +8168,7 @@
     <col min="20" max="20" width="5.7109375" style="5" customWidth="1"/>
     <col min="21" max="21" width="6.140625" style="5" customWidth="1"/>
     <col min="22" max="22" width="5.7109375" style="5" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="5" customWidth="1"/>
-    <col min="24" max="24" width="5.7109375" style="5" customWidth="1"/>
+    <col min="23" max="24" width="6.7109375" style="5" customWidth="1"/>
     <col min="25" max="25" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="5.85546875" style="5" customWidth="1"/>
     <col min="27" max="16384" width="11.42578125" style="5"/>
@@ -8377,7 +8382,7 @@
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="35" t="s">
-        <v>124</v>
+        <v>242</v>
       </c>
       <c r="X4" s="36"/>
     </row>
@@ -8513,15 +8518,15 @@
       </c>
       <c r="R7" s="22"/>
       <c r="S7" s="35" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="T7" s="36"/>
       <c r="U7" s="35" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="V7" s="36"/>
       <c r="W7" s="35" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="X7" s="36"/>
     </row>
@@ -9481,7 +9486,7 @@
       </c>
       <c r="P34" s="68"/>
       <c r="Q34" s="35" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="R34" s="36"/>
       <c r="S34" s="21" t="s">
@@ -9577,15 +9582,15 @@
       </c>
       <c r="R36" s="26"/>
       <c r="S36" s="35" t="s">
-        <v>123</v>
+        <v>242</v>
       </c>
       <c r="T36" s="36"/>
       <c r="U36" s="35" t="s">
-        <v>123</v>
+        <v>243</v>
       </c>
       <c r="V36" s="36"/>
       <c r="W36" s="35" t="s">
-        <v>123</v>
+        <v>243</v>
       </c>
       <c r="X36" s="36"/>
     </row>
@@ -9615,11 +9620,11 @@
         <v>45</v>
       </c>
       <c r="O37" s="35" t="s">
-        <v>152</v>
+        <v>242</v>
       </c>
       <c r="P37" s="36"/>
       <c r="Q37" s="35" t="s">
-        <v>152</v>
+        <v>242</v>
       </c>
       <c r="R37" s="36"/>
       <c r="S37" s="21" t="s">
@@ -9669,7 +9674,7 @@
       </c>
       <c r="R38" s="26"/>
       <c r="S38" s="35" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="T38" s="36"/>
       <c r="U38" s="21" t="s">
@@ -9707,7 +9712,7 @@
         <v>49</v>
       </c>
       <c r="O39" s="35" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="P39" s="36"/>
       <c r="Q39" s="83" t="s">
@@ -10615,7 +10620,7 @@
       <c r="C66" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Xe524nFCx6bXV6lOIpMMS5jP996AfIafj6iK299GrdD7kpvf4IeSIycKfuLjwFGS4zSu2tB310/InEqNBds53A==" saltValue="0Bp3Y7SZUBqTdFnHoP6csQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="aUVD3VdlkK1YpPyFtrXQSGA4kaJBiGelKjiebi575loUWUwItxNTduIjU42h9Ev50qZN2VgPxOJa2kw/nK9NjA==" saltValue="fEtkS+8VALBPYHMd5wj1cg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="456">
     <mergeCell ref="S38:T38"/>
     <mergeCell ref="Q37:R37"/>
@@ -13697,6 +13702,7 @@
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="F43:G43"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="B2:C2"/>
@@ -13994,7 +14000,6 @@
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="Q35:R35"/>
     <mergeCell ref="J44:K44"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="H33:I33"/>
@@ -25869,16 +25874,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3852" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C96D9547-4521-444D-A1BF-2F128D54CA99}"/>
+  <xr:revisionPtr revIDLastSave="3865" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD523C02-A485-4649-B6CD-780259312918}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3312" uniqueCount="246">
   <si>
     <t>Uke 01</t>
   </si>
@@ -584,6 +584,9 @@
     <t>SE MØ 2</t>
   </si>
   <si>
+    <t>A/AFIS-opptak</t>
+  </si>
+  <si>
     <t>SF TC 1</t>
   </si>
   <si>
@@ -641,9 +644,6 @@
     <t>9 SE RTC 1</t>
   </si>
   <si>
-    <t>9 SE SUR SB</t>
-  </si>
-  <si>
     <t>9 SF SUR SB</t>
   </si>
   <si>
@@ -663,6 +663,9 @@
   </si>
   <si>
     <t>Eksamen</t>
+  </si>
+  <si>
+    <t>9 SE SUR SB</t>
   </si>
   <si>
     <t>SF ADC</t>
@@ -10004,7 +10007,7 @@
       </c>
       <c r="R45" s="32"/>
       <c r="S45" s="27" t="s">
-        <v>9</v>
+        <v>169</v>
       </c>
       <c r="T45" s="28"/>
       <c r="U45" s="25" t="s">
@@ -10042,15 +10045,15 @@
         <v>15</v>
       </c>
       <c r="O46" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="20"/>
       <c r="Q46" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R46" s="20"/>
       <c r="S46" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T46" s="20"/>
       <c r="U46" s="31" t="s">
@@ -10293,7 +10296,7 @@
       </c>
       <c r="E52" s="18"/>
       <c r="F52" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G52" s="18"/>
       <c r="H52" s="25" t="s">
@@ -10301,7 +10304,7 @@
       </c>
       <c r="I52" s="26"/>
       <c r="J52" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K52" s="18"/>
       <c r="L52" s="5"/>
@@ -10402,15 +10405,15 @@
         <v>40</v>
       </c>
       <c r="O54" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P54" s="20"/>
       <c r="Q54" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R54" s="20"/>
       <c r="S54" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T54" s="20"/>
       <c r="U54" s="17" t="s">
@@ -10452,7 +10455,7 @@
       </c>
       <c r="P55" s="32"/>
       <c r="Q55" s="31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R55" s="32"/>
       <c r="S55" s="31" t="s">
@@ -10582,15 +10585,15 @@
         <v>50</v>
       </c>
       <c r="O58" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P58" s="20"/>
       <c r="Q58" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R58" s="20"/>
       <c r="S58" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T58" s="20"/>
       <c r="U58" s="57"/>
@@ -11177,7 +11180,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -11210,7 +11213,7 @@
         <v>46150</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -11294,23 +11297,23 @@
         <v>10</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E3" s="20"/>
       <c r="F3" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G3" s="20"/>
       <c r="H3" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I3" s="20"/>
       <c r="J3" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K3" s="20"/>
       <c r="N3" s="1" t="s">
@@ -11319,15 +11322,15 @@
       <c r="O3" s="45"/>
       <c r="P3" s="46"/>
       <c r="Q3" s="41" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R3" s="42"/>
       <c r="S3" s="41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T3" s="42"/>
       <c r="U3" s="41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="V3" s="42"/>
       <c r="W3" s="27" t="s">
@@ -11340,23 +11343,23 @@
         <v>15</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G4" s="20"/>
       <c r="H4" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I4" s="20"/>
       <c r="J4" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K4" s="20"/>
       <c r="N4" s="1" t="s">
@@ -11365,15 +11368,15 @@
       <c r="O4" s="45"/>
       <c r="P4" s="46"/>
       <c r="Q4" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R4" s="42"/>
       <c r="S4" s="41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T4" s="42"/>
       <c r="U4" s="41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V4" s="42"/>
       <c r="W4" s="27" t="s">
@@ -11412,7 +11415,7 @@
       <c r="O5" s="45"/>
       <c r="P5" s="46"/>
       <c r="Q5" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R5" s="32"/>
       <c r="S5" s="31" t="s">
@@ -11420,11 +11423,11 @@
       </c>
       <c r="T5" s="32"/>
       <c r="U5" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V5" s="32"/>
       <c r="W5" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="X5" s="32"/>
     </row>
@@ -11479,23 +11482,23 @@
         <v>26</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I7" s="18"/>
       <c r="J7" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K7" s="18"/>
       <c r="N7" s="6" t="s">
@@ -11508,11 +11511,11 @@
       </c>
       <c r="R7" s="28"/>
       <c r="S7" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T7" s="32"/>
       <c r="U7" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V7" s="32"/>
       <c r="W7" s="35" t="s">
@@ -11525,23 +11528,23 @@
         <v>28</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I8" s="20"/>
       <c r="J8" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K8" s="20"/>
       <c r="N8" s="6" t="s">
@@ -11550,7 +11553,7 @@
       <c r="O8" s="45"/>
       <c r="P8" s="46"/>
       <c r="Q8" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R8" s="20"/>
       <c r="S8" s="27" t="s">
@@ -11596,19 +11599,19 @@
       <c r="O9" s="45"/>
       <c r="P9" s="46"/>
       <c r="Q9" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="R9" s="89"/>
       <c r="S9" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T9" s="89"/>
       <c r="U9" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V9" s="89"/>
       <c r="W9" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="X9" s="89"/>
     </row>
@@ -11642,11 +11645,11 @@
       <c r="O10" s="45"/>
       <c r="P10" s="46"/>
       <c r="Q10" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R10" s="32"/>
       <c r="S10" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T10" s="32"/>
       <c r="U10" s="27" t="s">
@@ -11654,7 +11657,7 @@
       </c>
       <c r="V10" s="28"/>
       <c r="W10" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="X10" s="20"/>
     </row>
@@ -11675,7 +11678,7 @@
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="25" t="s">
@@ -11692,15 +11695,15 @@
       </c>
       <c r="R11" s="32"/>
       <c r="S11" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T11" s="20"/>
       <c r="U11" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X11" s="32"/>
     </row>
@@ -11721,7 +11724,7 @@
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="25" t="s">
@@ -11734,11 +11737,11 @@
       <c r="O12" s="39"/>
       <c r="P12" s="40"/>
       <c r="Q12" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R12" s="20"/>
       <c r="S12" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T12" s="20"/>
       <c r="U12" s="31" t="s">
@@ -11746,7 +11749,7 @@
       </c>
       <c r="V12" s="32"/>
       <c r="W12" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="X12" s="20"/>
     </row>
@@ -11754,10 +11757,10 @@
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="C13" s="34"/>
+      <c r="B13" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="26"/>
       <c r="D13" s="33" t="s">
         <v>189</v>
       </c>
@@ -11830,15 +11833,15 @@
       </c>
       <c r="R14" s="32"/>
       <c r="S14" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T14" s="20"/>
       <c r="U14" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="X14" s="20"/>
     </row>
@@ -11872,7 +11875,7 @@
       <c r="O15" s="39"/>
       <c r="P15" s="40"/>
       <c r="Q15" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R15" s="20"/>
       <c r="S15" s="31" t="s">
@@ -11880,11 +11883,11 @@
       </c>
       <c r="T15" s="32"/>
       <c r="U15" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X15" s="32"/>
     </row>
@@ -11914,15 +11917,15 @@
       <c r="O16" s="43"/>
       <c r="P16" s="44"/>
       <c r="Q16" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R16" s="32"/>
       <c r="S16" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T16" s="32"/>
       <c r="U16" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V16" s="32"/>
       <c r="W16" s="27"/>
@@ -11957,10 +11960,6 @@
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="5"/>
-      <c r="B18" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="26"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -12128,7 +12127,7 @@
         <v>10</v>
       </c>
       <c r="O23" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P23" s="32"/>
       <c r="Q23" s="27" t="s">
@@ -12140,7 +12139,7 @@
       </c>
       <c r="T23" s="28"/>
       <c r="U23" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V23" s="32"/>
       <c r="W23" s="23" t="s">
@@ -12174,25 +12173,25 @@
         <v>15</v>
       </c>
       <c r="O24" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P24" s="32"/>
       <c r="Q24" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R24" s="32"/>
       <c r="S24" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T24" s="32"/>
       <c r="U24" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V24" s="32"/>
-      <c r="W24" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="X24" s="32"/>
+      <c r="W24" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="X24" s="28"/>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" s="1" t="s">
@@ -12312,23 +12311,23 @@
         <v>26</v>
       </c>
       <c r="O27" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P27" s="20"/>
       <c r="Q27" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R27" s="20"/>
       <c r="S27" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T27" s="20"/>
       <c r="U27" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V27" s="20"/>
       <c r="W27" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="X27" s="20"/>
     </row>
@@ -12351,30 +12350,30 @@
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
       <c r="J28" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K28" s="32"/>
       <c r="N28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O28" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P28" s="89"/>
       <c r="Q28" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="R28" s="89"/>
       <c r="S28" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T28" s="89"/>
       <c r="U28" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V28" s="89"/>
       <c r="W28" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="X28" s="89"/>
     </row>
@@ -12383,7 +12382,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="17" t="s">
@@ -12404,23 +12403,23 @@
         <v>32</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P29" s="22"/>
       <c r="Q29" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R29" s="22"/>
       <c r="S29" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T29" s="22"/>
       <c r="U29" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V29" s="22"/>
       <c r="W29" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="X29" s="22"/>
     </row>
@@ -12429,44 +12428,44 @@
         <v>35</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C30" s="32"/>
       <c r="D30" s="31" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
       <c r="J30" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K30" s="32"/>
       <c r="N30" s="6" t="s">
         <v>35</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P30" s="22"/>
       <c r="Q30" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R30" s="22"/>
       <c r="S30" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T30" s="22"/>
       <c r="U30" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V30" s="22"/>
       <c r="W30" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X30" s="22"/>
     </row>
@@ -12496,7 +12495,7 @@
         <v>37</v>
       </c>
       <c r="O31" s="33" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="P31" s="34"/>
       <c r="Q31" s="33" t="s">
@@ -12511,10 +12510,10 @@
         <v>189</v>
       </c>
       <c r="V31" s="34"/>
-      <c r="W31" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="X31" s="34"/>
+      <c r="W31" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="X31" s="32"/>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="1" t="s">
@@ -12544,23 +12543,23 @@
         <v>40</v>
       </c>
       <c r="O32" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R32" s="18"/>
       <c r="S32" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="T32" s="18"/>
       <c r="U32" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V32" s="18"/>
       <c r="W32" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="X32" s="18"/>
     </row>
@@ -12592,23 +12591,23 @@
         <v>45</v>
       </c>
       <c r="O33" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P33" s="20"/>
       <c r="Q33" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R33" s="20"/>
       <c r="S33" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T33" s="20"/>
       <c r="U33" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="X33" s="20"/>
     </row>
@@ -12640,23 +12639,23 @@
         <v>48</v>
       </c>
       <c r="O34" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P34" s="32"/>
       <c r="Q34" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R34" s="32"/>
       <c r="S34" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T34" s="32"/>
       <c r="U34" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V34" s="32"/>
       <c r="W34" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X34" s="32"/>
     </row>
@@ -12665,21 +12664,21 @@
         <v>49</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C35" s="32"/>
       <c r="D35" s="31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G35" s="32"/>
       <c r="H35" s="43"/>
       <c r="I35" s="44"/>
       <c r="J35" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K35" s="32"/>
       <c r="L35" s="7"/>
@@ -12688,23 +12687,23 @@
         <v>49</v>
       </c>
       <c r="O35" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P35" s="20"/>
       <c r="Q35" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R35" s="20"/>
       <c r="S35" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T35" s="20"/>
       <c r="U35" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="X35" s="20"/>
     </row>
@@ -12713,15 +12712,15 @@
         <v>50</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C36" s="32"/>
       <c r="D36" s="31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G36" s="32"/>
       <c r="H36" s="43"/>
@@ -12736,17 +12735,17 @@
       <c r="O36" s="27"/>
       <c r="P36" s="28"/>
       <c r="Q36" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R36" s="32"/>
       <c r="S36" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T36" s="32"/>
       <c r="U36" s="27"/>
       <c r="V36" s="28"/>
       <c r="W36" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X36" s="32"/>
     </row>
@@ -12776,7 +12775,7 @@
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>1</v>
@@ -12811,7 +12810,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>1</v>
@@ -12903,7 +12902,7 @@
       </c>
       <c r="C42" s="24"/>
       <c r="D42" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E42" s="20"/>
       <c r="F42" s="21" t="s">
@@ -12928,19 +12927,19 @@
       </c>
       <c r="P42" s="24"/>
       <c r="Q42" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R42" s="32"/>
       <c r="S42" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T42" s="32"/>
       <c r="U42" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V42" s="32"/>
       <c r="W42" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X42" s="32"/>
     </row>
@@ -12953,19 +12952,19 @@
       </c>
       <c r="C43" s="28"/>
       <c r="D43" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E43" s="20"/>
       <c r="F43" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G43" s="20"/>
       <c r="H43" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I43" s="20"/>
       <c r="J43" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K43" s="20"/>
       <c r="L43" s="7"/>
@@ -12999,46 +12998,46 @@
         <v>21</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C44" s="32"/>
       <c r="D44" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E44" s="32"/>
       <c r="F44" s="85" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G44" s="86"/>
       <c r="H44" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I44" s="32"/>
       <c r="J44" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K44" s="32"/>
       <c r="N44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="O44" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P44" s="20"/>
       <c r="Q44" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R44" s="20"/>
       <c r="S44" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T44" s="20"/>
       <c r="U44" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V44" s="20"/>
       <c r="W44" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="X44" s="20"/>
     </row>
@@ -13051,11 +13050,11 @@
       </c>
       <c r="C45" s="22"/>
       <c r="D45" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E45" s="32"/>
       <c r="F45" s="31" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="21" t="s">
@@ -13095,23 +13094,23 @@
         <v>26</v>
       </c>
       <c r="B46" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C46" s="89"/>
       <c r="D46" s="88" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E46" s="89"/>
       <c r="F46" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G46" s="89"/>
       <c r="H46" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I46" s="89"/>
       <c r="J46" s="88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K46" s="89"/>
       <c r="N46" s="6" t="s">
@@ -13143,15 +13142,15 @@
         <v>28</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E47" s="86"/>
       <c r="F47" s="85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G47" s="86"/>
       <c r="H47" s="27" t="s">
@@ -13159,14 +13158,14 @@
       </c>
       <c r="I47" s="28"/>
       <c r="J47" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K47" s="32"/>
       <c r="N47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O47" s="17" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="P47" s="18"/>
       <c r="Q47" s="17" t="s">
@@ -13195,7 +13194,7 @@
       </c>
       <c r="C48" s="89"/>
       <c r="D48" s="88" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E48" s="89"/>
       <c r="F48" s="88" t="s">
@@ -13239,7 +13238,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C49" s="18"/>
       <c r="D49" s="25" t="s">
@@ -13247,38 +13246,38 @@
       </c>
       <c r="E49" s="26"/>
       <c r="F49" s="41" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G49" s="42"/>
       <c r="H49" s="41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="42"/>
       <c r="J49" s="41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K49" s="42"/>
       <c r="N49" s="6" t="s">
         <v>35</v>
       </c>
       <c r="O49" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P49" s="20"/>
       <c r="Q49" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R49" s="20"/>
       <c r="S49" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T49" s="20"/>
       <c r="U49" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="X49" s="20"/>
     </row>
@@ -13310,15 +13309,15 @@
         <v>37</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P50" s="22"/>
       <c r="Q50" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R50" s="22"/>
       <c r="S50" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T50" s="22"/>
       <c r="U50" s="29" t="s">
@@ -13335,7 +13334,7 @@
         <v>40</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C51" s="18"/>
       <c r="D51" s="25" t="s">
@@ -13343,15 +13342,15 @@
       </c>
       <c r="E51" s="26"/>
       <c r="F51" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I51" s="20"/>
       <c r="J51" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K51" s="20"/>
       <c r="L51" s="7"/>
@@ -13360,23 +13359,23 @@
         <v>40</v>
       </c>
       <c r="O51" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P51" s="32"/>
       <c r="Q51" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R51" s="32"/>
       <c r="S51" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T51" s="32"/>
       <c r="U51" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V51" s="32"/>
       <c r="W51" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="X51" s="32"/>
     </row>
@@ -13385,7 +13384,7 @@
         <v>45</v>
       </c>
       <c r="B52" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C52" s="32"/>
       <c r="D52" s="25" t="s">
@@ -13393,15 +13392,15 @@
       </c>
       <c r="E52" s="26"/>
       <c r="F52" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G52" s="42"/>
       <c r="H52" s="41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I52" s="42"/>
       <c r="J52" s="41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K52" s="42"/>
       <c r="L52" s="7"/>
@@ -13422,11 +13421,11 @@
       </c>
       <c r="T52" s="18"/>
       <c r="U52" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V52" s="32"/>
       <c r="W52" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X52" s="32"/>
     </row>
@@ -13435,23 +13434,23 @@
         <v>48</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C53" s="32"/>
       <c r="D53" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E53" s="32"/>
       <c r="F53" s="31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G53" s="32"/>
       <c r="H53" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I53" s="32"/>
       <c r="J53" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K53" s="32"/>
       <c r="L53" s="7"/>
@@ -13460,23 +13459,23 @@
         <v>48</v>
       </c>
       <c r="O53" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P53" s="20"/>
       <c r="Q53" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R53" s="20"/>
       <c r="S53" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T53" s="20"/>
       <c r="U53" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="V53" s="20"/>
       <c r="W53" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="X53" s="20"/>
     </row>
@@ -13485,30 +13484,30 @@
         <v>49</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E54" s="20"/>
       <c r="F54" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G54" s="20"/>
       <c r="H54" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I54" s="20"/>
       <c r="J54" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K54" s="20"/>
       <c r="N54" s="12" t="s">
         <v>49</v>
       </c>
       <c r="O54" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P54" s="32"/>
       <c r="Q54" s="23" t="s">
@@ -13533,17 +13532,17 @@
         <v>50</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="27"/>
       <c r="E55" s="28"/>
       <c r="F55" s="31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G55" s="32"/>
       <c r="H55" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I55" s="32"/>
       <c r="J55" s="27"/>
@@ -13554,15 +13553,15 @@
         <v>50</v>
       </c>
       <c r="O55" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P55" s="32"/>
       <c r="Q55" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R55" s="32"/>
       <c r="S55" s="31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T55" s="32"/>
       <c r="U55" s="27"/>
@@ -13575,7 +13574,7 @@
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="85" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E56" s="86"/>
       <c r="F56" s="5"/>
@@ -13585,18 +13584,16 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="O56" s="87" t="s">
-        <v>196</v>
-      </c>
-      <c r="P56" s="87"/>
+        <v>210</v>
+      </c>
+      <c r="O56" s="27"/>
+      <c r="P56" s="28"/>
       <c r="Q56" s="87" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R56" s="87"/>
       <c r="S56" s="87" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T56" s="87"/>
       <c r="U56" s="27"/>
@@ -13616,8 +13613,10 @@
       <c r="K57" s="5"/>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
-      <c r="O57" s="9"/>
-      <c r="P57" s="9"/>
+      <c r="O57" s="87" t="s">
+        <v>197</v>
+      </c>
+      <c r="P57" s="87"/>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
@@ -13704,6 +13703,8 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="462">
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="O56:P56"/>
     <mergeCell ref="O55:P55"/>
     <mergeCell ref="Q55:R55"/>
     <mergeCell ref="S55:T55"/>
@@ -13912,7 +13913,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="H15:I15"/>
-    <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="H13:I13"/>
@@ -13931,7 +13931,7 @@
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="H23:I23"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:I12"/>
@@ -14024,7 +14024,6 @@
     <mergeCell ref="W14:X14"/>
     <mergeCell ref="O25:P25"/>
     <mergeCell ref="U14:V14"/>
-    <mergeCell ref="W31:X31"/>
     <mergeCell ref="S25:T25"/>
     <mergeCell ref="U26:V26"/>
     <mergeCell ref="Q25:R25"/>
@@ -14047,7 +14046,7 @@
     <mergeCell ref="S31:T31"/>
     <mergeCell ref="S24:T24"/>
     <mergeCell ref="W23:X23"/>
-    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="W31:X31"/>
     <mergeCell ref="S8:T8"/>
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="W8:X8"/>
@@ -14143,7 +14142,7 @@
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="D56:E56"/>
-    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="O57:P57"/>
     <mergeCell ref="Q56:R56"/>
     <mergeCell ref="S56:T56"/>
     <mergeCell ref="U56:V56"/>
@@ -14216,7 +14215,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -14249,7 +14248,7 @@
         <v>46192</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -14487,23 +14486,23 @@
         <v>26</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K7" s="22"/>
       <c r="N7" s="6" t="s">
@@ -14525,23 +14524,23 @@
         <v>28</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G8" s="22"/>
       <c r="H8" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K8" s="22"/>
       <c r="N8" s="6" t="s">
@@ -14563,23 +14562,23 @@
         <v>32</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K9" s="22"/>
       <c r="N9" s="6" t="s">
@@ -14639,23 +14638,23 @@
         <v>37</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G11" s="22"/>
       <c r="H11" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K11" s="22"/>
       <c r="N11" s="1" t="s">
@@ -14836,7 +14835,7 @@
     <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
     <row r="19" spans="1:24" ht="11.25" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -14869,7 +14868,7 @@
         <v>46199</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -14995,13 +14994,13 @@
       <c r="B22" s="79"/>
       <c r="C22" s="80"/>
       <c r="D22" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E22" s="74"/>
       <c r="F22" s="79"/>
       <c r="G22" s="80"/>
       <c r="H22" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I22" s="74"/>
       <c r="J22" s="27"/>
@@ -15177,13 +15176,13 @@
       <c r="B27" s="79"/>
       <c r="C27" s="80"/>
       <c r="D27" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E27" s="74"/>
       <c r="F27" s="57"/>
       <c r="G27" s="58"/>
       <c r="H27" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I27" s="74"/>
       <c r="J27" s="27"/>
@@ -15493,7 +15492,7 @@
     </row>
     <row r="37" spans="1:24" ht="11.25" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -15528,7 +15527,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -15835,15 +15834,15 @@
       <c r="O44" s="79"/>
       <c r="P44" s="80"/>
       <c r="Q44" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R44" s="22"/>
       <c r="S44" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T44" s="22"/>
       <c r="U44" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="V44" s="22"/>
       <c r="W44" s="27"/>
@@ -15869,15 +15868,15 @@
       <c r="O45" s="79"/>
       <c r="P45" s="80"/>
       <c r="Q45" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R45" s="22"/>
       <c r="S45" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T45" s="22"/>
       <c r="U45" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="V45" s="22"/>
       <c r="W45" s="27"/>
@@ -15954,23 +15953,23 @@
         <v>40</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G48" s="22"/>
       <c r="H48" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I48" s="22"/>
       <c r="J48" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K48" s="22"/>
       <c r="N48" s="1" t="s">
@@ -16696,7 +16695,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -16729,7 +16728,7 @@
         <v>46234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -16974,7 +16973,7 @@
       <c r="O7" s="27"/>
       <c r="P7" s="28"/>
       <c r="Q7" s="90" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="R7" s="91"/>
       <c r="S7" s="57"/>
@@ -17014,7 +17013,7 @@
       <c r="O8" s="79"/>
       <c r="P8" s="80"/>
       <c r="Q8" s="90" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="R8" s="91"/>
       <c r="S8" s="79"/>
@@ -17370,7 +17369,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -17403,7 +17402,7 @@
         <v>46241</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -17451,7 +17450,7 @@
       </c>
       <c r="I20" s="22"/>
       <c r="J20" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K20" s="74"/>
       <c r="N20" s="1" t="s">
@@ -17691,7 +17690,7 @@
       </c>
       <c r="I27" s="22"/>
       <c r="J27" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K27" s="74"/>
       <c r="N27" s="6" t="s">
@@ -17799,7 +17798,7 @@
       </c>
       <c r="I30" s="22"/>
       <c r="J30" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K30" s="74"/>
       <c r="N30" s="1" t="s">
@@ -17962,7 +17961,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -17997,7 +17996,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -18060,7 +18059,7 @@
       <c r="U38" s="57"/>
       <c r="V38" s="58"/>
       <c r="W38" s="27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="X38" s="28"/>
     </row>
@@ -18107,7 +18106,7 @@
       <c r="F40" s="79"/>
       <c r="G40" s="80"/>
       <c r="H40" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I40" s="74"/>
       <c r="J40" s="27"/>
@@ -18291,7 +18290,7 @@
       <c r="F45" s="57"/>
       <c r="G45" s="58"/>
       <c r="H45" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I45" s="74"/>
       <c r="J45" s="27"/>
@@ -18377,7 +18376,7 @@
       <c r="F48" s="27"/>
       <c r="G48" s="28"/>
       <c r="H48" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I48" s="74"/>
       <c r="J48" s="27"/>
@@ -19111,7 +19110,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -19144,7 +19143,7 @@
         <v>46276</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -19182,23 +19181,23 @@
         <v>7</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C2" s="28"/>
       <c r="D2" s="27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E2" s="28"/>
       <c r="F2" s="27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G2" s="28"/>
       <c r="H2" s="27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I2" s="28"/>
       <c r="J2" s="27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K2" s="28"/>
       <c r="N2" s="1" t="s">
@@ -19655,7 +19654,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -19688,7 +19687,7 @@
         <v>46283</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -20248,7 +20247,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -20283,7 +20282,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -21370,7 +21369,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -21403,7 +21402,7 @@
         <v>46318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -21929,7 +21928,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -21962,7 +21961,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -22491,7 +22490,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -22526,7 +22525,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -23578,7 +23577,7 @@
     <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
     <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -23611,7 +23610,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -24123,7 +24122,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -24156,7 +24155,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -24695,7 +24694,7 @@
     </row>
     <row r="38" spans="2:25">
       <c r="B38" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3868" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE863CD-16E4-4A5C-B41D-9045DE36E287}"/>
+  <xr:revisionPtr revIDLastSave="3872" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E225BB68-1C2A-470A-9527-6704511C7AC8}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3312" uniqueCount="246">
   <si>
     <t>Uke 01</t>
   </si>
@@ -632,9 +632,6 @@
     <t>9 SF SUR SK</t>
   </si>
   <si>
-    <t>9 SE TC 1</t>
-  </si>
-  <si>
     <t>9 SF DU 2</t>
   </si>
   <si>
@@ -644,7 +641,7 @@
     <t>9 SE RTC 1</t>
   </si>
   <si>
-    <t>8 SF SUR SB</t>
+    <t>9 SE TC 1</t>
   </si>
   <si>
     <t>9 SF SUR SB</t>
@@ -11530,10 +11527,10 @@
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="24"/>
+      <c r="B8" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="32"/>
       <c r="D8" s="23" t="s">
         <v>172</v>
       </c>
@@ -11602,19 +11599,19 @@
       <c r="O9" s="51"/>
       <c r="P9" s="52"/>
       <c r="Q9" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R9" s="38"/>
       <c r="S9" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="T9" s="38"/>
       <c r="U9" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="V9" s="38"/>
       <c r="W9" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X9" s="38"/>
     </row>
@@ -11681,7 +11678,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I11" s="30"/>
       <c r="J11" s="31" t="s">
@@ -11727,7 +11724,7 @@
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I12" s="30"/>
       <c r="J12" s="31" t="s">
@@ -11760,24 +11757,24 @@
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="49" t="s">
         <v>189</v>
-      </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="49" t="s">
-        <v>190</v>
       </c>
       <c r="E13" s="50"/>
       <c r="F13" s="49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G13" s="50"/>
       <c r="H13" s="49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I13" s="50"/>
       <c r="J13" s="49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K13" s="50"/>
       <c r="N13" s="12" t="s">
@@ -11786,19 +11783,19 @@
       <c r="O13" s="51"/>
       <c r="P13" s="52"/>
       <c r="Q13" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R13" s="38"/>
       <c r="S13" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T13" s="38"/>
       <c r="U13" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="V13" s="38"/>
       <c r="W13" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="X13" s="38"/>
     </row>
@@ -11936,7 +11933,7 @@
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="18"/>
@@ -11962,11 +11959,6 @@
       <c r="S17" s="4"/>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="5"/>
-      <c r="B18" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="32"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -11996,7 +11988,7 @@
     </row>
     <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -12029,7 +12021,7 @@
         <v>46157</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>1</v>
@@ -12117,11 +12109,11 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E23" s="28"/>
       <c r="F23" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G23" s="28"/>
       <c r="H23" s="35"/>
@@ -12226,23 +12218,23 @@
         <v>21</v>
       </c>
       <c r="O25" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P25" s="38"/>
       <c r="Q25" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R25" s="38"/>
       <c r="S25" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T25" s="38"/>
       <c r="U25" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="V25" s="38"/>
       <c r="W25" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="X25" s="38"/>
     </row>
@@ -12364,23 +12356,23 @@
         <v>28</v>
       </c>
       <c r="O28" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P28" s="38"/>
       <c r="Q28" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R28" s="38"/>
       <c r="S28" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="T28" s="38"/>
       <c r="U28" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="V28" s="38"/>
       <c r="W28" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X28" s="38"/>
     </row>
@@ -12389,44 +12381,44 @@
         <v>32</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C29" s="30"/>
       <c r="D29" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G29" s="30"/>
       <c r="H29" s="35"/>
       <c r="I29" s="36"/>
       <c r="J29" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K29" s="30"/>
       <c r="N29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="O29" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P29" s="28"/>
       <c r="Q29" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R29" s="28"/>
       <c r="S29" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T29" s="28"/>
       <c r="U29" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="V29" s="28"/>
       <c r="W29" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X29" s="28"/>
     </row>
@@ -12439,7 +12431,7 @@
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E30" s="20"/>
       <c r="F30" s="19" t="s">
@@ -12456,23 +12448,23 @@
         <v>35</v>
       </c>
       <c r="O30" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P30" s="28"/>
       <c r="Q30" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R30" s="28"/>
       <c r="S30" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T30" s="28"/>
       <c r="U30" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="V30" s="28"/>
       <c r="W30" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X30" s="28"/>
     </row>
@@ -12502,19 +12494,19 @@
         <v>37</v>
       </c>
       <c r="O31" s="49" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P31" s="50"/>
       <c r="Q31" s="49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R31" s="50"/>
       <c r="S31" s="49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T31" s="50"/>
       <c r="U31" s="49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V31" s="50"/>
       <c r="W31" s="19" t="s">
@@ -12675,7 +12667,7 @@
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E35" s="20"/>
       <c r="F35" s="19" t="s">
@@ -12723,7 +12715,7 @@
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E36" s="20"/>
       <c r="F36" s="19" t="s">
@@ -12782,7 +12774,7 @@
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>1</v>
@@ -12817,7 +12809,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>1</v>
@@ -12913,11 +12905,11 @@
       </c>
       <c r="E42" s="24"/>
       <c r="F42" s="27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G42" s="28"/>
       <c r="H42" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I42" s="28"/>
       <c r="J42" s="27" t="s">
@@ -13013,7 +13005,7 @@
       </c>
       <c r="E44" s="20"/>
       <c r="F44" s="39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G44" s="40"/>
       <c r="H44" s="19" t="s">
@@ -13061,7 +13053,7 @@
       </c>
       <c r="E45" s="20"/>
       <c r="F45" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="27" t="s">
@@ -13101,23 +13093,23 @@
         <v>26</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C46" s="38"/>
       <c r="D46" s="37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I46" s="38"/>
       <c r="J46" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K46" s="38"/>
       <c r="N46" s="6" t="s">
@@ -13153,11 +13145,11 @@
       </c>
       <c r="C47" s="24"/>
       <c r="D47" s="39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E47" s="40"/>
       <c r="F47" s="39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G47" s="40"/>
       <c r="H47" s="17" t="s">
@@ -13172,23 +13164,23 @@
         <v>28</v>
       </c>
       <c r="O47" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P47" s="30"/>
       <c r="Q47" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R47" s="30"/>
       <c r="S47" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T47" s="30"/>
       <c r="U47" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V47" s="30"/>
       <c r="W47" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="X47" s="30"/>
     </row>
@@ -13197,23 +13189,23 @@
         <v>32</v>
       </c>
       <c r="B48" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C48" s="38"/>
       <c r="D48" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G48" s="38"/>
       <c r="H48" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I48" s="38"/>
       <c r="J48" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K48" s="38"/>
       <c r="N48" s="6" t="s">
@@ -13245,7 +13237,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C49" s="30"/>
       <c r="D49" s="31" t="s">
@@ -13316,15 +13308,15 @@
         <v>37</v>
       </c>
       <c r="O50" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P50" s="28"/>
       <c r="Q50" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R50" s="28"/>
       <c r="S50" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T50" s="28"/>
       <c r="U50" s="25" t="s">
@@ -13341,7 +13333,7 @@
         <v>40</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C51" s="30"/>
       <c r="D51" s="31" t="s">
@@ -13449,7 +13441,7 @@
       </c>
       <c r="E53" s="20"/>
       <c r="F53" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G53" s="20"/>
       <c r="H53" s="19" t="s">
@@ -13545,7 +13537,7 @@
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G55" s="20"/>
       <c r="H55" s="19" t="s">
@@ -13581,7 +13573,7 @@
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E56" s="40"/>
       <c r="F56" s="5"/>
@@ -13591,16 +13583,16 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O56" s="17"/>
       <c r="P56" s="18"/>
       <c r="Q56" s="53" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R56" s="53"/>
       <c r="S56" s="53" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T56" s="53"/>
       <c r="U56" s="17"/>
@@ -13621,7 +13613,7 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
       <c r="O57" s="53" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="53"/>
       <c r="Q57" s="9"/>
@@ -13708,7 +13700,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="463">
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="462">
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="O57:P57"/>
     <mergeCell ref="Q56:R56"/>
@@ -13935,7 +13928,6 @@
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="H23:I23"/>
-    <mergeCell ref="B18:C18"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:I12"/>
@@ -14222,7 +14214,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -14255,7 +14247,7 @@
         <v>46192</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -14493,23 +14485,23 @@
         <v>26</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E7" s="28"/>
       <c r="F7" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G7" s="28"/>
       <c r="H7" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I7" s="28"/>
       <c r="J7" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K7" s="28"/>
       <c r="N7" s="6" t="s">
@@ -14531,23 +14523,23 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C8" s="28"/>
       <c r="D8" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E8" s="28"/>
       <c r="F8" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G8" s="28"/>
       <c r="H8" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I8" s="28"/>
       <c r="J8" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K8" s="28"/>
       <c r="N8" s="6" t="s">
@@ -14569,23 +14561,23 @@
         <v>32</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G9" s="28"/>
       <c r="H9" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I9" s="28"/>
       <c r="J9" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K9" s="28"/>
       <c r="N9" s="6" t="s">
@@ -14645,23 +14637,23 @@
         <v>37</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G11" s="28"/>
       <c r="H11" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I11" s="28"/>
       <c r="J11" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K11" s="28"/>
       <c r="N11" s="1" t="s">
@@ -14842,7 +14834,7 @@
     <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
     <row r="19" spans="1:24" ht="11.25" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -14875,7 +14867,7 @@
         <v>46199</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -15001,13 +14993,13 @@
       <c r="B22" s="70"/>
       <c r="C22" s="71"/>
       <c r="D22" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E22" s="83"/>
       <c r="F22" s="70"/>
       <c r="G22" s="71"/>
       <c r="H22" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I22" s="83"/>
       <c r="J22" s="17"/>
@@ -15183,13 +15175,13 @@
       <c r="B27" s="70"/>
       <c r="C27" s="71"/>
       <c r="D27" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E27" s="83"/>
       <c r="F27" s="84"/>
       <c r="G27" s="85"/>
       <c r="H27" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I27" s="83"/>
       <c r="J27" s="17"/>
@@ -15499,7 +15491,7 @@
     </row>
     <row r="37" spans="1:24" ht="11.25" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -15534,7 +15526,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -15841,15 +15833,15 @@
       <c r="O44" s="70"/>
       <c r="P44" s="71"/>
       <c r="Q44" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R44" s="28"/>
       <c r="S44" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T44" s="28"/>
       <c r="U44" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="V44" s="28"/>
       <c r="W44" s="17"/>
@@ -15875,15 +15867,15 @@
       <c r="O45" s="70"/>
       <c r="P45" s="71"/>
       <c r="Q45" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R45" s="28"/>
       <c r="S45" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T45" s="28"/>
       <c r="U45" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="V45" s="28"/>
       <c r="W45" s="17"/>
@@ -15960,23 +15952,23 @@
         <v>40</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C48" s="28"/>
       <c r="D48" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E48" s="28"/>
       <c r="F48" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G48" s="28"/>
       <c r="H48" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I48" s="28"/>
       <c r="J48" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K48" s="28"/>
       <c r="N48" s="1" t="s">
@@ -16702,7 +16694,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -16735,7 +16727,7 @@
         <v>46234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -16980,7 +16972,7 @@
       <c r="O7" s="17"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="90" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R7" s="91"/>
       <c r="S7" s="84"/>
@@ -17020,7 +17012,7 @@
       <c r="O8" s="70"/>
       <c r="P8" s="71"/>
       <c r="Q8" s="90" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R8" s="91"/>
       <c r="S8" s="70"/>
@@ -17376,7 +17368,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -17409,7 +17401,7 @@
         <v>46241</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -17457,7 +17449,7 @@
       </c>
       <c r="I20" s="28"/>
       <c r="J20" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K20" s="83"/>
       <c r="N20" s="1" t="s">
@@ -17697,7 +17689,7 @@
       </c>
       <c r="I27" s="28"/>
       <c r="J27" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K27" s="83"/>
       <c r="N27" s="6" t="s">
@@ -17805,7 +17797,7 @@
       </c>
       <c r="I30" s="28"/>
       <c r="J30" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K30" s="83"/>
       <c r="N30" s="1" t="s">
@@ -17968,7 +17960,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -18003,7 +17995,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -18066,7 +18058,7 @@
       <c r="U38" s="84"/>
       <c r="V38" s="85"/>
       <c r="W38" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X38" s="18"/>
     </row>
@@ -18113,7 +18105,7 @@
       <c r="F40" s="70"/>
       <c r="G40" s="71"/>
       <c r="H40" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I40" s="83"/>
       <c r="J40" s="17"/>
@@ -18297,7 +18289,7 @@
       <c r="F45" s="84"/>
       <c r="G45" s="85"/>
       <c r="H45" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I45" s="83"/>
       <c r="J45" s="17"/>
@@ -18383,7 +18375,7 @@
       <c r="F48" s="17"/>
       <c r="G48" s="18"/>
       <c r="H48" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I48" s="83"/>
       <c r="J48" s="17"/>
@@ -19117,7 +19109,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -19150,7 +19142,7 @@
         <v>46276</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -19188,23 +19180,23 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G2" s="18"/>
       <c r="H2" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I2" s="18"/>
       <c r="J2" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K2" s="18"/>
       <c r="N2" s="1" t="s">
@@ -19661,7 +19653,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -19694,7 +19686,7 @@
         <v>46283</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -20254,7 +20246,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -20289,7 +20281,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -21376,7 +21368,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -21409,7 +21401,7 @@
         <v>46318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -21935,7 +21927,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -21968,7 +21960,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -22497,7 +22489,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -22532,7 +22524,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -23584,7 +23576,7 @@
     <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
     <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -23617,7 +23609,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -24129,7 +24121,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -24162,7 +24154,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -24701,7 +24693,7 @@
     </row>
     <row r="38" spans="2:25">
       <c r="B38" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3885" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBDBDE26-447B-4F8F-B453-C708664B0598}"/>
+  <xr:revisionPtr revIDLastSave="3894" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE79FBA0-AE96-40C9-8044-B155AA0AAED9}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3318" uniqueCount="250">
   <si>
     <t>Uke 01</t>
   </si>
@@ -590,6 +590,9 @@
     <t>SF TC 1</t>
   </si>
   <si>
+    <t>Pappaperm</t>
+  </si>
+  <si>
     <t>SF TC-kurs OV</t>
   </si>
   <si>
@@ -597,6 +600,12 @@
   </si>
   <si>
     <t>9 SE MØ 2</t>
+  </si>
+  <si>
+    <t>SF MØ 2 SM</t>
+  </si>
+  <si>
+    <t>SF ZV 2 OFF</t>
   </si>
   <si>
     <t>Uke 19</t>
@@ -626,9 +635,6 @@
     <t>9 SF VA 1</t>
   </si>
   <si>
-    <t>Pappaperm</t>
-  </si>
-  <si>
     <t>9 SF DU 2</t>
   </si>
   <si>
@@ -650,7 +656,7 @@
     <t>Pilot OL</t>
   </si>
   <si>
-    <t>9 SE SUR SK</t>
+    <t>9 SE SUR SK KE</t>
   </si>
   <si>
     <t>Uke 20</t>
@@ -678,6 +684,9 @@
   </si>
   <si>
     <t>9 SF ADC</t>
+  </si>
+  <si>
+    <t>9 SE SUR SK</t>
   </si>
   <si>
     <t>SE VA 1</t>
@@ -10179,22 +10188,22 @@
       <c r="N49" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O49" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="P49" s="37"/>
-      <c r="Q49" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="R49" s="41"/>
-      <c r="S49" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="T49" s="37"/>
-      <c r="U49" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V49" s="21"/>
+      <c r="O49" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="P49" s="47"/>
+      <c r="Q49" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="R49" s="47"/>
+      <c r="S49" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="T49" s="47"/>
+      <c r="U49" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="V49" s="47"/>
       <c r="W49" s="30"/>
       <c r="X49" s="31"/>
     </row>
@@ -10299,7 +10308,7 @@
       </c>
       <c r="E52" s="25"/>
       <c r="F52" s="24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G52" s="25"/>
       <c r="H52" s="40" t="s">
@@ -10307,7 +10316,7 @@
       </c>
       <c r="I52" s="41"/>
       <c r="J52" s="24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K52" s="25"/>
       <c r="L52" s="5"/>
@@ -10408,15 +10417,15 @@
         <v>40</v>
       </c>
       <c r="O54" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P54" s="39"/>
       <c r="Q54" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R54" s="39"/>
       <c r="S54" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T54" s="39"/>
       <c r="U54" s="24" t="s">
@@ -10458,7 +10467,7 @@
       </c>
       <c r="P55" s="37"/>
       <c r="Q55" s="36" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R55" s="37"/>
       <c r="S55" s="36" t="s">
@@ -10607,6 +10616,18 @@
     <row r="59" spans="1:24">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
+      <c r="O59" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="P59" s="37"/>
+      <c r="Q59" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="R59" s="41"/>
+      <c r="S59" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="T59" s="37"/>
     </row>
     <row r="60" spans="1:24">
       <c r="A60" s="5">
@@ -10621,6 +10642,10 @@
       <c r="G60" s="5" t="s">
         <v>80</v>
       </c>
+      <c r="O60" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="P60" s="41"/>
     </row>
     <row r="61" spans="1:24">
       <c r="A61" s="5">
@@ -10674,7 +10699,8 @@
       <c r="C66" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="456">
+  <mergeCells count="460">
+    <mergeCell ref="O60:P60"/>
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="D58:E58"/>
     <mergeCell ref="F58:G58"/>
@@ -10718,9 +10744,6 @@
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="O30:P30"/>
-    <mergeCell ref="W50:X50"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="S51:T51"/>
     <mergeCell ref="W51:X51"/>
     <mergeCell ref="S49:T49"/>
     <mergeCell ref="U51:V51"/>
@@ -10742,7 +10765,6 @@
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H29:I29"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="F29:G29"/>
@@ -10764,8 +10786,6 @@
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="F16:G16"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:G27"/>
@@ -11059,12 +11079,6 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="D39:E39"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F39:G39"/>
     <mergeCell ref="W16:X16"/>
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="F51:G51"/>
@@ -11083,6 +11097,24 @@
     <mergeCell ref="Q33:R33"/>
     <mergeCell ref="S50:T50"/>
     <mergeCell ref="S48:T48"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="S51:T51"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="Q50:R50"/>
     <mergeCell ref="O49:P49"/>
     <mergeCell ref="S45:T45"/>
     <mergeCell ref="O46:P46"/>
@@ -11104,9 +11136,9 @@
     <mergeCell ref="S31:T31"/>
     <mergeCell ref="Q28:R28"/>
     <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="Q59:R59"/>
+    <mergeCell ref="S59:T59"/>
+    <mergeCell ref="O59:P59"/>
     <mergeCell ref="S38:T38"/>
     <mergeCell ref="Q37:R37"/>
     <mergeCell ref="S37:T37"/>
@@ -11128,9 +11160,6 @@
     <mergeCell ref="O52:P52"/>
     <mergeCell ref="O58:P58"/>
     <mergeCell ref="Q58:R58"/>
-    <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="O50:P50"/>
-    <mergeCell ref="Q50:R50"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11182,7 +11211,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -11215,7 +11244,7 @@
         <v>46150</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -11299,7 +11328,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C3" s="39"/>
       <c r="D3" s="38" t="s">
@@ -11324,15 +11353,15 @@
       <c r="O3" s="42"/>
       <c r="P3" s="43"/>
       <c r="Q3" s="22" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="R3" s="23"/>
       <c r="S3" s="22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="T3" s="23"/>
       <c r="U3" s="22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="V3" s="23"/>
       <c r="W3" s="20" t="s">
@@ -11345,7 +11374,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C4" s="39"/>
       <c r="D4" s="38" t="s">
@@ -11370,15 +11399,15 @@
       <c r="O4" s="42"/>
       <c r="P4" s="43"/>
       <c r="Q4" s="22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R4" s="23"/>
       <c r="S4" s="22" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="T4" s="23"/>
       <c r="U4" s="22" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="V4" s="23"/>
       <c r="W4" s="20" t="s">
@@ -11417,7 +11446,7 @@
       <c r="O5" s="42"/>
       <c r="P5" s="43"/>
       <c r="Q5" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R5" s="37"/>
       <c r="S5" s="36" t="s">
@@ -11425,11 +11454,11 @@
       </c>
       <c r="T5" s="37"/>
       <c r="U5" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="V5" s="37"/>
       <c r="W5" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="X5" s="37"/>
     </row>
@@ -11484,23 +11513,23 @@
         <v>26</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C7" s="47"/>
       <c r="D7" s="46" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="46" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G7" s="47"/>
       <c r="H7" s="46" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="I7" s="47"/>
       <c r="J7" s="46" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="K7" s="47"/>
       <c r="N7" s="6" t="s">
@@ -11513,11 +11542,11 @@
       </c>
       <c r="R7" s="21"/>
       <c r="S7" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="V7" s="37"/>
       <c r="W7" s="48" t="s">
@@ -11534,19 +11563,19 @@
       </c>
       <c r="C8" s="41"/>
       <c r="D8" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G8" s="39"/>
       <c r="H8" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K8" s="39"/>
       <c r="N8" s="6" t="s">
@@ -11601,19 +11630,19 @@
       <c r="O9" s="42"/>
       <c r="P9" s="43"/>
       <c r="Q9" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R9" s="35"/>
       <c r="S9" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="T9" s="35"/>
       <c r="U9" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="V9" s="35"/>
       <c r="W9" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="X9" s="35"/>
     </row>
@@ -11647,11 +11676,11 @@
       <c r="O10" s="42"/>
       <c r="P10" s="43"/>
       <c r="Q10" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="T10" s="37"/>
       <c r="U10" s="20" t="s">
@@ -11659,7 +11688,7 @@
       </c>
       <c r="V10" s="21"/>
       <c r="W10" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="X10" s="39"/>
     </row>
@@ -11680,7 +11709,7 @@
       </c>
       <c r="G11" s="25"/>
       <c r="H11" s="24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I11" s="25"/>
       <c r="J11" s="40" t="s">
@@ -11701,11 +11730,11 @@
       </c>
       <c r="T11" s="39"/>
       <c r="U11" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V11" s="39"/>
       <c r="W11" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="X11" s="37"/>
     </row>
@@ -11726,7 +11755,7 @@
       </c>
       <c r="G12" s="25"/>
       <c r="H12" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I12" s="25"/>
       <c r="J12" s="40" t="s">
@@ -11739,11 +11768,11 @@
       <c r="O12" s="30"/>
       <c r="P12" s="31"/>
       <c r="Q12" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R12" s="39"/>
       <c r="S12" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T12" s="39"/>
       <c r="U12" s="36" t="s">
@@ -11760,15 +11789,15 @@
         <v>45</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G13" s="25"/>
       <c r="H13" s="46" t="s">
@@ -11776,7 +11805,7 @@
       </c>
       <c r="I13" s="47"/>
       <c r="J13" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K13" s="25"/>
       <c r="N13" s="12" t="s">
@@ -11785,19 +11814,19 @@
       <c r="O13" s="42"/>
       <c r="P13" s="43"/>
       <c r="Q13" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R13" s="35"/>
       <c r="S13" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="T13" s="35"/>
       <c r="U13" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V13" s="35"/>
       <c r="W13" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="X13" s="35"/>
     </row>
@@ -11889,7 +11918,7 @@
       </c>
       <c r="V15" s="39"/>
       <c r="W15" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="X15" s="37"/>
     </row>
@@ -11919,15 +11948,15 @@
       <c r="O16" s="44"/>
       <c r="P16" s="45"/>
       <c r="Q16" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T16" s="37"/>
       <c r="U16" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="V16" s="37"/>
       <c r="W16" s="20"/>
@@ -11935,7 +11964,7 @@
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="21"/>
@@ -11962,11 +11991,11 @@
     </row>
     <row r="18" spans="1:24">
       <c r="B18" s="24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C18" s="25"/>
       <c r="H18" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I18" s="25"/>
       <c r="N18" s="4"/>
@@ -11998,7 +12027,7 @@
     </row>
     <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -12031,7 +12060,7 @@
         <v>46157</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>1</v>
@@ -12119,11 +12148,11 @@
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="28" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E23" s="29"/>
       <c r="F23" s="28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G23" s="29"/>
       <c r="H23" s="44"/>
@@ -12136,7 +12165,7 @@
         <v>10</v>
       </c>
       <c r="O23" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P23" s="37"/>
       <c r="Q23" s="20" t="s">
@@ -12148,7 +12177,7 @@
       </c>
       <c r="T23" s="21"/>
       <c r="U23" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="V23" s="37"/>
       <c r="W23" s="46" t="s">
@@ -12182,19 +12211,19 @@
         <v>15</v>
       </c>
       <c r="O24" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="P24" s="37"/>
       <c r="Q24" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="T24" s="37"/>
       <c r="U24" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="V24" s="37"/>
       <c r="W24" s="20" t="s">
@@ -12228,23 +12257,23 @@
         <v>21</v>
       </c>
       <c r="O25" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P25" s="35"/>
       <c r="Q25" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R25" s="35"/>
       <c r="S25" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="T25" s="35"/>
       <c r="U25" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V25" s="35"/>
       <c r="W25" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="X25" s="35"/>
     </row>
@@ -12320,23 +12349,23 @@
         <v>26</v>
       </c>
       <c r="O27" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P27" s="39"/>
       <c r="Q27" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R27" s="39"/>
       <c r="S27" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T27" s="39"/>
       <c r="U27" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V27" s="39"/>
       <c r="W27" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="X27" s="39"/>
     </row>
@@ -12359,30 +12388,30 @@
       <c r="H28" s="30"/>
       <c r="I28" s="31"/>
       <c r="J28" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K28" s="37"/>
       <c r="N28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O28" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P28" s="35"/>
       <c r="Q28" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R28" s="35"/>
       <c r="S28" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="T28" s="35"/>
       <c r="U28" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="V28" s="35"/>
       <c r="W28" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="X28" s="35"/>
     </row>
@@ -12391,44 +12420,44 @@
         <v>32</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C29" s="25"/>
       <c r="D29" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E29" s="25"/>
       <c r="F29" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G29" s="25"/>
       <c r="H29" s="44"/>
       <c r="I29" s="45"/>
       <c r="J29" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K29" s="25"/>
       <c r="N29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="O29" s="28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P29" s="29"/>
       <c r="Q29" s="28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R29" s="29"/>
       <c r="S29" s="28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T29" s="29"/>
       <c r="U29" s="28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="V29" s="29"/>
       <c r="W29" s="28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="X29" s="29"/>
     </row>
@@ -12437,44 +12466,44 @@
         <v>35</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="36" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E30" s="37"/>
       <c r="F30" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G30" s="37"/>
       <c r="H30" s="30"/>
       <c r="I30" s="31"/>
       <c r="J30" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K30" s="37"/>
       <c r="N30" s="6" t="s">
         <v>35</v>
       </c>
       <c r="O30" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P30" s="29"/>
       <c r="Q30" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R30" s="29"/>
       <c r="S30" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="T30" s="29"/>
       <c r="U30" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="V30" s="29"/>
       <c r="W30" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="X30" s="29"/>
     </row>
@@ -12504,23 +12533,23 @@
         <v>37</v>
       </c>
       <c r="O31" s="50" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P31" s="51"/>
       <c r="Q31" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="T31" s="51"/>
       <c r="U31" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="V31" s="51"/>
       <c r="W31" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="X31" s="37"/>
     </row>
@@ -12552,23 +12581,23 @@
         <v>40</v>
       </c>
       <c r="O32" s="24" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="P32" s="25"/>
       <c r="Q32" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R32" s="25"/>
       <c r="S32" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="T32" s="25"/>
       <c r="U32" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="V32" s="25"/>
       <c r="W32" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="X32" s="25"/>
     </row>
@@ -12648,23 +12677,23 @@
         <v>48</v>
       </c>
       <c r="O34" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P34" s="37"/>
       <c r="Q34" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R34" s="37"/>
       <c r="S34" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T34" s="37"/>
       <c r="U34" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="V34" s="37"/>
       <c r="W34" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="X34" s="37"/>
     </row>
@@ -12673,21 +12702,21 @@
         <v>49</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="36" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E35" s="37"/>
       <c r="F35" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G35" s="37"/>
       <c r="H35" s="44"/>
       <c r="I35" s="45"/>
       <c r="J35" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K35" s="37"/>
       <c r="L35" s="7"/>
@@ -12721,15 +12750,15 @@
         <v>50</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="36" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E36" s="37"/>
       <c r="F36" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G36" s="37"/>
       <c r="H36" s="44"/>
@@ -12744,17 +12773,17 @@
       <c r="O36" s="20"/>
       <c r="P36" s="21"/>
       <c r="Q36" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R36" s="37"/>
       <c r="S36" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T36" s="37"/>
       <c r="U36" s="20"/>
       <c r="V36" s="21"/>
       <c r="W36" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="X36" s="37"/>
     </row>
@@ -12784,7 +12813,7 @@
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>1</v>
@@ -12819,7 +12848,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>1</v>
@@ -12915,11 +12944,11 @@
       </c>
       <c r="E42" s="39"/>
       <c r="F42" s="28" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G42" s="29"/>
       <c r="H42" s="28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I42" s="29"/>
       <c r="J42" s="28" t="s">
@@ -12936,19 +12965,19 @@
       </c>
       <c r="P42" s="47"/>
       <c r="Q42" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T42" s="37"/>
       <c r="U42" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="V42" s="37"/>
       <c r="W42" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="X42" s="37"/>
     </row>
@@ -12961,19 +12990,19 @@
       </c>
       <c r="C43" s="21"/>
       <c r="D43" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E43" s="39"/>
       <c r="F43" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G43" s="39"/>
       <c r="H43" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I43" s="39"/>
       <c r="J43" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K43" s="39"/>
       <c r="L43" s="7"/>
@@ -13007,46 +13036,46 @@
         <v>21</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E44" s="37"/>
       <c r="F44" s="17" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G44" s="18"/>
       <c r="H44" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I44" s="37"/>
       <c r="J44" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K44" s="37"/>
       <c r="N44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="O44" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P44" s="39"/>
       <c r="Q44" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R44" s="39"/>
       <c r="S44" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T44" s="39"/>
       <c r="U44" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V44" s="39"/>
       <c r="W44" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="X44" s="39"/>
     </row>
@@ -13059,11 +13088,11 @@
       </c>
       <c r="C45" s="29"/>
       <c r="D45" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E45" s="37"/>
       <c r="F45" s="36" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G45" s="37"/>
       <c r="H45" s="28" t="s">
@@ -13103,23 +13132,23 @@
         <v>26</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C46" s="35"/>
       <c r="D46" s="34" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E46" s="35"/>
       <c r="F46" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G46" s="35"/>
       <c r="H46" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I46" s="35"/>
       <c r="J46" s="34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K46" s="35"/>
       <c r="N46" s="6" t="s">
@@ -13151,15 +13180,15 @@
         <v>28</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C47" s="39"/>
       <c r="D47" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E47" s="18"/>
       <c r="F47" s="17" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G47" s="18"/>
       <c r="H47" s="20" t="s">
@@ -13167,30 +13196,30 @@
       </c>
       <c r="I47" s="21"/>
       <c r="J47" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K47" s="37"/>
       <c r="N47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O47" s="24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P47" s="25"/>
       <c r="Q47" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="R47" s="25"/>
       <c r="S47" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="T47" s="25"/>
       <c r="U47" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="V47" s="25"/>
       <c r="W47" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="X47" s="25"/>
     </row>
@@ -13199,23 +13228,23 @@
         <v>32</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C48" s="35"/>
       <c r="D48" s="34" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E48" s="35"/>
       <c r="F48" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G48" s="35"/>
       <c r="H48" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I48" s="35"/>
       <c r="J48" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K48" s="35"/>
       <c r="N48" s="6" t="s">
@@ -13247,7 +13276,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C49" s="25"/>
       <c r="D49" s="40" t="s">
@@ -13255,15 +13284,15 @@
       </c>
       <c r="E49" s="41"/>
       <c r="F49" s="22" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G49" s="23"/>
       <c r="H49" s="22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I49" s="23"/>
       <c r="J49" s="22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K49" s="23"/>
       <c r="N49" s="6" t="s">
@@ -13318,15 +13347,15 @@
         <v>37</v>
       </c>
       <c r="O50" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P50" s="29"/>
       <c r="Q50" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R50" s="29"/>
       <c r="S50" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="T50" s="29"/>
       <c r="U50" s="52" t="s">
@@ -13343,7 +13372,7 @@
         <v>40</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="40" t="s">
@@ -13368,23 +13397,23 @@
         <v>40</v>
       </c>
       <c r="O51" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="P51" s="37"/>
       <c r="Q51" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="R51" s="37"/>
       <c r="S51" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="T51" s="37"/>
       <c r="U51" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="V51" s="37"/>
       <c r="W51" s="36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="X51" s="37"/>
     </row>
@@ -13393,7 +13422,7 @@
         <v>45</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C52" s="37"/>
       <c r="D52" s="40" t="s">
@@ -13401,15 +13430,15 @@
       </c>
       <c r="E52" s="41"/>
       <c r="F52" s="22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G52" s="23"/>
       <c r="H52" s="22" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I52" s="23"/>
       <c r="J52" s="22" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K52" s="23"/>
       <c r="L52" s="7"/>
@@ -13430,11 +13459,11 @@
       </c>
       <c r="T52" s="25"/>
       <c r="U52" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="V52" s="37"/>
       <c r="W52" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="X52" s="37"/>
     </row>
@@ -13443,23 +13472,23 @@
         <v>48</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C53" s="37"/>
       <c r="D53" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E53" s="37"/>
       <c r="F53" s="36" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G53" s="37"/>
       <c r="H53" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I53" s="37"/>
       <c r="J53" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K53" s="37"/>
       <c r="L53" s="7"/>
@@ -13516,7 +13545,7 @@
         <v>49</v>
       </c>
       <c r="O54" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P54" s="37"/>
       <c r="Q54" s="46" t="s">
@@ -13547,11 +13576,11 @@
       <c r="D55" s="20"/>
       <c r="E55" s="21"/>
       <c r="F55" s="36" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G55" s="37"/>
       <c r="H55" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I55" s="37"/>
       <c r="J55" s="20"/>
@@ -13562,15 +13591,15 @@
         <v>50</v>
       </c>
       <c r="O55" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P55" s="37"/>
       <c r="Q55" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R55" s="37"/>
       <c r="S55" s="36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T55" s="37"/>
       <c r="U55" s="20"/>
@@ -13583,7 +13612,7 @@
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E56" s="18"/>
       <c r="F56" s="5"/>
@@ -13593,16 +13622,16 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="O56" s="20"/>
       <c r="P56" s="21"/>
       <c r="Q56" s="19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R56" s="19"/>
       <c r="S56" s="19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T56" s="19"/>
       <c r="U56" s="20"/>
@@ -13623,7 +13652,7 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
       <c r="O57" s="19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P57" s="19"/>
       <c r="Q57" s="9"/>
@@ -14225,7 +14254,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -14258,7 +14287,7 @@
         <v>46192</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -14496,23 +14525,23 @@
         <v>26</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C7" s="29"/>
       <c r="D7" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E7" s="29"/>
       <c r="F7" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G7" s="29"/>
       <c r="H7" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I7" s="29"/>
       <c r="J7" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K7" s="29"/>
       <c r="N7" s="6" t="s">
@@ -14534,23 +14563,23 @@
         <v>28</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C8" s="29"/>
       <c r="D8" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E8" s="29"/>
       <c r="F8" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G8" s="29"/>
       <c r="H8" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I8" s="29"/>
       <c r="J8" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K8" s="29"/>
       <c r="N8" s="6" t="s">
@@ -14572,23 +14601,23 @@
         <v>32</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E9" s="29"/>
       <c r="F9" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G9" s="29"/>
       <c r="H9" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I9" s="29"/>
       <c r="J9" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K9" s="29"/>
       <c r="N9" s="6" t="s">
@@ -14648,23 +14677,23 @@
         <v>37</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I11" s="29"/>
       <c r="J11" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K11" s="29"/>
       <c r="N11" s="1" t="s">
@@ -14845,7 +14874,7 @@
     <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
     <row r="19" spans="1:24" ht="11.25" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -14878,7 +14907,7 @@
         <v>46199</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -15004,13 +15033,13 @@
       <c r="B22" s="76"/>
       <c r="C22" s="77"/>
       <c r="D22" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E22" s="71"/>
       <c r="F22" s="76"/>
       <c r="G22" s="77"/>
       <c r="H22" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I22" s="71"/>
       <c r="J22" s="20"/>
@@ -15186,13 +15215,13 @@
       <c r="B27" s="76"/>
       <c r="C27" s="77"/>
       <c r="D27" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E27" s="71"/>
       <c r="F27" s="88"/>
       <c r="G27" s="89"/>
       <c r="H27" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I27" s="71"/>
       <c r="J27" s="20"/>
@@ -15502,7 +15531,7 @@
     </row>
     <row r="37" spans="1:24" ht="11.25" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -15537,7 +15566,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -15844,15 +15873,15 @@
       <c r="O44" s="76"/>
       <c r="P44" s="77"/>
       <c r="Q44" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R44" s="29"/>
       <c r="S44" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T44" s="29"/>
       <c r="U44" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="V44" s="29"/>
       <c r="W44" s="20"/>
@@ -15878,15 +15907,15 @@
       <c r="O45" s="76"/>
       <c r="P45" s="77"/>
       <c r="Q45" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R45" s="29"/>
       <c r="S45" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T45" s="29"/>
       <c r="U45" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="V45" s="29"/>
       <c r="W45" s="20"/>
@@ -15963,23 +15992,23 @@
         <v>40</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C48" s="29"/>
       <c r="D48" s="28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E48" s="29"/>
       <c r="F48" s="28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G48" s="29"/>
       <c r="H48" s="28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I48" s="29"/>
       <c r="J48" s="28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K48" s="29"/>
       <c r="N48" s="1" t="s">
@@ -16705,7 +16734,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -16738,7 +16767,7 @@
         <v>46234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -16983,7 +17012,7 @@
       <c r="O7" s="20"/>
       <c r="P7" s="21"/>
       <c r="Q7" s="90" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R7" s="91"/>
       <c r="S7" s="88"/>
@@ -17023,7 +17052,7 @@
       <c r="O8" s="76"/>
       <c r="P8" s="77"/>
       <c r="Q8" s="90" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R8" s="91"/>
       <c r="S8" s="76"/>
@@ -17379,7 +17408,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -17412,7 +17441,7 @@
         <v>46241</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -17460,7 +17489,7 @@
       </c>
       <c r="I20" s="29"/>
       <c r="J20" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K20" s="71"/>
       <c r="N20" s="1" t="s">
@@ -17700,7 +17729,7 @@
       </c>
       <c r="I27" s="29"/>
       <c r="J27" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K27" s="71"/>
       <c r="N27" s="6" t="s">
@@ -17808,7 +17837,7 @@
       </c>
       <c r="I30" s="29"/>
       <c r="J30" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K30" s="71"/>
       <c r="N30" s="1" t="s">
@@ -17971,7 +18000,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -18006,7 +18035,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -18069,7 +18098,7 @@
       <c r="U38" s="88"/>
       <c r="V38" s="89"/>
       <c r="W38" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="X38" s="21"/>
     </row>
@@ -18116,7 +18145,7 @@
       <c r="F40" s="76"/>
       <c r="G40" s="77"/>
       <c r="H40" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I40" s="71"/>
       <c r="J40" s="20"/>
@@ -18300,7 +18329,7 @@
       <c r="F45" s="88"/>
       <c r="G45" s="89"/>
       <c r="H45" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I45" s="71"/>
       <c r="J45" s="20"/>
@@ -18386,7 +18415,7 @@
       <c r="F48" s="20"/>
       <c r="G48" s="21"/>
       <c r="H48" s="70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I48" s="71"/>
       <c r="J48" s="20"/>
@@ -19120,7 +19149,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -19153,7 +19182,7 @@
         <v>46276</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -19191,23 +19220,23 @@
         <v>7</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G2" s="21"/>
       <c r="H2" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I2" s="21"/>
       <c r="J2" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K2" s="21"/>
       <c r="N2" s="1" t="s">
@@ -19664,7 +19693,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -19697,7 +19726,7 @@
         <v>46283</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -20257,7 +20286,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -20292,7 +20321,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -21379,7 +21408,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -21412,7 +21441,7 @@
         <v>46318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -21938,7 +21967,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -21971,7 +22000,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -22500,7 +22529,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -22535,7 +22564,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -23587,7 +23616,7 @@
     <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
     <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -23620,7 +23649,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -24132,7 +24161,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -24165,7 +24194,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -24704,7 +24733,7 @@
     </row>
     <row r="38" spans="2:25">
       <c r="B38" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3919" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C05CFDA0-396F-4240-A318-58D8CDEC2774}"/>
+  <xr:revisionPtr revIDLastSave="3921" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7C5323-517A-4754-AB46-B1323B073ACC}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -11764,10 +11764,10 @@
         <v>170</v>
       </c>
       <c r="G12" s="22"/>
-      <c r="H12" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="I12" s="22"/>
+      <c r="H12" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="I12" s="30"/>
       <c r="J12" s="25" t="s">
         <v>67</v>
       </c>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3921" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7C5323-517A-4754-AB46-B1323B073ACC}"/>
+  <xr:revisionPtr revIDLastSave="3922" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFF8BC32-285E-49A5-8DE0-C656C36378C3}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3317" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3317" uniqueCount="252">
   <si>
     <t>Uke 01</t>
   </si>
@@ -828,6 +828,9 @@
   </si>
   <si>
     <t>Booking Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -11719,7 +11722,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="29" t="s">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="I11" s="30"/>
       <c r="J11" s="25" t="s">

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3969" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0622F96-3B0D-47C1-8AD1-BB6E82DF1D5A}"/>
+  <xr:revisionPtr revIDLastSave="3972" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64B1F39E-7DD8-4501-90AA-F61F196C0011}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="256">
   <si>
     <t>Uke 01</t>
   </si>
@@ -14538,16 +14538,26 @@
       <c r="N6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O6" s="76"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="88"/>
-      <c r="V6" s="89"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="21"/>
+      <c r="O6" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="T6" s="71"/>
+      <c r="U6" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="V6" s="71"/>
+      <c r="W6" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="X6" s="71"/>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
@@ -15830,18 +15840,26 @@
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="76"/>
-      <c r="C42" s="77"/>
+      <c r="B42" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="71"/>
       <c r="D42" s="70" t="s">
         <v>228</v>
       </c>
       <c r="E42" s="71"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="88"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="21"/>
+      <c r="F42" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="G42" s="71"/>
+      <c r="H42" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="I42" s="71"/>
+      <c r="J42" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="K42" s="71"/>
       <c r="N42" s="1" t="s">
         <v>24</v>
       </c>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3976" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1644C45A-02AC-47EA-81B8-08CE9D7FEF13}"/>
+  <xr:revisionPtr revIDLastSave="3980" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEB7CBDB-6E01-4834-8093-19CDF95EC7C9}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="257">
   <si>
     <t>Uke 01</t>
   </si>
@@ -680,6 +680,9 @@
     <t>Eksamen</t>
   </si>
   <si>
+    <t>Prosjekt/Oslo</t>
+  </si>
+  <si>
     <t>SE VA 2/SUR SB</t>
   </si>
   <si>
@@ -1252,6 +1255,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1295,12 +1304,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2014,10 +2017,10 @@
         <v>16</v>
       </c>
       <c r="S4" s="28"/>
-      <c r="T4" s="54" t="s">
+      <c r="T4" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="55"/>
+      <c r="U4" s="57"/>
       <c r="V4" s="66" t="s">
         <v>18</v>
       </c>
@@ -2112,10 +2115,10 @@
       <c r="Q6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R6" s="54" t="s">
+      <c r="R6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="55"/>
+      <c r="S6" s="57"/>
       <c r="T6" s="68" t="s">
         <v>12</v>
       </c>
@@ -2218,18 +2221,18 @@
         <v>13</v>
       </c>
       <c r="S8" s="28"/>
-      <c r="T8" s="49" t="s">
+      <c r="T8" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="U8" s="50"/>
-      <c r="V8" s="49" t="s">
+      <c r="U8" s="52"/>
+      <c r="V8" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="W8" s="50"/>
-      <c r="X8" s="49" t="s">
+      <c r="W8" s="52"/>
+      <c r="X8" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="Y8" s="50"/>
+      <c r="Y8" s="52"/>
       <c r="Z8" s="29" t="s">
         <v>31</v>
       </c>
@@ -2371,10 +2374,10 @@
         <v>38</v>
       </c>
       <c r="S11" s="34"/>
-      <c r="T11" s="54" t="s">
+      <c r="T11" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="U11" s="55"/>
+      <c r="U11" s="57"/>
       <c r="V11" s="66" t="s">
         <v>39</v>
       </c>
@@ -2422,18 +2425,18 @@
         <v>41</v>
       </c>
       <c r="S12" s="34"/>
-      <c r="T12" s="49" t="s">
+      <c r="T12" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="U12" s="50"/>
-      <c r="V12" s="49" t="s">
+      <c r="U12" s="52"/>
+      <c r="V12" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="W12" s="50"/>
-      <c r="X12" s="49" t="s">
+      <c r="W12" s="52"/>
+      <c r="X12" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Y12" s="50"/>
+      <c r="Y12" s="52"/>
       <c r="Z12" s="29" t="s">
         <v>44</v>
       </c>
@@ -2469,22 +2472,22 @@
       <c r="Q13" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="R13" s="54" t="s">
+      <c r="R13" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="S13" s="55"/>
-      <c r="T13" s="54" t="s">
+      <c r="S13" s="57"/>
+      <c r="T13" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="U13" s="55"/>
-      <c r="V13" s="49" t="s">
+      <c r="U13" s="57"/>
+      <c r="V13" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="W13" s="50"/>
-      <c r="X13" s="49" t="s">
+      <c r="W13" s="52"/>
+      <c r="X13" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Y13" s="50"/>
+      <c r="Y13" s="52"/>
       <c r="Z13" s="29" t="s">
         <v>31</v>
       </c>
@@ -2725,10 +2728,10 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
-      <c r="T19" s="49" t="s">
+      <c r="T19" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="U19" s="50"/>
+      <c r="U19" s="52"/>
     </row>
     <row r="20" spans="1:27">
       <c r="B20" s="4"/>
@@ -2872,10 +2875,10 @@
         <v>56</v>
       </c>
       <c r="E24" s="34"/>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="48"/>
+      <c r="G24" s="50"/>
       <c r="H24" s="27" t="s">
         <v>57</v>
       </c>
@@ -3002,18 +3005,18 @@
         <v>58</v>
       </c>
       <c r="S26" s="28"/>
-      <c r="T26" s="45" t="s">
+      <c r="T26" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="U26" s="46"/>
+      <c r="U26" s="48"/>
       <c r="V26" s="27" t="s">
         <v>58</v>
       </c>
       <c r="W26" s="28"/>
-      <c r="X26" s="49" t="s">
+      <c r="X26" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Y26" s="50"/>
+      <c r="Y26" s="52"/>
       <c r="Z26" s="25" t="s">
         <v>33</v>
       </c>
@@ -3088,10 +3091,10 @@
         <v>9</v>
       </c>
       <c r="G28" s="18"/>
-      <c r="H28" s="60" t="s">
+      <c r="H28" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="61"/>
+      <c r="I28" s="46"/>
       <c r="J28" s="33" t="s">
         <v>56</v>
       </c>
@@ -3161,10 +3164,10 @@
         <v>9</v>
       </c>
       <c r="S29" s="18"/>
-      <c r="T29" s="54" t="s">
+      <c r="T29" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="U29" s="55"/>
+      <c r="U29" s="57"/>
       <c r="V29" s="17" t="s">
         <v>9</v>
       </c>
@@ -3173,10 +3176,10 @@
         <v>33</v>
       </c>
       <c r="Y29" s="26"/>
-      <c r="Z29" s="58" t="s">
+      <c r="Z29" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="AA29" s="59"/>
+      <c r="AA29" s="61"/>
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="6" t="s">
@@ -3214,10 +3217,10 @@
         <v>9</v>
       </c>
       <c r="S30" s="18"/>
-      <c r="T30" s="54" t="s">
+      <c r="T30" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="U30" s="55"/>
+      <c r="U30" s="57"/>
       <c r="V30" s="19" t="s">
         <v>14</v>
       </c>
@@ -3243,14 +3246,14 @@
         <v>56</v>
       </c>
       <c r="E31" s="34"/>
-      <c r="F31" s="58" t="s">
+      <c r="F31" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="G31" s="59"/>
-      <c r="H31" s="58" t="s">
+      <c r="G31" s="61"/>
+      <c r="H31" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="I31" s="59"/>
+      <c r="I31" s="61"/>
       <c r="J31" s="33" t="s">
         <v>56</v>
       </c>
@@ -3300,10 +3303,10 @@
         <v>9</v>
       </c>
       <c r="G32" s="18"/>
-      <c r="H32" s="60" t="s">
+      <c r="H32" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I32" s="61"/>
+      <c r="I32" s="46"/>
       <c r="J32" s="33" t="s">
         <v>56</v>
       </c>
@@ -3320,10 +3323,10 @@
         <v>9</v>
       </c>
       <c r="S32" s="18"/>
-      <c r="T32" s="54" t="s">
+      <c r="T32" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="U32" s="55"/>
+      <c r="U32" s="57"/>
       <c r="V32" s="23" t="s">
         <v>11</v>
       </c>
@@ -3373,10 +3376,10 @@
         <v>38</v>
       </c>
       <c r="S33" s="34"/>
-      <c r="T33" s="45" t="s">
+      <c r="T33" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="U33" s="46"/>
+      <c r="U33" s="48"/>
       <c r="V33" s="33" t="s">
         <v>38</v>
       </c>
@@ -3455,14 +3458,14 @@
         <v>56</v>
       </c>
       <c r="E35" s="34"/>
-      <c r="F35" s="58" t="s">
+      <c r="F35" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="G35" s="59"/>
-      <c r="H35" s="58" t="s">
+      <c r="G35" s="61"/>
+      <c r="H35" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="I35" s="59"/>
+      <c r="I35" s="61"/>
       <c r="J35" s="33" t="s">
         <v>56</v>
       </c>
@@ -3475,22 +3478,22 @@
       <c r="Q35" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="R35" s="54" t="s">
+      <c r="R35" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="S35" s="55"/>
-      <c r="T35" s="49" t="s">
+      <c r="S35" s="57"/>
+      <c r="T35" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="50"/>
-      <c r="V35" s="49" t="s">
+      <c r="U35" s="52"/>
+      <c r="V35" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="W35" s="50"/>
-      <c r="X35" s="49" t="s">
+      <c r="W35" s="52"/>
+      <c r="X35" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="Y35" s="50"/>
+      <c r="Y35" s="52"/>
       <c r="Z35" s="29" t="s">
         <v>44</v>
       </c>
@@ -3532,18 +3535,18 @@
         <v>9</v>
       </c>
       <c r="S36" s="18"/>
-      <c r="T36" s="49" t="s">
+      <c r="T36" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="U36" s="50"/>
-      <c r="V36" s="49" t="s">
+      <c r="U36" s="52"/>
+      <c r="V36" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="W36" s="50"/>
-      <c r="X36" s="49" t="s">
+      <c r="W36" s="52"/>
+      <c r="X36" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Y36" s="50"/>
+      <c r="Y36" s="52"/>
       <c r="Z36" s="29" t="s">
         <v>31</v>
       </c>
@@ -3581,22 +3584,22 @@
       <c r="Q37" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="R37" s="54" t="s">
+      <c r="R37" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="S37" s="55"/>
-      <c r="T37" s="49" t="s">
+      <c r="S37" s="57"/>
+      <c r="T37" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="U37" s="50"/>
-      <c r="V37" s="49" t="s">
+      <c r="U37" s="52"/>
+      <c r="V37" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="W37" s="50"/>
-      <c r="X37" s="49" t="s">
+      <c r="W37" s="52"/>
+      <c r="X37" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Y37" s="50"/>
+      <c r="Y37" s="52"/>
       <c r="Z37" s="29" t="s">
         <v>31</v>
       </c>
@@ -3767,26 +3770,26 @@
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="47" t="s">
+      <c r="B42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="48"/>
-      <c r="D42" s="47" t="s">
+      <c r="C42" s="50"/>
+      <c r="D42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="48"/>
-      <c r="F42" s="47" t="s">
+      <c r="E42" s="50"/>
+      <c r="F42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G42" s="48"/>
-      <c r="H42" s="47" t="s">
+      <c r="G42" s="50"/>
+      <c r="H42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I42" s="48"/>
-      <c r="J42" s="47" t="s">
+      <c r="I42" s="50"/>
+      <c r="J42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K42" s="48"/>
+      <c r="K42" s="50"/>
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
@@ -3795,26 +3798,26 @@
       <c r="Q42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="R42" s="47" t="s">
+      <c r="R42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="S42" s="48"/>
-      <c r="T42" s="47" t="s">
+      <c r="S42" s="50"/>
+      <c r="T42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="U42" s="48"/>
-      <c r="V42" s="47" t="s">
+      <c r="U42" s="50"/>
+      <c r="V42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="W42" s="48"/>
-      <c r="X42" s="47" t="s">
+      <c r="W42" s="50"/>
+      <c r="X42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="Y42" s="48"/>
-      <c r="Z42" s="47" t="s">
+      <c r="Y42" s="50"/>
+      <c r="Z42" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AA42" s="48"/>
+      <c r="AA42" s="50"/>
     </row>
     <row r="43" spans="1:27">
       <c r="A43" s="1" t="s">
@@ -3852,10 +3855,10 @@
         <v>9</v>
       </c>
       <c r="S43" s="18"/>
-      <c r="T43" s="56" t="s">
+      <c r="T43" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="U43" s="57"/>
+      <c r="U43" s="59"/>
       <c r="V43" s="17" t="s">
         <v>9</v>
       </c>
@@ -3901,26 +3904,26 @@
       <c r="Q44" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R44" s="45" t="s">
+      <c r="R44" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="S44" s="46"/>
-      <c r="T44" s="45" t="s">
+      <c r="S44" s="48"/>
+      <c r="T44" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="U44" s="46"/>
-      <c r="V44" s="45" t="s">
+      <c r="U44" s="48"/>
+      <c r="V44" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="W44" s="46"/>
-      <c r="X44" s="45" t="s">
+      <c r="W44" s="48"/>
+      <c r="X44" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="Y44" s="46"/>
-      <c r="Z44" s="54" t="s">
+      <c r="Y44" s="48"/>
+      <c r="Z44" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="AA44" s="55"/>
+      <c r="AA44" s="57"/>
     </row>
     <row r="45" spans="1:27" ht="15" customHeight="1">
       <c r="A45" s="1" t="s">
@@ -4011,10 +4014,10 @@
         <v>9</v>
       </c>
       <c r="S46" s="18"/>
-      <c r="T46" s="54" t="s">
+      <c r="T46" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="U46" s="55"/>
+      <c r="U46" s="57"/>
       <c r="V46" s="17" t="s">
         <v>9</v>
       </c>
@@ -4032,10 +4035,10 @@
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="54" t="s">
+      <c r="B47" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="55"/>
+      <c r="C47" s="57"/>
       <c r="D47" s="17" t="s">
         <v>9</v>
       </c>
@@ -4060,22 +4063,22 @@
       <c r="Q47" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="R47" s="45" t="s">
+      <c r="R47" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="S47" s="46"/>
-      <c r="T47" s="45" t="s">
+      <c r="S47" s="48"/>
+      <c r="T47" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="U47" s="46"/>
-      <c r="V47" s="54" t="s">
+      <c r="U47" s="48"/>
+      <c r="V47" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="W47" s="55"/>
-      <c r="X47" s="54" t="s">
+      <c r="W47" s="57"/>
+      <c r="X47" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="Y47" s="55"/>
+      <c r="Y47" s="57"/>
       <c r="Z47" s="17" t="s">
         <v>9</v>
       </c>
@@ -4142,18 +4145,18 @@
         <v>31</v>
       </c>
       <c r="C49" s="30"/>
-      <c r="D49" s="49" t="s">
+      <c r="D49" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E49" s="50"/>
-      <c r="F49" s="49" t="s">
+      <c r="E49" s="52"/>
+      <c r="F49" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G49" s="50"/>
-      <c r="H49" s="49" t="s">
+      <c r="G49" s="52"/>
+      <c r="H49" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="I49" s="50"/>
+      <c r="I49" s="52"/>
       <c r="J49" s="29" t="s">
         <v>31</v>
       </c>
@@ -4170,18 +4173,18 @@
         <v>44</v>
       </c>
       <c r="S49" s="30"/>
-      <c r="T49" s="56" t="s">
+      <c r="T49" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="U49" s="57"/>
-      <c r="V49" s="49" t="s">
+      <c r="U49" s="59"/>
+      <c r="V49" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="W49" s="50"/>
-      <c r="X49" s="49" t="s">
+      <c r="W49" s="52"/>
+      <c r="X49" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="Y49" s="50"/>
+      <c r="Y49" s="52"/>
       <c r="Z49" s="29" t="s">
         <v>44</v>
       </c>
@@ -4195,18 +4198,18 @@
         <v>44</v>
       </c>
       <c r="C50" s="30"/>
-      <c r="D50" s="49" t="s">
+      <c r="D50" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E50" s="50"/>
-      <c r="F50" s="49" t="s">
+      <c r="E50" s="52"/>
+      <c r="F50" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G50" s="50"/>
-      <c r="H50" s="49" t="s">
+      <c r="G50" s="52"/>
+      <c r="H50" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I50" s="50"/>
+      <c r="I50" s="52"/>
       <c r="J50" s="29" t="s">
         <v>44</v>
       </c>
@@ -4223,18 +4226,18 @@
         <v>9</v>
       </c>
       <c r="S50" s="18"/>
-      <c r="T50" s="54" t="s">
+      <c r="T50" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="U50" s="55"/>
-      <c r="V50" s="49" t="s">
+      <c r="U50" s="57"/>
+      <c r="V50" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="W50" s="50"/>
-      <c r="X50" s="49" t="s">
+      <c r="W50" s="52"/>
+      <c r="X50" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Y50" s="50"/>
+      <c r="Y50" s="52"/>
       <c r="Z50" s="17" t="s">
         <v>9</v>
       </c>
@@ -4267,26 +4270,26 @@
       <c r="Q51" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="R51" s="54" t="s">
+      <c r="R51" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="S51" s="55"/>
-      <c r="T51" s="54" t="s">
+      <c r="S51" s="57"/>
+      <c r="T51" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="U51" s="55"/>
-      <c r="V51" s="54" t="s">
+      <c r="U51" s="57"/>
+      <c r="V51" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="W51" s="55"/>
-      <c r="X51" s="54" t="s">
+      <c r="W51" s="57"/>
+      <c r="X51" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="Y51" s="55"/>
-      <c r="Z51" s="54" t="s">
+      <c r="Y51" s="57"/>
+      <c r="Z51" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="AA51" s="55"/>
+      <c r="AA51" s="57"/>
     </row>
     <row r="52" spans="1:27">
       <c r="A52" s="1" t="s">
@@ -4340,10 +4343,10 @@
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B53" s="54" t="s">
+      <c r="B53" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="C53" s="55"/>
+      <c r="C53" s="57"/>
       <c r="D53" s="19" t="s">
         <v>14</v>
       </c>
@@ -4367,10 +4370,10 @@
         <v>31</v>
       </c>
       <c r="S53" s="30"/>
-      <c r="T53" s="54" t="s">
+      <c r="T53" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="U53" s="55"/>
+      <c r="U53" s="57"/>
       <c r="V53" s="23" t="s">
         <v>11</v>
       </c>
@@ -4392,18 +4395,18 @@
         <v>31</v>
       </c>
       <c r="C54" s="30"/>
-      <c r="D54" s="49" t="s">
+      <c r="D54" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E54" s="50"/>
-      <c r="F54" s="49" t="s">
+      <c r="E54" s="52"/>
+      <c r="F54" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G54" s="50"/>
-      <c r="H54" s="49" t="s">
+      <c r="G54" s="52"/>
+      <c r="H54" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I54" s="50"/>
+      <c r="I54" s="52"/>
       <c r="J54" s="29" t="s">
         <v>31</v>
       </c>
@@ -4415,18 +4418,18 @@
         <v>31</v>
       </c>
       <c r="S54" s="30"/>
-      <c r="T54" s="56" t="s">
+      <c r="T54" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="U54" s="57"/>
-      <c r="V54" s="49" t="s">
+      <c r="U54" s="59"/>
+      <c r="V54" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="W54" s="50"/>
-      <c r="X54" s="49" t="s">
+      <c r="W54" s="52"/>
+      <c r="X54" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Y54" s="50"/>
+      <c r="Y54" s="52"/>
       <c r="Z54" s="29" t="s">
         <v>31</v>
       </c>
@@ -4459,26 +4462,26 @@
       <c r="Q55" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="R55" s="54" t="s">
+      <c r="R55" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="S55" s="55"/>
-      <c r="T55" s="54" t="s">
+      <c r="S55" s="57"/>
+      <c r="T55" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="U55" s="55"/>
-      <c r="V55" s="54" t="s">
+      <c r="U55" s="57"/>
+      <c r="V55" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="W55" s="55"/>
-      <c r="X55" s="54" t="s">
+      <c r="W55" s="57"/>
+      <c r="X55" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="Y55" s="55"/>
-      <c r="Z55" s="54" t="s">
+      <c r="Y55" s="57"/>
+      <c r="Z55" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="AA55" s="55"/>
+      <c r="AA55" s="57"/>
     </row>
     <row r="56" spans="1:27">
       <c r="A56" s="1" t="s">
@@ -5157,26 +5160,26 @@
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="47" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="47" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="47" t="s">
+      <c r="G2" s="50"/>
+      <c r="H2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="47" t="s">
+      <c r="I2" s="50"/>
+      <c r="J2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="48"/>
+      <c r="K2" s="50"/>
       <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
@@ -5405,10 +5408,10 @@
         <v>9</v>
       </c>
       <c r="E7" s="18"/>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="46"/>
+      <c r="G7" s="48"/>
       <c r="H7" s="17" t="s">
         <v>9</v>
       </c>
@@ -5472,10 +5475,10 @@
         <v>9</v>
       </c>
       <c r="P8" s="18"/>
-      <c r="Q8" s="49" t="s">
+      <c r="Q8" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="50"/>
+      <c r="R8" s="52"/>
       <c r="S8" s="31" t="s">
         <v>93</v>
       </c>
@@ -5497,10 +5500,10 @@
         <v>44</v>
       </c>
       <c r="C9" s="30"/>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="50"/>
+      <c r="E9" s="52"/>
       <c r="F9" s="27" t="s">
         <v>13</v>
       </c>
@@ -5589,26 +5592,26 @@
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="45" t="s">
+      <c r="C11" s="48"/>
+      <c r="D11" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="46"/>
+      <c r="E11" s="48"/>
       <c r="F11" s="33" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="34"/>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="46"/>
-      <c r="J11" s="45" t="s">
+      <c r="I11" s="48"/>
+      <c r="J11" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="K11" s="46"/>
+      <c r="K11" s="48"/>
       <c r="N11" s="1" t="s">
         <v>37</v>
       </c>
@@ -5637,22 +5640,22 @@
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="46"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="33" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="34"/>
-      <c r="F12" s="49" t="s">
+      <c r="F12" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="50"/>
-      <c r="H12" s="49" t="s">
+      <c r="G12" s="52"/>
+      <c r="H12" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="50"/>
+      <c r="I12" s="52"/>
       <c r="J12" s="29" t="s">
         <v>44</v>
       </c>
@@ -5664,18 +5667,18 @@
         <v>44</v>
       </c>
       <c r="P12" s="30"/>
-      <c r="Q12" s="49" t="s">
+      <c r="Q12" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="R12" s="50"/>
-      <c r="S12" s="49" t="s">
+      <c r="R12" s="52"/>
+      <c r="S12" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="T12" s="50"/>
-      <c r="U12" s="49" t="s">
+      <c r="T12" s="52"/>
+      <c r="U12" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="V12" s="50"/>
+      <c r="V12" s="52"/>
       <c r="W12" s="29" t="s">
         <v>44</v>
       </c>
@@ -5697,14 +5700,14 @@
         <v>27</v>
       </c>
       <c r="G13" s="34"/>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="46"/>
-      <c r="J13" s="45" t="s">
+      <c r="I13" s="48"/>
+      <c r="J13" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="46"/>
+      <c r="K13" s="48"/>
       <c r="N13" s="12" t="s">
         <v>45</v>
       </c>
@@ -5737,18 +5740,18 @@
         <v>31</v>
       </c>
       <c r="C14" s="30"/>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="50"/>
-      <c r="F14" s="49" t="s">
+      <c r="E14" s="52"/>
+      <c r="F14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="50"/>
-      <c r="H14" s="49" t="s">
+      <c r="G14" s="52"/>
+      <c r="H14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="50"/>
+      <c r="I14" s="52"/>
       <c r="J14" s="29" t="s">
         <v>31</v>
       </c>
@@ -5760,18 +5763,18 @@
         <v>31</v>
       </c>
       <c r="P14" s="30"/>
-      <c r="Q14" s="49" t="s">
+      <c r="Q14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="R14" s="50"/>
-      <c r="S14" s="49" t="s">
+      <c r="R14" s="52"/>
+      <c r="S14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="T14" s="50"/>
-      <c r="U14" s="49" t="s">
+      <c r="T14" s="52"/>
+      <c r="U14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="V14" s="50"/>
+      <c r="V14" s="52"/>
       <c r="W14" s="29" t="s">
         <v>31</v>
       </c>
@@ -5785,18 +5788,18 @@
         <v>31</v>
       </c>
       <c r="C15" s="30"/>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="50"/>
-      <c r="F15" s="49" t="s">
+      <c r="E15" s="52"/>
+      <c r="F15" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="50"/>
-      <c r="H15" s="49" t="s">
+      <c r="G15" s="52"/>
+      <c r="H15" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="50"/>
+      <c r="I15" s="52"/>
       <c r="J15" s="29" t="s">
         <v>31</v>
       </c>
@@ -5854,14 +5857,14 @@
       <c r="P16" s="30"/>
       <c r="Q16" s="17"/>
       <c r="R16" s="18"/>
-      <c r="S16" s="49" t="s">
+      <c r="S16" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="T16" s="50"/>
-      <c r="U16" s="49" t="s">
+      <c r="T16" s="52"/>
+      <c r="U16" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="V16" s="50"/>
+      <c r="V16" s="52"/>
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
@@ -6009,10 +6012,10 @@
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="60" t="s">
+      <c r="B21" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="61"/>
+      <c r="C21" s="46"/>
       <c r="D21" s="27" t="s">
         <v>58</v>
       </c>
@@ -6057,10 +6060,10 @@
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="60" t="s">
+      <c r="B22" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="61"/>
+      <c r="C22" s="46"/>
       <c r="D22" s="27" t="s">
         <v>58</v>
       </c>
@@ -6249,10 +6252,10 @@
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="46"/>
+      <c r="C26" s="48"/>
       <c r="D26" s="33" t="s">
         <v>103</v>
       </c>
@@ -6272,18 +6275,18 @@
       <c r="N26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O26" s="49" t="s">
+      <c r="O26" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="P26" s="50"/>
+      <c r="P26" s="52"/>
       <c r="Q26" s="17" t="s">
         <v>9</v>
       </c>
       <c r="R26" s="18"/>
-      <c r="S26" s="49" t="s">
+      <c r="S26" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="T26" s="50"/>
+      <c r="T26" s="52"/>
       <c r="U26" s="17" t="s">
         <v>9</v>
       </c>
@@ -6301,18 +6304,18 @@
         <v>31</v>
       </c>
       <c r="C27" s="30"/>
-      <c r="D27" s="49" t="s">
+      <c r="D27" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="49" t="s">
+      <c r="E27" s="52"/>
+      <c r="F27" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="50"/>
-      <c r="H27" s="49" t="s">
+      <c r="G27" s="52"/>
+      <c r="H27" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="50"/>
+      <c r="I27" s="52"/>
       <c r="J27" s="29" t="s">
         <v>31</v>
       </c>
@@ -6320,10 +6323,10 @@
       <c r="N27" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O27" s="45" t="s">
+      <c r="O27" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="P27" s="46"/>
+      <c r="P27" s="48"/>
       <c r="Q27" s="33" t="s">
         <v>103</v>
       </c>
@@ -6349,18 +6352,18 @@
         <v>44</v>
       </c>
       <c r="C28" s="30"/>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="50"/>
-      <c r="F28" s="49" t="s">
+      <c r="E28" s="52"/>
+      <c r="F28" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="50"/>
-      <c r="H28" s="49" t="s">
+      <c r="G28" s="52"/>
+      <c r="H28" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I28" s="50"/>
+      <c r="I28" s="52"/>
       <c r="J28" s="29" t="s">
         <v>44</v>
       </c>
@@ -6420,22 +6423,22 @@
         <v>9</v>
       </c>
       <c r="P29" s="18"/>
-      <c r="Q29" s="49" t="s">
+      <c r="Q29" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="R29" s="50"/>
+      <c r="R29" s="52"/>
       <c r="S29" s="17" t="s">
         <v>9</v>
       </c>
       <c r="T29" s="18"/>
-      <c r="U29" s="49" t="s">
+      <c r="U29" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="V29" s="50"/>
-      <c r="W29" s="49" t="s">
+      <c r="V29" s="52"/>
+      <c r="W29" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="X29" s="50"/>
+      <c r="X29" s="52"/>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="1" t="s">
@@ -6545,18 +6548,18 @@
         <v>44</v>
       </c>
       <c r="C32" s="30"/>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="50"/>
+      <c r="E32" s="52"/>
       <c r="F32" s="17" t="s">
         <v>9</v>
       </c>
       <c r="G32" s="18"/>
-      <c r="H32" s="49" t="s">
+      <c r="H32" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I32" s="50"/>
+      <c r="I32" s="52"/>
       <c r="J32" s="29" t="s">
         <v>44</v>
       </c>
@@ -6566,43 +6569,43 @@
       <c r="N32" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O32" s="49" t="s">
+      <c r="O32" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="49" t="s">
+      <c r="P32" s="52"/>
+      <c r="Q32" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="R32" s="50"/>
-      <c r="S32" s="49" t="s">
+      <c r="R32" s="52"/>
+      <c r="S32" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="T32" s="50"/>
-      <c r="U32" s="49" t="s">
+      <c r="T32" s="52"/>
+      <c r="U32" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="V32" s="50"/>
-      <c r="W32" s="49" t="s">
+      <c r="V32" s="52"/>
+      <c r="W32" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="X32" s="50"/>
+      <c r="X32" s="52"/>
     </row>
     <row r="33" spans="1:24">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="46"/>
+      <c r="C33" s="48"/>
       <c r="D33" s="33" t="s">
         <v>103</v>
       </c>
       <c r="E33" s="34"/>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G33" s="50"/>
+      <c r="G33" s="52"/>
       <c r="H33" s="33" t="s">
         <v>103</v>
       </c>
@@ -6616,10 +6619,10 @@
       <c r="N33" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O33" s="49" t="s">
+      <c r="O33" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="P33" s="50"/>
+      <c r="P33" s="52"/>
       <c r="Q33" s="33" t="s">
         <v>103</v>
       </c>
@@ -6632,35 +6635,35 @@
         <v>103</v>
       </c>
       <c r="V33" s="34"/>
-      <c r="W33" s="49" t="s">
+      <c r="W33" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="X33" s="50"/>
+      <c r="X33" s="52"/>
     </row>
     <row r="34" spans="1:24">
       <c r="A34" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="58" t="s">
+      <c r="B34" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="59"/>
-      <c r="D34" s="58" t="s">
+      <c r="C34" s="61"/>
+      <c r="D34" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="59"/>
-      <c r="F34" s="58" t="s">
+      <c r="E34" s="61"/>
+      <c r="F34" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="G34" s="59"/>
-      <c r="H34" s="58" t="s">
+      <c r="G34" s="61"/>
+      <c r="H34" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="I34" s="59"/>
-      <c r="J34" s="58" t="s">
+      <c r="I34" s="61"/>
+      <c r="J34" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="K34" s="59"/>
+      <c r="K34" s="61"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
       <c r="N34" s="12" t="s">
@@ -6710,47 +6713,47 @@
       </c>
       <c r="O35" s="17"/>
       <c r="P35" s="18"/>
-      <c r="Q35" s="49" t="s">
+      <c r="Q35" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="R35" s="50"/>
-      <c r="S35" s="49" t="s">
+      <c r="R35" s="52"/>
+      <c r="S35" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="T35" s="50"/>
-      <c r="U35" s="49" t="s">
+      <c r="T35" s="52"/>
+      <c r="U35" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="V35" s="50"/>
-      <c r="W35" s="49" t="s">
+      <c r="V35" s="52"/>
+      <c r="W35" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="X35" s="50"/>
+      <c r="X35" s="52"/>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="58" t="s">
+      <c r="B36" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="59"/>
-      <c r="D36" s="58" t="s">
+      <c r="C36" s="61"/>
+      <c r="D36" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="E36" s="59"/>
-      <c r="F36" s="58" t="s">
+      <c r="E36" s="61"/>
+      <c r="F36" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="G36" s="59"/>
-      <c r="H36" s="58" t="s">
+      <c r="G36" s="61"/>
+      <c r="H36" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="I36" s="59"/>
-      <c r="J36" s="58" t="s">
+      <c r="I36" s="61"/>
+      <c r="J36" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="K36" s="59"/>
+      <c r="K36" s="61"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
       <c r="O36" s="9"/>
@@ -7062,10 +7065,10 @@
         <v>111</v>
       </c>
       <c r="R44" s="26"/>
-      <c r="S44" s="49" t="s">
+      <c r="S44" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="T44" s="50"/>
+      <c r="T44" s="52"/>
       <c r="U44" s="29" t="s">
         <v>31</v>
       </c>
@@ -7131,10 +7134,10 @@
         <v>90</v>
       </c>
       <c r="C46" s="32"/>
-      <c r="D46" s="49" t="s">
+      <c r="D46" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E46" s="50"/>
+      <c r="E46" s="52"/>
       <c r="F46" s="17" t="s">
         <v>9</v>
       </c>
@@ -7143,10 +7146,10 @@
         <v>9</v>
       </c>
       <c r="I46" s="18"/>
-      <c r="J46" s="58" t="s">
+      <c r="J46" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="K46" s="59"/>
+      <c r="K46" s="61"/>
       <c r="L46" s="7"/>
       <c r="N46" s="6" t="s">
         <v>26</v>
@@ -7261,14 +7264,14 @@
         <v>9</v>
       </c>
       <c r="T48" s="18"/>
-      <c r="U48" s="49" t="s">
+      <c r="U48" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="V48" s="50"/>
-      <c r="W48" s="49" t="s">
+      <c r="V48" s="52"/>
+      <c r="W48" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="X48" s="50"/>
+      <c r="X48" s="52"/>
     </row>
     <row r="49" spans="1:24">
       <c r="A49" s="6" t="s">
@@ -7298,18 +7301,18 @@
       <c r="N49" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O49" s="49" t="s">
+      <c r="O49" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="P49" s="50"/>
-      <c r="Q49" s="49" t="s">
+      <c r="P49" s="52"/>
+      <c r="Q49" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="R49" s="50"/>
-      <c r="S49" s="49" t="s">
+      <c r="R49" s="52"/>
+      <c r="S49" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="T49" s="50"/>
+      <c r="T49" s="52"/>
       <c r="U49" s="19" t="s">
         <v>68</v>
       </c>
@@ -7347,26 +7350,26 @@
       <c r="N50" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O50" s="49" t="s">
+      <c r="O50" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="P50" s="50"/>
-      <c r="Q50" s="49" t="s">
+      <c r="P50" s="52"/>
+      <c r="Q50" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="R50" s="50"/>
+      <c r="R50" s="52"/>
       <c r="S50" s="17" t="s">
         <v>9</v>
       </c>
       <c r="T50" s="18"/>
-      <c r="U50" s="49" t="s">
+      <c r="U50" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="V50" s="50"/>
-      <c r="W50" s="49" t="s">
+      <c r="V50" s="52"/>
+      <c r="W50" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="X50" s="50"/>
+      <c r="X50" s="52"/>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" s="1" t="s">
@@ -7376,18 +7379,18 @@
         <v>93</v>
       </c>
       <c r="C51" s="32"/>
-      <c r="D51" s="49" t="s">
+      <c r="D51" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E51" s="50"/>
-      <c r="F51" s="49" t="s">
+      <c r="E51" s="52"/>
+      <c r="F51" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G51" s="50"/>
-      <c r="H51" s="49" t="s">
+      <c r="G51" s="52"/>
+      <c r="H51" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="I51" s="50"/>
+      <c r="I51" s="52"/>
       <c r="J51" s="17" t="s">
         <v>9</v>
       </c>
@@ -7443,10 +7446,10 @@
       <c r="N52" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O52" s="49" t="s">
+      <c r="O52" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="P52" s="50"/>
+      <c r="P52" s="52"/>
       <c r="Q52" s="33" t="s">
         <v>114</v>
       </c>
@@ -7516,22 +7519,22 @@
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="58" t="s">
+      <c r="B54" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="59"/>
-      <c r="D54" s="58" t="s">
+      <c r="C54" s="61"/>
+      <c r="D54" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="E54" s="59"/>
-      <c r="F54" s="49" t="s">
+      <c r="E54" s="61"/>
+      <c r="F54" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G54" s="50"/>
-      <c r="H54" s="49" t="s">
+      <c r="G54" s="52"/>
+      <c r="H54" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I54" s="50"/>
+      <c r="I54" s="52"/>
       <c r="J54" s="78" t="s">
         <v>108</v>
       </c>
@@ -7567,18 +7570,18 @@
       </c>
       <c r="B55" s="17"/>
       <c r="C55" s="18"/>
-      <c r="D55" s="49" t="s">
+      <c r="D55" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E55" s="50"/>
-      <c r="F55" s="49" t="s">
+      <c r="E55" s="52"/>
+      <c r="F55" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G55" s="50"/>
-      <c r="H55" s="49" t="s">
+      <c r="G55" s="52"/>
+      <c r="H55" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I55" s="50"/>
+      <c r="I55" s="52"/>
       <c r="J55" s="70"/>
       <c r="K55" s="71"/>
       <c r="L55" s="9"/>
@@ -7587,35 +7590,35 @@
       </c>
       <c r="O55" s="70"/>
       <c r="P55" s="71"/>
-      <c r="Q55" s="49" t="s">
+      <c r="Q55" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="R55" s="50"/>
-      <c r="S55" s="49" t="s">
+      <c r="R55" s="52"/>
+      <c r="S55" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="T55" s="50"/>
-      <c r="U55" s="49" t="s">
+      <c r="T55" s="52"/>
+      <c r="U55" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="V55" s="50"/>
-      <c r="W55" s="49" t="s">
+      <c r="V55" s="52"/>
+      <c r="W55" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="X55" s="50"/>
+      <c r="X55" s="52"/>
     </row>
     <row r="56" spans="1:24">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="58" t="s">
+      <c r="B56" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="59"/>
-      <c r="D56" s="58" t="s">
+      <c r="C56" s="61"/>
+      <c r="D56" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="E56" s="59"/>
+      <c r="E56" s="61"/>
       <c r="F56" s="78" t="s">
         <v>108</v>
       </c>
@@ -8343,45 +8346,45 @@
         <v>118</v>
       </c>
       <c r="C2" s="28"/>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="48"/>
+      <c r="E2" s="50"/>
       <c r="F2" s="27" t="s">
         <v>72</v>
       </c>
       <c r="G2" s="28"/>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="47" t="s">
+      <c r="I2" s="50"/>
+      <c r="J2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="48"/>
+      <c r="K2" s="50"/>
       <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="O2" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="47" t="s">
+      <c r="P2" s="50"/>
+      <c r="Q2" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="R2" s="48"/>
-      <c r="S2" s="47" t="s">
+      <c r="R2" s="50"/>
+      <c r="S2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="48"/>
-      <c r="U2" s="47" t="s">
+      <c r="T2" s="50"/>
+      <c r="U2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="V2" s="48"/>
-      <c r="W2" s="47" t="s">
+      <c r="V2" s="50"/>
+      <c r="W2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="48"/>
+      <c r="X2" s="50"/>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
@@ -8458,18 +8461,18 @@
       <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="54" t="s">
+      <c r="O4" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="54" t="s">
+      <c r="P4" s="57"/>
+      <c r="Q4" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="R4" s="55"/>
-      <c r="S4" s="54" t="s">
+      <c r="R4" s="57"/>
+      <c r="S4" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="T4" s="55"/>
+      <c r="T4" s="57"/>
       <c r="U4" s="33" t="s">
         <v>124</v>
       </c>
@@ -8746,18 +8749,18 @@
       <c r="N10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O10" s="54" t="s">
+      <c r="O10" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="54" t="s">
+      <c r="P10" s="57"/>
+      <c r="Q10" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="55"/>
-      <c r="S10" s="54" t="s">
+      <c r="R10" s="57"/>
+      <c r="S10" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="T10" s="55"/>
+      <c r="T10" s="57"/>
       <c r="U10" s="31" t="s">
         <v>127</v>
       </c>
@@ -8771,26 +8774,26 @@
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="49" t="s">
+      <c r="C11" s="52"/>
+      <c r="D11" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="49" t="s">
+      <c r="E11" s="52"/>
+      <c r="F11" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="50"/>
-      <c r="H11" s="49" t="s">
+      <c r="G11" s="52"/>
+      <c r="H11" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="50"/>
-      <c r="J11" s="49" t="s">
+      <c r="I11" s="52"/>
+      <c r="J11" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="K11" s="50"/>
+      <c r="K11" s="52"/>
       <c r="N11" s="1" t="s">
         <v>37</v>
       </c>
@@ -8867,26 +8870,26 @@
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="49" t="s">
+      <c r="C13" s="52"/>
+      <c r="D13" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="49" t="s">
+      <c r="E13" s="52"/>
+      <c r="F13" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="50"/>
-      <c r="H13" s="49" t="s">
+      <c r="G13" s="52"/>
+      <c r="H13" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="I13" s="50"/>
-      <c r="J13" s="49" t="s">
+      <c r="I13" s="52"/>
+      <c r="J13" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="K13" s="50"/>
+      <c r="K13" s="52"/>
       <c r="N13" s="12" t="s">
         <v>45</v>
       </c>
@@ -8923,14 +8926,14 @@
         <v>103</v>
       </c>
       <c r="E14" s="34"/>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="50"/>
-      <c r="H14" s="49" t="s">
+      <c r="G14" s="52"/>
+      <c r="H14" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="50"/>
+      <c r="I14" s="52"/>
       <c r="J14" s="19" t="s">
         <v>68</v>
       </c>
@@ -9011,22 +9014,22 @@
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="49" t="s">
+      <c r="C16" s="52"/>
+      <c r="D16" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="50"/>
+      <c r="E16" s="52"/>
       <c r="F16" s="84"/>
       <c r="G16" s="85"/>
       <c r="H16" s="84"/>
       <c r="I16" s="85"/>
-      <c r="J16" s="49" t="s">
+      <c r="J16" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="K16" s="50"/>
+      <c r="K16" s="52"/>
       <c r="N16" s="1" t="s">
         <v>50</v>
       </c>
@@ -9189,14 +9192,14 @@
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="48"/>
-      <c r="D26" s="47" t="s">
+      <c r="C26" s="50"/>
+      <c r="D26" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="48"/>
+      <c r="E26" s="50"/>
       <c r="F26" s="21" t="s">
         <v>8</v>
       </c>
@@ -9210,18 +9213,18 @@
       <c r="N26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O26" s="47" t="s">
+      <c r="O26" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="47" t="s">
+      <c r="P26" s="50"/>
+      <c r="Q26" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="R26" s="48"/>
-      <c r="S26" s="47" t="s">
+      <c r="R26" s="50"/>
+      <c r="S26" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="T26" s="48"/>
+      <c r="T26" s="50"/>
       <c r="U26" s="27" t="s">
         <v>91</v>
       </c>
@@ -9666,10 +9669,10 @@
       <c r="N36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O36" s="45" t="s">
+      <c r="O36" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="P36" s="46"/>
+      <c r="P36" s="48"/>
       <c r="Q36" s="29" t="s">
         <v>128</v>
       </c>
@@ -9971,45 +9974,45 @@
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="54"/>
       <c r="D44" s="33" t="s">
         <v>56</v>
       </c>
       <c r="E44" s="34"/>
-      <c r="F44" s="47" t="s">
+      <c r="F44" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G44" s="48"/>
-      <c r="H44" s="47" t="s">
+      <c r="G44" s="50"/>
+      <c r="H44" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I44" s="48"/>
-      <c r="J44" s="47" t="s">
+      <c r="I44" s="50"/>
+      <c r="J44" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K44" s="48"/>
+      <c r="K44" s="50"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O44" s="47" t="s">
+      <c r="O44" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="P44" s="48"/>
-      <c r="Q44" s="47" t="s">
+      <c r="P44" s="50"/>
+      <c r="Q44" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="R44" s="48"/>
-      <c r="S44" s="47" t="s">
+      <c r="R44" s="50"/>
+      <c r="S44" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="T44" s="48"/>
-      <c r="U44" s="47" t="s">
+      <c r="T44" s="50"/>
+      <c r="U44" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="V44" s="48"/>
+      <c r="V44" s="50"/>
       <c r="W44" s="43"/>
       <c r="X44" s="44"/>
     </row>
@@ -10017,8 +10020,8 @@
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="51"/>
-      <c r="C45" s="52"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="54"/>
       <c r="D45" s="33" t="s">
         <v>56</v>
       </c>
@@ -10063,8 +10066,8 @@
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
+      <c r="B46" s="53"/>
+      <c r="C46" s="54"/>
       <c r="D46" s="33" t="s">
         <v>56</v>
       </c>
@@ -10109,8 +10112,8 @@
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B47" s="51"/>
-      <c r="C47" s="52"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="54"/>
       <c r="D47" s="33" t="s">
         <v>56</v>
       </c>
@@ -10153,8 +10156,8 @@
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B48" s="51"/>
-      <c r="C48" s="52"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="54"/>
       <c r="D48" s="33" t="s">
         <v>56</v>
       </c>
@@ -10241,8 +10244,8 @@
       <c r="A50" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B50" s="51"/>
-      <c r="C50" s="52"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="54"/>
       <c r="D50" s="33" t="s">
         <v>56</v>
       </c>
@@ -10285,8 +10288,8 @@
       <c r="A51" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B51" s="51"/>
-      <c r="C51" s="52"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="54"/>
       <c r="D51" s="33" t="s">
         <v>56</v>
       </c>
@@ -10331,8 +10334,8 @@
       <c r="A52" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="51"/>
-      <c r="C52" s="52"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="54"/>
       <c r="D52" s="33" t="s">
         <v>56</v>
       </c>
@@ -10383,14 +10386,14 @@
         <v>56</v>
       </c>
       <c r="E53" s="34"/>
-      <c r="F53" s="45" t="s">
+      <c r="F53" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="G53" s="46"/>
-      <c r="H53" s="45" t="s">
+      <c r="G53" s="48"/>
+      <c r="H53" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="I53" s="46"/>
+      <c r="I53" s="48"/>
       <c r="J53" s="29" t="s">
         <v>60</v>
       </c>
@@ -10429,14 +10432,14 @@
         <v>56</v>
       </c>
       <c r="E54" s="34"/>
-      <c r="F54" s="45" t="s">
+      <c r="F54" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="G54" s="46"/>
-      <c r="H54" s="45" t="s">
+      <c r="G54" s="48"/>
+      <c r="H54" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="I54" s="46"/>
+      <c r="I54" s="48"/>
       <c r="J54" s="29" t="s">
         <v>67</v>
       </c>
@@ -10458,10 +10461,10 @@
         <v>173</v>
       </c>
       <c r="T54" s="24"/>
-      <c r="U54" s="45" t="s">
+      <c r="U54" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="V54" s="46"/>
+      <c r="V54" s="48"/>
       <c r="W54" s="43"/>
       <c r="X54" s="44"/>
     </row>
@@ -10469,8 +10472,8 @@
       <c r="A55" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="51"/>
-      <c r="C55" s="52"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="54"/>
       <c r="D55" s="33" t="s">
         <v>56</v>
       </c>
@@ -11312,47 +11315,47 @@
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="47" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="47" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="47" t="s">
+      <c r="G2" s="50"/>
+      <c r="H2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="47" t="s">
+      <c r="I2" s="50"/>
+      <c r="J2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="48"/>
+      <c r="K2" s="50"/>
       <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="47" t="s">
+      <c r="O2" s="53"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="48"/>
-      <c r="S2" s="47" t="s">
+      <c r="R2" s="50"/>
+      <c r="S2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="48"/>
-      <c r="U2" s="47" t="s">
+      <c r="T2" s="50"/>
+      <c r="U2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="V2" s="48"/>
-      <c r="W2" s="47" t="s">
+      <c r="V2" s="50"/>
+      <c r="W2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="48"/>
+      <c r="X2" s="50"/>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
@@ -11381,8 +11384,8 @@
       <c r="N3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="51"/>
-      <c r="P3" s="52"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="54"/>
       <c r="Q3" s="31" t="s">
         <v>182</v>
       </c>
@@ -11427,8 +11430,8 @@
       <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="51"/>
-      <c r="P4" s="52"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="54"/>
       <c r="Q4" s="31" t="s">
         <v>185</v>
       </c>
@@ -11474,8 +11477,8 @@
       <c r="N5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="51"/>
-      <c r="P5" s="52"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="54"/>
       <c r="Q5" s="19" t="s">
         <v>187</v>
       </c>
@@ -11520,8 +11523,8 @@
       <c r="N6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O6" s="51"/>
-      <c r="P6" s="52"/>
+      <c r="O6" s="53"/>
+      <c r="P6" s="54"/>
       <c r="Q6" s="27" t="s">
         <v>91</v>
       </c>
@@ -11612,8 +11615,8 @@
       <c r="N8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="51"/>
-      <c r="P8" s="52"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="54"/>
       <c r="Q8" s="23" t="s">
         <v>170</v>
       </c>
@@ -11658,8 +11661,8 @@
       <c r="N9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O9" s="51"/>
-      <c r="P9" s="52"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="54"/>
       <c r="Q9" s="37" t="s">
         <v>189</v>
       </c>
@@ -11704,8 +11707,8 @@
       <c r="N10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O10" s="51"/>
-      <c r="P10" s="52"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="54"/>
       <c r="Q10" s="19" t="s">
         <v>188</v>
       </c>
@@ -11735,14 +11738,14 @@
         <v>136</v>
       </c>
       <c r="E11" s="32"/>
-      <c r="F11" s="45" t="s">
+      <c r="F11" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="G11" s="46"/>
-      <c r="H11" s="45" t="s">
+      <c r="G11" s="48"/>
+      <c r="H11" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="I11" s="46"/>
+      <c r="I11" s="48"/>
       <c r="J11" s="29" t="s">
         <v>60</v>
       </c>
@@ -11785,10 +11788,10 @@
         <v>170</v>
       </c>
       <c r="G12" s="24"/>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="I12" s="46"/>
+      <c r="I12" s="48"/>
       <c r="J12" s="29" t="s">
         <v>67</v>
       </c>
@@ -11842,8 +11845,8 @@
       <c r="N13" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O13" s="51"/>
-      <c r="P13" s="52"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="54"/>
       <c r="Q13" s="37" t="s">
         <v>194</v>
       </c>
@@ -12124,47 +12127,47 @@
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="47" t="s">
+      <c r="C22" s="50"/>
+      <c r="D22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="48"/>
-      <c r="F22" s="47" t="s">
+      <c r="E22" s="50"/>
+      <c r="F22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="48"/>
+      <c r="G22" s="50"/>
       <c r="H22" s="35"/>
       <c r="I22" s="36"/>
-      <c r="J22" s="47" t="s">
+      <c r="J22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K22" s="48"/>
+      <c r="K22" s="50"/>
       <c r="N22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O22" s="47" t="s">
+      <c r="O22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="47" t="s">
+      <c r="P22" s="50"/>
+      <c r="Q22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="R22" s="48"/>
-      <c r="S22" s="47" t="s">
+      <c r="R22" s="50"/>
+      <c r="S22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="T22" s="48"/>
-      <c r="U22" s="47" t="s">
+      <c r="T22" s="50"/>
+      <c r="U22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="V22" s="48"/>
-      <c r="W22" s="47" t="s">
+      <c r="V22" s="50"/>
+      <c r="W22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="X22" s="48"/>
+      <c r="X22" s="50"/>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="1" t="s">
@@ -12276,10 +12279,10 @@
       <c r="G25" s="20"/>
       <c r="H25" s="43"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="49" t="s">
+      <c r="J25" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="K25" s="50"/>
+      <c r="K25" s="52"/>
       <c r="N25" s="1" t="s">
         <v>21</v>
       </c>
@@ -12346,7 +12349,7 @@
       </c>
       <c r="V26" s="28"/>
       <c r="W26" s="27" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="X26" s="28"/>
     </row>
@@ -12354,14 +12357,14 @@
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="45" t="s">
+      <c r="C27" s="48"/>
+      <c r="D27" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="46"/>
+      <c r="E27" s="48"/>
       <c r="F27" s="33" t="s">
         <v>142</v>
       </c>
@@ -12401,7 +12404,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="19" t="s">
@@ -12447,44 +12450,44 @@
         <v>32</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="E29" s="46"/>
-      <c r="F29" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="G29" s="46"/>
+      <c r="D29" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="48"/>
+      <c r="F29" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="G29" s="48"/>
       <c r="H29" s="35"/>
       <c r="I29" s="36"/>
-      <c r="J29" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="K29" s="46"/>
+      <c r="J29" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="K29" s="48"/>
       <c r="N29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="O29" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P29" s="28"/>
       <c r="Q29" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R29" s="28"/>
       <c r="S29" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T29" s="28"/>
       <c r="U29" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V29" s="28"/>
       <c r="W29" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="X29" s="28"/>
     </row>
@@ -12497,7 +12500,7 @@
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E30" s="20"/>
       <c r="F30" s="19" t="s">
@@ -12514,23 +12517,23 @@
         <v>35</v>
       </c>
       <c r="O30" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P30" s="28"/>
       <c r="Q30" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R30" s="28"/>
       <c r="S30" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T30" s="28"/>
       <c r="U30" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="V30" s="28"/>
       <c r="W30" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="X30" s="28"/>
     </row>
@@ -12559,22 +12562,22 @@
       <c r="N31" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O31" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="P31" s="46"/>
-      <c r="Q31" s="45" t="s">
+      <c r="O31" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="R31" s="46"/>
-      <c r="S31" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="T31" s="46"/>
-      <c r="U31" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="V31" s="46"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="R31" s="48"/>
+      <c r="S31" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="T31" s="48"/>
+      <c r="U31" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="V31" s="48"/>
       <c r="W31" s="19" t="s">
         <v>188</v>
       </c>
@@ -12584,14 +12587,14 @@
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="C32" s="46"/>
-      <c r="D32" s="45" t="s">
+      <c r="C32" s="48"/>
+      <c r="D32" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="E32" s="46"/>
+      <c r="E32" s="48"/>
       <c r="F32" s="33" t="s">
         <v>124</v>
       </c>
@@ -12608,7 +12611,7 @@
         <v>40</v>
       </c>
       <c r="O32" s="33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P32" s="34"/>
       <c r="Q32" s="33" t="s">
@@ -12646,10 +12649,10 @@
       <c r="G33" s="20"/>
       <c r="H33" s="43"/>
       <c r="I33" s="44"/>
-      <c r="J33" s="49" t="s">
+      <c r="J33" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="K33" s="50"/>
+      <c r="K33" s="52"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="12" t="s">
@@ -12694,10 +12697,10 @@
       <c r="G34" s="20"/>
       <c r="H34" s="43"/>
       <c r="I34" s="44"/>
-      <c r="J34" s="49" t="s">
+      <c r="J34" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="K34" s="50"/>
+      <c r="K34" s="52"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
       <c r="N34" s="1" t="s">
@@ -12733,7 +12736,7 @@
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E35" s="20"/>
       <c r="F35" s="19" t="s">
@@ -12781,7 +12784,7 @@
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E36" s="20"/>
       <c r="F36" s="19" t="s">
@@ -12840,7 +12843,7 @@
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>1</v>
@@ -12875,7 +12878,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>1</v>
@@ -12912,51 +12915,51 @@
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="47" t="s">
+      <c r="B41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="48"/>
-      <c r="D41" s="47" t="s">
+      <c r="C41" s="50"/>
+      <c r="D41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="48"/>
-      <c r="F41" s="47" t="s">
+      <c r="E41" s="50"/>
+      <c r="F41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="48"/>
-      <c r="H41" s="47" t="s">
+      <c r="G41" s="50"/>
+      <c r="H41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I41" s="48"/>
-      <c r="J41" s="60" t="s">
+      <c r="I41" s="50"/>
+      <c r="J41" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K41" s="61"/>
+      <c r="K41" s="46"/>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O41" s="47" t="s">
+      <c r="O41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="47" t="s">
+      <c r="P41" s="50"/>
+      <c r="Q41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="R41" s="48"/>
-      <c r="S41" s="47" t="s">
+      <c r="R41" s="50"/>
+      <c r="S41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="T41" s="48"/>
-      <c r="U41" s="47" t="s">
+      <c r="T41" s="50"/>
+      <c r="U41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="V41" s="48"/>
-      <c r="W41" s="47" t="s">
+      <c r="V41" s="50"/>
+      <c r="W41" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="X41" s="48"/>
+      <c r="X41" s="50"/>
     </row>
     <row r="42" spans="1:24">
       <c r="A42" s="1" t="s">
@@ -12978,10 +12981,10 @@
         <v>200</v>
       </c>
       <c r="I42" s="28"/>
-      <c r="J42" s="60" t="s">
+      <c r="J42" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K42" s="61"/>
+      <c r="K42" s="46"/>
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="1" t="s">
@@ -13071,7 +13074,7 @@
       </c>
       <c r="E44" s="20"/>
       <c r="F44" s="39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G44" s="40"/>
       <c r="H44" s="19" t="s">
@@ -13119,17 +13122,17 @@
       </c>
       <c r="E45" s="20"/>
       <c r="F45" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="27" t="s">
         <v>91</v>
       </c>
       <c r="I45" s="28"/>
-      <c r="J45" s="60" t="s">
+      <c r="J45" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K45" s="61"/>
+      <c r="K45" s="46"/>
       <c r="N45" s="1" t="s">
         <v>24</v>
       </c>
@@ -13163,7 +13166,7 @@
       </c>
       <c r="C46" s="38"/>
       <c r="D46" s="37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="37" t="s">
@@ -13211,11 +13214,11 @@
       </c>
       <c r="C47" s="24"/>
       <c r="D47" s="39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E47" s="40"/>
       <c r="F47" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G47" s="40"/>
       <c r="H47" s="17" t="s">
@@ -13230,23 +13233,23 @@
         <v>28</v>
       </c>
       <c r="O47" s="33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P47" s="34"/>
       <c r="Q47" s="33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R47" s="34"/>
       <c r="S47" s="33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T47" s="34"/>
       <c r="U47" s="33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="V47" s="34"/>
       <c r="W47" s="33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="X47" s="34"/>
     </row>
@@ -13259,7 +13262,7 @@
       </c>
       <c r="C48" s="38"/>
       <c r="D48" s="37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="37" t="s">
@@ -13303,7 +13306,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C49" s="34"/>
       <c r="D49" s="29" t="s">
@@ -13374,15 +13377,15 @@
         <v>37</v>
       </c>
       <c r="O50" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P50" s="28"/>
       <c r="Q50" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R50" s="28"/>
       <c r="S50" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T50" s="28"/>
       <c r="U50" s="25" t="s">
@@ -13399,7 +13402,7 @@
         <v>40</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C51" s="34"/>
       <c r="D51" s="29" t="s">
@@ -13507,7 +13510,7 @@
       </c>
       <c r="E53" s="20"/>
       <c r="F53" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G53" s="20"/>
       <c r="H53" s="19" t="s">
@@ -13603,7 +13606,7 @@
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G55" s="20"/>
       <c r="H55" s="19" t="s">
@@ -13639,7 +13642,7 @@
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E56" s="40"/>
       <c r="F56" s="5"/>
@@ -13649,18 +13652,18 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O56" s="17"/>
       <c r="P56" s="18"/>
-      <c r="Q56" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="R56" s="53"/>
-      <c r="S56" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="T56" s="53"/>
+      <c r="Q56" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="R56" s="55"/>
+      <c r="S56" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="T56" s="55"/>
       <c r="U56" s="17"/>
       <c r="V56" s="18"/>
       <c r="W56" s="17"/>
@@ -13678,10 +13681,10 @@
       <c r="K57" s="5"/>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
-      <c r="O57" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="P57" s="53"/>
+      <c r="O57" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="P57" s="55"/>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
@@ -13766,6 +13769,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="463">
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="O57:P57"/>
@@ -14280,7 +14284,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -14313,7 +14317,7 @@
         <v>46192</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -14350,26 +14354,26 @@
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="47" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="47" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="47" t="s">
+      <c r="G2" s="50"/>
+      <c r="H2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="47" t="s">
+      <c r="I2" s="50"/>
+      <c r="J2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="48"/>
+      <c r="K2" s="50"/>
       <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
@@ -14398,22 +14402,22 @@
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="49" t="s">
+      <c r="C3" s="52"/>
+      <c r="D3" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="49" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="49" t="s">
+      <c r="G3" s="52"/>
+      <c r="H3" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="50"/>
+      <c r="I3" s="52"/>
       <c r="J3" s="17"/>
       <c r="K3" s="18"/>
       <c r="N3" s="1" t="s">
@@ -14444,22 +14448,22 @@
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="50"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E4" s="28"/>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="50"/>
-      <c r="H4" s="49" t="s">
+      <c r="G4" s="52"/>
+      <c r="H4" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="50"/>
+      <c r="I4" s="52"/>
       <c r="J4" s="17"/>
       <c r="K4" s="18"/>
       <c r="N4" s="1" t="s">
@@ -14480,14 +14484,14 @@
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="49" t="s">
+      <c r="C5" s="52"/>
+      <c r="D5" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="50"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="17"/>
       <c r="G5" s="18"/>
       <c r="H5" s="17"/>
@@ -14525,7 +14529,7 @@
       <c r="B6" s="17"/>
       <c r="C6" s="18"/>
       <c r="D6" s="27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E6" s="28"/>
       <c r="F6" s="17"/>
@@ -14563,23 +14567,23 @@
         <v>26</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E7" s="28"/>
       <c r="F7" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G7" s="28"/>
       <c r="H7" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I7" s="28"/>
       <c r="J7" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K7" s="28"/>
       <c r="N7" s="6" t="s">
@@ -14601,23 +14605,23 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C8" s="28"/>
       <c r="D8" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E8" s="28"/>
       <c r="F8" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G8" s="28"/>
       <c r="H8" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I8" s="28"/>
       <c r="J8" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K8" s="28"/>
       <c r="N8" s="6" t="s">
@@ -14639,23 +14643,23 @@
         <v>32</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G9" s="28"/>
       <c r="H9" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I9" s="28"/>
       <c r="J9" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K9" s="28"/>
       <c r="N9" s="6" t="s">
@@ -14678,10 +14682,10 @@
       </c>
       <c r="B10" s="70"/>
       <c r="C10" s="71"/>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="50"/>
+      <c r="E10" s="52"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
       <c r="H10" s="17"/>
@@ -14717,23 +14721,23 @@
         <v>37</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G11" s="28"/>
       <c r="H11" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I11" s="28"/>
       <c r="J11" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K11" s="28"/>
       <c r="N11" s="1" t="s">
@@ -14914,7 +14918,7 @@
     <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
     <row r="19" spans="1:24" ht="11.25" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -14947,7 +14951,7 @@
         <v>46199</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -14985,21 +14989,21 @@
         <v>7</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C20" s="83"/>
       <c r="D20" s="27" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E20" s="83"/>
       <c r="F20" s="27" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G20" s="83"/>
-      <c r="H20" s="47" t="s">
+      <c r="H20" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="48"/>
+      <c r="I20" s="50"/>
       <c r="J20" s="27" t="s">
         <v>88</v>
       </c>
@@ -15075,17 +15079,17 @@
       <c r="B22" s="70"/>
       <c r="C22" s="71"/>
       <c r="D22" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E22" s="83"/>
       <c r="F22" s="70"/>
       <c r="G22" s="71"/>
       <c r="H22" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I22" s="83"/>
       <c r="J22" s="27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K22" s="28"/>
       <c r="N22" s="1" t="s">
@@ -15153,19 +15157,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="27" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="E24" s="28"/>
       <c r="F24" s="27" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="G24" s="28"/>
       <c r="H24" s="27" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="I24" s="28"/>
       <c r="J24" s="27" t="s">
@@ -15269,17 +15273,17 @@
       <c r="B27" s="70"/>
       <c r="C27" s="71"/>
       <c r="D27" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E27" s="83"/>
       <c r="F27" s="84"/>
       <c r="G27" s="85"/>
       <c r="H27" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I27" s="83"/>
       <c r="J27" s="27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K27" s="28"/>
       <c r="N27" s="6" t="s">
@@ -15587,7 +15591,7 @@
     </row>
     <row r="37" spans="1:24" ht="11.25" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -15622,7 +15626,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -15659,26 +15663,26 @@
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="47" t="s">
+      <c r="B38" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="48"/>
+      <c r="C38" s="50"/>
       <c r="D38" s="82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E38" s="83"/>
-      <c r="F38" s="47" t="s">
+      <c r="F38" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="48"/>
-      <c r="H38" s="47" t="s">
+      <c r="G38" s="50"/>
+      <c r="H38" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I38" s="48"/>
-      <c r="J38" s="47" t="s">
+      <c r="I38" s="50"/>
+      <c r="J38" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K38" s="48"/>
+      <c r="K38" s="50"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="1" t="s">
@@ -15712,7 +15716,7 @@
       <c r="B39" s="70"/>
       <c r="C39" s="71"/>
       <c r="D39" s="82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E39" s="83"/>
       <c r="F39" s="17"/>
@@ -15844,7 +15848,7 @@
       </c>
       <c r="C42" s="83"/>
       <c r="D42" s="82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E42" s="83"/>
       <c r="F42" s="82" t="s">
@@ -15890,7 +15894,7 @@
       <c r="B43" s="17"/>
       <c r="C43" s="18"/>
       <c r="D43" s="82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E43" s="83"/>
       <c r="F43" s="84"/>
@@ -15943,15 +15947,15 @@
       <c r="O44" s="70"/>
       <c r="P44" s="71"/>
       <c r="Q44" s="27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="R44" s="28"/>
       <c r="S44" s="27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="T44" s="28"/>
       <c r="U44" s="27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="V44" s="28"/>
       <c r="W44" s="17"/>
@@ -15977,15 +15981,15 @@
       <c r="O45" s="70"/>
       <c r="P45" s="71"/>
       <c r="Q45" s="27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="R45" s="28"/>
       <c r="S45" s="27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="T45" s="28"/>
       <c r="U45" s="27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="V45" s="28"/>
       <c r="W45" s="17"/>
@@ -16062,23 +16066,23 @@
         <v>40</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C48" s="28"/>
       <c r="D48" s="27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E48" s="28"/>
       <c r="F48" s="27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G48" s="28"/>
       <c r="H48" s="27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I48" s="28"/>
       <c r="J48" s="27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K48" s="28"/>
       <c r="N48" s="1" t="s">
@@ -16804,7 +16808,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -16837,7 +16841,7 @@
         <v>46234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -16974,7 +16978,7 @@
       <c r="U4" s="17"/>
       <c r="V4" s="18"/>
       <c r="W4" s="27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="X4" s="28"/>
     </row>
@@ -17476,7 +17480,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -17509,7 +17513,7 @@
         <v>46241</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -17557,7 +17561,7 @@
       </c>
       <c r="I20" s="28"/>
       <c r="J20" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K20" s="83"/>
       <c r="N20" s="1" t="s">
@@ -17797,7 +17801,7 @@
       </c>
       <c r="I27" s="28"/>
       <c r="J27" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K27" s="83"/>
       <c r="N27" s="6" t="s">
@@ -17905,7 +17909,7 @@
       </c>
       <c r="I30" s="28"/>
       <c r="J30" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K30" s="83"/>
       <c r="N30" s="1" t="s">
@@ -18068,7 +18072,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -18103,7 +18107,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -18145,7 +18149,7 @@
       <c r="D38" s="70"/>
       <c r="E38" s="71"/>
       <c r="F38" s="82" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G38" s="83"/>
       <c r="H38" s="84"/>
@@ -18170,7 +18174,7 @@
       <c r="U38" s="84"/>
       <c r="V38" s="85"/>
       <c r="W38" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="X38" s="18"/>
     </row>
@@ -18183,7 +18187,7 @@
       <c r="D39" s="70"/>
       <c r="E39" s="71"/>
       <c r="F39" s="82" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G39" s="83"/>
       <c r="H39" s="84"/>
@@ -18221,7 +18225,7 @@
       <c r="F40" s="70"/>
       <c r="G40" s="71"/>
       <c r="H40" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I40" s="83"/>
       <c r="J40" s="17"/>
@@ -18285,7 +18289,7 @@
       </c>
       <c r="E42" s="28"/>
       <c r="F42" s="82" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G42" s="83"/>
       <c r="H42" s="27" t="s">
@@ -18413,7 +18417,7 @@
       <c r="F45" s="84"/>
       <c r="G45" s="85"/>
       <c r="H45" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I45" s="83"/>
       <c r="J45" s="17"/>
@@ -18505,7 +18509,7 @@
       <c r="F48" s="17"/>
       <c r="G48" s="18"/>
       <c r="H48" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I48" s="83"/>
       <c r="J48" s="17"/>
@@ -19243,7 +19247,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -19276,7 +19280,7 @@
         <v>46276</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -19314,23 +19318,23 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G2" s="18"/>
       <c r="H2" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I2" s="18"/>
       <c r="J2" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K2" s="18"/>
       <c r="N2" s="1" t="s">
@@ -19787,7 +19791,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -19820,7 +19824,7 @@
         <v>46283</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -20380,7 +20384,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -20415,7 +20419,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -21502,7 +21506,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -21535,7 +21539,7 @@
         <v>46318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -22061,7 +22065,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -22094,7 +22098,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -22623,7 +22627,7 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -22658,7 +22662,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -23710,7 +23714,7 @@
     <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
     <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -23743,7 +23747,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -24255,7 +24259,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -24288,7 +24292,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -24827,7 +24831,7 @@
     </row>
     <row r="38" spans="2:25">
       <c r="B38" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>
@@ -25796,6 +25800,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="294cf202-ea3b-4503-9866-4c6f0069ff97">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001EA62548CDE95149AC1BC8AF3B662818" ma:contentTypeVersion="18" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="6b6114bc50e08fd23ab8a89130bf9f95">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="294cf202-ea3b-4503-9866-4c6f0069ff97" xmlns:ns3="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd29bd8d73cdc406ea9db8e88d30c8e6" ns2:_="" ns3:_="">
     <xsd:import namespace="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
@@ -26044,7 +26059,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -26053,25 +26068,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="294cf202-ea3b-4503-9866-4c6f0069ff97">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}"/>
 </file>
--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4015" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDDEF558-4861-4D5A-831A-677336F9ACA4}"/>
+  <xr:revisionPtr revIDLastSave="4016" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FC7D726-8162-41F5-A907-07DD0C51A63C}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -13779,6 +13779,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="462">
     <mergeCell ref="W24:X24"/>
     <mergeCell ref="O56:P56"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4225" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84C0F501-82AB-4FD8-9BCE-413E81F06EFD}"/>
+  <xr:revisionPtr revIDLastSave="4289" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2210E350-4F4C-4C7C-AF28-43D6EC3E1E00}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3724" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3955" uniqueCount="268">
   <si>
     <t>Uke 01</t>
   </si>
@@ -876,6 +876,9 @@
   </si>
   <si>
     <t>SE EV 5</t>
+  </si>
+  <si>
+    <t>9 SF HF 5</t>
   </si>
 </sst>
 </file>
@@ -14429,23 +14432,25 @@
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="29"/>
+      <c r="B3" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="30"/>
+      <c r="F3" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="30"/>
+      <c r="J3" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K3" s="30"/>
       <c r="N3" s="1" t="s">
         <v>10</v>
@@ -14475,36 +14480,48 @@
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="20"/>
+      <c r="B4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="30"/>
       <c r="D4" s="43" t="s">
         <v>226</v>
       </c>
       <c r="E4" s="44"/>
-      <c r="F4" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="29"/>
+      <c r="F4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="30"/>
+      <c r="H4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="30"/>
+      <c r="J4" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K4" s="30"/>
       <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="67"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="68"/>
-      <c r="U4" s="29"/>
+      <c r="O4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" s="30"/>
+      <c r="S4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="30"/>
+      <c r="U4" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V4" s="30"/>
-      <c r="W4" s="29"/>
+      <c r="W4" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X4" s="30"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
@@ -14512,18 +14529,24 @@
         <v>21</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E5" s="20"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="29"/>
+      <c r="F5" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K5" s="30"/>
       <c r="N5" s="1" t="s">
         <v>21</v>
@@ -14553,18 +14576,26 @@
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30"/>
+      <c r="B6" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="60"/>
       <c r="D6" s="43" t="s">
         <v>226</v>
       </c>
       <c r="E6" s="44"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
+      <c r="F6" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="60"/>
+      <c r="H6" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="60"/>
+      <c r="J6" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="60"/>
       <c r="N6" s="1" t="s">
         <v>24</v>
       </c>
@@ -14616,15 +14647,25 @@
       <c r="N7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O7" s="29"/>
+      <c r="O7" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="P7" s="30"/>
-      <c r="Q7" s="29"/>
+      <c r="Q7" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="R7" s="30"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="84"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="84"/>
-      <c r="W7" s="29"/>
+      <c r="S7" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="30"/>
+      <c r="U7" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="V7" s="30"/>
+      <c r="W7" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X7" s="30"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
@@ -14654,15 +14695,25 @@
       <c r="N8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="67"/>
-      <c r="P8" s="68"/>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="68"/>
-      <c r="S8" s="67"/>
-      <c r="T8" s="68"/>
-      <c r="U8" s="29"/>
+      <c r="O8" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" s="30"/>
+      <c r="S8" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="30"/>
+      <c r="U8" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V8" s="30"/>
-      <c r="W8" s="29"/>
+      <c r="W8" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X8" s="30"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
@@ -14692,32 +14743,50 @@
       <c r="N9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O9" s="67"/>
-      <c r="P9" s="68"/>
-      <c r="Q9" s="67"/>
-      <c r="R9" s="68"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="84"/>
-      <c r="U9" s="83"/>
-      <c r="V9" s="84"/>
-      <c r="W9" s="29"/>
+      <c r="O9" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R9" s="30"/>
+      <c r="S9" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="30"/>
+      <c r="U9" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="V9" s="30"/>
+      <c r="W9" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X9" s="30"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="67"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="29"/>
+      <c r="B10" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="30"/>
+      <c r="F10" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I10" s="30"/>
-      <c r="J10" s="29"/>
+      <c r="J10" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K10" s="30"/>
       <c r="N10" s="6" t="s">
         <v>35</v>
@@ -14795,124 +14864,210 @@
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="29"/>
+      <c r="B12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C12" s="30"/>
-      <c r="D12" s="29"/>
+      <c r="D12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E12" s="30"/>
-      <c r="F12" s="29"/>
+      <c r="F12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G12" s="30"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="29"/>
+      <c r="H12" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="I12" s="20"/>
+      <c r="J12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K12" s="30"/>
       <c r="N12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O12" s="29"/>
+      <c r="O12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="P12" s="30"/>
-      <c r="Q12" s="29"/>
+      <c r="Q12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="R12" s="30"/>
-      <c r="S12" s="29"/>
+      <c r="S12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="T12" s="30"/>
-      <c r="U12" s="29"/>
+      <c r="U12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V12" s="30"/>
-      <c r="W12" s="29"/>
+      <c r="W12" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X12" s="30"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="30"/>
+      <c r="B13" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="F13" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G13" s="24"/>
+      <c r="H13" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="I13" s="24"/>
+      <c r="J13" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="K13" s="24"/>
       <c r="N13" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O13" s="67"/>
-      <c r="P13" s="68"/>
-      <c r="Q13" s="67"/>
-      <c r="R13" s="68"/>
-      <c r="S13" s="67"/>
-      <c r="T13" s="68"/>
-      <c r="U13" s="29"/>
+      <c r="O13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R13" s="30"/>
+      <c r="S13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T13" s="30"/>
+      <c r="U13" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V13" s="30"/>
-      <c r="W13" s="29"/>
+      <c r="W13" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X13" s="30"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="29"/>
+      <c r="B14" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K14" s="30"/>
       <c r="N14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O14" s="29"/>
+      <c r="O14" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="P14" s="30"/>
-      <c r="Q14" s="29"/>
+      <c r="Q14" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="R14" s="30"/>
-      <c r="S14" s="29"/>
+      <c r="S14" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="T14" s="30"/>
-      <c r="U14" s="29"/>
+      <c r="U14" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V14" s="30"/>
-      <c r="W14" s="29"/>
+      <c r="W14" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X14" s="30"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="29"/>
+      <c r="B15" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C15" s="30"/>
-      <c r="D15" s="29"/>
+      <c r="D15" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E15" s="30"/>
-      <c r="F15" s="29"/>
+      <c r="F15" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G15" s="30"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="29"/>
+      <c r="H15" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K15" s="30"/>
       <c r="N15" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O15" s="29"/>
+      <c r="O15" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="P15" s="30"/>
-      <c r="Q15" s="29"/>
+      <c r="Q15" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="R15" s="30"/>
-      <c r="S15" s="29"/>
+      <c r="S15" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="T15" s="30"/>
-      <c r="U15" s="83"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="29"/>
+      <c r="U15" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="V15" s="30"/>
+      <c r="W15" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X15" s="30"/>
     </row>
     <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="30"/>
+      <c r="B16" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="20"/>
       <c r="H16" s="29"/>
       <c r="I16" s="30"/>
       <c r="J16" s="29"/>
@@ -15063,14 +15218,22 @@
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="67"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="68"/>
+      <c r="B21" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="30"/>
+      <c r="D21" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="30"/>
+      <c r="F21" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="30"/>
+      <c r="H21" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="30"/>
       <c r="J21" s="43" t="s">
         <v>88</v>
       </c>
@@ -15103,14 +15266,18 @@
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="68"/>
+      <c r="B22" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="30"/>
       <c r="D22" s="59" t="s">
         <v>226</v>
       </c>
       <c r="E22" s="60"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="68"/>
+      <c r="F22" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="30"/>
       <c r="H22" s="59" t="s">
         <v>226</v>
       </c>
@@ -15122,8 +15289,10 @@
       <c r="N22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O22" s="67"/>
-      <c r="P22" s="68"/>
+      <c r="O22" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P22" s="30"/>
       <c r="Q22" s="37" t="s">
         <v>8</v>
       </c>
@@ -15145,15 +15314,25 @@
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="29"/>
+      <c r="B23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="30"/>
+      <c r="D23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="30"/>
+      <c r="F23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="30"/>
+      <c r="H23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="30"/>
+      <c r="J23" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K23" s="30"/>
       <c r="N23" s="1" t="s">
         <v>21</v>
@@ -15231,15 +15410,25 @@
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="29"/>
+      <c r="B25" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C25" s="30"/>
-      <c r="D25" s="29"/>
+      <c r="D25" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E25" s="30"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="84"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="29"/>
+      <c r="F25" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="30"/>
+      <c r="J25" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K25" s="30"/>
       <c r="N25" s="6" t="s">
         <v>26</v>
@@ -15269,42 +15458,66 @@
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="67"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="29"/>
+      <c r="B26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="30"/>
+      <c r="F26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I26" s="30"/>
-      <c r="J26" s="29"/>
+      <c r="J26" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K26" s="30"/>
       <c r="N26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O26" s="67"/>
-      <c r="P26" s="68"/>
-      <c r="Q26" s="67"/>
-      <c r="R26" s="68"/>
-      <c r="S26" s="67"/>
-      <c r="T26" s="68"/>
-      <c r="U26" s="29"/>
+      <c r="O26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R26" s="30"/>
+      <c r="S26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="30"/>
+      <c r="U26" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V26" s="30"/>
-      <c r="W26" s="29"/>
+      <c r="W26" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X26" s="30"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="67"/>
-      <c r="C27" s="68"/>
+      <c r="B27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="30"/>
       <c r="D27" s="59" t="s">
         <v>226</v>
       </c>
       <c r="E27" s="60"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="84"/>
+      <c r="F27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="30"/>
       <c r="H27" s="59" t="s">
         <v>226</v>
       </c>
@@ -15316,30 +15529,50 @@
       <c r="N27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O27" s="67"/>
-      <c r="P27" s="68"/>
-      <c r="Q27" s="67"/>
-      <c r="R27" s="68"/>
-      <c r="S27" s="83"/>
-      <c r="T27" s="84"/>
-      <c r="U27" s="83"/>
-      <c r="V27" s="84"/>
-      <c r="W27" s="29"/>
+      <c r="O27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R27" s="30"/>
+      <c r="S27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="30"/>
+      <c r="U27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="V27" s="30"/>
+      <c r="W27" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X27" s="30"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="68"/>
-      <c r="H28" s="29"/>
+      <c r="B28" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="30"/>
+      <c r="F28" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I28" s="30"/>
-      <c r="J28" s="29"/>
+      <c r="J28" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K28" s="30"/>
       <c r="N28" s="6" t="s">
         <v>35</v>
@@ -15373,13 +15606,21 @@
         <v>8</v>
       </c>
       <c r="C29" s="38"/>
-      <c r="D29" s="29"/>
+      <c r="D29" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E29" s="30"/>
-      <c r="F29" s="29"/>
+      <c r="F29" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G29" s="30"/>
-      <c r="H29" s="29"/>
+      <c r="H29" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I29" s="30"/>
-      <c r="J29" s="29"/>
+      <c r="J29" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K29" s="30"/>
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
@@ -15411,15 +15652,25 @@
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="29"/>
+      <c r="B30" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C30" s="30"/>
-      <c r="D30" s="29"/>
+      <c r="D30" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E30" s="30"/>
-      <c r="F30" s="29"/>
+      <c r="F30" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G30" s="30"/>
-      <c r="H30" s="29"/>
+      <c r="H30" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I30" s="30"/>
-      <c r="J30" s="29"/>
+      <c r="J30" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K30" s="30"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
@@ -15451,45 +15702,75 @@
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="29"/>
+      <c r="B31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="30"/>
+      <c r="D31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="30"/>
+      <c r="F31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I31" s="30"/>
-      <c r="J31" s="29"/>
+      <c r="J31" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K31" s="30"/>
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
       <c r="N31" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O31" s="67"/>
-      <c r="P31" s="68"/>
-      <c r="Q31" s="67"/>
-      <c r="R31" s="68"/>
-      <c r="S31" s="67"/>
-      <c r="T31" s="68"/>
-      <c r="U31" s="29"/>
+      <c r="O31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R31" s="30"/>
+      <c r="S31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T31" s="30"/>
+      <c r="U31" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V31" s="30"/>
-      <c r="W31" s="29"/>
+      <c r="W31" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X31" s="30"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="29"/>
+      <c r="B32" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C32" s="30"/>
-      <c r="D32" s="29"/>
+      <c r="D32" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E32" s="30"/>
-      <c r="F32" s="29"/>
+      <c r="F32" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G32" s="30"/>
-      <c r="H32" s="29"/>
+      <c r="H32" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I32" s="30"/>
-      <c r="J32" s="29"/>
+      <c r="J32" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K32" s="30"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
@@ -15521,45 +15802,75 @@
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="29"/>
+      <c r="B33" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C33" s="30"/>
-      <c r="D33" s="29"/>
+      <c r="D33" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E33" s="30"/>
-      <c r="F33" s="29"/>
+      <c r="F33" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G33" s="30"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="84"/>
-      <c r="J33" s="29"/>
+      <c r="H33" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="30"/>
+      <c r="J33" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K33" s="30"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O33" s="29"/>
+      <c r="O33" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="P33" s="30"/>
-      <c r="Q33" s="29"/>
+      <c r="Q33" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="R33" s="30"/>
-      <c r="S33" s="29"/>
+      <c r="S33" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="T33" s="30"/>
-      <c r="U33" s="83"/>
-      <c r="V33" s="84"/>
-      <c r="W33" s="29"/>
+      <c r="U33" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="V33" s="30"/>
+      <c r="W33" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X33" s="30"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="29"/>
+      <c r="B34" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C34" s="30"/>
-      <c r="D34" s="29"/>
+      <c r="D34" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E34" s="30"/>
-      <c r="F34" s="29"/>
+      <c r="F34" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G34" s="30"/>
-      <c r="H34" s="29"/>
+      <c r="H34" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I34" s="30"/>
-      <c r="J34" s="29"/>
+      <c r="J34" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K34" s="30"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
@@ -15740,17 +16051,25 @@
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="67"/>
-      <c r="C39" s="68"/>
+      <c r="B39" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="30"/>
       <c r="D39" s="59" t="s">
         <v>233</v>
       </c>
       <c r="E39" s="60"/>
-      <c r="F39" s="29"/>
+      <c r="F39" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G39" s="30"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="29"/>
+      <c r="H39" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="30"/>
+      <c r="J39" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K39" s="30"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
@@ -15782,15 +16101,25 @@
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="67"/>
-      <c r="C40" s="68"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="29"/>
+      <c r="B40" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="30"/>
+      <c r="D40" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="30"/>
+      <c r="H40" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I40" s="30"/>
-      <c r="J40" s="29"/>
+      <c r="J40" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K40" s="30"/>
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
@@ -15918,17 +16247,25 @@
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="29"/>
+      <c r="B43" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C43" s="30"/>
       <c r="D43" s="59" t="s">
         <v>233</v>
       </c>
       <c r="E43" s="60"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="84"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="84"/>
-      <c r="J43" s="29"/>
+      <c r="F43" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="30"/>
+      <c r="H43" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="30"/>
+      <c r="J43" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K43" s="30"/>
       <c r="N43" s="6" t="s">
         <v>26</v>
@@ -15958,55 +16295,81 @@
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="67"/>
-      <c r="C44" s="68"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="29"/>
+      <c r="B44" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="30"/>
+      <c r="D44" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="30"/>
+      <c r="F44" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="30"/>
+      <c r="H44" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I44" s="30"/>
-      <c r="J44" s="29"/>
+      <c r="J44" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K44" s="30"/>
       <c r="N44" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O44" s="67"/>
-      <c r="P44" s="68"/>
+      <c r="O44" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P44" s="30"/>
       <c r="Q44" s="43" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="R44" s="44"/>
       <c r="S44" s="43" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="T44" s="44"/>
       <c r="U44" s="43" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="V44" s="44"/>
-      <c r="W44" s="29"/>
+      <c r="W44" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X44" s="30"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="67"/>
-      <c r="C45" s="68"/>
-      <c r="D45" s="67"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="84"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="84"/>
-      <c r="J45" s="29"/>
+      <c r="B45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="30"/>
+      <c r="D45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="30"/>
+      <c r="F45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="30"/>
+      <c r="H45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="30"/>
+      <c r="J45" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K45" s="30"/>
       <c r="N45" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O45" s="67"/>
-      <c r="P45" s="68"/>
+      <c r="O45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P45" s="30"/>
       <c r="Q45" s="43" t="s">
         <v>234</v>
       </c>
@@ -16019,22 +16382,34 @@
         <v>234</v>
       </c>
       <c r="V45" s="44"/>
-      <c r="W45" s="29"/>
+      <c r="W45" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X45" s="30"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B46" s="67"/>
-      <c r="C46" s="68"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="29"/>
+      <c r="B46" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="30"/>
+      <c r="D46" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="30"/>
+      <c r="F46" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" s="30"/>
+      <c r="H46" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I46" s="30"/>
-      <c r="J46" s="29"/>
+      <c r="J46" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K46" s="30"/>
       <c r="N46" s="6" t="s">
         <v>35</v>
@@ -16064,28 +16439,48 @@
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="29"/>
+      <c r="B47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C47" s="30"/>
-      <c r="D47" s="29"/>
+      <c r="D47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E47" s="30"/>
-      <c r="F47" s="29"/>
+      <c r="F47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G47" s="30"/>
-      <c r="H47" s="29"/>
+      <c r="H47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I47" s="30"/>
-      <c r="J47" s="29"/>
+      <c r="J47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K47" s="30"/>
       <c r="N47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O47" s="29"/>
+      <c r="O47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="P47" s="30"/>
-      <c r="Q47" s="29"/>
+      <c r="Q47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="R47" s="30"/>
-      <c r="S47" s="29"/>
+      <c r="S47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="T47" s="30"/>
-      <c r="U47" s="29"/>
+      <c r="U47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V47" s="30"/>
-      <c r="W47" s="29"/>
+      <c r="W47" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X47" s="30"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.2">
@@ -16140,43 +16535,73 @@
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="67"/>
-      <c r="C49" s="68"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="68"/>
-      <c r="H49" s="29"/>
+      <c r="B49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="30"/>
+      <c r="D49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="30"/>
+      <c r="F49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="30"/>
+      <c r="H49" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I49" s="30"/>
-      <c r="J49" s="29"/>
+      <c r="J49" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K49" s="30"/>
       <c r="N49" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O49" s="67"/>
-      <c r="P49" s="68"/>
-      <c r="Q49" s="67"/>
-      <c r="R49" s="68"/>
-      <c r="S49" s="67"/>
-      <c r="T49" s="68"/>
-      <c r="U49" s="29"/>
+      <c r="O49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R49" s="30"/>
+      <c r="S49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T49" s="30"/>
+      <c r="U49" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V49" s="30"/>
-      <c r="W49" s="29"/>
+      <c r="W49" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X49" s="30"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="29"/>
+      <c r="B50" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C50" s="30"/>
-      <c r="D50" s="29"/>
+      <c r="D50" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E50" s="30"/>
-      <c r="F50" s="29"/>
+      <c r="F50" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G50" s="30"/>
-      <c r="H50" s="29"/>
+      <c r="H50" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I50" s="30"/>
-      <c r="J50" s="29"/>
+      <c r="J50" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K50" s="30"/>
       <c r="N50" s="1" t="s">
         <v>48</v>
@@ -16206,56 +16631,96 @@
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="29"/>
+      <c r="B51" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C51" s="30"/>
-      <c r="D51" s="29"/>
+      <c r="D51" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E51" s="30"/>
-      <c r="F51" s="29"/>
+      <c r="F51" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G51" s="30"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="84"/>
-      <c r="J51" s="29"/>
+      <c r="H51" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I51" s="30"/>
+      <c r="J51" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K51" s="30"/>
       <c r="N51" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O51" s="29"/>
+      <c r="O51" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="P51" s="30"/>
-      <c r="Q51" s="29"/>
+      <c r="Q51" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="R51" s="30"/>
-      <c r="S51" s="29"/>
+      <c r="S51" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="T51" s="30"/>
-      <c r="U51" s="83"/>
-      <c r="V51" s="84"/>
-      <c r="W51" s="29"/>
+      <c r="U51" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="V51" s="30"/>
+      <c r="W51" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X51" s="30"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="29"/>
+      <c r="B52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="C52" s="30"/>
-      <c r="D52" s="29"/>
+      <c r="D52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="E52" s="30"/>
-      <c r="F52" s="29"/>
+      <c r="F52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="G52" s="30"/>
-      <c r="H52" s="29"/>
+      <c r="H52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="I52" s="30"/>
-      <c r="J52" s="29"/>
+      <c r="J52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="K52" s="30"/>
       <c r="N52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O52" s="29"/>
+      <c r="O52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="P52" s="30"/>
-      <c r="Q52" s="29"/>
+      <c r="Q52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="R52" s="30"/>
-      <c r="S52" s="29"/>
+      <c r="S52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="T52" s="30"/>
-      <c r="U52" s="29"/>
+      <c r="U52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="V52" s="30"/>
-      <c r="W52" s="29"/>
+      <c r="W52" s="29" t="s">
+        <v>9</v>
+      </c>
       <c r="X52" s="30"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.2">
@@ -16334,6 +16799,7 @@
       <c r="M61" s="7"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="aikEXxIRInqJDIagUDjyUfWlDat/KCz2w1HFDQcceVxB429RIcZrJbCAh+QvvN3MW4eDHx5Y6+unaPeB0CzphQ==" saltValue="824JZQCGfKcu83MqJotRKA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="450">
     <mergeCell ref="O52:P52"/>
     <mergeCell ref="Q52:R52"/>
@@ -16788,7 +17254,7 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="81" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;22TURNUS SIMULATOROPERATØRER</oddHeader>
     <oddFooter>&amp;CUtarbeidet av Stein Mathisen

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4366" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77A7D53C-5D9C-4128-8749-B4F868F67ACF}"/>
+  <xr:revisionPtr revIDLastSave="4374" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2922AEFB-31A1-46B1-B35D-3EF2752E8DB7}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="38730" windowHeight="21210" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3997" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4010" uniqueCount="273">
   <si>
     <t>Uke 01</t>
   </si>
@@ -891,6 +891,9 @@
   </si>
   <si>
     <t>Uke 51</t>
+  </si>
+  <si>
+    <t>SF RTC AW</t>
   </si>
 </sst>
 </file>
@@ -17729,14 +17732,22 @@
       </c>
       <c r="B10" s="59"/>
       <c r="C10" s="60"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20"/>
+      <c r="D10" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="36"/>
+      <c r="H10" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="36"/>
+      <c r="J10" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" s="36"/>
       <c r="N10" s="6" t="s">
         <v>35</v>
       </c>
@@ -17767,14 +17778,22 @@
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="20"/>
+      <c r="D11" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="36"/>
+      <c r="H11" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="36"/>
       <c r="N11" s="1" t="s">
         <v>37</v>
       </c>
@@ -19450,12 +19469,18 @@
       <c r="P52" s="36"/>
       <c r="Q52" s="19"/>
       <c r="R52" s="20"/>
-      <c r="S52" s="19"/>
-      <c r="T52" s="20"/>
-      <c r="U52" s="19"/>
-      <c r="V52" s="20"/>
-      <c r="W52" s="19"/>
-      <c r="X52" s="20"/>
+      <c r="S52" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="T52" s="36"/>
+      <c r="U52" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="V52" s="36"/>
+      <c r="W52" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="X52" s="36"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
@@ -21444,8 +21469,10 @@
         <v>106</v>
       </c>
       <c r="G33" s="24"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="78"/>
+      <c r="H33" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="I33" s="36"/>
       <c r="J33" s="23" t="s">
         <v>106</v>
       </c>
@@ -22052,8 +22079,10 @@
         <v>67</v>
       </c>
       <c r="I48" s="26"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="20"/>
+      <c r="J48" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="K48" s="36"/>
       <c r="N48" s="1" t="s">
         <v>37</v>
       </c>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30215"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4483" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66B5B5FC-3B02-4A3C-875A-06BB14189895}"/>
+  <xr:revisionPtr revIDLastSave="4484" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6A068FB-7C9E-4C21-8680-BFE429D6B9A3}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -56,17 +56,17 @@
   <commentList>
     <comment ref="U37" authorId="0" shapeId="0" xr:uid="{65E4B43F-4DA4-4023-9E8A-D4F24A3B2C8C}">
       <text>
-        <t>[Kommentartråd]
-Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
-Kommentar:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     RTC SUR KURS</t>
       </text>
     </comment>
     <comment ref="W37" authorId="1" shapeId="0" xr:uid="{BC2FB818-859F-40F5-95A2-BC57CF0AD42E}">
       <text>
-        <t>[Kommentartråd]
-Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
-Kommentar:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     KUT SUR (RTC)?</t>
       </text>
     </comment>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="274">
   <si>
     <t>Uke 01</t>
   </si>
@@ -785,9 +785,6 @@
     <t>BM ELPAC</t>
   </si>
   <si>
-    <t>Verdensrekordforsøk</t>
-  </si>
-  <si>
     <t>Uke 27</t>
   </si>
   <si>
@@ -795,12 +792,6 @@
   </si>
   <si>
     <t>Møte m/Komp</t>
-  </si>
-  <si>
-    <t>9 SF HF 5</t>
-  </si>
-  <si>
-    <t>SF HF 5</t>
   </si>
   <si>
     <t>ELPAC-kurs</t>
@@ -831,6 +822,12 @@
   </si>
   <si>
     <t>SF TC 3</t>
+  </si>
+  <si>
+    <t>9 SF HF 5</t>
+  </si>
+  <si>
+    <t>SF HF 5</t>
   </si>
   <si>
     <t>Uke 33</t>
@@ -906,7 +903,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1179,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1460,6 +1457,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1833,7 +1836,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="5" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -1862,7 +1865,7 @@
     <col min="28" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1935,7 +1938,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1986,7 +1989,7 @@
       </c>
       <c r="AA2" s="20"/>
     </row>
-    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2037,7 +2040,7 @@
       </c>
       <c r="AA3" s="44"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2088,7 +2091,7 @@
       </c>
       <c r="AA4" s="20"/>
     </row>
-    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -2139,7 +2142,7 @@
       </c>
       <c r="AA5" s="32"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2190,7 +2193,7 @@
       </c>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -2241,7 +2244,7 @@
       </c>
       <c r="AA7" s="28"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -2292,7 +2295,7 @@
       </c>
       <c r="AA8" s="36"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -2343,7 +2346,7 @@
       </c>
       <c r="AA9" s="32"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -2394,7 +2397,7 @@
       </c>
       <c r="AA10" s="22"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -2445,7 +2448,7 @@
       </c>
       <c r="AA11" s="44"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -2496,7 +2499,7 @@
       </c>
       <c r="AA12" s="36"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -2547,7 +2550,7 @@
       </c>
       <c r="AA13" s="36"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,7 +2601,7 @@
       </c>
       <c r="AA14" s="32"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -2649,7 +2652,7 @@
       </c>
       <c r="AA15" s="20"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -2696,7 +2699,7 @@
       <c r="Z16" s="17"/>
       <c r="AA16" s="18"/>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2731,7 +2734,7 @@
       <c r="Z17" s="17"/>
       <c r="AA17" s="18"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2766,7 +2769,7 @@
       <c r="Z18" s="17"/>
       <c r="AA18" s="18"/>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -2787,7 +2790,7 @@
       </c>
       <c r="U19" s="26"/>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -2808,7 +2811,7 @@
       </c>
       <c r="U20" s="32"/>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2826,7 +2829,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2844,7 +2847,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -2917,7 +2920,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -2970,7 +2973,7 @@
       </c>
       <c r="AA24" s="22"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -3023,7 +3026,7 @@
       </c>
       <c r="AA25" s="22"/>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -3076,7 +3079,7 @@
       </c>
       <c r="AA26" s="32"/>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -3129,7 +3132,7 @@
       </c>
       <c r="AA27" s="28"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
@@ -3182,7 +3185,7 @@
       </c>
       <c r="AA28" s="18"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27">
       <c r="A29" s="6" t="s">
         <v>26</v>
       </c>
@@ -3235,7 +3238,7 @@
       </c>
       <c r="AA29" s="46"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27">
       <c r="A30" s="6" t="s">
         <v>28</v>
       </c>
@@ -3288,7 +3291,7 @@
       </c>
       <c r="AA30" s="18"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -3341,7 +3344,7 @@
       </c>
       <c r="AA31" s="28"/>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -3394,7 +3397,7 @@
       </c>
       <c r="AA32" s="32"/>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
@@ -3447,7 +3450,7 @@
       </c>
       <c r="AA33" s="28"/>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -3500,7 +3503,7 @@
       </c>
       <c r="AA34" s="32"/>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27">
       <c r="A35" s="12" t="s">
         <v>45</v>
       </c>
@@ -3553,7 +3556,7 @@
       </c>
       <c r="AA35" s="36"/>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27">
       <c r="A36" s="1" t="s">
         <v>48</v>
       </c>
@@ -3606,7 +3609,7 @@
       </c>
       <c r="AA36" s="36"/>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27">
       <c r="A37" s="12" t="s">
         <v>49</v>
       </c>
@@ -3659,7 +3662,7 @@
       </c>
       <c r="AA37" s="36"/>
     </row>
-    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -3708,7 +3711,7 @@
       <c r="Z38" s="17"/>
       <c r="AA38" s="18"/>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27">
       <c r="A39" s="4"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -3729,7 +3732,7 @@
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27">
       <c r="A40" s="7"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -3747,7 +3750,7 @@
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27">
       <c r="A41" s="1" t="s">
         <v>69</v>
       </c>
@@ -3820,7 +3823,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -3873,7 +3876,7 @@
       </c>
       <c r="AA42" s="30"/>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -3926,7 +3929,7 @@
       </c>
       <c r="AA43" s="18"/>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -3979,7 +3982,7 @@
       </c>
       <c r="AA44" s="38"/>
     </row>
-    <row r="45" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="15" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -4032,7 +4035,7 @@
       </c>
       <c r="AA45" s="28"/>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -4085,7 +4088,7 @@
       </c>
       <c r="AA46" s="22"/>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27">
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
@@ -4138,7 +4141,7 @@
       </c>
       <c r="AA47" s="18"/>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27">
       <c r="A48" s="6" t="s">
         <v>28</v>
       </c>
@@ -4191,7 +4194,7 @@
       </c>
       <c r="AA48" s="28"/>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27">
       <c r="A49" s="6" t="s">
         <v>32</v>
       </c>
@@ -4244,7 +4247,7 @@
       </c>
       <c r="AA49" s="36"/>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27">
       <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
@@ -4297,7 +4300,7 @@
       </c>
       <c r="AA50" s="18"/>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -4345,7 +4348,7 @@
       </c>
       <c r="AA51" s="38"/>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -4393,7 +4396,7 @@
       </c>
       <c r="AA52" s="36"/>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27">
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
@@ -4441,7 +4444,7 @@
       </c>
       <c r="AA53" s="22"/>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27">
       <c r="A54" s="1" t="s">
         <v>48</v>
       </c>
@@ -4489,7 +4492,7 @@
       </c>
       <c r="AA54" s="36"/>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27">
       <c r="A55" s="12" t="s">
         <v>49</v>
       </c>
@@ -4537,7 +4540,7 @@
       </c>
       <c r="AA55" s="38"/>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -4577,7 +4580,7 @@
       <c r="Z56" s="17"/>
       <c r="AA56" s="18"/>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -4591,7 +4594,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -4605,7 +4608,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -4619,7 +4622,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -5113,7 +5116,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -5142,7 +5145,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -5210,7 +5213,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -5258,7 +5261,7 @@
       </c>
       <c r="X2" s="22"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -5306,7 +5309,7 @@
       </c>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -5354,7 +5357,7 @@
       </c>
       <c r="X4" s="22"/>
     </row>
-    <row r="5" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="11.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5402,7 +5405,7 @@
       </c>
       <c r="X5" s="22"/>
     </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -5450,7 +5453,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -5498,7 +5501,7 @@
       </c>
       <c r="X7" s="24"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -5546,7 +5549,7 @@
       </c>
       <c r="X8" s="36"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -5594,7 +5597,7 @@
       </c>
       <c r="X9" s="22"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -5642,7 +5645,7 @@
       </c>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -5690,7 +5693,7 @@
       </c>
       <c r="X11" s="28"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -5738,7 +5741,7 @@
       </c>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -5786,7 +5789,7 @@
       </c>
       <c r="X13" s="28"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -5834,7 +5837,7 @@
       </c>
       <c r="X14" s="36"/>
     </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -5882,7 +5885,7 @@
       </c>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -5922,7 +5925,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -5946,7 +5949,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -5970,7 +5973,7 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24">
       <c r="A19" s="7"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -5994,7 +5997,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24">
       <c r="A20" s="1" t="s">
         <v>97</v>
       </c>
@@ -6062,7 +6065,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -6110,7 +6113,7 @@
       </c>
       <c r="X21" s="68"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -6158,7 +6161,7 @@
       </c>
       <c r="X22" s="22"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -6206,7 +6209,7 @@
       </c>
       <c r="X23" s="36"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -6254,7 +6257,7 @@
       </c>
       <c r="X24" s="36"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -6302,7 +6305,7 @@
       </c>
       <c r="X25" s="22"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -6350,7 +6353,7 @@
       </c>
       <c r="X26" s="36"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24">
       <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
@@ -6398,7 +6401,7 @@
       </c>
       <c r="X27" s="28"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24">
       <c r="A28" s="6" t="s">
         <v>32</v>
       </c>
@@ -6446,7 +6449,7 @@
       </c>
       <c r="X28" s="34"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24">
       <c r="A29" s="6" t="s">
         <v>35</v>
       </c>
@@ -6494,7 +6497,7 @@
       </c>
       <c r="X29" s="26"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -6544,7 +6547,7 @@
       </c>
       <c r="X30" s="34"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -6594,7 +6597,7 @@
       </c>
       <c r="X31" s="28"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24">
       <c r="A32" s="12" t="s">
         <v>45</v>
       </c>
@@ -6644,7 +6647,7 @@
       </c>
       <c r="X32" s="26"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -6694,7 +6697,7 @@
       </c>
       <c r="X33" s="26"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24">
       <c r="A34" s="12" t="s">
         <v>49</v>
       </c>
@@ -6744,7 +6747,7 @@
       </c>
       <c r="X34" s="34"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -6784,7 +6787,7 @@
       </c>
       <c r="X35" s="26"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -6819,7 +6822,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24">
       <c r="A37" s="5"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -6842,7 +6845,7 @@
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -6865,12 +6868,12 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24">
       <c r="M39" s="7"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
         <v>109</v>
       </c>
@@ -6939,7 +6942,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -6988,7 +6991,7 @@
       </c>
       <c r="X41" s="22"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -7036,7 +7039,7 @@
       </c>
       <c r="X42" s="22"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -7084,7 +7087,7 @@
       </c>
       <c r="X43" s="22"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -7132,7 +7135,7 @@
       </c>
       <c r="X44" s="44"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -7180,7 +7183,7 @@
       </c>
       <c r="X45" s="22"/>
     </row>
-    <row r="46" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" ht="10.5" customHeight="1">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -7229,7 +7232,7 @@
       </c>
       <c r="X46" s="36"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -7278,7 +7281,7 @@
       </c>
       <c r="X47" s="36"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -7327,7 +7330,7 @@
       </c>
       <c r="X48" s="26"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -7376,7 +7379,7 @@
       </c>
       <c r="X49" s="44"/>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -7425,7 +7428,7 @@
       </c>
       <c r="X50" s="26"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -7473,7 +7476,7 @@
       </c>
       <c r="X51" s="28"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -7521,7 +7524,7 @@
       </c>
       <c r="X52" s="36"/>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -7569,7 +7572,7 @@
       </c>
       <c r="X53" s="28"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -7618,7 +7621,7 @@
       </c>
       <c r="X54" s="28"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -7661,7 +7664,7 @@
       </c>
       <c r="X55" s="26"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
@@ -7698,7 +7701,7 @@
       <c r="W56" s="9"/>
       <c r="X56" s="9"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24">
       <c r="A57" s="7"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -7723,7 +7726,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -7737,7 +7740,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -7751,7 +7754,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -7771,7 +7774,7 @@
       <c r="W60" s="9"/>
       <c r="X60" s="9"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -7783,34 +7786,34 @@
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24">
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="R62" s="9"/>
     </row>
-    <row r="71" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="13:13">
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="13:13">
       <c r="M72" s="5"/>
     </row>
-    <row r="73" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="13:13">
       <c r="M73" s="5"/>
     </row>
-    <row r="74" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="13:13">
       <c r="M74" s="5"/>
     </row>
-    <row r="75" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="13:13">
       <c r="M75" s="5"/>
     </row>
-    <row r="76" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="13:13">
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="13:13">
       <c r="M77" s="5"/>
     </row>
-    <row r="78" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="13:13">
       <c r="M78" s="5"/>
     </row>
   </sheetData>
@@ -8294,7 +8297,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -8324,7 +8327,7 @@
     <col min="27" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
@@ -8392,7 +8395,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -8440,7 +8443,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -8488,7 +8491,7 @@
       </c>
       <c r="X3" s="64"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -8536,7 +8539,7 @@
       </c>
       <c r="X4" s="28"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -8584,7 +8587,7 @@
       </c>
       <c r="X5" s="64"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -8632,7 +8635,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -8680,7 +8683,7 @@
       </c>
       <c r="X7" s="28"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -8728,7 +8731,7 @@
       </c>
       <c r="X8" s="34"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -8776,7 +8779,7 @@
       </c>
       <c r="X9" s="28"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -8824,7 +8827,7 @@
       </c>
       <c r="X10" s="34"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -8872,7 +8875,7 @@
       </c>
       <c r="X11" s="28"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -8920,7 +8923,7 @@
       </c>
       <c r="X12" s="28"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -8968,7 +8971,7 @@
       </c>
       <c r="X13" s="28"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -9016,7 +9019,7 @@
       </c>
       <c r="X14" s="64"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -9064,7 +9067,7 @@
       </c>
       <c r="X15" s="64"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -9104,7 +9107,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1">
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="7"/>
@@ -9117,7 +9120,7 @@
       </c>
       <c r="V17" s="28"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1">
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="7"/>
@@ -9126,7 +9129,7 @@
       </c>
       <c r="P18" s="28"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1">
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="7"/>
@@ -9135,7 +9138,7 @@
       </c>
       <c r="P19" s="64"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1">
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="7"/>
@@ -9144,7 +9147,7 @@
       </c>
       <c r="P20" s="64"/>
     </row>
-    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" ht="11.25" customHeight="1">
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="7"/>
@@ -9153,7 +9156,7 @@
       </c>
       <c r="P21" s="64"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1">
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="7"/>
@@ -9162,17 +9165,17 @@
       </c>
       <c r="P22" s="64"/>
     </row>
-    <row r="23" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="11.25" customHeight="1">
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" ht="11.25" customHeight="1">
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24">
       <c r="A25" s="1" t="s">
         <v>154</v>
       </c>
@@ -9242,7 +9245,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -9288,7 +9291,7 @@
       </c>
       <c r="X26" s="22"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -9334,7 +9337,7 @@
       </c>
       <c r="X27" s="20"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -9380,7 +9383,7 @@
       </c>
       <c r="X28" s="70"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -9426,7 +9429,7 @@
       </c>
       <c r="X29" s="36"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -9472,7 +9475,7 @@
       </c>
       <c r="X30" s="22"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
@@ -9518,7 +9521,7 @@
       </c>
       <c r="X31" s="36"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24">
       <c r="A32" s="6" t="s">
         <v>28</v>
       </c>
@@ -9564,7 +9567,7 @@
       </c>
       <c r="X32" s="70"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24">
       <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
@@ -9606,7 +9609,7 @@
       </c>
       <c r="X33" s="32"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -9652,7 +9655,7 @@
       </c>
       <c r="X34" s="22"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -9698,7 +9701,7 @@
       </c>
       <c r="X35" s="28"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
@@ -9744,7 +9747,7 @@
       </c>
       <c r="X36" s="32"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24">
       <c r="A37" s="12" t="s">
         <v>45</v>
       </c>
@@ -9790,7 +9793,7 @@
       </c>
       <c r="X37" s="28"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
@@ -9836,7 +9839,7 @@
       </c>
       <c r="X38" s="36"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24">
       <c r="A39" s="12" t="s">
         <v>49</v>
       </c>
@@ -9882,7 +9885,7 @@
       </c>
       <c r="X39" s="32"/>
     </row>
-    <row r="40" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" ht="11.25" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
@@ -9924,7 +9927,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" ht="11.25" customHeight="1">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -9939,7 +9942,7 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" ht="11.25" customHeight="1">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -9954,7 +9957,7 @@
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" ht="11.25" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>166</v>
       </c>
@@ -10024,7 +10027,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" ht="11.25" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -10070,7 +10073,7 @@
       <c r="W44" s="53"/>
       <c r="X44" s="54"/>
     </row>
-    <row r="45" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" ht="11.25" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -10116,7 +10119,7 @@
       <c r="W45" s="53"/>
       <c r="X45" s="54"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -10162,7 +10165,7 @@
       <c r="W46" s="53"/>
       <c r="X46" s="54"/>
     </row>
-    <row r="47" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" ht="11.25" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -10206,7 +10209,7 @@
       <c r="W47" s="53"/>
       <c r="X47" s="54"/>
     </row>
-    <row r="48" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" ht="11.25" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
@@ -10250,7 +10253,7 @@
       <c r="W48" s="53"/>
       <c r="X48" s="54"/>
     </row>
-    <row r="49" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" ht="11.25" customHeight="1">
       <c r="A49" s="6" t="s">
         <v>26</v>
       </c>
@@ -10294,7 +10297,7 @@
       <c r="W49" s="53"/>
       <c r="X49" s="54"/>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24">
       <c r="A50" s="6" t="s">
         <v>28</v>
       </c>
@@ -10338,7 +10341,7 @@
       <c r="W50" s="53"/>
       <c r="X50" s="54"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24">
       <c r="A51" s="6" t="s">
         <v>32</v>
       </c>
@@ -10384,7 +10387,7 @@
       <c r="W51" s="53"/>
       <c r="X51" s="54"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24">
       <c r="A52" s="6" t="s">
         <v>35</v>
       </c>
@@ -10430,7 +10433,7 @@
       <c r="W52" s="53"/>
       <c r="X52" s="54"/>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24">
       <c r="A53" s="1" t="s">
         <v>37</v>
       </c>
@@ -10476,7 +10479,7 @@
       <c r="W53" s="53"/>
       <c r="X53" s="54"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24">
       <c r="A54" s="1" t="s">
         <v>40</v>
       </c>
@@ -10522,7 +10525,7 @@
       <c r="W54" s="53"/>
       <c r="X54" s="54"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24">
       <c r="A55" s="12" t="s">
         <v>45</v>
       </c>
@@ -10568,7 +10571,7 @@
       <c r="W55" s="53"/>
       <c r="X55" s="54"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24">
       <c r="A56" s="1" t="s">
         <v>48</v>
       </c>
@@ -10614,7 +10617,7 @@
       <c r="W56" s="53"/>
       <c r="X56" s="54"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24">
       <c r="A57" s="12" t="s">
         <v>49</v>
       </c>
@@ -10660,7 +10663,7 @@
       <c r="W57" s="53"/>
       <c r="X57" s="54"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24">
       <c r="A58" s="1" t="s">
         <v>50</v>
       </c>
@@ -10700,7 +10703,7 @@
       <c r="W58" s="53"/>
       <c r="X58" s="54"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="O59" s="43" t="s">
@@ -10716,7 +10719,7 @@
       </c>
       <c r="T59" s="44"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -10734,7 +10737,7 @@
       </c>
       <c r="P60" s="36"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -10748,7 +10751,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24">
       <c r="A62" s="8">
         <v>3</v>
       </c>
@@ -10762,7 +10765,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24">
       <c r="A63" s="5">
         <v>4</v>
       </c>
@@ -10770,17 +10773,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -11268,7 +11271,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -11297,7 +11300,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>178</v>
       </c>
@@ -11365,7 +11368,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -11411,7 +11414,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -11457,7 +11460,7 @@
       </c>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -11503,7 +11506,7 @@
       </c>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -11550,7 +11553,7 @@
       </c>
       <c r="X5" s="44"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -11596,7 +11599,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -11642,7 +11645,7 @@
       </c>
       <c r="X7" s="70"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -11688,7 +11691,7 @@
       </c>
       <c r="X8" s="70"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -11734,7 +11737,7 @@
       </c>
       <c r="X9" s="88"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -11780,7 +11783,7 @@
       </c>
       <c r="X10" s="34"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -11826,7 +11829,7 @@
       </c>
       <c r="X11" s="44"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -11872,7 +11875,7 @@
       </c>
       <c r="X12" s="34"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -11918,7 +11921,7 @@
       </c>
       <c r="X13" s="88"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -11964,7 +11967,7 @@
       </c>
       <c r="X14" s="34"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -12010,7 +12013,7 @@
       </c>
       <c r="X15" s="44"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -12050,7 +12053,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24">
       <c r="A17" s="12" t="s">
         <v>195</v>
       </c>
@@ -12077,7 +12080,7 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24">
       <c r="B18" s="27" t="s">
         <v>196</v>
       </c>
@@ -12089,7 +12092,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24">
       <c r="A19" s="5"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -12098,7 +12101,7 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -12109,7 +12112,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
         <v>197</v>
       </c>
@@ -12177,7 +12180,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -12223,7 +12226,7 @@
       </c>
       <c r="X22" s="30"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -12269,7 +12272,7 @@
       </c>
       <c r="X23" s="20"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -12315,7 +12318,7 @@
       </c>
       <c r="X24" s="18"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -12361,7 +12364,7 @@
       </c>
       <c r="X25" s="88"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -12407,7 +12410,7 @@
       </c>
       <c r="X26" s="22"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -12453,7 +12456,7 @@
       </c>
       <c r="X27" s="34"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -12499,7 +12502,7 @@
       </c>
       <c r="X28" s="88"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -12545,7 +12548,7 @@
       </c>
       <c r="X29" s="22"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -12591,7 +12594,7 @@
       </c>
       <c r="X30" s="22"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -12637,7 +12640,7 @@
       </c>
       <c r="X31" s="44"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -12685,7 +12688,7 @@
       </c>
       <c r="X32" s="28"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -12733,7 +12736,7 @@
       </c>
       <c r="X33" s="34"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -12781,7 +12784,7 @@
       </c>
       <c r="X34" s="44"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -12829,7 +12832,7 @@
       </c>
       <c r="X35" s="34"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -12871,7 +12874,7 @@
       </c>
       <c r="X36" s="44"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="4"/>
@@ -12879,7 +12882,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="4"/>
@@ -12887,7 +12890,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24">
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="4"/>
@@ -12895,7 +12898,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
         <v>212</v>
       </c>
@@ -12965,7 +12968,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -13015,7 +13018,7 @@
       </c>
       <c r="X41" s="30"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -13065,7 +13068,7 @@
       </c>
       <c r="X42" s="18"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -13115,7 +13118,7 @@
       </c>
       <c r="X43" s="18"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -13163,7 +13166,7 @@
       </c>
       <c r="X44" s="32"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -13211,7 +13214,7 @@
       </c>
       <c r="X45" s="22"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -13259,7 +13262,7 @@
       </c>
       <c r="X46" s="22"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -13307,7 +13310,7 @@
       </c>
       <c r="X47" s="40"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -13355,7 +13358,7 @@
       </c>
       <c r="X48" s="20"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -13403,7 +13406,7 @@
       </c>
       <c r="X49" s="22"/>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -13451,7 +13454,7 @@
       </c>
       <c r="X50" s="22"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -13501,7 +13504,7 @@
       </c>
       <c r="X51" s="22"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -13551,7 +13554,7 @@
       </c>
       <c r="X52" s="32"/>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -13601,7 +13604,7 @@
       </c>
       <c r="X53" s="32"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -13649,7 +13652,7 @@
       </c>
       <c r="X54" s="20"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -13691,7 +13694,7 @@
       <c r="W55" s="17"/>
       <c r="X55" s="18"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24">
       <c r="A56" s="8"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -13721,7 +13724,7 @@
       <c r="W56" s="17"/>
       <c r="X56" s="18"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24">
       <c r="A57" s="8"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -13746,7 +13749,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24">
       <c r="A58" s="8"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -13759,7 +13762,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24">
       <c r="A59" s="5">
         <v>1</v>
       </c>
@@ -13784,7 +13787,7 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24">
       <c r="A60" s="5">
         <v>2</v>
       </c>
@@ -13798,7 +13801,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24">
       <c r="A61" s="8">
         <v>3</v>
       </c>
@@ -13812,7 +13815,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24">
       <c r="A62" s="5">
         <v>4</v>
       </c>
@@ -14304,7 +14307,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -14333,7 +14336,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
@@ -14401,7 +14404,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -14449,7 +14452,7 @@
       </c>
       <c r="X2" s="20"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -14497,7 +14500,7 @@
       </c>
       <c r="X3" s="20"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -14545,7 +14548,7 @@
       </c>
       <c r="X4" s="24"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -14593,7 +14596,7 @@
       </c>
       <c r="X5" s="20"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -14641,7 +14644,7 @@
       </c>
       <c r="X6" s="24"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -14689,7 +14692,7 @@
       </c>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -14737,7 +14740,7 @@
       </c>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -14785,7 +14788,7 @@
       </c>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -14833,7 +14836,7 @@
       </c>
       <c r="X10" s="20"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -14881,7 +14884,7 @@
       </c>
       <c r="X11" s="20"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -14929,7 +14932,7 @@
       </c>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -14977,7 +14980,7 @@
       </c>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -15025,7 +15028,7 @@
       </c>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -15073,7 +15076,7 @@
       </c>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -15117,9 +15120,9 @@
       </c>
       <c r="X16" s="20"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1"/>
+    <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
+    <row r="19" spans="1:24" ht="11.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -15187,7 +15190,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -15235,7 +15238,7 @@
       </c>
       <c r="X20" s="20"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -15283,7 +15286,7 @@
       </c>
       <c r="X21" s="20"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -15331,7 +15334,7 @@
       </c>
       <c r="X22" s="20"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -15379,7 +15382,7 @@
       </c>
       <c r="X23" s="20"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -15427,7 +15430,7 @@
       </c>
       <c r="X24" s="20"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -15475,7 +15478,7 @@
       </c>
       <c r="X25" s="20"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -15523,7 +15526,7 @@
       </c>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -15571,7 +15574,7 @@
       </c>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -15619,16 +15622,16 @@
       </c>
       <c r="X28" s="20"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="20"/>
+      <c r="B29" s="92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="93"/>
       <c r="D29" s="17" t="s">
-        <v>236</v>
+        <v>9</v>
       </c>
       <c r="E29" s="18"/>
       <c r="F29" s="17" t="s">
@@ -15669,7 +15672,7 @@
       </c>
       <c r="X29" s="20"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -15719,7 +15722,7 @@
       </c>
       <c r="X30" s="20"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -15769,7 +15772,7 @@
       </c>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -15819,7 +15822,7 @@
       </c>
       <c r="X32" s="20"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -15869,7 +15872,7 @@
       </c>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -15919,7 +15922,7 @@
       </c>
       <c r="X34" s="20"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -15944,13 +15947,13 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" ht="11.25" customHeight="1">
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" ht="11.25" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -15985,7 +15988,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -16018,16 +16021,16 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" ht="11.25" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C38" s="24"/>
       <c r="D38" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E38" s="24"/>
       <c r="F38" s="29" t="s">
@@ -16068,16 +16071,16 @@
       </c>
       <c r="X38" s="20"/>
     </row>
-    <row r="39" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" ht="10.5" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C39" s="24"/>
       <c r="D39" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E39" s="24"/>
       <c r="F39" s="17" t="s">
@@ -16118,7 +16121,7 @@
       </c>
       <c r="X39" s="20"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -16168,7 +16171,7 @@
       </c>
       <c r="X40" s="20"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -16216,7 +16219,7 @@
       </c>
       <c r="X41" s="20"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -16225,7 +16228,7 @@
       </c>
       <c r="C42" s="24"/>
       <c r="D42" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E42" s="24"/>
       <c r="F42" s="23" t="s">
@@ -16264,16 +16267,16 @@
       </c>
       <c r="X42" s="20"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C43" s="24"/>
       <c r="D43" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E43" s="24"/>
       <c r="F43" s="17" t="s">
@@ -16312,7 +16315,7 @@
       </c>
       <c r="X43" s="20"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -16360,7 +16363,7 @@
       </c>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -16408,7 +16411,7 @@
       </c>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -16456,7 +16459,7 @@
       </c>
       <c r="X46" s="20"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -16504,28 +16507,28 @@
       </c>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G48" s="22"/>
       <c r="H48" s="21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I48" s="22"/>
       <c r="J48" s="21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K48" s="22"/>
       <c r="N48" s="1" t="s">
@@ -16552,7 +16555,7 @@
       </c>
       <c r="X48" s="20"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -16600,7 +16603,7 @@
       </c>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -16648,7 +16651,7 @@
       </c>
       <c r="X50" s="20"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -16696,7 +16699,7 @@
       </c>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -16744,7 +16747,7 @@
       </c>
       <c r="X52" s="18"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -16758,7 +16761,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -16774,7 +16777,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -16790,7 +16793,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -16800,15 +16803,15 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24">
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24">
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -17290,7 +17293,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -17319,9 +17322,9 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -17354,7 +17357,7 @@
         <v>46234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -17387,7 +17390,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -17435,7 +17438,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -17481,7 +17484,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -17527,7 +17530,7 @@
       </c>
       <c r="X4" s="22"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -17563,7 +17566,7 @@
       </c>
       <c r="X5" s="36"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -17611,7 +17614,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -17645,17 +17648,17 @@
       <c r="Q7" s="77"/>
       <c r="R7" s="78"/>
       <c r="S7" s="27" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="T7" s="28"/>
       <c r="U7" s="27" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="V7" s="28"/>
       <c r="W7" s="17"/>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -17693,7 +17696,7 @@
       <c r="W8" s="17"/>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -17731,7 +17734,7 @@
       </c>
       <c r="X9" s="20"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -17777,7 +17780,7 @@
       </c>
       <c r="X10" s="22"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -17823,7 +17826,7 @@
       </c>
       <c r="X11" s="22"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -17865,7 +17868,7 @@
       </c>
       <c r="X12" s="20"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -17913,7 +17916,7 @@
       </c>
       <c r="X13" s="20"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -17945,7 +17948,7 @@
       <c r="Q14" s="17"/>
       <c r="R14" s="18"/>
       <c r="S14" s="21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="T14" s="22"/>
       <c r="U14" s="17"/>
@@ -17953,7 +17956,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -17991,7 +17994,7 @@
       </c>
       <c r="X15" s="20"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -18029,7 +18032,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -18051,13 +18054,13 @@
       <c r="S17" s="17"/>
       <c r="T17" s="18"/>
       <c r="U17" s="45" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="V17" s="46"/>
       <c r="W17" s="17"/>
       <c r="X17" s="18"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -18079,13 +18082,13 @@
       <c r="S18" s="17"/>
       <c r="T18" s="18"/>
       <c r="U18" s="45" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="V18" s="46"/>
       <c r="W18" s="17"/>
       <c r="X18" s="18"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -18109,7 +18112,7 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -18133,9 +18136,9 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -18168,7 +18171,7 @@
         <v>46241</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>1</v>
@@ -18201,7 +18204,7 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -18249,7 +18252,7 @@
       </c>
       <c r="X22" s="30"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -18275,11 +18278,11 @@
       </c>
       <c r="R23" s="36"/>
       <c r="S23" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="T23" s="64"/>
       <c r="U23" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="V23" s="64"/>
       <c r="W23" s="35" t="s">
@@ -18287,7 +18290,7 @@
       </c>
       <c r="X23" s="36"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -18327,7 +18330,7 @@
       </c>
       <c r="T24" s="22"/>
       <c r="U24" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="V24" s="64"/>
       <c r="W24" s="35" t="s">
@@ -18335,22 +18338,22 @@
       </c>
       <c r="X24" s="36"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="33" t="s">
+      <c r="C25" s="97"/>
+      <c r="D25" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="33" t="s">
+      <c r="E25" s="97"/>
+      <c r="F25" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="G25" s="34"/>
+      <c r="G25" s="97"/>
       <c r="H25" s="17"/>
       <c r="I25" s="18"/>
       <c r="J25" s="17"/>
@@ -18359,25 +18362,25 @@
         <v>21</v>
       </c>
       <c r="O25" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P25" s="34"/>
       <c r="Q25" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R25" s="34"/>
       <c r="S25" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="T25" s="34"/>
       <c r="U25" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="V25" s="34"/>
       <c r="W25" s="17"/>
       <c r="X25" s="18"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -18425,53 +18428,53 @@
       </c>
       <c r="X26" s="93"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="96" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="33" t="s">
+      <c r="C27" s="97"/>
+      <c r="D27" s="96" t="s">
         <v>137</v>
       </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="33" t="s">
+      <c r="E27" s="97"/>
+      <c r="F27" s="96" t="s">
         <v>137</v>
       </c>
-      <c r="G27" s="34"/>
+      <c r="G27" s="97"/>
       <c r="H27" s="61"/>
       <c r="I27" s="62"/>
       <c r="J27" s="21" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="K27" s="22"/>
       <c r="N27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O27" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P27" s="34"/>
       <c r="Q27" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R27" s="34"/>
       <c r="S27" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="T27" s="34"/>
       <c r="U27" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="V27" s="34"/>
       <c r="W27" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="X27" s="64"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -18501,21 +18504,21 @@
       <c r="O28" s="61"/>
       <c r="P28" s="62"/>
       <c r="Q28" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R28" s="34"/>
       <c r="S28" s="61"/>
       <c r="T28" s="62"/>
       <c r="U28" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="V28" s="34"/>
       <c r="W28" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="X28" s="64"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -18561,26 +18564,26 @@
       </c>
       <c r="X29" s="20"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="33" t="s">
+      <c r="C30" s="97"/>
+      <c r="D30" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="33" t="s">
+      <c r="E30" s="97"/>
+      <c r="F30" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="97"/>
       <c r="H30" s="17"/>
       <c r="I30" s="18"/>
       <c r="J30" s="21" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="K30" s="22"/>
       <c r="N30" s="6" t="s">
@@ -18607,7 +18610,7 @@
       </c>
       <c r="X30" s="22"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -18655,7 +18658,7 @@
       </c>
       <c r="X31" s="22"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -18699,7 +18702,7 @@
       </c>
       <c r="X32" s="26"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -18733,7 +18736,7 @@
       </c>
       <c r="R33" s="36"/>
       <c r="S33" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="T33" s="64"/>
       <c r="U33" s="25" t="s">
@@ -18745,7 +18748,7 @@
       </c>
       <c r="X33" s="26"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -18787,7 +18790,7 @@
       </c>
       <c r="X34" s="26"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -18835,7 +18838,7 @@
       </c>
       <c r="X35" s="20"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -18865,17 +18868,17 @@
       <c r="W36" s="17"/>
       <c r="X36" s="18"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24">
       <c r="A39" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>1</v>
@@ -18910,7 +18913,7 @@
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>1</v>
@@ -18943,7 +18946,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -18956,7 +18959,7 @@
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G40" s="24"/>
       <c r="H40" s="29" t="s">
@@ -18989,11 +18992,11 @@
       </c>
       <c r="V40" s="30"/>
       <c r="W40" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="X40" s="38"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24">
       <c r="A41" s="1" t="s">
         <v>10</v>
       </c>
@@ -19002,7 +19005,7 @@
       <c r="D41" s="61"/>
       <c r="E41" s="62"/>
       <c r="F41" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G41" s="24"/>
       <c r="H41" s="77"/>
@@ -19025,7 +19028,7 @@
       </c>
       <c r="R41" s="36"/>
       <c r="S41" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="T41" s="34"/>
       <c r="U41" s="35" t="s">
@@ -19037,7 +19040,7 @@
       </c>
       <c r="X41" s="36"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -19067,7 +19070,7 @@
       </c>
       <c r="R42" s="22"/>
       <c r="S42" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="T42" s="34"/>
       <c r="U42" s="21" t="s">
@@ -19079,7 +19082,7 @@
       </c>
       <c r="X42" s="36"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
@@ -19101,7 +19104,7 @@
       </c>
       <c r="P43" s="28"/>
       <c r="Q43" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R43" s="34"/>
       <c r="S43" s="25" t="s">
@@ -19109,15 +19112,15 @@
       </c>
       <c r="T43" s="26"/>
       <c r="U43" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="V43" s="34"/>
       <c r="W43" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="X43" s="34"/>
     </row>
-    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
@@ -19130,7 +19133,7 @@
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G44" s="24"/>
       <c r="H44" s="21" t="s">
@@ -19165,7 +19168,7 @@
       </c>
       <c r="X44" s="22"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24">
       <c r="A45" s="6" t="s">
         <v>26</v>
       </c>
@@ -19197,7 +19200,7 @@
       </c>
       <c r="P45" s="28"/>
       <c r="Q45" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R45" s="34"/>
       <c r="S45" s="25" t="s">
@@ -19205,15 +19208,15 @@
       </c>
       <c r="T45" s="26"/>
       <c r="U45" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="V45" s="34"/>
       <c r="W45" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="X45" s="34"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24">
       <c r="A46" s="6" t="s">
         <v>28</v>
       </c>
@@ -19247,7 +19250,7 @@
       </c>
       <c r="P46" s="28"/>
       <c r="Q46" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R46" s="34"/>
       <c r="S46" s="25" t="s">
@@ -19255,7 +19258,7 @@
       </c>
       <c r="T46" s="26"/>
       <c r="U46" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="V46" s="34"/>
       <c r="W46" s="25" t="s">
@@ -19263,16 +19266,16 @@
       </c>
       <c r="X46" s="26"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24">
       <c r="A47" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C47" s="22"/>
       <c r="D47" s="21" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="17"/>
@@ -19307,16 +19310,16 @@
       </c>
       <c r="X47" s="46"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24">
       <c r="A48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="21" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="17"/>
@@ -19324,7 +19327,7 @@
       <c r="H48" s="17"/>
       <c r="I48" s="18"/>
       <c r="J48" s="21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="K48" s="22"/>
       <c r="N48" s="6" t="s">
@@ -19335,15 +19338,15 @@
       </c>
       <c r="P48" s="28"/>
       <c r="Q48" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="R48" s="64"/>
       <c r="S48" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="T48" s="64"/>
       <c r="U48" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="V48" s="64"/>
       <c r="W48" s="25" t="s">
@@ -19351,7 +19354,7 @@
       </c>
       <c r="X48" s="26"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24">
       <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
@@ -19360,7 +19363,7 @@
       <c r="D49" s="17"/>
       <c r="E49" s="18"/>
       <c r="F49" s="21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G49" s="22"/>
       <c r="H49" s="17"/>
@@ -19375,15 +19378,15 @@
       </c>
       <c r="P49" s="28"/>
       <c r="Q49" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="R49" s="64"/>
       <c r="S49" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="T49" s="64"/>
       <c r="U49" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="V49" s="64"/>
       <c r="W49" s="25" t="s">
@@ -19391,7 +19394,7 @@
       </c>
       <c r="X49" s="26"/>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24">
       <c r="A50" s="1" t="s">
         <v>40</v>
       </c>
@@ -19425,11 +19428,11 @@
       <c r="U50" s="17"/>
       <c r="V50" s="18"/>
       <c r="W50" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="X50" s="64"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24">
       <c r="A51" s="12" t="s">
         <v>45</v>
       </c>
@@ -19469,11 +19472,11 @@
       <c r="U51" s="17"/>
       <c r="V51" s="18"/>
       <c r="W51" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="X51" s="64"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24">
       <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
@@ -19501,19 +19504,19 @@
       <c r="Q52" s="17"/>
       <c r="R52" s="18"/>
       <c r="S52" s="27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T52" s="28"/>
       <c r="U52" s="27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V52" s="28"/>
       <c r="W52" s="27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="X52" s="28"/>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24">
       <c r="A53" s="12" t="s">
         <v>49</v>
       </c>
@@ -19549,7 +19552,7 @@
       <c r="W53" s="17"/>
       <c r="X53" s="18"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24">
       <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
@@ -19581,7 +19584,7 @@
       <c r="W54" s="17"/>
       <c r="X54" s="18"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24">
       <c r="A55" s="5"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -19617,7 +19620,7 @@
       </c>
       <c r="X55" s="46"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24">
       <c r="A56" s="5"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -19645,7 +19648,7 @@
       <c r="W56" s="17"/>
       <c r="X56" s="18"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24">
       <c r="A57" s="5"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -19668,7 +19671,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -19682,7 +19685,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -19696,7 +19699,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -19710,7 +19713,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -19718,22 +19721,22 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1">
       <c r="A65" s="8"/>
     </row>
   </sheetData>
@@ -20227,7 +20230,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -20256,9 +20259,9 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -20291,7 +20294,7 @@
         <v>46276</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -20324,43 +20327,43 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E2" s="38"/>
       <c r="F2" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G2" s="38"/>
       <c r="H2" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I2" s="38"/>
       <c r="J2" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K2" s="38"/>
       <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="O2" s="94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P2" s="95"/>
       <c r="Q2" s="94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R2" s="95"/>
       <c r="S2" s="94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T2" s="95"/>
       <c r="U2" s="29" t="s">
@@ -20372,7 +20375,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -20381,7 +20384,7 @@
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="35" t="s">
@@ -20389,7 +20392,7 @@
       </c>
       <c r="G3" s="36"/>
       <c r="H3" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I3" s="34"/>
       <c r="J3" s="35" t="s">
@@ -20400,15 +20403,15 @@
         <v>10</v>
       </c>
       <c r="O3" s="94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P3" s="95"/>
       <c r="Q3" s="94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R3" s="95"/>
       <c r="S3" s="94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T3" s="95"/>
       <c r="U3" s="77"/>
@@ -20416,7 +20419,7 @@
       <c r="W3" s="17"/>
       <c r="X3" s="18"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -20425,7 +20428,7 @@
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="35" t="s">
@@ -20433,7 +20436,7 @@
       </c>
       <c r="G4" s="36"/>
       <c r="H4" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I4" s="34"/>
       <c r="J4" s="17"/>
@@ -20452,24 +20455,24 @@
       <c r="W4" s="17"/>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="61"/>
       <c r="E5" s="62"/>
       <c r="F5" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G5" s="34"/>
       <c r="H5" s="17"/>
       <c r="I5" s="18"/>
       <c r="J5" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K5" s="34"/>
       <c r="N5" s="1" t="s">
@@ -20486,7 +20489,7 @@
       <c r="W5" s="17"/>
       <c r="X5" s="18"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -20534,24 +20537,24 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="17"/>
       <c r="E7" s="18"/>
       <c r="F7" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G7" s="34"/>
       <c r="H7" s="77"/>
       <c r="I7" s="78"/>
       <c r="J7" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K7" s="34"/>
       <c r="N7" s="6" t="s">
@@ -20568,24 +20571,24 @@
       <c r="W7" s="17"/>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="61"/>
       <c r="E8" s="62"/>
       <c r="F8" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G8" s="34"/>
       <c r="H8" s="17"/>
       <c r="I8" s="18"/>
       <c r="J8" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K8" s="34"/>
       <c r="N8" s="6" t="s">
@@ -20602,7 +20605,7 @@
       <c r="W8" s="17"/>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -20634,7 +20637,7 @@
       <c r="W9" s="17"/>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -20672,7 +20675,7 @@
       <c r="W10" s="17"/>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="11.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -20704,7 +20707,7 @@
       <c r="W11" s="17"/>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="11.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -20742,7 +20745,7 @@
       <c r="W12" s="17"/>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="11.25" customHeight="1">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -20770,7 +20773,7 @@
       <c r="W13" s="17"/>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="11.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -20798,7 +20801,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="11.25" customHeight="1">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -20826,7 +20829,7 @@
       <c r="W15" s="17"/>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -20860,7 +20863,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -20873,7 +20876,7 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -20886,9 +20889,9 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -20921,7 +20924,7 @@
         <v>46283</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -20954,7 +20957,7 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -21002,7 +21005,7 @@
       </c>
       <c r="X20" s="30"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -21040,7 +21043,7 @@
       <c r="W21" s="17"/>
       <c r="X21" s="18"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -21088,7 +21091,7 @@
       </c>
       <c r="X22" s="20"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -21097,7 +21100,7 @@
       </c>
       <c r="C23" s="36"/>
       <c r="D23" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E23" s="34"/>
       <c r="F23" s="35" t="s">
@@ -21126,7 +21129,7 @@
       <c r="W23" s="17"/>
       <c r="X23" s="18"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -21174,7 +21177,7 @@
       </c>
       <c r="X24" s="22"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -21183,7 +21186,7 @@
       </c>
       <c r="C25" s="36"/>
       <c r="D25" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="35" t="s">
@@ -21222,20 +21225,20 @@
       </c>
       <c r="X25" s="20"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C26" s="34"/>
       <c r="D26" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E26" s="34"/>
       <c r="F26" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G26" s="34"/>
       <c r="H26" s="69" t="s">
@@ -21260,12 +21263,12 @@
       <c r="W26" s="17"/>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C27" s="34"/>
       <c r="D27" s="25" t="s">
@@ -21273,7 +21276,7 @@
       </c>
       <c r="E27" s="26"/>
       <c r="F27" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G27" s="34"/>
       <c r="H27" s="35" t="s">
@@ -21298,7 +21301,7 @@
       <c r="W27" s="17"/>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -21315,7 +21318,7 @@
       </c>
       <c r="G28" s="22"/>
       <c r="H28" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="21" t="s">
@@ -21336,7 +21339,7 @@
       <c r="W28" s="17"/>
       <c r="X28" s="18"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -21349,7 +21352,7 @@
       </c>
       <c r="G29" s="26"/>
       <c r="H29" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I29" s="34"/>
       <c r="J29" s="25" t="s">
@@ -21372,7 +21375,7 @@
       <c r="W29" s="17"/>
       <c r="X29" s="18"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -21389,7 +21392,7 @@
       </c>
       <c r="G30" s="22"/>
       <c r="H30" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I30" s="34"/>
       <c r="J30" s="21" t="s">
@@ -21412,7 +21415,7 @@
       <c r="W30" s="17"/>
       <c r="X30" s="18"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -21446,7 +21449,7 @@
       <c r="W31" s="17"/>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -21480,7 +21483,7 @@
       <c r="W32" s="17"/>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -21497,7 +21500,7 @@
       </c>
       <c r="G33" s="26"/>
       <c r="H33" s="27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I33" s="28"/>
       <c r="J33" s="25" t="s">
@@ -21520,7 +21523,7 @@
       <c r="W33" s="17"/>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -21560,7 +21563,7 @@
       <c r="W34" s="17"/>
       <c r="X34" s="18"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24">
       <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
@@ -21597,7 +21600,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24">
       <c r="A36" s="5"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -21622,7 +21625,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -21648,9 +21651,9 @@
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24">
       <c r="A38" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>1</v>
@@ -21685,7 +21688,7 @@
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>1</v>
@@ -21718,7 +21721,7 @@
         <v>46311</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -21768,7 +21771,7 @@
       </c>
       <c r="X39" s="30"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
         <v>10</v>
       </c>
@@ -21806,7 +21809,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24">
       <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
@@ -21846,7 +21849,7 @@
       <c r="W41" s="17"/>
       <c r="X41" s="18"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -21859,7 +21862,7 @@
       </c>
       <c r="E42" s="36"/>
       <c r="F42" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G42" s="34"/>
       <c r="H42" s="43" t="s">
@@ -21886,7 +21889,7 @@
       <c r="W42" s="17"/>
       <c r="X42" s="18"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24">
       <c r="A43" s="1" t="s">
         <v>24</v>
       </c>
@@ -21903,7 +21906,7 @@
       </c>
       <c r="G43" s="22"/>
       <c r="H43" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I43" s="34"/>
       <c r="J43" s="21" t="s">
@@ -21934,7 +21937,7 @@
       </c>
       <c r="X43" s="22"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24">
       <c r="A44" s="6" t="s">
         <v>26</v>
       </c>
@@ -21970,7 +21973,7 @@
       <c r="W44" s="17"/>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24">
       <c r="A45" s="6" t="s">
         <v>28</v>
       </c>
@@ -22006,7 +22009,7 @@
       <c r="W45" s="17"/>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24">
       <c r="A46" s="6" t="s">
         <v>32</v>
       </c>
@@ -22019,7 +22022,7 @@
       </c>
       <c r="E46" s="36"/>
       <c r="F46" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G46" s="34"/>
       <c r="H46" s="35" t="s">
@@ -22044,16 +22047,16 @@
       <c r="W46" s="17"/>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24">
       <c r="A47" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C47" s="34"/>
       <c r="D47" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E47" s="34"/>
       <c r="F47" s="21" t="s">
@@ -22082,16 +22085,16 @@
       <c r="W47" s="17"/>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C48" s="34"/>
       <c r="D48" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E48" s="34"/>
       <c r="F48" s="25" t="s">
@@ -22103,7 +22106,7 @@
       </c>
       <c r="I48" s="36"/>
       <c r="J48" s="27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K48" s="28"/>
       <c r="N48" s="1" t="s">
@@ -22120,7 +22123,7 @@
       <c r="W48" s="17"/>
       <c r="X48" s="18"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24">
       <c r="A49" s="1" t="s">
         <v>40</v>
       </c>
@@ -22129,7 +22132,7 @@
       </c>
       <c r="C49" s="26"/>
       <c r="D49" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E49" s="34"/>
       <c r="F49" s="21" t="s">
@@ -22158,7 +22161,7 @@
       <c r="W49" s="17"/>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A50" s="12" t="s">
         <v>45</v>
       </c>
@@ -22175,7 +22178,7 @@
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I50" s="34"/>
       <c r="J50" s="17"/>
@@ -22194,7 +22197,7 @@
       <c r="W50" s="17"/>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24">
       <c r="A51" s="1" t="s">
         <v>48</v>
       </c>
@@ -22211,7 +22214,7 @@
       </c>
       <c r="G51" s="44"/>
       <c r="H51" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I51" s="34"/>
       <c r="J51" s="17"/>
@@ -22230,7 +22233,7 @@
       <c r="W51" s="17"/>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24">
       <c r="A52" s="12" t="s">
         <v>49</v>
       </c>
@@ -22268,7 +22271,7 @@
       <c r="W52" s="17"/>
       <c r="X52" s="18"/>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24">
       <c r="A53" s="1" t="s">
         <v>50</v>
       </c>
@@ -22306,7 +22309,7 @@
       <c r="W53" s="17"/>
       <c r="X53" s="18"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24">
       <c r="A54" s="1" t="s">
         <v>51</v>
       </c>
@@ -22331,7 +22334,7 @@
       </c>
       <c r="K54" s="46"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24">
       <c r="A55" s="1" t="s">
         <v>51</v>
       </c>
@@ -22352,10 +22355,10 @@
       </c>
       <c r="K55" s="46"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24">
       <c r="A56" s="7"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24">
       <c r="A57" s="5">
         <v>1</v>
       </c>
@@ -22369,7 +22372,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24">
       <c r="A58" s="5">
         <v>2</v>
       </c>
@@ -22383,7 +22386,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24">
       <c r="A59" s="8">
         <v>3</v>
       </c>
@@ -22398,7 +22401,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24">
       <c r="A60" s="5">
         <v>4</v>
       </c>
@@ -22406,13 +22409,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
     </row>
-    <row r="62" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" s="4" customFormat="1">
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
@@ -22425,7 +22428,7 @@
       <c r="W62" s="5"/>
       <c r="X62" s="5"/>
     </row>
-    <row r="63" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" s="4" customFormat="1">
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
@@ -22438,7 +22441,7 @@
       <c r="W63" s="5"/>
       <c r="X63" s="5"/>
     </row>
-    <row r="64" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" s="4" customFormat="1">
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
@@ -22937,7 +22940,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -22967,9 +22970,9 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -23002,7 +23005,7 @@
         <v>46318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -23035,7 +23038,7 @@
         <v>46339</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -23083,7 +23086,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -23111,7 +23114,7 @@
       <c r="W3" s="17"/>
       <c r="X3" s="18"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -23139,7 +23142,7 @@
       <c r="W4" s="17"/>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -23167,7 +23170,7 @@
       <c r="W5" s="17"/>
       <c r="X5" s="18"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -23215,7 +23218,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -23243,7 +23246,7 @@
       <c r="W7" s="17"/>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -23273,7 +23276,7 @@
       <c r="W8" s="17"/>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -23303,7 +23306,7 @@
       <c r="W9" s="17"/>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -23333,7 +23336,7 @@
       <c r="W10" s="17"/>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -23361,7 +23364,7 @@
       <c r="W11" s="17"/>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -23389,7 +23392,7 @@
       <c r="W12" s="17"/>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -23417,7 +23420,7 @@
       <c r="W13" s="17"/>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -23445,7 +23448,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -23473,7 +23476,7 @@
       <c r="W15" s="17"/>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -23501,7 +23504,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24">
       <c r="A17" s="5"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -23522,7 +23525,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -23546,9 +23549,9 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -23581,7 +23584,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -23614,7 +23617,7 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -23662,7 +23665,7 @@
       </c>
       <c r="X20" s="30"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -23690,7 +23693,7 @@
       <c r="W21" s="17"/>
       <c r="X21" s="18"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -23718,7 +23721,7 @@
       <c r="W22" s="17"/>
       <c r="X22" s="18"/>
     </row>
-    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -23746,7 +23749,7 @@
       <c r="W23" s="17"/>
       <c r="X23" s="18"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -23794,7 +23797,7 @@
       </c>
       <c r="X24" s="22"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -23822,7 +23825,7 @@
       <c r="W25" s="17"/>
       <c r="X25" s="18"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -23852,7 +23855,7 @@
       <c r="W26" s="17"/>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -23882,7 +23885,7 @@
       <c r="W27" s="17"/>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -23912,7 +23915,7 @@
       <c r="W28" s="17"/>
       <c r="X28" s="18"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -23942,7 +23945,7 @@
       <c r="W29" s="17"/>
       <c r="X29" s="18"/>
     </row>
-    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -23972,7 +23975,7 @@
       <c r="W30" s="17"/>
       <c r="X30" s="18"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -24002,7 +24005,7 @@
       <c r="W31" s="17"/>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -24032,7 +24035,7 @@
       <c r="W32" s="17"/>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -24062,7 +24065,7 @@
       <c r="W33" s="17"/>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -24092,7 +24095,7 @@
       <c r="W34" s="17"/>
       <c r="X34" s="18"/>
     </row>
-    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -24113,7 +24116,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -24128,9 +24131,9 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -24165,7 +24168,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -24198,7 +24201,7 @@
         <v>46353</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -24248,7 +24251,7 @@
       </c>
       <c r="X38" s="30"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -24278,7 +24281,7 @@
       <c r="W39" s="17"/>
       <c r="X39" s="18"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -24306,7 +24309,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -24334,7 +24337,7 @@
       <c r="W41" s="17"/>
       <c r="X41" s="18"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -24382,7 +24385,7 @@
       </c>
       <c r="X42" s="22"/>
     </row>
-    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -24410,7 +24413,7 @@
       <c r="W43" s="17"/>
       <c r="X43" s="18"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -24438,7 +24441,7 @@
       <c r="W44" s="17"/>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -24466,7 +24469,7 @@
       <c r="W45" s="17"/>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -24496,7 +24499,7 @@
       <c r="W46" s="17"/>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -24526,7 +24529,7 @@
       <c r="W47" s="17"/>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
@@ -24556,7 +24559,7 @@
       <c r="W48" s="17"/>
       <c r="X48" s="18"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -24586,7 +24589,7 @@
       <c r="W49" s="17"/>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -24614,7 +24617,7 @@
       <c r="W50" s="17"/>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -24642,7 +24645,7 @@
       <c r="W51" s="17"/>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -24670,7 +24673,7 @@
       <c r="W52" s="17"/>
       <c r="X52" s="18"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -24684,7 +24687,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -24698,7 +24701,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -24713,7 +24716,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -24721,17 +24724,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -25204,7 +25207,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:Y61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="1" style="5" customWidth="1"/>
     <col min="2" max="2" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -25234,10 +25237,10 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
+    <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -25270,7 +25273,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -25303,7 +25306,7 @@
         <v>46381</v>
       </c>
     </row>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:25">
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
@@ -25349,7 +25352,7 @@
       <c r="X3" s="53"/>
       <c r="Y3" s="54"/>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:25">
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
@@ -25379,7 +25382,7 @@
       <c r="X4" s="53"/>
       <c r="Y4" s="54"/>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:25">
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
@@ -25407,7 +25410,7 @@
       <c r="X5" s="53"/>
       <c r="Y5" s="54"/>
     </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:25">
       <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
@@ -25435,7 +25438,7 @@
       <c r="X6" s="53"/>
       <c r="Y6" s="54"/>
     </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:25">
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
@@ -25481,7 +25484,7 @@
       <c r="X7" s="53"/>
       <c r="Y7" s="54"/>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:25">
       <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
@@ -25509,7 +25512,7 @@
       <c r="X8" s="53"/>
       <c r="Y8" s="54"/>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:25">
       <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
@@ -25537,7 +25540,7 @@
       <c r="X9" s="53"/>
       <c r="Y9" s="54"/>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:25">
       <c r="B10" s="6" t="s">
         <v>32</v>
       </c>
@@ -25565,7 +25568,7 @@
       <c r="X10" s="53"/>
       <c r="Y10" s="54"/>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:25">
       <c r="B11" s="6" t="s">
         <v>35</v>
       </c>
@@ -25593,7 +25596,7 @@
       <c r="X11" s="53"/>
       <c r="Y11" s="54"/>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:25">
       <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
@@ -25621,7 +25624,7 @@
       <c r="X12" s="53"/>
       <c r="Y12" s="54"/>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:25">
       <c r="B13" s="1" t="s">
         <v>40</v>
       </c>
@@ -25649,7 +25652,7 @@
       <c r="X13" s="53"/>
       <c r="Y13" s="54"/>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:25">
       <c r="B14" s="12" t="s">
         <v>45</v>
       </c>
@@ -25677,7 +25680,7 @@
       <c r="X14" s="53"/>
       <c r="Y14" s="54"/>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:25">
       <c r="B15" s="1" t="s">
         <v>48</v>
       </c>
@@ -25705,7 +25708,7 @@
       <c r="X15" s="53"/>
       <c r="Y15" s="54"/>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:25">
       <c r="B16" s="12" t="s">
         <v>49</v>
       </c>
@@ -25733,7 +25736,7 @@
       <c r="X16" s="53"/>
       <c r="Y16" s="54"/>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:25">
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
@@ -25761,7 +25764,7 @@
       <c r="X17" s="53"/>
       <c r="Y17" s="54"/>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:25">
       <c r="B18" s="5"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -25784,7 +25787,7 @@
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:25">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -25796,9 +25799,9 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:25">
       <c r="B20" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -25831,7 +25834,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -25864,7 +25867,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:25">
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
@@ -25910,7 +25913,7 @@
       <c r="X21" s="53"/>
       <c r="Y21" s="54"/>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:25">
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
@@ -25938,7 +25941,7 @@
       <c r="X22" s="53"/>
       <c r="Y22" s="54"/>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:25">
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
@@ -25970,7 +25973,7 @@
       <c r="X23" s="53"/>
       <c r="Y23" s="54"/>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:25">
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
@@ -25998,7 +26001,7 @@
       <c r="X24" s="53"/>
       <c r="Y24" s="54"/>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:25">
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
@@ -26044,7 +26047,7 @@
       <c r="X25" s="53"/>
       <c r="Y25" s="54"/>
     </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:25">
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
@@ -26072,7 +26075,7 @@
       <c r="X26" s="53"/>
       <c r="Y26" s="54"/>
     </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:25">
       <c r="B27" s="6" t="s">
         <v>28</v>
       </c>
@@ -26102,7 +26105,7 @@
       <c r="X27" s="53"/>
       <c r="Y27" s="54"/>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:25">
       <c r="B28" s="6" t="s">
         <v>32</v>
       </c>
@@ -26136,7 +26139,7 @@
       <c r="X28" s="53"/>
       <c r="Y28" s="54"/>
     </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:25">
       <c r="B29" s="6" t="s">
         <v>35</v>
       </c>
@@ -26164,7 +26167,7 @@
       <c r="X29" s="53"/>
       <c r="Y29" s="54"/>
     </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:25">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
@@ -26194,7 +26197,7 @@
       <c r="X30" s="53"/>
       <c r="Y30" s="54"/>
     </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:25">
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
@@ -26224,7 +26227,7 @@
       <c r="X31" s="53"/>
       <c r="Y31" s="54"/>
     </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:25">
       <c r="B32" s="12" t="s">
         <v>45</v>
       </c>
@@ -26254,7 +26257,7 @@
       <c r="X32" s="53"/>
       <c r="Y32" s="54"/>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25">
       <c r="B33" s="1" t="s">
         <v>48</v>
       </c>
@@ -26284,7 +26287,7 @@
       <c r="X33" s="53"/>
       <c r="Y33" s="54"/>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25">
       <c r="B34" s="12" t="s">
         <v>49</v>
       </c>
@@ -26314,7 +26317,7 @@
       <c r="X34" s="53"/>
       <c r="Y34" s="54"/>
     </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:25">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -26344,7 +26347,7 @@
       <c r="X35" s="53"/>
       <c r="Y35" s="54"/>
     </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:25">
       <c r="B36" s="5"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -26369,7 +26372,7 @@
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25">
       <c r="B37" s="5"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -26394,9 +26397,9 @@
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25">
       <c r="B38" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>
@@ -26441,7 +26444,7 @@
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25">
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
@@ -26478,7 +26481,7 @@
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
     </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:25">
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
@@ -26505,7 +26508,7 @@
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
     </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:25">
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
@@ -26532,7 +26535,7 @@
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25">
       <c r="B42" s="1" t="s">
         <v>21</v>
       </c>
@@ -26559,7 +26562,7 @@
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25">
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
@@ -26596,7 +26599,7 @@
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25">
       <c r="B44" s="6" t="s">
         <v>26</v>
       </c>
@@ -26623,7 +26626,7 @@
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25">
       <c r="B45" s="6" t="s">
         <v>28</v>
       </c>
@@ -26650,7 +26653,7 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25">
       <c r="B46" s="6" t="s">
         <v>32</v>
       </c>
@@ -26677,7 +26680,7 @@
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25">
       <c r="B47" s="6" t="s">
         <v>35</v>
       </c>
@@ -26704,7 +26707,7 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25">
       <c r="B48" s="1" t="s">
         <v>37</v>
       </c>
@@ -26731,7 +26734,7 @@
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
     </row>
-    <row r="49" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:25">
       <c r="B49" s="1" t="s">
         <v>40</v>
       </c>
@@ -26758,7 +26761,7 @@
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
     </row>
-    <row r="50" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:25">
       <c r="B50" s="12" t="s">
         <v>45</v>
       </c>
@@ -26785,7 +26788,7 @@
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
     </row>
-    <row r="51" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:25">
       <c r="B51" s="1" t="s">
         <v>48</v>
       </c>
@@ -26812,7 +26815,7 @@
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
     </row>
-    <row r="52" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:25">
       <c r="B52" s="12" t="s">
         <v>49</v>
       </c>
@@ -26839,7 +26842,7 @@
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
     </row>
-    <row r="53" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:25">
       <c r="B53" s="1" t="s">
         <v>50</v>
       </c>
@@ -26866,7 +26869,7 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
     </row>
-    <row r="54" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:25">
       <c r="B54" s="5"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -26891,7 +26894,7 @@
       <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
     </row>
-    <row r="55" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:25">
       <c r="B55" s="5">
         <v>1</v>
       </c>
@@ -26907,7 +26910,7 @@
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:25">
       <c r="B56" s="5">
         <v>2</v>
       </c>
@@ -26921,7 +26924,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:25">
       <c r="B57" s="8">
         <v>3</v>
       </c>
@@ -26936,7 +26939,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:25">
       <c r="B58" s="5">
         <v>4</v>
       </c>
@@ -26950,7 +26953,7 @@
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:25">
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="E59" s="5"/>
@@ -26960,7 +26963,7 @@
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:25">
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="E60" s="5"/>
@@ -26970,7 +26973,7 @@
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:25">
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
     </row>
@@ -27644,45 +27647,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
-    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}"/>
 </file>
--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4484" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6A068FB-7C9E-4C21-8680-BFE429D6B9A3}"/>
+  <xr:revisionPtr revIDLastSave="4485" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7E04FCB-E4A2-411E-AC34-27E6F8D039D3}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -56,17 +56,17 @@
   <commentList>
     <comment ref="U37" authorId="0" shapeId="0" xr:uid="{65E4B43F-4DA4-4023-9E8A-D4F24A3B2C8C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     RTC SUR KURS</t>
       </text>
     </comment>
     <comment ref="W37" authorId="1" shapeId="0" xr:uid="{BC2FB818-859F-40F5-95A2-BC57CF0AD42E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     KUT SUR (RTC)?</t>
       </text>
     </comment>
@@ -794,6 +794,12 @@
     <t>Møte m/Komp</t>
   </si>
   <si>
+    <t>9 SF HF 5</t>
+  </si>
+  <si>
+    <t>SF HF 5</t>
+  </si>
+  <si>
     <t>ELPAC-kurs</t>
   </si>
   <si>
@@ -822,12 +828,6 @@
   </si>
   <si>
     <t>SF TC 3</t>
-  </si>
-  <si>
-    <t>9 SF HF 5</t>
-  </si>
-  <si>
-    <t>SF HF 5</t>
   </si>
   <si>
     <t>Uke 33</t>
@@ -903,7 +903,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1457,12 +1457,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1836,7 +1830,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="5" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -1865,7 +1859,7 @@
     <col min="28" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1938,7 +1932,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1989,7 +1983,7 @@
       </c>
       <c r="AA2" s="20"/>
     </row>
-    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2040,7 +2034,7 @@
       </c>
       <c r="AA3" s="44"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2091,7 +2085,7 @@
       </c>
       <c r="AA4" s="20"/>
     </row>
-    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -2142,7 +2136,7 @@
       </c>
       <c r="AA5" s="32"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2193,7 +2187,7 @@
       </c>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -2244,7 +2238,7 @@
       </c>
       <c r="AA7" s="28"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -2295,7 +2289,7 @@
       </c>
       <c r="AA8" s="36"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -2346,7 +2340,7 @@
       </c>
       <c r="AA9" s="32"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -2397,7 +2391,7 @@
       </c>
       <c r="AA10" s="22"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -2448,7 +2442,7 @@
       </c>
       <c r="AA11" s="44"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -2499,7 +2493,7 @@
       </c>
       <c r="AA12" s="36"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -2550,7 +2544,7 @@
       </c>
       <c r="AA13" s="36"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -2601,7 +2595,7 @@
       </c>
       <c r="AA14" s="32"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -2652,7 +2646,7 @@
       </c>
       <c r="AA15" s="20"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -2699,7 +2693,7 @@
       <c r="Z16" s="17"/>
       <c r="AA16" s="18"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2734,7 +2728,7 @@
       <c r="Z17" s="17"/>
       <c r="AA17" s="18"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2769,7 +2763,7 @@
       <c r="Z18" s="17"/>
       <c r="AA18" s="18"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -2790,7 +2784,7 @@
       </c>
       <c r="U19" s="26"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -2811,7 +2805,7 @@
       </c>
       <c r="U20" s="32"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2829,7 +2823,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2847,7 +2841,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -2920,7 +2914,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -2973,7 +2967,7 @@
       </c>
       <c r="AA24" s="22"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -3026,7 +3020,7 @@
       </c>
       <c r="AA25" s="22"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -3079,7 +3073,7 @@
       </c>
       <c r="AA26" s="32"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -3132,7 +3126,7 @@
       </c>
       <c r="AA27" s="28"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
@@ -3185,7 +3179,7 @@
       </c>
       <c r="AA28" s="18"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>26</v>
       </c>
@@ -3238,7 +3232,7 @@
       </c>
       <c r="AA29" s="46"/>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>28</v>
       </c>
@@ -3291,7 +3285,7 @@
       </c>
       <c r="AA30" s="18"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -3344,7 +3338,7 @@
       </c>
       <c r="AA31" s="28"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -3397,7 +3391,7 @@
       </c>
       <c r="AA32" s="32"/>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
@@ -3450,7 +3444,7 @@
       </c>
       <c r="AA33" s="28"/>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -3503,7 +3497,7 @@
       </c>
       <c r="AA34" s="32"/>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>45</v>
       </c>
@@ -3556,7 +3550,7 @@
       </c>
       <c r="AA35" s="36"/>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>48</v>
       </c>
@@ -3609,7 +3603,7 @@
       </c>
       <c r="AA36" s="36"/>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>49</v>
       </c>
@@ -3662,7 +3656,7 @@
       </c>
       <c r="AA37" s="36"/>
     </row>
-    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -3711,7 +3705,7 @@
       <c r="Z38" s="17"/>
       <c r="AA38" s="18"/>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -3732,7 +3726,7 @@
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -3750,7 +3744,7 @@
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>69</v>
       </c>
@@ -3823,7 +3817,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -3876,7 +3870,7 @@
       </c>
       <c r="AA42" s="30"/>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -3929,7 +3923,7 @@
       </c>
       <c r="AA43" s="18"/>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -3982,7 +3976,7 @@
       </c>
       <c r="AA44" s="38"/>
     </row>
-    <row r="45" spans="1:27" ht="15" customHeight="1">
+    <row r="45" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -4035,7 +4029,7 @@
       </c>
       <c r="AA45" s="28"/>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -4088,7 +4082,7 @@
       </c>
       <c r="AA46" s="22"/>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
@@ -4141,7 +4135,7 @@
       </c>
       <c r="AA47" s="18"/>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>28</v>
       </c>
@@ -4194,7 +4188,7 @@
       </c>
       <c r="AA48" s="28"/>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>32</v>
       </c>
@@ -4247,7 +4241,7 @@
       </c>
       <c r="AA49" s="36"/>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
@@ -4300,7 +4294,7 @@
       </c>
       <c r="AA50" s="18"/>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -4348,7 +4342,7 @@
       </c>
       <c r="AA51" s="38"/>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -4396,7 +4390,7 @@
       </c>
       <c r="AA52" s="36"/>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
@@ -4444,7 +4438,7 @@
       </c>
       <c r="AA53" s="22"/>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>48</v>
       </c>
@@ -4492,7 +4486,7 @@
       </c>
       <c r="AA54" s="36"/>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>49</v>
       </c>
@@ -4540,7 +4534,7 @@
       </c>
       <c r="AA55" s="38"/>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -4580,7 +4574,7 @@
       <c r="Z56" s="17"/>
       <c r="AA56" s="18"/>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -4594,7 +4588,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -4608,7 +4602,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -4622,7 +4616,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -5116,7 +5110,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X78"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -5145,7 +5139,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -5213,7 +5207,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -5261,7 +5255,7 @@
       </c>
       <c r="X2" s="22"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -5309,7 +5303,7 @@
       </c>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -5357,7 +5351,7 @@
       </c>
       <c r="X4" s="22"/>
     </row>
-    <row r="5" spans="1:24" ht="11.25" customHeight="1">
+    <row r="5" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5405,7 +5399,7 @@
       </c>
       <c r="X5" s="22"/>
     </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -5453,7 +5447,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -5501,7 +5495,7 @@
       </c>
       <c r="X7" s="24"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -5549,7 +5543,7 @@
       </c>
       <c r="X8" s="36"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -5597,7 +5591,7 @@
       </c>
       <c r="X9" s="22"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -5645,7 +5639,7 @@
       </c>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -5693,7 +5687,7 @@
       </c>
       <c r="X11" s="28"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -5741,7 +5735,7 @@
       </c>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -5789,7 +5783,7 @@
       </c>
       <c r="X13" s="28"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -5837,7 +5831,7 @@
       </c>
       <c r="X14" s="36"/>
     </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -5885,7 +5879,7 @@
       </c>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -5925,7 +5919,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -5949,7 +5943,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -5973,7 +5967,7 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -5997,7 +5991,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>97</v>
       </c>
@@ -6065,7 +6059,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -6113,7 +6107,7 @@
       </c>
       <c r="X21" s="68"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -6161,7 +6155,7 @@
       </c>
       <c r="X22" s="22"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -6209,7 +6203,7 @@
       </c>
       <c r="X23" s="36"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -6257,7 +6251,7 @@
       </c>
       <c r="X24" s="36"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -6305,7 +6299,7 @@
       </c>
       <c r="X25" s="22"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -6353,7 +6347,7 @@
       </c>
       <c r="X26" s="36"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
@@ -6401,7 +6395,7 @@
       </c>
       <c r="X27" s="28"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>32</v>
       </c>
@@ -6449,7 +6443,7 @@
       </c>
       <c r="X28" s="34"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>35</v>
       </c>
@@ -6497,7 +6491,7 @@
       </c>
       <c r="X29" s="26"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -6547,7 +6541,7 @@
       </c>
       <c r="X30" s="34"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -6597,7 +6591,7 @@
       </c>
       <c r="X31" s="28"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>45</v>
       </c>
@@ -6647,7 +6641,7 @@
       </c>
       <c r="X32" s="26"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -6697,7 +6691,7 @@
       </c>
       <c r="X33" s="26"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>49</v>
       </c>
@@ -6747,7 +6741,7 @@
       </c>
       <c r="X34" s="34"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -6787,7 +6781,7 @@
       </c>
       <c r="X35" s="26"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -6822,7 +6816,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -6845,7 +6839,7 @@
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -6868,12 +6862,12 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="M39" s="7"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>109</v>
       </c>
@@ -6942,7 +6936,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -6991,7 +6985,7 @@
       </c>
       <c r="X41" s="22"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -7039,7 +7033,7 @@
       </c>
       <c r="X42" s="22"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -7087,7 +7081,7 @@
       </c>
       <c r="X43" s="22"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -7135,7 +7129,7 @@
       </c>
       <c r="X44" s="44"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -7183,7 +7177,7 @@
       </c>
       <c r="X45" s="22"/>
     </row>
-    <row r="46" spans="1:24" ht="10.5" customHeight="1">
+    <row r="46" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -7232,7 +7226,7 @@
       </c>
       <c r="X46" s="36"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -7281,7 +7275,7 @@
       </c>
       <c r="X47" s="36"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -7330,7 +7324,7 @@
       </c>
       <c r="X48" s="26"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -7379,7 +7373,7 @@
       </c>
       <c r="X49" s="44"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -7428,7 +7422,7 @@
       </c>
       <c r="X50" s="26"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -7476,7 +7470,7 @@
       </c>
       <c r="X51" s="28"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -7524,7 +7518,7 @@
       </c>
       <c r="X52" s="36"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -7572,7 +7566,7 @@
       </c>
       <c r="X53" s="28"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -7621,7 +7615,7 @@
       </c>
       <c r="X54" s="28"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -7664,7 +7658,7 @@
       </c>
       <c r="X55" s="26"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
@@ -7701,7 +7695,7 @@
       <c r="W56" s="9"/>
       <c r="X56" s="9"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -7726,7 +7720,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -7740,7 +7734,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -7754,7 +7748,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -7774,7 +7768,7 @@
       <c r="W60" s="9"/>
       <c r="X60" s="9"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -7786,34 +7780,34 @@
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="R62" s="9"/>
     </row>
-    <row r="71" spans="13:13">
+    <row r="71" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="13:13">
+    <row r="72" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M72" s="5"/>
     </row>
-    <row r="73" spans="13:13">
+    <row r="73" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M73" s="5"/>
     </row>
-    <row r="74" spans="13:13">
+    <row r="74" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M74" s="5"/>
     </row>
-    <row r="75" spans="13:13">
+    <row r="75" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M75" s="5"/>
     </row>
-    <row r="76" spans="13:13">
+    <row r="76" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="13:13">
+    <row r="77" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M77" s="5"/>
     </row>
-    <row r="78" spans="13:13">
+    <row r="78" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M78" s="5"/>
     </row>
   </sheetData>
@@ -8297,7 +8291,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X66"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -8327,7 +8321,7 @@
     <col min="27" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
@@ -8395,7 +8389,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -8443,7 +8437,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -8491,7 +8485,7 @@
       </c>
       <c r="X3" s="64"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -8539,7 +8533,7 @@
       </c>
       <c r="X4" s="28"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -8587,7 +8581,7 @@
       </c>
       <c r="X5" s="64"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -8635,7 +8629,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -8683,7 +8677,7 @@
       </c>
       <c r="X7" s="28"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -8731,7 +8725,7 @@
       </c>
       <c r="X8" s="34"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -8779,7 +8773,7 @@
       </c>
       <c r="X9" s="28"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -8827,7 +8821,7 @@
       </c>
       <c r="X10" s="34"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -8875,7 +8869,7 @@
       </c>
       <c r="X11" s="28"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -8923,7 +8917,7 @@
       </c>
       <c r="X12" s="28"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -8971,7 +8965,7 @@
       </c>
       <c r="X13" s="28"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -9019,7 +9013,7 @@
       </c>
       <c r="X14" s="64"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -9067,7 +9061,7 @@
       </c>
       <c r="X15" s="64"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -9107,7 +9101,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="7"/>
@@ -9120,7 +9114,7 @@
       </c>
       <c r="V17" s="28"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="7"/>
@@ -9129,7 +9123,7 @@
       </c>
       <c r="P18" s="28"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="7"/>
@@ -9138,7 +9132,7 @@
       </c>
       <c r="P19" s="64"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="7"/>
@@ -9147,7 +9141,7 @@
       </c>
       <c r="P20" s="64"/>
     </row>
-    <row r="21" spans="1:24" ht="11.25" customHeight="1">
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="7"/>
@@ -9156,7 +9150,7 @@
       </c>
       <c r="P21" s="64"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="7"/>
@@ -9165,17 +9159,17 @@
       </c>
       <c r="P22" s="64"/>
     </row>
-    <row r="23" spans="1:24" ht="11.25" customHeight="1">
+    <row r="23" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:24" ht="11.25" customHeight="1">
+    <row r="24" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>154</v>
       </c>
@@ -9245,7 +9239,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -9291,7 +9285,7 @@
       </c>
       <c r="X26" s="22"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -9337,7 +9331,7 @@
       </c>
       <c r="X27" s="20"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -9383,7 +9377,7 @@
       </c>
       <c r="X28" s="70"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -9429,7 +9423,7 @@
       </c>
       <c r="X29" s="36"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -9475,7 +9469,7 @@
       </c>
       <c r="X30" s="22"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
@@ -9521,7 +9515,7 @@
       </c>
       <c r="X31" s="36"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>28</v>
       </c>
@@ -9567,7 +9561,7 @@
       </c>
       <c r="X32" s="70"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
@@ -9609,7 +9603,7 @@
       </c>
       <c r="X33" s="32"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -9655,7 +9649,7 @@
       </c>
       <c r="X34" s="22"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -9701,7 +9695,7 @@
       </c>
       <c r="X35" s="28"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
@@ -9747,7 +9741,7 @@
       </c>
       <c r="X36" s="32"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>45</v>
       </c>
@@ -9793,7 +9787,7 @@
       </c>
       <c r="X37" s="28"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
@@ -9839,7 +9833,7 @@
       </c>
       <c r="X38" s="36"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>49</v>
       </c>
@@ -9885,7 +9879,7 @@
       </c>
       <c r="X39" s="32"/>
     </row>
-    <row r="40" spans="1:24" ht="11.25" customHeight="1">
+    <row r="40" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
@@ -9927,7 +9921,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24" ht="11.25" customHeight="1">
+    <row r="41" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -9942,7 +9936,7 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="11.25" customHeight="1">
+    <row r="42" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -9957,7 +9951,7 @@
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="11.25" customHeight="1">
+    <row r="43" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>166</v>
       </c>
@@ -10027,7 +10021,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="11.25" customHeight="1">
+    <row r="44" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -10073,7 +10067,7 @@
       <c r="W44" s="53"/>
       <c r="X44" s="54"/>
     </row>
-    <row r="45" spans="1:24" ht="11.25" customHeight="1">
+    <row r="45" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -10119,7 +10113,7 @@
       <c r="W45" s="53"/>
       <c r="X45" s="54"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -10165,7 +10159,7 @@
       <c r="W46" s="53"/>
       <c r="X46" s="54"/>
     </row>
-    <row r="47" spans="1:24" ht="11.25" customHeight="1">
+    <row r="47" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -10209,7 +10203,7 @@
       <c r="W47" s="53"/>
       <c r="X47" s="54"/>
     </row>
-    <row r="48" spans="1:24" ht="11.25" customHeight="1">
+    <row r="48" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
@@ -10253,7 +10247,7 @@
       <c r="W48" s="53"/>
       <c r="X48" s="54"/>
     </row>
-    <row r="49" spans="1:24" ht="11.25" customHeight="1">
+    <row r="49" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>26</v>
       </c>
@@ -10297,7 +10291,7 @@
       <c r="W49" s="53"/>
       <c r="X49" s="54"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>28</v>
       </c>
@@ -10341,7 +10335,7 @@
       <c r="W50" s="53"/>
       <c r="X50" s="54"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>32</v>
       </c>
@@ -10387,7 +10381,7 @@
       <c r="W51" s="53"/>
       <c r="X51" s="54"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>35</v>
       </c>
@@ -10433,7 +10427,7 @@
       <c r="W52" s="53"/>
       <c r="X52" s="54"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>37</v>
       </c>
@@ -10479,7 +10473,7 @@
       <c r="W53" s="53"/>
       <c r="X53" s="54"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>40</v>
       </c>
@@ -10525,7 +10519,7 @@
       <c r="W54" s="53"/>
       <c r="X54" s="54"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>45</v>
       </c>
@@ -10571,7 +10565,7 @@
       <c r="W55" s="53"/>
       <c r="X55" s="54"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>48</v>
       </c>
@@ -10617,7 +10611,7 @@
       <c r="W56" s="53"/>
       <c r="X56" s="54"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>49</v>
       </c>
@@ -10663,7 +10657,7 @@
       <c r="W57" s="53"/>
       <c r="X57" s="54"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>50</v>
       </c>
@@ -10703,7 +10697,7 @@
       <c r="W58" s="53"/>
       <c r="X58" s="54"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="O59" s="43" t="s">
@@ -10719,7 +10713,7 @@
       </c>
       <c r="T59" s="44"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -10737,7 +10731,7 @@
       </c>
       <c r="P60" s="36"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -10751,7 +10745,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>3</v>
       </c>
@@ -10765,7 +10759,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>4</v>
       </c>
@@ -10773,17 +10767,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -11271,7 +11265,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X62"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -11300,7 +11294,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>178</v>
       </c>
@@ -11368,7 +11362,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -11414,7 +11408,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -11460,7 +11454,7 @@
       </c>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -11506,7 +11500,7 @@
       </c>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -11553,7 +11547,7 @@
       </c>
       <c r="X5" s="44"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -11599,7 +11593,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -11645,7 +11639,7 @@
       </c>
       <c r="X7" s="70"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -11691,7 +11685,7 @@
       </c>
       <c r="X8" s="70"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -11737,7 +11731,7 @@
       </c>
       <c r="X9" s="88"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -11783,7 +11777,7 @@
       </c>
       <c r="X10" s="34"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -11829,7 +11823,7 @@
       </c>
       <c r="X11" s="44"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -11875,7 +11869,7 @@
       </c>
       <c r="X12" s="34"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -11921,7 +11915,7 @@
       </c>
       <c r="X13" s="88"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -11967,7 +11961,7 @@
       </c>
       <c r="X14" s="34"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -12013,7 +12007,7 @@
       </c>
       <c r="X15" s="44"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -12053,7 +12047,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>195</v>
       </c>
@@ -12080,7 +12074,7 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B18" s="27" t="s">
         <v>196</v>
       </c>
@@ -12092,7 +12086,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -12101,7 +12095,7 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -12112,7 +12106,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>197</v>
       </c>
@@ -12180,7 +12174,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -12226,7 +12220,7 @@
       </c>
       <c r="X22" s="30"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -12272,7 +12266,7 @@
       </c>
       <c r="X23" s="20"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -12318,7 +12312,7 @@
       </c>
       <c r="X24" s="18"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -12364,7 +12358,7 @@
       </c>
       <c r="X25" s="88"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -12410,7 +12404,7 @@
       </c>
       <c r="X26" s="22"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -12456,7 +12450,7 @@
       </c>
       <c r="X27" s="34"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -12502,7 +12496,7 @@
       </c>
       <c r="X28" s="88"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -12548,7 +12542,7 @@
       </c>
       <c r="X29" s="22"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -12594,7 +12588,7 @@
       </c>
       <c r="X30" s="22"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -12640,7 +12634,7 @@
       </c>
       <c r="X31" s="44"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -12688,7 +12682,7 @@
       </c>
       <c r="X32" s="28"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -12736,7 +12730,7 @@
       </c>
       <c r="X33" s="34"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -12784,7 +12778,7 @@
       </c>
       <c r="X34" s="44"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -12832,7 +12826,7 @@
       </c>
       <c r="X35" s="34"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -12874,7 +12868,7 @@
       </c>
       <c r="X36" s="44"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="4"/>
@@ -12882,7 +12876,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="4"/>
@@ -12890,7 +12884,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="4"/>
@@ -12898,7 +12892,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>212</v>
       </c>
@@ -12968,7 +12962,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -13018,7 +13012,7 @@
       </c>
       <c r="X41" s="30"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -13068,7 +13062,7 @@
       </c>
       <c r="X42" s="18"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -13118,7 +13112,7 @@
       </c>
       <c r="X43" s="18"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -13166,7 +13160,7 @@
       </c>
       <c r="X44" s="32"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -13214,7 +13208,7 @@
       </c>
       <c r="X45" s="22"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -13262,7 +13256,7 @@
       </c>
       <c r="X46" s="22"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -13310,7 +13304,7 @@
       </c>
       <c r="X47" s="40"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -13358,7 +13352,7 @@
       </c>
       <c r="X48" s="20"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -13406,7 +13400,7 @@
       </c>
       <c r="X49" s="22"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -13454,7 +13448,7 @@
       </c>
       <c r="X50" s="22"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -13504,7 +13498,7 @@
       </c>
       <c r="X51" s="22"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -13554,7 +13548,7 @@
       </c>
       <c r="X52" s="32"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -13604,7 +13598,7 @@
       </c>
       <c r="X53" s="32"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -13652,7 +13646,7 @@
       </c>
       <c r="X54" s="20"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -13694,7 +13688,7 @@
       <c r="W55" s="17"/>
       <c r="X55" s="18"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -13724,7 +13718,7 @@
       <c r="W56" s="17"/>
       <c r="X56" s="18"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="8"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -13749,7 +13743,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="8"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -13762,7 +13756,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>1</v>
       </c>
@@ -13787,7 +13781,7 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>2</v>
       </c>
@@ -13801,7 +13795,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>3</v>
       </c>
@@ -13815,7 +13809,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>4</v>
       </c>
@@ -14307,7 +14301,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -14336,7 +14330,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
@@ -14404,7 +14398,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -14452,7 +14446,7 @@
       </c>
       <c r="X2" s="20"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -14500,7 +14494,7 @@
       </c>
       <c r="X3" s="20"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -14548,7 +14542,7 @@
       </c>
       <c r="X4" s="24"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -14596,7 +14590,7 @@
       </c>
       <c r="X5" s="20"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -14644,7 +14638,7 @@
       </c>
       <c r="X6" s="24"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -14692,7 +14686,7 @@
       </c>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -14740,7 +14734,7 @@
       </c>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -14788,7 +14782,7 @@
       </c>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -14836,7 +14830,7 @@
       </c>
       <c r="X10" s="20"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -14884,7 +14878,7 @@
       </c>
       <c r="X11" s="20"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -14932,7 +14926,7 @@
       </c>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -14980,7 +14974,7 @@
       </c>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -15028,7 +15022,7 @@
       </c>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -15076,7 +15070,7 @@
       </c>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -15120,9 +15114,9 @@
       </c>
       <c r="X16" s="20"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -15190,7 +15184,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -15238,7 +15232,7 @@
       </c>
       <c r="X20" s="20"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -15286,7 +15280,7 @@
       </c>
       <c r="X21" s="20"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -15334,7 +15328,7 @@
       </c>
       <c r="X22" s="20"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -15382,7 +15376,7 @@
       </c>
       <c r="X23" s="20"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -15430,7 +15424,7 @@
       </c>
       <c r="X24" s="20"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -15478,7 +15472,7 @@
       </c>
       <c r="X25" s="20"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -15526,7 +15520,7 @@
       </c>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -15574,7 +15568,7 @@
       </c>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -15622,14 +15616,14 @@
       </c>
       <c r="X28" s="20"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="92" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="93"/>
+      <c r="B29" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="20"/>
       <c r="D29" s="17" t="s">
         <v>9</v>
       </c>
@@ -15672,7 +15666,7 @@
       </c>
       <c r="X29" s="20"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -15722,7 +15716,7 @@
       </c>
       <c r="X30" s="20"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -15772,7 +15766,7 @@
       </c>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -15822,7 +15816,7 @@
       </c>
       <c r="X32" s="20"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -15872,7 +15866,7 @@
       </c>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -15922,7 +15916,7 @@
       </c>
       <c r="X34" s="20"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -15947,11 +15941,11 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" ht="11.25" customHeight="1">
+    <row r="36" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24" ht="11.25" customHeight="1">
+    <row r="37" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>236</v>
       </c>
@@ -16021,7 +16015,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="11.25" customHeight="1">
+    <row r="38" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -16071,7 +16065,7 @@
       </c>
       <c r="X38" s="20"/>
     </row>
-    <row r="39" spans="1:24" ht="10.5" customHeight="1">
+    <row r="39" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -16121,7 +16115,7 @@
       </c>
       <c r="X39" s="20"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -16171,7 +16165,7 @@
       </c>
       <c r="X40" s="20"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -16219,7 +16213,7 @@
       </c>
       <c r="X41" s="20"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -16267,7 +16261,7 @@
       </c>
       <c r="X42" s="20"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -16315,7 +16309,7 @@
       </c>
       <c r="X43" s="20"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -16363,7 +16357,7 @@
       </c>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -16411,7 +16405,7 @@
       </c>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -16459,7 +16453,7 @@
       </c>
       <c r="X46" s="20"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -16507,28 +16501,28 @@
       </c>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G48" s="22"/>
       <c r="H48" s="21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I48" s="22"/>
       <c r="J48" s="21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K48" s="22"/>
       <c r="N48" s="1" t="s">
@@ -16555,7 +16549,7 @@
       </c>
       <c r="X48" s="20"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -16603,7 +16597,7 @@
       </c>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -16651,7 +16645,7 @@
       </c>
       <c r="X50" s="20"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -16699,7 +16693,7 @@
       </c>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -16747,7 +16741,7 @@
       </c>
       <c r="X52" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -16761,7 +16755,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -16777,7 +16771,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -16793,7 +16787,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -16803,15 +16797,15 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -16823,6 +16817,7 @@
       <c r="M61" s="7"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="+6jSgkkNiV+maZO3pBI4WGSqZKCRQCO7p4X5phxaruOPfji6sgoP8KcuJxr3RNQI17lvKA3+P6ehAED8O79olg==" saltValue="WeXAg8bY3G1sxKWiqVwdzQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="450">
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H7:I7"/>
@@ -17293,7 +17288,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -17322,9 +17317,9 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -17357,7 +17352,7 @@
         <v>46234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -17390,7 +17385,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -17438,7 +17433,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -17484,7 +17479,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -17530,7 +17525,7 @@
       </c>
       <c r="X4" s="22"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -17566,7 +17561,7 @@
       </c>
       <c r="X5" s="36"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -17614,7 +17609,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -17648,17 +17643,17 @@
       <c r="Q7" s="77"/>
       <c r="R7" s="78"/>
       <c r="S7" s="27" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T7" s="28"/>
       <c r="U7" s="27" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="V7" s="28"/>
       <c r="W7" s="17"/>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -17696,7 +17691,7 @@
       <c r="W8" s="17"/>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -17734,7 +17729,7 @@
       </c>
       <c r="X9" s="20"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -17780,7 +17775,7 @@
       </c>
       <c r="X10" s="22"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -17826,7 +17821,7 @@
       </c>
       <c r="X11" s="22"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -17868,7 +17863,7 @@
       </c>
       <c r="X12" s="20"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -17916,7 +17911,7 @@
       </c>
       <c r="X13" s="20"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -17948,7 +17943,7 @@
       <c r="Q14" s="17"/>
       <c r="R14" s="18"/>
       <c r="S14" s="21" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T14" s="22"/>
       <c r="U14" s="17"/>
@@ -17956,7 +17951,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -17994,7 +17989,7 @@
       </c>
       <c r="X15" s="20"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -18032,7 +18027,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -18054,13 +18049,13 @@
       <c r="S17" s="17"/>
       <c r="T17" s="18"/>
       <c r="U17" s="45" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="V17" s="46"/>
       <c r="W17" s="17"/>
       <c r="X17" s="18"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -18082,13 +18077,13 @@
       <c r="S18" s="17"/>
       <c r="T18" s="18"/>
       <c r="U18" s="45" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="V18" s="46"/>
       <c r="W18" s="17"/>
       <c r="X18" s="18"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -18112,7 +18107,7 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -18136,9 +18131,9 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -18171,7 +18166,7 @@
         <v>46241</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>1</v>
@@ -18204,7 +18199,7 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -18252,7 +18247,7 @@
       </c>
       <c r="X22" s="30"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -18278,11 +18273,11 @@
       </c>
       <c r="R23" s="36"/>
       <c r="S23" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="T23" s="64"/>
       <c r="U23" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="V23" s="64"/>
       <c r="W23" s="35" t="s">
@@ -18290,7 +18285,7 @@
       </c>
       <c r="X23" s="36"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -18330,7 +18325,7 @@
       </c>
       <c r="T24" s="22"/>
       <c r="U24" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="V24" s="64"/>
       <c r="W24" s="35" t="s">
@@ -18338,22 +18333,22 @@
       </c>
       <c r="X24" s="36"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="96" t="s">
+      <c r="B25" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="97"/>
-      <c r="D25" s="96" t="s">
+      <c r="C25" s="34"/>
+      <c r="D25" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="E25" s="97"/>
-      <c r="F25" s="96" t="s">
+      <c r="E25" s="34"/>
+      <c r="F25" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="G25" s="97"/>
+      <c r="G25" s="34"/>
       <c r="H25" s="17"/>
       <c r="I25" s="18"/>
       <c r="J25" s="17"/>
@@ -18362,25 +18357,25 @@
         <v>21</v>
       </c>
       <c r="O25" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P25" s="34"/>
       <c r="Q25" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R25" s="34"/>
       <c r="S25" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T25" s="34"/>
       <c r="U25" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="V25" s="34"/>
       <c r="W25" s="17"/>
       <c r="X25" s="18"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -18428,53 +18423,53 @@
       </c>
       <c r="X26" s="93"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="96" t="s">
+      <c r="B27" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="97"/>
-      <c r="D27" s="96" t="s">
+      <c r="C27" s="34"/>
+      <c r="D27" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="E27" s="97"/>
-      <c r="F27" s="96" t="s">
+      <c r="E27" s="34"/>
+      <c r="F27" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="G27" s="97"/>
+      <c r="G27" s="34"/>
       <c r="H27" s="61"/>
       <c r="I27" s="62"/>
       <c r="J27" s="21" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="K27" s="22"/>
       <c r="N27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O27" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P27" s="34"/>
       <c r="Q27" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R27" s="34"/>
       <c r="S27" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T27" s="34"/>
       <c r="U27" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="V27" s="34"/>
       <c r="W27" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="X27" s="64"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -18504,21 +18499,21 @@
       <c r="O28" s="61"/>
       <c r="P28" s="62"/>
       <c r="Q28" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R28" s="34"/>
       <c r="S28" s="61"/>
       <c r="T28" s="62"/>
       <c r="U28" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="V28" s="34"/>
       <c r="W28" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="X28" s="64"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -18564,26 +18559,26 @@
       </c>
       <c r="X29" s="20"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="97"/>
-      <c r="D30" s="96" t="s">
+      <c r="C30" s="34"/>
+      <c r="D30" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="97"/>
-      <c r="F30" s="96" t="s">
+      <c r="E30" s="34"/>
+      <c r="F30" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="G30" s="97"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="17"/>
       <c r="I30" s="18"/>
       <c r="J30" s="21" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="K30" s="22"/>
       <c r="N30" s="6" t="s">
@@ -18610,7 +18605,7 @@
       </c>
       <c r="X30" s="22"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -18658,7 +18653,7 @@
       </c>
       <c r="X31" s="22"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -18702,7 +18697,7 @@
       </c>
       <c r="X32" s="26"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -18736,7 +18731,7 @@
       </c>
       <c r="R33" s="36"/>
       <c r="S33" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="T33" s="64"/>
       <c r="U33" s="25" t="s">
@@ -18748,7 +18743,7 @@
       </c>
       <c r="X33" s="26"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -18790,7 +18785,7 @@
       </c>
       <c r="X34" s="26"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -18838,7 +18833,7 @@
       </c>
       <c r="X35" s="20"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -18868,15 +18863,15 @@
       <c r="W36" s="17"/>
       <c r="X36" s="18"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>251</v>
       </c>
@@ -18946,7 +18941,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -18996,7 +18991,7 @@
       </c>
       <c r="X40" s="38"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>10</v>
       </c>
@@ -19028,7 +19023,7 @@
       </c>
       <c r="R41" s="36"/>
       <c r="S41" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T41" s="34"/>
       <c r="U41" s="35" t="s">
@@ -19040,7 +19035,7 @@
       </c>
       <c r="X41" s="36"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -19070,7 +19065,7 @@
       </c>
       <c r="R42" s="22"/>
       <c r="S42" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T42" s="34"/>
       <c r="U42" s="21" t="s">
@@ -19082,7 +19077,7 @@
       </c>
       <c r="X42" s="36"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
@@ -19104,7 +19099,7 @@
       </c>
       <c r="P43" s="28"/>
       <c r="Q43" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R43" s="34"/>
       <c r="S43" s="25" t="s">
@@ -19112,15 +19107,15 @@
       </c>
       <c r="T43" s="26"/>
       <c r="U43" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="V43" s="34"/>
       <c r="W43" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="X43" s="34"/>
     </row>
-    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
@@ -19168,7 +19163,7 @@
       </c>
       <c r="X44" s="22"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>26</v>
       </c>
@@ -19200,7 +19195,7 @@
       </c>
       <c r="P45" s="28"/>
       <c r="Q45" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R45" s="34"/>
       <c r="S45" s="25" t="s">
@@ -19208,15 +19203,15 @@
       </c>
       <c r="T45" s="26"/>
       <c r="U45" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="V45" s="34"/>
       <c r="W45" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="X45" s="34"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>28</v>
       </c>
@@ -19250,7 +19245,7 @@
       </c>
       <c r="P46" s="28"/>
       <c r="Q46" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R46" s="34"/>
       <c r="S46" s="25" t="s">
@@ -19258,7 +19253,7 @@
       </c>
       <c r="T46" s="26"/>
       <c r="U46" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="V46" s="34"/>
       <c r="W46" s="25" t="s">
@@ -19266,16 +19261,16 @@
       </c>
       <c r="X46" s="26"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C47" s="22"/>
       <c r="D47" s="21" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="17"/>
@@ -19310,16 +19305,16 @@
       </c>
       <c r="X47" s="46"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="21" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="17"/>
@@ -19327,7 +19322,7 @@
       <c r="H48" s="17"/>
       <c r="I48" s="18"/>
       <c r="J48" s="21" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K48" s="22"/>
       <c r="N48" s="6" t="s">
@@ -19338,15 +19333,15 @@
       </c>
       <c r="P48" s="28"/>
       <c r="Q48" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="R48" s="64"/>
       <c r="S48" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="T48" s="64"/>
       <c r="U48" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="V48" s="64"/>
       <c r="W48" s="25" t="s">
@@ -19354,7 +19349,7 @@
       </c>
       <c r="X48" s="26"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
@@ -19363,7 +19358,7 @@
       <c r="D49" s="17"/>
       <c r="E49" s="18"/>
       <c r="F49" s="21" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G49" s="22"/>
       <c r="H49" s="17"/>
@@ -19378,15 +19373,15 @@
       </c>
       <c r="P49" s="28"/>
       <c r="Q49" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="R49" s="64"/>
       <c r="S49" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="T49" s="64"/>
       <c r="U49" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="V49" s="64"/>
       <c r="W49" s="25" t="s">
@@ -19394,7 +19389,7 @@
       </c>
       <c r="X49" s="26"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>40</v>
       </c>
@@ -19428,11 +19423,11 @@
       <c r="U50" s="17"/>
       <c r="V50" s="18"/>
       <c r="W50" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="X50" s="64"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>45</v>
       </c>
@@ -19472,11 +19467,11 @@
       <c r="U51" s="17"/>
       <c r="V51" s="18"/>
       <c r="W51" s="63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="X51" s="64"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
@@ -19516,7 +19511,7 @@
       </c>
       <c r="X52" s="28"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>49</v>
       </c>
@@ -19552,7 +19547,7 @@
       <c r="W53" s="17"/>
       <c r="X53" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
@@ -19584,7 +19579,7 @@
       <c r="W54" s="17"/>
       <c r="X54" s="18"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -19620,7 +19615,7 @@
       </c>
       <c r="X55" s="46"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -19648,7 +19643,7 @@
       <c r="W56" s="17"/>
       <c r="X56" s="18"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -19671,7 +19666,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -19685,7 +19680,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -19699,7 +19694,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -19713,7 +19708,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -19721,22 +19716,22 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="8"/>
     </row>
   </sheetData>
@@ -20230,7 +20225,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X64"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -20259,7 +20254,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>256</v>
       </c>
@@ -20327,7 +20322,7 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -20375,7 +20370,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -20384,7 +20379,7 @@
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="35" t="s">
@@ -20392,7 +20387,7 @@
       </c>
       <c r="G3" s="36"/>
       <c r="H3" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I3" s="34"/>
       <c r="J3" s="35" t="s">
@@ -20419,7 +20414,7 @@
       <c r="W3" s="17"/>
       <c r="X3" s="18"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -20428,7 +20423,7 @@
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="35" t="s">
@@ -20436,7 +20431,7 @@
       </c>
       <c r="G4" s="36"/>
       <c r="H4" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I4" s="34"/>
       <c r="J4" s="17"/>
@@ -20455,24 +20450,24 @@
       <c r="W4" s="17"/>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="61"/>
       <c r="E5" s="62"/>
       <c r="F5" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G5" s="34"/>
       <c r="H5" s="17"/>
       <c r="I5" s="18"/>
       <c r="J5" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K5" s="34"/>
       <c r="N5" s="1" t="s">
@@ -20489,7 +20484,7 @@
       <c r="W5" s="17"/>
       <c r="X5" s="18"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -20537,24 +20532,24 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="17"/>
       <c r="E7" s="18"/>
       <c r="F7" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G7" s="34"/>
       <c r="H7" s="77"/>
       <c r="I7" s="78"/>
       <c r="J7" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K7" s="34"/>
       <c r="N7" s="6" t="s">
@@ -20571,24 +20566,24 @@
       <c r="W7" s="17"/>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="61"/>
       <c r="E8" s="62"/>
       <c r="F8" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G8" s="34"/>
       <c r="H8" s="17"/>
       <c r="I8" s="18"/>
       <c r="J8" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K8" s="34"/>
       <c r="N8" s="6" t="s">
@@ -20605,7 +20600,7 @@
       <c r="W8" s="17"/>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -20637,7 +20632,7 @@
       <c r="W9" s="17"/>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -20675,7 +20670,7 @@
       <c r="W10" s="17"/>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24" ht="11.25" customHeight="1">
+    <row r="11" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -20707,7 +20702,7 @@
       <c r="W11" s="17"/>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24" ht="11.25" customHeight="1">
+    <row r="12" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -20745,7 +20740,7 @@
       <c r="W12" s="17"/>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24" ht="11.25" customHeight="1">
+    <row r="13" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -20773,7 +20768,7 @@
       <c r="W13" s="17"/>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" ht="11.25" customHeight="1">
+    <row r="14" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -20801,7 +20796,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24" ht="11.25" customHeight="1">
+    <row r="15" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -20829,7 +20824,7 @@
       <c r="W15" s="17"/>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -20863,7 +20858,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -20876,7 +20871,7 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -20889,7 +20884,7 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>259</v>
       </c>
@@ -20957,7 +20952,7 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -21005,7 +21000,7 @@
       </c>
       <c r="X20" s="30"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -21043,7 +21038,7 @@
       <c r="W21" s="17"/>
       <c r="X21" s="18"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -21091,7 +21086,7 @@
       </c>
       <c r="X22" s="20"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -21100,7 +21095,7 @@
       </c>
       <c r="C23" s="36"/>
       <c r="D23" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E23" s="34"/>
       <c r="F23" s="35" t="s">
@@ -21129,7 +21124,7 @@
       <c r="W23" s="17"/>
       <c r="X23" s="18"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -21177,7 +21172,7 @@
       </c>
       <c r="X24" s="22"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -21186,7 +21181,7 @@
       </c>
       <c r="C25" s="36"/>
       <c r="D25" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="35" t="s">
@@ -21225,20 +21220,20 @@
       </c>
       <c r="X25" s="20"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C26" s="34"/>
       <c r="D26" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E26" s="34"/>
       <c r="F26" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G26" s="34"/>
       <c r="H26" s="69" t="s">
@@ -21263,12 +21258,12 @@
       <c r="W26" s="17"/>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C27" s="34"/>
       <c r="D27" s="25" t="s">
@@ -21276,7 +21271,7 @@
       </c>
       <c r="E27" s="26"/>
       <c r="F27" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G27" s="34"/>
       <c r="H27" s="35" t="s">
@@ -21301,7 +21296,7 @@
       <c r="W27" s="17"/>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -21318,7 +21313,7 @@
       </c>
       <c r="G28" s="22"/>
       <c r="H28" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="21" t="s">
@@ -21339,7 +21334,7 @@
       <c r="W28" s="17"/>
       <c r="X28" s="18"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -21352,7 +21347,7 @@
       </c>
       <c r="G29" s="26"/>
       <c r="H29" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I29" s="34"/>
       <c r="J29" s="25" t="s">
@@ -21375,7 +21370,7 @@
       <c r="W29" s="17"/>
       <c r="X29" s="18"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -21392,7 +21387,7 @@
       </c>
       <c r="G30" s="22"/>
       <c r="H30" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I30" s="34"/>
       <c r="J30" s="21" t="s">
@@ -21415,7 +21410,7 @@
       <c r="W30" s="17"/>
       <c r="X30" s="18"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -21449,7 +21444,7 @@
       <c r="W31" s="17"/>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -21483,7 +21478,7 @@
       <c r="W32" s="17"/>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="33" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -21523,7 +21518,7 @@
       <c r="W33" s="17"/>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -21563,7 +21558,7 @@
       <c r="W34" s="17"/>
       <c r="X34" s="18"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
@@ -21600,7 +21595,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -21625,7 +21620,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -21651,7 +21646,7 @@
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>261</v>
       </c>
@@ -21721,7 +21716,7 @@
         <v>46311</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -21771,7 +21766,7 @@
       </c>
       <c r="X39" s="30"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>10</v>
       </c>
@@ -21809,7 +21804,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
@@ -21849,7 +21844,7 @@
       <c r="W41" s="17"/>
       <c r="X41" s="18"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -21862,7 +21857,7 @@
       </c>
       <c r="E42" s="36"/>
       <c r="F42" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G42" s="34"/>
       <c r="H42" s="43" t="s">
@@ -21889,7 +21884,7 @@
       <c r="W42" s="17"/>
       <c r="X42" s="18"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>24</v>
       </c>
@@ -21906,7 +21901,7 @@
       </c>
       <c r="G43" s="22"/>
       <c r="H43" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I43" s="34"/>
       <c r="J43" s="21" t="s">
@@ -21937,7 +21932,7 @@
       </c>
       <c r="X43" s="22"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>26</v>
       </c>
@@ -21973,7 +21968,7 @@
       <c r="W44" s="17"/>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>28</v>
       </c>
@@ -22009,7 +22004,7 @@
       <c r="W45" s="17"/>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>32</v>
       </c>
@@ -22022,7 +22017,7 @@
       </c>
       <c r="E46" s="36"/>
       <c r="F46" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G46" s="34"/>
       <c r="H46" s="35" t="s">
@@ -22047,16 +22042,16 @@
       <c r="W46" s="17"/>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C47" s="34"/>
       <c r="D47" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E47" s="34"/>
       <c r="F47" s="21" t="s">
@@ -22085,16 +22080,16 @@
       <c r="W47" s="17"/>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C48" s="34"/>
       <c r="D48" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E48" s="34"/>
       <c r="F48" s="25" t="s">
@@ -22123,7 +22118,7 @@
       <c r="W48" s="17"/>
       <c r="X48" s="18"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>40</v>
       </c>
@@ -22132,7 +22127,7 @@
       </c>
       <c r="C49" s="26"/>
       <c r="D49" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E49" s="34"/>
       <c r="F49" s="21" t="s">
@@ -22161,7 +22156,7 @@
       <c r="W49" s="17"/>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>45</v>
       </c>
@@ -22178,7 +22173,7 @@
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I50" s="34"/>
       <c r="J50" s="17"/>
@@ -22197,7 +22192,7 @@
       <c r="W50" s="17"/>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>48</v>
       </c>
@@ -22214,7 +22209,7 @@
       </c>
       <c r="G51" s="44"/>
       <c r="H51" s="33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I51" s="34"/>
       <c r="J51" s="17"/>
@@ -22233,7 +22228,7 @@
       <c r="W51" s="17"/>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>49</v>
       </c>
@@ -22271,7 +22266,7 @@
       <c r="W52" s="17"/>
       <c r="X52" s="18"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>50</v>
       </c>
@@ -22309,7 +22304,7 @@
       <c r="W53" s="17"/>
       <c r="X53" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>51</v>
       </c>
@@ -22334,7 +22329,7 @@
       </c>
       <c r="K54" s="46"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>51</v>
       </c>
@@ -22355,10 +22350,10 @@
       </c>
       <c r="K55" s="46"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="7"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>1</v>
       </c>
@@ -22372,7 +22367,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>2</v>
       </c>
@@ -22386,7 +22381,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>3</v>
       </c>
@@ -22401,7 +22396,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>4</v>
       </c>
@@ -22409,13 +22404,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
     </row>
-    <row r="62" spans="1:24" s="4" customFormat="1">
+    <row r="62" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
@@ -22428,7 +22423,7 @@
       <c r="W62" s="5"/>
       <c r="X62" s="5"/>
     </row>
-    <row r="63" spans="1:24" s="4" customFormat="1">
+    <row r="63" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
@@ -22441,7 +22436,7 @@
       <c r="W63" s="5"/>
       <c r="X63" s="5"/>
     </row>
-    <row r="64" spans="1:24" s="4" customFormat="1">
+    <row r="64" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
@@ -22940,7 +22935,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X60"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -22970,7 +22965,7 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>263</v>
       </c>
@@ -23038,7 +23033,7 @@
         <v>46339</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -23086,7 +23081,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -23114,7 +23109,7 @@
       <c r="W3" s="17"/>
       <c r="X3" s="18"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -23142,7 +23137,7 @@
       <c r="W4" s="17"/>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -23170,7 +23165,7 @@
       <c r="W5" s="17"/>
       <c r="X5" s="18"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -23218,7 +23213,7 @@
       </c>
       <c r="X6" s="22"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -23246,7 +23241,7 @@
       <c r="W7" s="17"/>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -23276,7 +23271,7 @@
       <c r="W8" s="17"/>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -23306,7 +23301,7 @@
       <c r="W9" s="17"/>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -23336,7 +23331,7 @@
       <c r="W10" s="17"/>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -23364,7 +23359,7 @@
       <c r="W11" s="17"/>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -23392,7 +23387,7 @@
       <c r="W12" s="17"/>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -23420,7 +23415,7 @@
       <c r="W13" s="17"/>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -23448,7 +23443,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -23476,7 +23471,7 @@
       <c r="W15" s="17"/>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -23504,7 +23499,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -23525,7 +23520,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -23549,7 +23544,7 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>265</v>
       </c>
@@ -23617,7 +23612,7 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -23665,7 +23660,7 @@
       </c>
       <c r="X20" s="30"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -23693,7 +23688,7 @@
       <c r="W21" s="17"/>
       <c r="X21" s="18"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -23721,7 +23716,7 @@
       <c r="W22" s="17"/>
       <c r="X22" s="18"/>
     </row>
-    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -23749,7 +23744,7 @@
       <c r="W23" s="17"/>
       <c r="X23" s="18"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -23797,7 +23792,7 @@
       </c>
       <c r="X24" s="22"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -23825,7 +23820,7 @@
       <c r="W25" s="17"/>
       <c r="X25" s="18"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -23855,7 +23850,7 @@
       <c r="W26" s="17"/>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -23885,7 +23880,7 @@
       <c r="W27" s="17"/>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -23915,7 +23910,7 @@
       <c r="W28" s="17"/>
       <c r="X28" s="18"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -23945,7 +23940,7 @@
       <c r="W29" s="17"/>
       <c r="X29" s="18"/>
     </row>
-    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -23975,7 +23970,7 @@
       <c r="W30" s="17"/>
       <c r="X30" s="18"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -24005,7 +24000,7 @@
       <c r="W31" s="17"/>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -24035,7 +24030,7 @@
       <c r="W32" s="17"/>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -24065,7 +24060,7 @@
       <c r="W33" s="17"/>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -24095,7 +24090,7 @@
       <c r="W34" s="17"/>
       <c r="X34" s="18"/>
     </row>
-    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -24116,7 +24111,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -24131,7 +24126,7 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>267</v>
       </c>
@@ -24201,7 +24196,7 @@
         <v>46353</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -24251,7 +24246,7 @@
       </c>
       <c r="X38" s="30"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -24281,7 +24276,7 @@
       <c r="W39" s="17"/>
       <c r="X39" s="18"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -24309,7 +24304,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -24337,7 +24332,7 @@
       <c r="W41" s="17"/>
       <c r="X41" s="18"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -24385,7 +24380,7 @@
       </c>
       <c r="X42" s="22"/>
     </row>
-    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -24413,7 +24408,7 @@
       <c r="W43" s="17"/>
       <c r="X43" s="18"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -24441,7 +24436,7 @@
       <c r="W44" s="17"/>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -24469,7 +24464,7 @@
       <c r="W45" s="17"/>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -24499,7 +24494,7 @@
       <c r="W46" s="17"/>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -24529,7 +24524,7 @@
       <c r="W47" s="17"/>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
@@ -24559,7 +24554,7 @@
       <c r="W48" s="17"/>
       <c r="X48" s="18"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -24589,7 +24584,7 @@
       <c r="W49" s="17"/>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -24617,7 +24612,7 @@
       <c r="W50" s="17"/>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -24645,7 +24640,7 @@
       <c r="W51" s="17"/>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -24673,7 +24668,7 @@
       <c r="W52" s="17"/>
       <c r="X52" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -24687,7 +24682,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -24701,7 +24696,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -24716,7 +24711,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -24724,17 +24719,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -25207,7 +25202,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:Y61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1" style="5" customWidth="1"/>
     <col min="2" max="2" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -25237,8 +25232,8 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
-    <row r="2" spans="2:25">
+    <row r="1" spans="2:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>269</v>
       </c>
@@ -25306,7 +25301,7 @@
         <v>46381</v>
       </c>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
@@ -25352,7 +25347,7 @@
       <c r="X3" s="53"/>
       <c r="Y3" s="54"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
@@ -25382,7 +25377,7 @@
       <c r="X4" s="53"/>
       <c r="Y4" s="54"/>
     </row>
-    <row r="5" spans="2:25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
@@ -25410,7 +25405,7 @@
       <c r="X5" s="53"/>
       <c r="Y5" s="54"/>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
@@ -25438,7 +25433,7 @@
       <c r="X6" s="53"/>
       <c r="Y6" s="54"/>
     </row>
-    <row r="7" spans="2:25">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
@@ -25484,7 +25479,7 @@
       <c r="X7" s="53"/>
       <c r="Y7" s="54"/>
     </row>
-    <row r="8" spans="2:25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
@@ -25512,7 +25507,7 @@
       <c r="X8" s="53"/>
       <c r="Y8" s="54"/>
     </row>
-    <row r="9" spans="2:25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
@@ -25540,7 +25535,7 @@
       <c r="X9" s="53"/>
       <c r="Y9" s="54"/>
     </row>
-    <row r="10" spans="2:25">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
         <v>32</v>
       </c>
@@ -25568,7 +25563,7 @@
       <c r="X10" s="53"/>
       <c r="Y10" s="54"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
         <v>35</v>
       </c>
@@ -25596,7 +25591,7 @@
       <c r="X11" s="53"/>
       <c r="Y11" s="54"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
@@ -25624,7 +25619,7 @@
       <c r="X12" s="53"/>
       <c r="Y12" s="54"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>40</v>
       </c>
@@ -25652,7 +25647,7 @@
       <c r="X13" s="53"/>
       <c r="Y13" s="54"/>
     </row>
-    <row r="14" spans="2:25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>45</v>
       </c>
@@ -25680,7 +25675,7 @@
       <c r="X14" s="53"/>
       <c r="Y14" s="54"/>
     </row>
-    <row r="15" spans="2:25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>48</v>
       </c>
@@ -25708,7 +25703,7 @@
       <c r="X15" s="53"/>
       <c r="Y15" s="54"/>
     </row>
-    <row r="16" spans="2:25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B16" s="12" t="s">
         <v>49</v>
       </c>
@@ -25736,7 +25731,7 @@
       <c r="X16" s="53"/>
       <c r="Y16" s="54"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
@@ -25764,7 +25759,7 @@
       <c r="X17" s="53"/>
       <c r="Y17" s="54"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -25787,7 +25782,7 @@
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -25799,7 +25794,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>271</v>
       </c>
@@ -25867,7 +25862,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
@@ -25913,7 +25908,7 @@
       <c r="X21" s="53"/>
       <c r="Y21" s="54"/>
     </row>
-    <row r="22" spans="2:25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
@@ -25941,7 +25936,7 @@
       <c r="X22" s="53"/>
       <c r="Y22" s="54"/>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
@@ -25973,7 +25968,7 @@
       <c r="X23" s="53"/>
       <c r="Y23" s="54"/>
     </row>
-    <row r="24" spans="2:25">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
@@ -26001,7 +25996,7 @@
       <c r="X24" s="53"/>
       <c r="Y24" s="54"/>
     </row>
-    <row r="25" spans="2:25">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
@@ -26047,7 +26042,7 @@
       <c r="X25" s="53"/>
       <c r="Y25" s="54"/>
     </row>
-    <row r="26" spans="2:25">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
@@ -26075,7 +26070,7 @@
       <c r="X26" s="53"/>
       <c r="Y26" s="54"/>
     </row>
-    <row r="27" spans="2:25">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B27" s="6" t="s">
         <v>28</v>
       </c>
@@ -26105,7 +26100,7 @@
       <c r="X27" s="53"/>
       <c r="Y27" s="54"/>
     </row>
-    <row r="28" spans="2:25">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B28" s="6" t="s">
         <v>32</v>
       </c>
@@ -26139,7 +26134,7 @@
       <c r="X28" s="53"/>
       <c r="Y28" s="54"/>
     </row>
-    <row r="29" spans="2:25">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B29" s="6" t="s">
         <v>35</v>
       </c>
@@ -26167,7 +26162,7 @@
       <c r="X29" s="53"/>
       <c r="Y29" s="54"/>
     </row>
-    <row r="30" spans="2:25">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
@@ -26197,7 +26192,7 @@
       <c r="X30" s="53"/>
       <c r="Y30" s="54"/>
     </row>
-    <row r="31" spans="2:25">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
@@ -26227,7 +26222,7 @@
       <c r="X31" s="53"/>
       <c r="Y31" s="54"/>
     </row>
-    <row r="32" spans="2:25">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B32" s="12" t="s">
         <v>45</v>
       </c>
@@ -26257,7 +26252,7 @@
       <c r="X32" s="53"/>
       <c r="Y32" s="54"/>
     </row>
-    <row r="33" spans="2:25">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>48</v>
       </c>
@@ -26287,7 +26282,7 @@
       <c r="X33" s="53"/>
       <c r="Y33" s="54"/>
     </row>
-    <row r="34" spans="2:25">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B34" s="12" t="s">
         <v>49</v>
       </c>
@@ -26317,7 +26312,7 @@
       <c r="X34" s="53"/>
       <c r="Y34" s="54"/>
     </row>
-    <row r="35" spans="2:25">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -26347,7 +26342,7 @@
       <c r="X35" s="53"/>
       <c r="Y35" s="54"/>
     </row>
-    <row r="36" spans="2:25">
+    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B36" s="5"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -26372,7 +26367,7 @@
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
     </row>
-    <row r="37" spans="2:25">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="5"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -26397,7 +26392,7 @@
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
     </row>
-    <row r="38" spans="2:25">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>273</v>
       </c>
@@ -26444,7 +26439,7 @@
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
     </row>
-    <row r="39" spans="2:25">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
@@ -26481,7 +26476,7 @@
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
     </row>
-    <row r="40" spans="2:25">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
@@ -26508,7 +26503,7 @@
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
     </row>
-    <row r="41" spans="2:25">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
@@ -26535,7 +26530,7 @@
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
     </row>
-    <row r="42" spans="2:25">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>21</v>
       </c>
@@ -26562,7 +26557,7 @@
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
     </row>
-    <row r="43" spans="2:25">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
@@ -26599,7 +26594,7 @@
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
     </row>
-    <row r="44" spans="2:25">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B44" s="6" t="s">
         <v>26</v>
       </c>
@@ -26626,7 +26621,7 @@
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
     </row>
-    <row r="45" spans="2:25">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B45" s="6" t="s">
         <v>28</v>
       </c>
@@ -26653,7 +26648,7 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
     </row>
-    <row r="46" spans="2:25">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B46" s="6" t="s">
         <v>32</v>
       </c>
@@ -26680,7 +26675,7 @@
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
     </row>
-    <row r="47" spans="2:25">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" s="6" t="s">
         <v>35</v>
       </c>
@@ -26707,7 +26702,7 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
     </row>
-    <row r="48" spans="2:25">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>37</v>
       </c>
@@ -26734,7 +26729,7 @@
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
     </row>
-    <row r="49" spans="2:25">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>40</v>
       </c>
@@ -26761,7 +26756,7 @@
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
     </row>
-    <row r="50" spans="2:25">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B50" s="12" t="s">
         <v>45</v>
       </c>
@@ -26788,7 +26783,7 @@
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
     </row>
-    <row r="51" spans="2:25">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
         <v>48</v>
       </c>
@@ -26815,7 +26810,7 @@
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
     </row>
-    <row r="52" spans="2:25">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B52" s="12" t="s">
         <v>49</v>
       </c>
@@ -26842,7 +26837,7 @@
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
     </row>
-    <row r="53" spans="2:25">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>50</v>
       </c>
@@ -26869,7 +26864,7 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
     </row>
-    <row r="54" spans="2:25">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B54" s="5"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -26894,7 +26889,7 @@
       <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
     </row>
-    <row r="55" spans="2:25">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B55" s="5">
         <v>1</v>
       </c>
@@ -26910,7 +26905,7 @@
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="2:25">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B56" s="5">
         <v>2</v>
       </c>
@@ -26924,7 +26919,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:25">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B57" s="8">
         <v>3</v>
       </c>
@@ -26939,7 +26934,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="2:25">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B58" s="5">
         <v>4</v>
       </c>
@@ -26953,7 +26948,7 @@
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="2:25">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="E59" s="5"/>
@@ -26963,7 +26958,7 @@
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="2:25">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="E60" s="5"/>
@@ -26973,7 +26968,7 @@
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="2:25">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
     </row>
@@ -27647,13 +27642,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4697" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC614FC3-B65C-4CCF-ADAA-F9678F49D86D}"/>
+  <xr:revisionPtr revIDLastSave="4704" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B57CA00-3A5A-4C1A-9C3C-7226A20E38A0}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -911,13 +911,13 @@
     <t>9 SF TC 3</t>
   </si>
   <si>
-    <t>9 SF MS 5 ?</t>
-  </si>
-  <si>
     <t>9 SF AN 1</t>
   </si>
   <si>
     <t>9 SF RTC AW</t>
+  </si>
+  <si>
+    <t>9 SF MS 5</t>
   </si>
 </sst>
 </file>
@@ -18564,17 +18564,17 @@
         <v>26</v>
       </c>
       <c r="O27" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P27" s="18"/>
       <c r="Q27" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="R27" s="18"/>
-      <c r="S27" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="T27" s="18"/>
+      <c r="S27" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="20"/>
       <c r="U27" s="61" t="s">
         <v>248</v>
       </c>
@@ -18720,11 +18720,11 @@
       </c>
       <c r="T30" s="20"/>
       <c r="U30" s="61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="V30" s="62"/>
       <c r="W30" s="61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="X30" s="62"/>
     </row>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="R33" s="34"/>
       <c r="S33" s="61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="T33" s="62"/>
       <c r="U33" s="29" t="s">
@@ -19272,19 +19272,19 @@
       </c>
       <c r="P43" s="25"/>
       <c r="Q43" s="61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R43" s="62"/>
       <c r="S43" s="61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="T43" s="62"/>
       <c r="U43" s="61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="V43" s="62"/>
       <c r="W43" s="61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="X43" s="62"/>
     </row>
@@ -19614,15 +19614,15 @@
       </c>
       <c r="R50" s="18"/>
       <c r="S50" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T50" s="25"/>
       <c r="U50" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V50" s="25"/>
       <c r="W50" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="X50" s="25"/>
     </row>
@@ -19968,7 +19968,7 @@
       <c r="A65" s="8"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="T/zNKvlxD/CiXBeBfqMXYog3XFzi344wTgs30nGLpSbcJpAtQxq0B2ktAnhRKKNM9rheRcQTm2SWCaRlNDjGFw==" saltValue="WIhnjcoG05m0XCPXzZ4SkA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="cklNF2+4cwAZJUNU4mSZnr1xyszRJKC5UEZ8HC+uulMCKGUwi00AxasNKzISEYEESxa6saQyOCOCiEqjEuNgdQ==" saltValue="wgH2YV/rS0W8lAc30OYwVg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="470">
     <mergeCell ref="S51:T51"/>
     <mergeCell ref="U51:V51"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4715" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{525C4E94-376F-4BC1-BD4D-633F68A080F4}"/>
+  <xr:revisionPtr revIDLastSave="4731" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BC5823F-8B1B-4CF2-9B56-22D1654B432B}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="6" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -56,17 +56,17 @@
   <commentList>
     <comment ref="U37" authorId="0" shapeId="0" xr:uid="{65E4B43F-4DA4-4023-9E8A-D4F24A3B2C8C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     RTC SUR KURS</t>
       </text>
     </comment>
     <comment ref="W37" authorId="1" shapeId="0" xr:uid="{BC2FB818-859F-40F5-95A2-BC57CF0AD42E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     KUT SUR (RTC)?</t>
       </text>
     </comment>
@@ -924,7 +924,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1851,7 +1851,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="5" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -1880,7 +1880,7 @@
     <col min="28" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AA2" s="42"/>
     </row>
-    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AA3" s="20"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AA4" s="42"/>
     </row>
-    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AA5" s="52"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AA6" s="34"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AA7" s="40"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AA8" s="36"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AA9" s="52"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="AA10" s="34"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="AA11" s="20"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AA12" s="36"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AA13" s="36"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AA14" s="52"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="AA15" s="42"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -2714,7 +2714,7 @@
       <c r="Z16" s="17"/>
       <c r="AA16" s="18"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2749,7 +2749,7 @@
       <c r="Z17" s="17"/>
       <c r="AA17" s="18"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2784,7 +2784,7 @@
       <c r="Z18" s="17"/>
       <c r="AA18" s="18"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="U19" s="38"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="U20" s="52"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2844,7 +2844,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2862,7 +2862,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AA24" s="34"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="AA25" s="34"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AA26" s="52"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AA27" s="40"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="AA28" s="18"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>26</v>
       </c>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="AA29" s="28"/>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>28</v>
       </c>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AA30" s="18"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AA31" s="40"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AA32" s="52"/>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AA33" s="40"/>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="AA34" s="52"/>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>45</v>
       </c>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AA35" s="36"/>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>48</v>
       </c>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AA36" s="36"/>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>49</v>
       </c>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AA37" s="36"/>
     </row>
-    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -3726,7 +3726,7 @@
       <c r="Z38" s="17"/>
       <c r="AA38" s="18"/>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -3747,7 +3747,7 @@
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -3765,7 +3765,7 @@
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>69</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AA42" s="30"/>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AA43" s="18"/>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AA44" s="46"/>
     </row>
-    <row r="45" spans="1:27" ht="15" customHeight="1">
+    <row r="45" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AA45" s="40"/>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AA46" s="34"/>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AA47" s="18"/>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>28</v>
       </c>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AA48" s="40"/>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>32</v>
       </c>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AA49" s="36"/>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AA50" s="18"/>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AA51" s="46"/>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="AA52" s="36"/>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AA53" s="34"/>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>48</v>
       </c>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AA54" s="36"/>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>49</v>
       </c>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="AA55" s="46"/>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -4595,7 +4595,7 @@
       <c r="Z56" s="17"/>
       <c r="AA56" s="18"/>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -5131,7 +5131,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X78"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -5160,7 +5160,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="X4" s="34"/>
     </row>
-    <row r="5" spans="1:24" ht="11.25" customHeight="1">
+    <row r="5" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="X5" s="34"/>
     </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="X6" s="34"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="X7" s="68"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="X8" s="36"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="X9" s="34"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="X11" s="40"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="X13" s="40"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="X14" s="36"/>
     </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="X15" s="34"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -5940,7 +5940,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -5964,7 +5964,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -5988,7 +5988,7 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -6012,7 +6012,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>97</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="X21" s="78"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="X22" s="34"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="X23" s="36"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="X24" s="36"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="X25" s="34"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="X26" s="36"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="X27" s="40"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>32</v>
       </c>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="X28" s="24"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>35</v>
       </c>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="X29" s="38"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="X30" s="24"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="X31" s="40"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>45</v>
       </c>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="X32" s="38"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="X33" s="38"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>49</v>
       </c>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="X34" s="24"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="X35" s="38"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -6837,7 +6837,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -6860,7 +6860,7 @@
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -6883,12 +6883,12 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="M39" s="7"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>109</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="X41" s="34"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="X42" s="34"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="X43" s="34"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="X44" s="20"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="X45" s="34"/>
     </row>
-    <row r="46" spans="1:24" ht="10.5" customHeight="1">
+    <row r="46" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="X46" s="36"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="X47" s="36"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="X48" s="38"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="X49" s="20"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="X50" s="38"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="X51" s="40"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="X52" s="36"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="X53" s="40"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="X54" s="40"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="X55" s="38"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
@@ -7716,7 +7716,7 @@
       <c r="W56" s="9"/>
       <c r="X56" s="9"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -7741,7 +7741,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -7789,7 +7789,7 @@
       <c r="W60" s="9"/>
       <c r="X60" s="9"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -7801,34 +7801,34 @@
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="R62" s="9"/>
     </row>
-    <row r="71" spans="13:13">
+    <row r="71" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="13:13">
+    <row r="72" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M72" s="5"/>
     </row>
-    <row r="73" spans="13:13">
+    <row r="73" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M73" s="5"/>
     </row>
-    <row r="74" spans="13:13">
+    <row r="74" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M74" s="5"/>
     </row>
-    <row r="75" spans="13:13">
+    <row r="75" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M75" s="5"/>
     </row>
-    <row r="76" spans="13:13">
+    <row r="76" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="13:13">
+    <row r="77" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M77" s="5"/>
     </row>
-    <row r="78" spans="13:13">
+    <row r="78" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M78" s="5"/>
     </row>
   </sheetData>
@@ -8312,7 +8312,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X66"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -8342,7 +8342,7 @@
     <col min="27" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
@@ -8410,7 +8410,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="X3" s="70"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="X4" s="40"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="X5" s="70"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="X6" s="34"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="X7" s="40"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="X8" s="24"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="X9" s="40"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="X10" s="24"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="X11" s="40"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="X12" s="40"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="X13" s="40"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="X14" s="70"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="X15" s="70"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -9122,7 +9122,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="7"/>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="V17" s="40"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="7"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P18" s="40"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="7"/>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="P19" s="70"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="7"/>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="P20" s="70"/>
     </row>
-    <row r="21" spans="1:24" ht="11.25" customHeight="1">
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="7"/>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="P21" s="70"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="7"/>
@@ -9180,17 +9180,17 @@
       </c>
       <c r="P22" s="70"/>
     </row>
-    <row r="23" spans="1:24" ht="11.25" customHeight="1">
+    <row r="23" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:24" ht="11.25" customHeight="1">
+    <row r="24" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>154</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="X26" s="34"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="X27" s="42"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="X28" s="32"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="X29" s="36"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="X30" s="34"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="X31" s="36"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>28</v>
       </c>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="X32" s="32"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="X33" s="52"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="X34" s="34"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="X35" s="40"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="X36" s="52"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>45</v>
       </c>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="X37" s="40"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="X38" s="36"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>49</v>
       </c>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="X39" s="52"/>
     </row>
-    <row r="40" spans="1:24" ht="11.25" customHeight="1">
+    <row r="40" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
@@ -9942,7 +9942,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24" ht="11.25" customHeight="1">
+    <row r="41" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -9957,7 +9957,7 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="11.25" customHeight="1">
+    <row r="42" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -9972,7 +9972,7 @@
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="11.25" customHeight="1">
+    <row r="43" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>166</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="11.25" customHeight="1">
+    <row r="44" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -10088,7 +10088,7 @@
       <c r="W44" s="53"/>
       <c r="X44" s="54"/>
     </row>
-    <row r="45" spans="1:24" ht="11.25" customHeight="1">
+    <row r="45" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -10134,7 +10134,7 @@
       <c r="W45" s="53"/>
       <c r="X45" s="54"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -10180,7 +10180,7 @@
       <c r="W46" s="53"/>
       <c r="X46" s="54"/>
     </row>
-    <row r="47" spans="1:24" ht="11.25" customHeight="1">
+    <row r="47" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -10224,7 +10224,7 @@
       <c r="W47" s="53"/>
       <c r="X47" s="54"/>
     </row>
-    <row r="48" spans="1:24" ht="11.25" customHeight="1">
+    <row r="48" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
@@ -10268,7 +10268,7 @@
       <c r="W48" s="53"/>
       <c r="X48" s="54"/>
     </row>
-    <row r="49" spans="1:24" ht="11.25" customHeight="1">
+    <row r="49" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>26</v>
       </c>
@@ -10312,7 +10312,7 @@
       <c r="W49" s="53"/>
       <c r="X49" s="54"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>28</v>
       </c>
@@ -10356,7 +10356,7 @@
       <c r="W50" s="53"/>
       <c r="X50" s="54"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>32</v>
       </c>
@@ -10402,7 +10402,7 @@
       <c r="W51" s="53"/>
       <c r="X51" s="54"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>35</v>
       </c>
@@ -10448,7 +10448,7 @@
       <c r="W52" s="53"/>
       <c r="X52" s="54"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>37</v>
       </c>
@@ -10494,7 +10494,7 @@
       <c r="W53" s="53"/>
       <c r="X53" s="54"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>40</v>
       </c>
@@ -10540,7 +10540,7 @@
       <c r="W54" s="53"/>
       <c r="X54" s="54"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>45</v>
       </c>
@@ -10586,7 +10586,7 @@
       <c r="W55" s="53"/>
       <c r="X55" s="54"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>48</v>
       </c>
@@ -10632,7 +10632,7 @@
       <c r="W56" s="53"/>
       <c r="X56" s="54"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>49</v>
       </c>
@@ -10678,7 +10678,7 @@
       <c r="W57" s="53"/>
       <c r="X57" s="54"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>50</v>
       </c>
@@ -10718,7 +10718,7 @@
       <c r="W58" s="53"/>
       <c r="X58" s="54"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="O59" s="19" t="s">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="T59" s="20"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="P60" s="36"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>3</v>
       </c>
@@ -10780,7 +10780,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>4</v>
       </c>
@@ -10788,17 +10788,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -11286,7 +11286,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X62"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -11315,7 +11315,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>178</v>
       </c>
@@ -11383,7 +11383,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="X5" s="20"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="X6" s="34"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="X7" s="32"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="X8" s="32"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="X9" s="91"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="X10" s="24"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="X11" s="20"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="X12" s="24"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="X13" s="91"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="X14" s="24"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="X15" s="20"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -12068,7 +12068,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>195</v>
       </c>
@@ -12095,7 +12095,7 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B18" s="39" t="s">
         <v>196</v>
       </c>
@@ -12107,7 +12107,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -12116,7 +12116,7 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -12127,7 +12127,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>197</v>
       </c>
@@ -12195,7 +12195,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="X22" s="30"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="X23" s="42"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -12333,7 +12333,7 @@
       </c>
       <c r="X24" s="18"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="X25" s="91"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="X26" s="34"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="X27" s="24"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="X28" s="91"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="X29" s="34"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="X30" s="34"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="X31" s="20"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="X32" s="40"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="X33" s="24"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="X34" s="20"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="X35" s="24"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -12889,7 +12889,7 @@
       </c>
       <c r="X36" s="20"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="4"/>
@@ -12897,7 +12897,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="4"/>
@@ -12905,7 +12905,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="4"/>
@@ -12913,7 +12913,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>212</v>
       </c>
@@ -12983,7 +12983,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="X41" s="30"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="X42" s="18"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="X43" s="18"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="X44" s="52"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="X45" s="34"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="X46" s="34"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="X47" s="60"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -13373,7 +13373,7 @@
       </c>
       <c r="X48" s="42"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -13421,7 +13421,7 @@
       </c>
       <c r="X49" s="34"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="X50" s="34"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="X51" s="34"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -13569,7 +13569,7 @@
       </c>
       <c r="X52" s="52"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -13619,7 +13619,7 @@
       </c>
       <c r="X53" s="52"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -13667,7 +13667,7 @@
       </c>
       <c r="X54" s="42"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -13709,7 +13709,7 @@
       <c r="W55" s="17"/>
       <c r="X55" s="18"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -13739,7 +13739,7 @@
       <c r="W56" s="17"/>
       <c r="X56" s="18"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="8"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -13764,7 +13764,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="8"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -13777,7 +13777,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>1</v>
       </c>
@@ -13802,7 +13802,7 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>2</v>
       </c>
@@ -13816,7 +13816,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>3</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>4</v>
       </c>
@@ -14322,7 +14322,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -14351,7 +14351,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
@@ -14419,7 +14419,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="X2" s="42"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="X3" s="42"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -14542,10 +14542,10 @@
       <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="O4" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="P4" s="34"/>
+      <c r="P4" s="68"/>
       <c r="Q4" s="17" t="s">
         <v>9</v>
       </c>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="X4" s="68"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="X5" s="42"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="X6" s="68"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -14707,7 +14707,7 @@
       </c>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -14755,7 +14755,7 @@
       </c>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -14782,10 +14782,10 @@
       <c r="N9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O9" s="33" t="s">
+      <c r="O9" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="P9" s="34"/>
+      <c r="P9" s="68"/>
       <c r="Q9" s="17" t="s">
         <v>9</v>
       </c>
@@ -14803,7 +14803,7 @@
       </c>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="X10" s="42"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="X11" s="42"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -14926,10 +14926,10 @@
       <c r="N12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O12" s="33" t="s">
+      <c r="O12" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="P12" s="34"/>
+      <c r="P12" s="68"/>
       <c r="Q12" s="17" t="s">
         <v>9</v>
       </c>
@@ -14947,7 +14947,7 @@
       </c>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -15135,9 +15135,9 @@
       </c>
       <c r="X16" s="42"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="X20" s="42"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="X21" s="42"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -15328,10 +15328,10 @@
       <c r="N22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O22" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="42"/>
+      <c r="O22" s="94" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="95"/>
       <c r="Q22" s="41" t="s">
         <v>8</v>
       </c>
@@ -15349,7 +15349,7 @@
       </c>
       <c r="X22" s="42"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -15397,7 +15397,7 @@
       </c>
       <c r="X23" s="42"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="X24" s="42"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="X25" s="42"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="X28" s="42"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="X29" s="42"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="X30" s="42"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="X32" s="42"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -15887,7 +15887,7 @@
       </c>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="X34" s="42"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -15962,11 +15962,11 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" ht="11.25" customHeight="1">
+    <row r="36" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24" ht="11.25" customHeight="1">
+    <row r="37" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>236</v>
       </c>
@@ -16036,7 +16036,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="11.25" customHeight="1">
+    <row r="38" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="X38" s="42"/>
     </row>
-    <row r="39" spans="1:24" ht="10.5" customHeight="1">
+    <row r="39" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="X39" s="42"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="X40" s="42"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="X41" s="42"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="X42" s="42"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="X43" s="42"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="X46" s="42"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="X48" s="42"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -16666,7 +16666,7 @@
       </c>
       <c r="X50" s="42"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="X52" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -16776,7 +16776,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -16792,7 +16792,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -16808,7 +16808,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -16818,15 +16818,15 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -17309,7 +17309,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -17338,7 +17338,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -17406,7 +17406,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="X3" s="18"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -17550,7 +17550,7 @@
       </c>
       <c r="X4" s="34"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="X5" s="36"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="X6" s="34"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -17742,7 +17742,7 @@
       </c>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="X9" s="42"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -17838,7 +17838,7 @@
       </c>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="X11" s="34"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="X12" s="42"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="X13" s="42"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -18030,7 +18030,7 @@
       </c>
       <c r="X14" s="34"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="X15" s="42"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="X16" s="36"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -18152,7 +18152,7 @@
       <c r="W17" s="17"/>
       <c r="X17" s="18"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -18180,7 +18180,7 @@
       <c r="W18" s="17"/>
       <c r="X18" s="18"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -18204,7 +18204,7 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -18228,7 +18228,7 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -18296,7 +18296,7 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="X22" s="30"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="X23" s="18"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -18440,7 +18440,7 @@
       </c>
       <c r="X24" s="36"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="X25" s="36"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -18536,7 +18536,7 @@
       </c>
       <c r="X26" s="95"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="X27" s="70"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="X28" s="34"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="X29" s="42"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="X30" s="70"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -18776,7 +18776,7 @@
       </c>
       <c r="X31" s="34"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="X32" s="38"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -18872,7 +18872,7 @@
       </c>
       <c r="X33" s="38"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -18920,7 +18920,7 @@
       </c>
       <c r="X34" s="38"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="X35" s="42"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -19016,15 +19016,15 @@
       <c r="W36" s="17"/>
       <c r="X36" s="18"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>255</v>
       </c>
@@ -19094,7 +19094,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -19144,7 +19144,7 @@
       </c>
       <c r="X40" s="46"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>10</v>
       </c>
@@ -19177,22 +19177,24 @@
         <v>56</v>
       </c>
       <c r="P41" s="40"/>
-      <c r="Q41" s="17"/>
+      <c r="Q41" s="17" t="s">
+        <v>9</v>
+      </c>
       <c r="R41" s="18"/>
       <c r="S41" s="17" t="s">
         <v>9</v>
       </c>
       <c r="T41" s="18"/>
-      <c r="U41" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="V41" s="36"/>
+      <c r="U41" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="V41" s="18"/>
       <c r="W41" s="17" t="s">
         <v>9</v>
       </c>
       <c r="X41" s="18"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -19240,7 +19242,7 @@
       </c>
       <c r="X42" s="38"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
@@ -19288,7 +19290,7 @@
       </c>
       <c r="X43" s="70"/>
     </row>
-    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
@@ -19336,7 +19338,7 @@
       </c>
       <c r="X44" s="34"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>26</v>
       </c>
@@ -19384,7 +19386,7 @@
       </c>
       <c r="X45" s="38"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>28</v>
       </c>
@@ -19417,10 +19419,10 @@
         <v>56</v>
       </c>
       <c r="P46" s="40"/>
-      <c r="Q46" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="R46" s="36"/>
+      <c r="Q46" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="R46" s="18"/>
       <c r="S46" s="17" t="s">
         <v>9</v>
       </c>
@@ -19434,7 +19436,7 @@
       </c>
       <c r="X46" s="36"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>32</v>
       </c>
@@ -19482,7 +19484,7 @@
       </c>
       <c r="X47" s="38"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>35</v>
       </c>
@@ -19530,7 +19532,7 @@
       </c>
       <c r="X48" s="36"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
@@ -19561,24 +19563,24 @@
         <v>56</v>
       </c>
       <c r="P49" s="40"/>
-      <c r="Q49" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="R49" s="24"/>
+      <c r="Q49" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="R49" s="36"/>
       <c r="S49" s="23" t="s">
         <v>248</v>
       </c>
       <c r="T49" s="24"/>
-      <c r="U49" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="V49" s="24"/>
+      <c r="U49" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="V49" s="36"/>
       <c r="W49" s="23" t="s">
         <v>248</v>
       </c>
       <c r="X49" s="24"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>40</v>
       </c>
@@ -19626,7 +19628,7 @@
       </c>
       <c r="X50" s="40"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>45</v>
       </c>
@@ -19674,7 +19676,7 @@
       </c>
       <c r="X51" s="28"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
@@ -19722,7 +19724,7 @@
       </c>
       <c r="X52" s="70"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>49</v>
       </c>
@@ -19770,7 +19772,7 @@
       </c>
       <c r="X53" s="24"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
@@ -19803,16 +19805,20 @@
         <v>248</v>
       </c>
       <c r="R54" s="24"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="18"/>
+      <c r="S54" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="T54" s="24"/>
       <c r="U54" s="23" t="s">
         <v>248</v>
       </c>
       <c r="V54" s="24"/>
-      <c r="W54" s="17"/>
-      <c r="X54" s="18"/>
-    </row>
-    <row r="55" spans="1:24">
+      <c r="W54" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="X54" s="24"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -19848,7 +19854,7 @@
       </c>
       <c r="X55" s="28"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -19876,7 +19882,7 @@
       <c r="W56" s="17"/>
       <c r="X56" s="18"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -19899,7 +19905,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -19913,7 +19919,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -19927,7 +19933,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -19941,7 +19947,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -19949,26 +19955,26 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="8"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cklNF2+4cwAZJUNU4mSZnr1xyszRJKC5UEZ8HC+uulMCKGUwi00AxasNKzISEYEESxa6saQyOCOCiEqjEuNgdQ==" saltValue="wgH2YV/rS0W8lAc30OYwVg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9bp0PKKz4fRL5H8RhKWqCf7rvAtVa4jnqFJQa3Xjch9cBVd2Bkhe9r93eOKUIQt7rZCkh1hFF016AIwY3y+uKw==" saltValue="iUHFgpKV91z8f/8Xe1URww==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="470">
     <mergeCell ref="J46:K46"/>
     <mergeCell ref="Q53:R53"/>
@@ -20459,7 +20465,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X64"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -20488,7 +20494,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>261</v>
       </c>
@@ -20556,7 +20562,7 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -20604,7 +20610,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -20648,7 +20654,7 @@
       <c r="W3" s="17"/>
       <c r="X3" s="18"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -20686,7 +20692,7 @@
       <c r="W4" s="17"/>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -20694,12 +20700,12 @@
         <v>248</v>
       </c>
       <c r="C5" s="24"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="23" t="s">
+      <c r="D5" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="17"/>
       <c r="I5" s="18"/>
       <c r="J5" s="23" t="s">
@@ -20720,7 +20726,7 @@
       <c r="W5" s="17"/>
       <c r="X5" s="18"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -20768,7 +20774,7 @@
       </c>
       <c r="X6" s="34"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -20778,10 +20784,8 @@
       <c r="C7" s="24"/>
       <c r="D7" s="17"/>
       <c r="E7" s="18"/>
-      <c r="F7" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="G7" s="24"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
       <c r="H7" s="21"/>
       <c r="I7" s="22"/>
       <c r="J7" s="23" t="s">
@@ -20802,20 +20806,16 @@
       <c r="W7" s="17"/>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="C8" s="24"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="25"/>
       <c r="E8" s="26"/>
-      <c r="F8" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="G8" s="24"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
       <c r="H8" s="17"/>
       <c r="I8" s="18"/>
       <c r="J8" s="23" t="s">
@@ -20836,7 +20836,7 @@
       <c r="W8" s="17"/>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -20870,7 +20870,7 @@
       <c r="W9" s="17"/>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -20908,7 +20908,7 @@
       <c r="W10" s="17"/>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24" ht="11.25" customHeight="1">
+    <row r="11" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -20942,7 +20942,7 @@
       <c r="W11" s="17"/>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24" ht="11.25" customHeight="1">
+    <row r="12" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -20980,7 +20980,7 @@
       <c r="W12" s="17"/>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24" ht="11.25" customHeight="1">
+    <row r="13" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -21008,7 +21008,7 @@
       <c r="W13" s="17"/>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" ht="11.25" customHeight="1">
+    <row r="14" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -21036,7 +21036,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24" ht="11.25" customHeight="1">
+    <row r="15" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -21064,7 +21064,7 @@
       <c r="W15" s="17"/>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -21096,7 +21096,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -21109,7 +21109,7 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -21122,7 +21122,7 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>264</v>
       </c>
@@ -21190,7 +21190,7 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -21238,7 +21238,7 @@
       </c>
       <c r="X20" s="30"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -21276,7 +21276,7 @@
       <c r="W21" s="17"/>
       <c r="X21" s="18"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="X22" s="42"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -21362,7 +21362,7 @@
       <c r="W23" s="17"/>
       <c r="X23" s="18"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="X24" s="34"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -21458,7 +21458,7 @@
       </c>
       <c r="X25" s="42"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -21496,7 +21496,7 @@
       <c r="W26" s="17"/>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -21534,7 +21534,7 @@
       <c r="W27" s="17"/>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -21572,7 +21572,7 @@
       <c r="W28" s="17"/>
       <c r="X28" s="18"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -21608,7 +21608,7 @@
       <c r="W29" s="17"/>
       <c r="X29" s="18"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -21648,7 +21648,7 @@
       <c r="W30" s="17"/>
       <c r="X30" s="18"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -21682,7 +21682,7 @@
       <c r="W31" s="17"/>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -21716,7 +21716,7 @@
       <c r="W32" s="17"/>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="33" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -21756,7 +21756,7 @@
       <c r="W33" s="17"/>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -21796,7 +21796,7 @@
       <c r="W34" s="17"/>
       <c r="X34" s="18"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
@@ -21833,7 +21833,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -21858,7 +21858,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -21884,7 +21884,7 @@
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>267</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>46311</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="X39" s="30"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>10</v>
       </c>
@@ -22042,7 +22042,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
@@ -22082,7 +22082,7 @@
       <c r="W41" s="17"/>
       <c r="X41" s="18"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -22122,7 +22122,7 @@
       <c r="W42" s="17"/>
       <c r="X42" s="18"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>24</v>
       </c>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="X43" s="34"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>26</v>
       </c>
@@ -22206,7 +22206,7 @@
       <c r="W44" s="17"/>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>28</v>
       </c>
@@ -22242,7 +22242,7 @@
       <c r="W45" s="17"/>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>32</v>
       </c>
@@ -22280,7 +22280,7 @@
       <c r="W46" s="17"/>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>35</v>
       </c>
@@ -22318,7 +22318,7 @@
       <c r="W47" s="17"/>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
@@ -22356,7 +22356,7 @@
       <c r="W48" s="17"/>
       <c r="X48" s="18"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>40</v>
       </c>
@@ -22394,7 +22394,7 @@
       <c r="W49" s="17"/>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>45</v>
       </c>
@@ -22430,7 +22430,7 @@
       <c r="W50" s="17"/>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>48</v>
       </c>
@@ -22466,7 +22466,7 @@
       <c r="W51" s="17"/>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>49</v>
       </c>
@@ -22504,7 +22504,7 @@
       <c r="W52" s="17"/>
       <c r="X52" s="18"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>50</v>
       </c>
@@ -22542,7 +22542,7 @@
       <c r="W53" s="17"/>
       <c r="X53" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>51</v>
       </c>
@@ -22567,7 +22567,7 @@
       </c>
       <c r="K54" s="28"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>51</v>
       </c>
@@ -22588,10 +22588,10 @@
       </c>
       <c r="K55" s="28"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="7"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>1</v>
       </c>
@@ -22605,7 +22605,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>2</v>
       </c>
@@ -22619,7 +22619,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>3</v>
       </c>
@@ -22634,7 +22634,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>4</v>
       </c>
@@ -22642,13 +22642,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
     </row>
-    <row r="62" spans="1:24" s="4" customFormat="1">
+    <row r="62" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
@@ -22661,7 +22661,7 @@
       <c r="W62" s="5"/>
       <c r="X62" s="5"/>
     </row>
-    <row r="63" spans="1:24" s="4" customFormat="1">
+    <row r="63" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
@@ -22674,7 +22674,7 @@
       <c r="W63" s="5"/>
       <c r="X63" s="5"/>
     </row>
-    <row r="64" spans="1:24" s="4" customFormat="1">
+    <row r="64" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
@@ -23173,7 +23173,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X60"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -23203,7 +23203,7 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>269</v>
       </c>
@@ -23271,7 +23271,7 @@
         <v>46339</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -23347,7 +23347,7 @@
       <c r="W3" s="17"/>
       <c r="X3" s="18"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -23375,7 +23375,7 @@
       <c r="W4" s="17"/>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -23403,7 +23403,7 @@
       <c r="W5" s="17"/>
       <c r="X5" s="18"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -23451,7 +23451,7 @@
       </c>
       <c r="X6" s="34"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -23479,7 +23479,7 @@
       <c r="W7" s="17"/>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -23509,7 +23509,7 @@
       <c r="W8" s="17"/>
       <c r="X8" s="18"/>
     </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -23539,7 +23539,7 @@
       <c r="W9" s="17"/>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -23569,7 +23569,7 @@
       <c r="W10" s="17"/>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -23597,7 +23597,7 @@
       <c r="W11" s="17"/>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -23625,7 +23625,7 @@
       <c r="W12" s="17"/>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -23653,7 +23653,7 @@
       <c r="W13" s="17"/>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -23681,7 +23681,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="18"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -23709,7 +23709,7 @@
       <c r="W15" s="17"/>
       <c r="X15" s="18"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -23737,7 +23737,7 @@
       <c r="W16" s="17"/>
       <c r="X16" s="18"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -23758,7 +23758,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -23782,7 +23782,7 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>271</v>
       </c>
@@ -23850,7 +23850,7 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="X20" s="30"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -23926,7 +23926,7 @@
       <c r="W21" s="17"/>
       <c r="X21" s="18"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -23954,7 +23954,7 @@
       <c r="W22" s="17"/>
       <c r="X22" s="18"/>
     </row>
-    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -23982,7 +23982,7 @@
       <c r="W23" s="17"/>
       <c r="X23" s="18"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="X24" s="34"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -24062,7 +24062,7 @@
       <c r="W25" s="17"/>
       <c r="X25" s="18"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -24092,7 +24092,7 @@
       <c r="W26" s="17"/>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -24122,7 +24122,7 @@
       <c r="W27" s="17"/>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -24152,7 +24152,7 @@
       <c r="W28" s="17"/>
       <c r="X28" s="18"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -24182,7 +24182,7 @@
       <c r="W29" s="17"/>
       <c r="X29" s="18"/>
     </row>
-    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -24212,7 +24212,7 @@
       <c r="W30" s="17"/>
       <c r="X30" s="18"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -24242,7 +24242,7 @@
       <c r="W31" s="17"/>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -24272,7 +24272,7 @@
       <c r="W32" s="17"/>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -24302,7 +24302,7 @@
       <c r="W33" s="17"/>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -24332,7 +24332,7 @@
       <c r="W34" s="17"/>
       <c r="X34" s="18"/>
     </row>
-    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -24353,7 +24353,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -24368,7 +24368,7 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>274</v>
       </c>
@@ -24438,7 +24438,7 @@
         <v>46353</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -24488,7 +24488,7 @@
       </c>
       <c r="X38" s="30"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -24518,7 +24518,7 @@
       <c r="W39" s="17"/>
       <c r="X39" s="18"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -24546,7 +24546,7 @@
       <c r="W40" s="17"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -24574,7 +24574,7 @@
       <c r="W41" s="17"/>
       <c r="X41" s="18"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -24622,7 +24622,7 @@
       </c>
       <c r="X42" s="34"/>
     </row>
-    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -24650,7 +24650,7 @@
       <c r="W43" s="17"/>
       <c r="X43" s="18"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -24678,7 +24678,7 @@
       <c r="W44" s="17"/>
       <c r="X44" s="18"/>
     </row>
-    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -24706,7 +24706,7 @@
       <c r="W45" s="17"/>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -24736,7 +24736,7 @@
       <c r="W46" s="17"/>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -24766,7 +24766,7 @@
       <c r="W47" s="17"/>
       <c r="X47" s="18"/>
     </row>
-    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
@@ -24796,7 +24796,7 @@
       <c r="W48" s="17"/>
       <c r="X48" s="18"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -24826,7 +24826,7 @@
       <c r="W49" s="17"/>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -24854,7 +24854,7 @@
       <c r="W50" s="17"/>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -24882,7 +24882,7 @@
       <c r="W51" s="17"/>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -24910,7 +24910,7 @@
       <c r="W52" s="17"/>
       <c r="X52" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -24924,7 +24924,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -24938,7 +24938,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -24953,7 +24953,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -24961,17 +24961,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -25444,7 +25444,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:Y61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1" style="5" customWidth="1"/>
     <col min="2" max="2" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -25474,8 +25474,8 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
-    <row r="2" spans="2:25">
+    <row r="1" spans="2:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>276</v>
       </c>
@@ -25543,7 +25543,7 @@
         <v>46381</v>
       </c>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
@@ -25589,7 +25589,7 @@
       <c r="X3" s="53"/>
       <c r="Y3" s="54"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
@@ -25619,7 +25619,7 @@
       <c r="X4" s="53"/>
       <c r="Y4" s="54"/>
     </row>
-    <row r="5" spans="2:25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
@@ -25647,7 +25647,7 @@
       <c r="X5" s="53"/>
       <c r="Y5" s="54"/>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
@@ -25675,7 +25675,7 @@
       <c r="X6" s="53"/>
       <c r="Y6" s="54"/>
     </row>
-    <row r="7" spans="2:25">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
@@ -25721,7 +25721,7 @@
       <c r="X7" s="53"/>
       <c r="Y7" s="54"/>
     </row>
-    <row r="8" spans="2:25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
@@ -25749,7 +25749,7 @@
       <c r="X8" s="53"/>
       <c r="Y8" s="54"/>
     </row>
-    <row r="9" spans="2:25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
@@ -25777,7 +25777,7 @@
       <c r="X9" s="53"/>
       <c r="Y9" s="54"/>
     </row>
-    <row r="10" spans="2:25">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
         <v>32</v>
       </c>
@@ -25805,7 +25805,7 @@
       <c r="X10" s="53"/>
       <c r="Y10" s="54"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
         <v>35</v>
       </c>
@@ -25833,7 +25833,7 @@
       <c r="X11" s="53"/>
       <c r="Y11" s="54"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
@@ -25861,7 +25861,7 @@
       <c r="X12" s="53"/>
       <c r="Y12" s="54"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>40</v>
       </c>
@@ -25889,7 +25889,7 @@
       <c r="X13" s="53"/>
       <c r="Y13" s="54"/>
     </row>
-    <row r="14" spans="2:25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>45</v>
       </c>
@@ -25917,7 +25917,7 @@
       <c r="X14" s="53"/>
       <c r="Y14" s="54"/>
     </row>
-    <row r="15" spans="2:25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>48</v>
       </c>
@@ -25945,7 +25945,7 @@
       <c r="X15" s="53"/>
       <c r="Y15" s="54"/>
     </row>
-    <row r="16" spans="2:25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B16" s="12" t="s">
         <v>49</v>
       </c>
@@ -25973,7 +25973,7 @@
       <c r="X16" s="53"/>
       <c r="Y16" s="54"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
@@ -26001,7 +26001,7 @@
       <c r="X17" s="53"/>
       <c r="Y17" s="54"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -26024,7 +26024,7 @@
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -26036,7 +26036,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>278</v>
       </c>
@@ -26104,7 +26104,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
@@ -26150,7 +26150,7 @@
       <c r="X21" s="53"/>
       <c r="Y21" s="54"/>
     </row>
-    <row r="22" spans="2:25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
@@ -26178,7 +26178,7 @@
       <c r="X22" s="53"/>
       <c r="Y22" s="54"/>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
@@ -26210,7 +26210,7 @@
       <c r="X23" s="53"/>
       <c r="Y23" s="54"/>
     </row>
-    <row r="24" spans="2:25">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
@@ -26238,7 +26238,7 @@
       <c r="X24" s="53"/>
       <c r="Y24" s="54"/>
     </row>
-    <row r="25" spans="2:25">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
@@ -26284,7 +26284,7 @@
       <c r="X25" s="53"/>
       <c r="Y25" s="54"/>
     </row>
-    <row r="26" spans="2:25">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
@@ -26312,7 +26312,7 @@
       <c r="X26" s="53"/>
       <c r="Y26" s="54"/>
     </row>
-    <row r="27" spans="2:25">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B27" s="6" t="s">
         <v>28</v>
       </c>
@@ -26342,7 +26342,7 @@
       <c r="X27" s="53"/>
       <c r="Y27" s="54"/>
     </row>
-    <row r="28" spans="2:25">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B28" s="6" t="s">
         <v>32</v>
       </c>
@@ -26376,7 +26376,7 @@
       <c r="X28" s="53"/>
       <c r="Y28" s="54"/>
     </row>
-    <row r="29" spans="2:25">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B29" s="6" t="s">
         <v>35</v>
       </c>
@@ -26404,7 +26404,7 @@
       <c r="X29" s="53"/>
       <c r="Y29" s="54"/>
     </row>
-    <row r="30" spans="2:25">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
@@ -26434,7 +26434,7 @@
       <c r="X30" s="53"/>
       <c r="Y30" s="54"/>
     </row>
-    <row r="31" spans="2:25">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
@@ -26464,7 +26464,7 @@
       <c r="X31" s="53"/>
       <c r="Y31" s="54"/>
     </row>
-    <row r="32" spans="2:25">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B32" s="12" t="s">
         <v>45</v>
       </c>
@@ -26494,7 +26494,7 @@
       <c r="X32" s="53"/>
       <c r="Y32" s="54"/>
     </row>
-    <row r="33" spans="2:25">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>48</v>
       </c>
@@ -26524,7 +26524,7 @@
       <c r="X33" s="53"/>
       <c r="Y33" s="54"/>
     </row>
-    <row r="34" spans="2:25">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B34" s="12" t="s">
         <v>49</v>
       </c>
@@ -26554,7 +26554,7 @@
       <c r="X34" s="53"/>
       <c r="Y34" s="54"/>
     </row>
-    <row r="35" spans="2:25">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -26584,7 +26584,7 @@
       <c r="X35" s="53"/>
       <c r="Y35" s="54"/>
     </row>
-    <row r="36" spans="2:25">
+    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B36" s="5"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -26609,7 +26609,7 @@
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
     </row>
-    <row r="37" spans="2:25">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="5"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -26634,7 +26634,7 @@
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
     </row>
-    <row r="38" spans="2:25">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>280</v>
       </c>
@@ -26681,7 +26681,7 @@
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
     </row>
-    <row r="39" spans="2:25">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
@@ -26718,7 +26718,7 @@
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
     </row>
-    <row r="40" spans="2:25">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
@@ -26745,7 +26745,7 @@
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
     </row>
-    <row r="41" spans="2:25">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
@@ -26772,7 +26772,7 @@
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
     </row>
-    <row r="42" spans="2:25">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>21</v>
       </c>
@@ -26799,7 +26799,7 @@
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
     </row>
-    <row r="43" spans="2:25">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
@@ -26836,7 +26836,7 @@
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
     </row>
-    <row r="44" spans="2:25">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B44" s="6" t="s">
         <v>26</v>
       </c>
@@ -26863,7 +26863,7 @@
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
     </row>
-    <row r="45" spans="2:25">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B45" s="6" t="s">
         <v>28</v>
       </c>
@@ -26890,7 +26890,7 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
     </row>
-    <row r="46" spans="2:25">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B46" s="6" t="s">
         <v>32</v>
       </c>
@@ -26917,7 +26917,7 @@
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
     </row>
-    <row r="47" spans="2:25">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" s="6" t="s">
         <v>35</v>
       </c>
@@ -26944,7 +26944,7 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
     </row>
-    <row r="48" spans="2:25">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>37</v>
       </c>
@@ -26971,7 +26971,7 @@
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
     </row>
-    <row r="49" spans="2:25">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>40</v>
       </c>
@@ -26998,7 +26998,7 @@
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
     </row>
-    <row r="50" spans="2:25">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B50" s="12" t="s">
         <v>45</v>
       </c>
@@ -27025,7 +27025,7 @@
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
     </row>
-    <row r="51" spans="2:25">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
         <v>48</v>
       </c>
@@ -27052,7 +27052,7 @@
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
     </row>
-    <row r="52" spans="2:25">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B52" s="12" t="s">
         <v>49</v>
       </c>
@@ -27079,7 +27079,7 @@
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
     </row>
-    <row r="53" spans="2:25">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>50</v>
       </c>
@@ -27106,7 +27106,7 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
     </row>
-    <row r="54" spans="2:25">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B54" s="5"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -27131,7 +27131,7 @@
       <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
     </row>
-    <row r="55" spans="2:25">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B55" s="5">
         <v>1</v>
       </c>
@@ -27147,7 +27147,7 @@
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="2:25">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B56" s="5">
         <v>2</v>
       </c>
@@ -27161,7 +27161,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:25">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B57" s="8">
         <v>3</v>
       </c>
@@ -27176,7 +27176,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="2:25">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B58" s="5">
         <v>4</v>
       </c>
@@ -27190,7 +27190,7 @@
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="2:25">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="E59" s="5"/>
@@ -27200,7 +27200,7 @@
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="2:25">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="E60" s="5"/>
@@ -27210,7 +27210,7 @@
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="2:25">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
     </row>
@@ -27884,13 +27884,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5052" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE060ADC-98B8-41C5-873E-FE5FD11A7018}"/>
+  <xr:revisionPtr revIDLastSave="5056" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{695146F3-1C70-4F42-AAB5-295F27FA9276}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -22545,10 +22545,10 @@
       <c r="N46" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O46" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="P46" s="78"/>
+      <c r="O46" s="53" t="s">
+        <v>296</v>
+      </c>
+      <c r="P46" s="54"/>
       <c r="Q46" s="77" t="s">
         <v>94</v>
       </c>
@@ -22873,10 +22873,8 @@
       <c r="N53" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O53" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="P53" s="20"/>
+      <c r="O53" s="23"/>
+      <c r="P53" s="24"/>
       <c r="Q53" s="19" t="s">
         <v>103</v>
       </c>
@@ -22919,8 +22917,10 @@
       <c r="N54" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O54" s="23"/>
-      <c r="P54" s="24"/>
+      <c r="O54" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="P54" s="78"/>
       <c r="Q54" s="19" t="s">
         <v>103</v>
       </c>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5056" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{695146F3-1C70-4F42-AAB5-295F27FA9276}"/>
+  <xr:revisionPtr revIDLastSave="5061" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12EB4A47-469D-4F23-AC39-F99A59A6DA5E}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4586" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4587" uniqueCount="310">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1002,6 +1002,9 @@
   </si>
   <si>
     <t>SF KUT SUR BN</t>
+  </si>
+  <si>
+    <t>Vernerunde</t>
   </si>
 </sst>
 </file>
@@ -23732,10 +23735,10 @@
         <v>9</v>
       </c>
       <c r="I2" s="26"/>
-      <c r="J2" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="26"/>
+      <c r="J2" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="K2" s="20"/>
       <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
@@ -23998,8 +24001,10 @@
       <c r="G8" s="42"/>
       <c r="H8" s="23"/>
       <c r="I8" s="24"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="24"/>
+      <c r="J8" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="K8" s="20"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="6" t="s">

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5063" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{431789FE-0C09-4DCA-905C-9F400E26CB62}"/>
+  <xr:revisionPtr revIDLastSave="5103" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C17BDD02-C165-441F-BE9B-D47761E9F506}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4587" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4608" uniqueCount="315">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1005,6 +1005,21 @@
   </si>
   <si>
     <t>Vernerunde</t>
+  </si>
+  <si>
+    <t>SE ZV 5</t>
+  </si>
+  <si>
+    <t>SE EV 1</t>
+  </si>
+  <si>
+    <t>SE DU 1</t>
+  </si>
+  <si>
+    <t>SF KR 1</t>
+  </si>
+  <si>
+    <t>TC-kurs</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1088,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1209,6 +1224,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1296,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1595,6 +1616,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -17946,14 +17973,14 @@
         <v>9</v>
       </c>
       <c r="T10" s="24"/>
-      <c r="U10" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="V10" s="24"/>
-      <c r="W10" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="X10" s="24"/>
+      <c r="U10" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="V10" s="26"/>
+      <c r="W10" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="X10" s="26"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
@@ -20091,7 +20118,7 @@
       <c r="A65" s="8"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hjYyUMenwKWLov5unNA4EuR72hjTjF/+EqnCDrvl8TBmODgazVmrBof3rw8JLzhNz+a+hLWWXOp5FCmYWgDsPQ==" saltValue="YYO3AbOtmCG6ROeDzVBdOQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="470">
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="F49:G49"/>
@@ -20805,7 +20832,7 @@
       </c>
       <c r="P4" s="38"/>
       <c r="Q4" s="37" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="R4" s="38"/>
       <c r="S4" s="37" t="s">
@@ -20849,7 +20876,7 @@
       </c>
       <c r="P5" s="38"/>
       <c r="Q5" s="37" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="R5" s="38"/>
       <c r="S5" s="37" t="s">
@@ -21791,7 +21818,7 @@
       </c>
       <c r="P29" s="18"/>
       <c r="Q29" s="43" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="R29" s="44"/>
       <c r="S29" s="17" t="s">
@@ -21837,7 +21864,7 @@
       <c r="O30" s="21"/>
       <c r="P30" s="22"/>
       <c r="Q30" s="43" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="R30" s="44"/>
       <c r="S30" s="17" t="s">
@@ -22359,21 +22386,19 @@
       </c>
       <c r="P42" s="40"/>
       <c r="Q42" s="39" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="R42" s="40"/>
       <c r="S42" s="39" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="T42" s="40"/>
       <c r="U42" s="17" t="s">
         <v>124</v>
       </c>
       <c r="V42" s="18"/>
-      <c r="W42" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="X42" s="20"/>
+      <c r="W42" s="23"/>
+      <c r="X42" s="24"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
@@ -22409,21 +22434,19 @@
       </c>
       <c r="P43" s="40"/>
       <c r="Q43" s="39" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="R43" s="40"/>
       <c r="S43" s="39" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="T43" s="40"/>
       <c r="U43" s="17" t="s">
         <v>124</v>
       </c>
       <c r="V43" s="18"/>
-      <c r="W43" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="X43" s="20"/>
+      <c r="W43" s="23"/>
+      <c r="X43" s="24"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -22463,17 +22486,15 @@
       </c>
       <c r="R44" s="18"/>
       <c r="S44" s="27" t="s">
-        <v>108</v>
+        <v>311</v>
       </c>
       <c r="T44" s="28"/>
       <c r="U44" s="17" t="s">
         <v>124</v>
       </c>
       <c r="V44" s="18"/>
-      <c r="W44" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="X44" s="20"/>
+      <c r="W44" s="23"/>
+      <c r="X44" s="24"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -22557,7 +22578,7 @@
       </c>
       <c r="R46" s="74"/>
       <c r="S46" s="27" t="s">
-        <v>108</v>
+        <v>311</v>
       </c>
       <c r="T46" s="28"/>
       <c r="U46" s="17" t="s">
@@ -22844,8 +22865,10 @@
         <v>124</v>
       </c>
       <c r="T52" s="18"/>
-      <c r="U52" s="23"/>
-      <c r="V52" s="24"/>
+      <c r="U52" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="V52" s="20"/>
       <c r="W52" s="17" t="s">
         <v>103</v>
       </c>
@@ -22886,8 +22909,10 @@
         <v>124</v>
       </c>
       <c r="T53" s="18"/>
-      <c r="U53" s="23"/>
-      <c r="V53" s="24"/>
+      <c r="U53" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="V53" s="20"/>
       <c r="W53" s="17" t="s">
         <v>103</v>
       </c>
@@ -22932,8 +22957,10 @@
         <v>103</v>
       </c>
       <c r="T54" s="18"/>
-      <c r="U54" s="33"/>
-      <c r="V54" s="34"/>
+      <c r="U54" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="V54" s="20"/>
       <c r="W54" s="23"/>
       <c r="X54" s="24"/>
     </row>
@@ -23890,14 +23917,10 @@
         <v>31</v>
       </c>
       <c r="T5" s="20"/>
-      <c r="U5" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="V5" s="20"/>
-      <c r="W5" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="X5" s="20"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="34"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="34"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -23978,14 +24001,12 @@
         <v>31</v>
       </c>
       <c r="T7" s="20"/>
-      <c r="U7" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="V7" s="20"/>
-      <c r="W7" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="X7" s="20"/>
+      <c r="U7" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="V7" s="103"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="34"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
@@ -24022,14 +24043,12 @@
         <v>31</v>
       </c>
       <c r="T8" s="20"/>
-      <c r="U8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="V8" s="20"/>
-      <c r="W8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="X8" s="20"/>
+      <c r="U8" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="V8" s="103"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="34"/>
     </row>
     <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -24288,10 +24307,14 @@
       <c r="N14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O14" s="23"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="24"/>
+      <c r="O14" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" s="20"/>
       <c r="S14" s="23"/>
       <c r="T14" s="24"/>
       <c r="U14" s="23"/>
@@ -24320,10 +24343,14 @@
       <c r="N15" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O15" s="23"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="24"/>
+      <c r="O15" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="R15" s="20"/>
       <c r="S15" s="23"/>
       <c r="T15" s="24"/>
       <c r="U15" s="33"/>
@@ -24348,10 +24375,14 @@
       <c r="N16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O16" s="23"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="24"/>
+      <c r="O16" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="20"/>
       <c r="S16" s="23"/>
       <c r="T16" s="24"/>
       <c r="U16" s="23"/>
@@ -24777,10 +24808,14 @@
         <v>31</v>
       </c>
       <c r="P26" s="20"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="22"/>
+      <c r="Q26" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="R26" s="18"/>
+      <c r="S26" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="T26" s="18"/>
       <c r="U26" s="19" t="s">
         <v>31</v>
       </c>
@@ -24967,8 +25002,10 @@
       <c r="N30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O30" s="23"/>
-      <c r="P30" s="24"/>
+      <c r="O30" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="P30" s="18"/>
       <c r="Q30" s="17" t="s">
         <v>103</v>
       </c>
@@ -25029,8 +25066,10 @@
         <v>103</v>
       </c>
       <c r="V31" s="18"/>
-      <c r="W31" s="23"/>
-      <c r="X31" s="24"/>
+      <c r="W31" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="X31" s="18"/>
     </row>
     <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -25071,8 +25110,10 @@
         <v>103</v>
       </c>
       <c r="T32" s="18"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="24"/>
+      <c r="U32" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="V32" s="18"/>
       <c r="W32" s="23"/>
       <c r="X32" s="24"/>
     </row>
@@ -25103,16 +25144,24 @@
       <c r="N33" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O33" s="23"/>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="24"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="24"/>
-      <c r="U33" s="33"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="23"/>
-      <c r="X33" s="24"/>
+      <c r="O33" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="P33" s="103"/>
+      <c r="Q33" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="R33" s="103"/>
+      <c r="S33" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="T33" s="103"/>
+      <c r="U33" s="23"/>
+      <c r="V33" s="24"/>
+      <c r="W33" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="X33" s="103"/>
     </row>
     <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -25133,16 +25182,24 @@
       <c r="N34" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O34" s="23"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="24"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="24"/>
+      <c r="O34" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="P34" s="103"/>
+      <c r="Q34" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="R34" s="103"/>
+      <c r="S34" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="T34" s="103"/>
       <c r="U34" s="23"/>
       <c r="V34" s="24"/>
-      <c r="W34" s="23"/>
-      <c r="X34" s="24"/>
+      <c r="W34" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="X34" s="103"/>
     </row>
     <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
@@ -25500,8 +25557,10 @@
       <c r="C43" s="24"/>
       <c r="D43" s="23"/>
       <c r="E43" s="24"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="34"/>
+      <c r="F43" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="G43" s="103"/>
       <c r="H43" s="35" t="s">
         <v>291</v>
       </c>
@@ -25542,8 +25601,10 @@
       <c r="C44" s="22"/>
       <c r="D44" s="21"/>
       <c r="E44" s="22"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="22"/>
+      <c r="F44" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="G44" s="103"/>
       <c r="H44" s="35" t="s">
         <v>291</v>
       </c>
@@ -25789,10 +25850,14 @@
       <c r="N49" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O49" s="21"/>
-      <c r="P49" s="22"/>
-      <c r="Q49" s="21"/>
-      <c r="R49" s="22"/>
+      <c r="O49" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="P49" s="103"/>
+      <c r="Q49" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="R49" s="103"/>
       <c r="S49" s="21"/>
       <c r="T49" s="22"/>
       <c r="U49" s="41" t="s">
@@ -25829,10 +25894,14 @@
       <c r="N50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O50" s="23"/>
-      <c r="P50" s="24"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="24"/>
+      <c r="O50" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="P50" s="103"/>
+      <c r="Q50" s="102" t="s">
+        <v>313</v>
+      </c>
+      <c r="R50" s="103"/>
       <c r="S50" s="17" t="s">
         <v>307</v>
       </c>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5557" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D581332F-998C-4836-8FCD-83ACFD5BE2B5}"/>
+  <xr:revisionPtr revIDLastSave="5566" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E19C653-941E-4618-B4A4-53DBEC2907B9}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4692" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4692" uniqueCount="317">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1023,6 +1023,9 @@
   </si>
   <si>
     <t>Uke 51</t>
+  </si>
+  <si>
+    <t>eCoach</t>
   </si>
 </sst>
 </file>
@@ -20845,10 +20848,10 @@
         <v>9</v>
       </c>
       <c r="G4" s="24"/>
-      <c r="H4" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="24"/>
+      <c r="H4" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="I4" s="20"/>
       <c r="J4" s="23" t="s">
         <v>9</v>
       </c>
@@ -20885,10 +20888,10 @@
         <v>106</v>
       </c>
       <c r="C5" s="26"/>
-      <c r="D5" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="24"/>
+      <c r="D5" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5" s="20"/>
       <c r="F5" s="25" t="s">
         <v>106</v>
       </c>
@@ -21173,18 +21176,18 @@
         <v>252</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E11" s="20"/>
+      <c r="D11" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="E11" s="38"/>
       <c r="F11" s="23" t="s">
         <v>9</v>
       </c>
       <c r="G11" s="24"/>
-      <c r="H11" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="I11" s="20"/>
+      <c r="H11" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I11" s="38"/>
       <c r="J11" s="19" t="s">
         <v>252</v>
       </c>
@@ -21317,18 +21320,18 @@
         <v>106</v>
       </c>
       <c r="C14" s="26"/>
-      <c r="D14" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="24"/>
+      <c r="D14" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="E14" s="38"/>
       <c r="F14" s="25" t="s">
         <v>106</v>
       </c>
       <c r="G14" s="26"/>
-      <c r="H14" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="24"/>
+      <c r="H14" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I14" s="38"/>
       <c r="J14" s="19" t="s">
         <v>252</v>
       </c>
@@ -21365,18 +21368,18 @@
         <v>67</v>
       </c>
       <c r="C15" s="28"/>
-      <c r="D15" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="24"/>
+      <c r="D15" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="E15" s="38"/>
       <c r="F15" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G15" s="28"/>
-      <c r="H15" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="24"/>
+      <c r="H15" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I15" s="38"/>
       <c r="J15" s="27" t="s">
         <v>67</v>
       </c>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5849" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30EFA7C6-3F9E-44FA-BFA3-92F26DFE3C2E}"/>
+  <xr:revisionPtr revIDLastSave="5850" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1B8240F-8F3E-4643-A6CD-7AD19AFC9937}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -21067,10 +21067,10 @@
         <v>9</v>
       </c>
       <c r="V7" s="18"/>
-      <c r="W7" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="X7" s="18"/>
+      <c r="W7" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="X7" s="40"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5850" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1B8240F-8F3E-4643-A6CD-7AD19AFC9937}"/>
+  <xr:revisionPtr revIDLastSave="5851" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{644A0937-59ED-47A9-9195-747585BCFBCA}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -23400,6 +23400,7 @@
       <c r="X66" s="5"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="abtbS9bUgpSUBvPN2b1PCdIzoB39qhfOrjCw5kLrn6gJM0rL9uKV9J/Mn8fdgRagvvMdVAF21VA/RhqWw++Dog==" saltValue="8ITZfm7LyOU/u8/BxmqjdQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="468">
     <mergeCell ref="S18:T18"/>
     <mergeCell ref="S56:T56"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5854" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EBBC73D-205B-4CF5-9C9E-18C8FEFD856F}"/>
+  <xr:revisionPtr revIDLastSave="5866" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69D230CB-F2B4-4FFB-9927-23DC992BA7D7}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4698" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="339">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1086,6 +1086,12 @@
   </si>
   <si>
     <t>Oppl AP</t>
+  </si>
+  <si>
+    <t>SF AN 3</t>
+  </si>
+  <si>
+    <t>SE AN 3</t>
   </si>
 </sst>
 </file>
@@ -24117,10 +24123,10 @@
         <v>293</v>
       </c>
       <c r="T4" s="24"/>
-      <c r="U4" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="V4" s="24"/>
+      <c r="U4" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="V4" s="48"/>
       <c r="W4" s="23" t="s">
         <v>293</v>
       </c>
@@ -24161,8 +24167,10 @@
         <v>31</v>
       </c>
       <c r="T5" s="18"/>
-      <c r="U5" s="89"/>
-      <c r="V5" s="90"/>
+      <c r="U5" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="V5" s="24"/>
       <c r="W5" s="89"/>
       <c r="X5" s="90"/>
     </row>
@@ -24218,10 +24226,14 @@
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="38"/>
+      <c r="B7" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="70"/>
+      <c r="D7" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="E7" s="70"/>
       <c r="F7" s="21" t="s">
         <v>270</v>
       </c>
@@ -24256,16 +24268,22 @@
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="76"/>
+      <c r="B8" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" s="70"/>
+      <c r="D8" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="E8" s="70"/>
       <c r="F8" s="21" t="s">
         <v>270</v>
       </c>
       <c r="G8" s="22"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="38"/>
+      <c r="H8" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="I8" s="70"/>
       <c r="J8" s="25" t="s">
         <v>290</v>
       </c>
@@ -24308,10 +24326,14 @@
         <v>270</v>
       </c>
       <c r="G9" s="22"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="38"/>
+      <c r="H9" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="I9" s="70"/>
+      <c r="J9" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="K9" s="70"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="6" t="s">
@@ -24546,8 +24568,10 @@
         <v>124</v>
       </c>
       <c r="I14" s="26"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="38"/>
+      <c r="J14" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="K14" s="70"/>
       <c r="N14" s="1" t="s">
         <v>48</v>
       </c>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5866" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69D230CB-F2B4-4FFB-9927-23DC992BA7D7}"/>
+  <xr:revisionPtr revIDLastSave="5872" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F51A85C-063B-4D3C-8294-99442036BD5A}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="340">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1092,6 +1092,9 @@
   </si>
   <si>
     <t>SE AN 3</t>
+  </si>
+  <si>
+    <t>9 SF SB 1</t>
   </si>
 </sst>
 </file>
@@ -20202,6 +20205,7 @@
       <c r="A65" s="8"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="9X2Oca31rDxUokv/yyWnmt4upa2g5nu/U1SDl3xWUn89j+DGiIzHDIHGs+HKy+/Vnc6ez3nkYkpO+GvxV9Rjaw==" saltValue="qAoFET+pSFRc3NRyje4iNg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="470">
     <mergeCell ref="J46:K46"/>
     <mergeCell ref="Q53:R53"/>
@@ -20906,10 +20910,10 @@
         <v>253</v>
       </c>
       <c r="I4" s="40"/>
-      <c r="J4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="38"/>
+      <c r="J4" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="K4" s="26"/>
       <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
@@ -20929,10 +20933,10 @@
         <v>72</v>
       </c>
       <c r="V4" s="48"/>
-      <c r="W4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="X4" s="38"/>
+      <c r="W4" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="X4" s="26"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -21326,10 +21330,10 @@
         <v>330</v>
       </c>
       <c r="C13" s="18"/>
-      <c r="D13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="38"/>
+      <c r="D13" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="26"/>
       <c r="F13" s="17" t="s">
         <v>330</v>
       </c>
@@ -23406,6 +23410,7 @@
       <c r="X66" s="5"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="vUYzY50fszWTIG9v2a8mNZ5w8Qvau7eRgRZm3hc7ZZpc0c+dzCI+Gi3NZfEQadmYT5mIitlm8IDZPciI0Hw2mQ==" saltValue="aWXrfQc0aVQMieV2gtxiOQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="468">
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="D57:E57"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5898" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB9709F4-41BE-48AC-85FA-A3CC24CB03F5}"/>
+  <xr:revisionPtr revIDLastSave="5901" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A1B8C5B-9744-4A45-8059-D2624F04501D}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="38730" windowHeight="21210" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -56,17 +56,17 @@
   <commentList>
     <comment ref="U37" authorId="0" shapeId="0" xr:uid="{65E4B43F-4DA4-4023-9E8A-D4F24A3B2C8C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     RTC SUR KURS</t>
       </text>
     </comment>
     <comment ref="W37" authorId="1" shapeId="0" xr:uid="{BC2FB818-859F-40F5-95A2-BC57CF0AD42E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     KUT SUR (RTC)?</t>
       </text>
     </comment>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4719" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4718" uniqueCount="345">
   <si>
     <t>Uke 01</t>
   </si>
@@ -833,290 +833,290 @@
     <t>Booking Q4</t>
   </si>
   <si>
+    <t>SF TC 3</t>
+  </si>
+  <si>
+    <t>9 SF TC 3</t>
+  </si>
+  <si>
+    <t>9 SF HF 5</t>
+  </si>
+  <si>
+    <t>9 SF MS 5</t>
+  </si>
+  <si>
+    <t>SF AN 1</t>
+  </si>
+  <si>
+    <t>SF HF 5</t>
+  </si>
+  <si>
+    <t>9 SF AN 1</t>
+  </si>
+  <si>
+    <t>SF RTC (ML)</t>
+  </si>
+  <si>
+    <t>Uke 33</t>
+  </si>
+  <si>
+    <t>Uke 36</t>
+  </si>
+  <si>
+    <t>Møte HR</t>
+  </si>
+  <si>
+    <t>Lofoten</t>
+  </si>
+  <si>
+    <t>Transisjonkurs</t>
+  </si>
+  <si>
+    <t>SF HF 1</t>
+  </si>
+  <si>
+    <t>9 SF RTC AW</t>
+  </si>
+  <si>
+    <t>Uke 37</t>
+  </si>
+  <si>
+    <t>Uke 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEAST </t>
+  </si>
+  <si>
+    <t>SF BR 4</t>
+  </si>
+  <si>
+    <t>SF EV 4</t>
+  </si>
+  <si>
+    <t>SF RTC SUR/1</t>
+  </si>
+  <si>
+    <t>SF TO 2</t>
+  </si>
+  <si>
+    <t>SE ZV 4</t>
+  </si>
+  <si>
+    <t>Uke 38</t>
+  </si>
+  <si>
+    <t>Uke 41</t>
+  </si>
+  <si>
+    <t>SE DU 1</t>
+  </si>
+  <si>
+    <t>SF DU 1</t>
+  </si>
+  <si>
+    <t>9 SF FL 1</t>
+  </si>
+  <si>
+    <t>SF RTC AW</t>
+  </si>
+  <si>
+    <t>Uke 39</t>
+  </si>
+  <si>
+    <t>Uke 42</t>
+  </si>
+  <si>
+    <t>SE BR 4</t>
+  </si>
+  <si>
+    <t>SE EV 1</t>
+  </si>
+  <si>
+    <t>SE AFIS gr. Utd</t>
+  </si>
+  <si>
+    <t>SF HD 1</t>
+  </si>
+  <si>
+    <t>SE ZV 5</t>
+  </si>
+  <si>
+    <t>Uke 43</t>
+  </si>
+  <si>
+    <t>Uke 46</t>
+  </si>
+  <si>
+    <t>Vernerunde</t>
+  </si>
+  <si>
+    <t>OPL-samling</t>
+  </si>
+  <si>
+    <t>SF ZV 4</t>
+  </si>
+  <si>
+    <t>SF VA 4</t>
+  </si>
+  <si>
+    <t>SF KR 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF MS SUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE VD SUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF VD SUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE MS SUR </t>
+  </si>
+  <si>
+    <t>TVS</t>
+  </si>
+  <si>
+    <t>Uke 44</t>
+  </si>
+  <si>
+    <t>Uke 47</t>
+  </si>
+  <si>
+    <t>SE NA 1</t>
+  </si>
+  <si>
+    <t>SF NA 1</t>
+  </si>
+  <si>
+    <t>Uke 45</t>
+  </si>
+  <si>
+    <t>Uke 48</t>
+  </si>
+  <si>
+    <t>F&amp;P</t>
+  </si>
+  <si>
+    <t>Booking Q1</t>
+  </si>
+  <si>
+    <t>SF RA 1</t>
+  </si>
+  <si>
+    <t>SF KUT SUR OV</t>
+  </si>
+  <si>
+    <t>SF KUT SUR BN</t>
+  </si>
+  <si>
+    <t>Uke 49</t>
+  </si>
+  <si>
+    <t>Uke 52</t>
+  </si>
+  <si>
+    <t>Uke 50</t>
+  </si>
+  <si>
+    <t>Uke 53</t>
+  </si>
+  <si>
+    <t>Uke 51</t>
+  </si>
+  <si>
+    <t>9 SF TO 2</t>
+  </si>
+  <si>
+    <t>9 SF BR 4</t>
+  </si>
+  <si>
+    <t>9 SF RTC SUR/1</t>
+  </si>
+  <si>
+    <t>9 SF EV 4</t>
+  </si>
+  <si>
+    <t>9 SE ZV 4</t>
+  </si>
+  <si>
+    <t>9 SE DU 1</t>
+  </si>
+  <si>
+    <t>9 SF AFIS gr. Utd</t>
+  </si>
+  <si>
+    <t>9 SE BR 4</t>
+  </si>
+  <si>
+    <t>9 SE EV 1</t>
+  </si>
+  <si>
+    <t>9 SE AFIS gr. Utd</t>
+  </si>
+  <si>
+    <t>9 SE ZV 5</t>
+  </si>
+  <si>
+    <t>9 SF HD 1</t>
+  </si>
+  <si>
+    <t>A-Lofoten</t>
+  </si>
+  <si>
+    <t>9 SF VA 4</t>
+  </si>
+  <si>
+    <t>9 SF ZV 4</t>
+  </si>
+  <si>
+    <t>9 SF GM 2/4</t>
+  </si>
+  <si>
+    <t>SF GM 2/4</t>
+  </si>
+  <si>
+    <t>9 SF RTC 2 AW</t>
+  </si>
+  <si>
+    <t>eCoach-kurs</t>
+  </si>
+  <si>
+    <t>SF GM 2/4 oppl</t>
+  </si>
+  <si>
+    <t>Oppl AP</t>
+  </si>
+  <si>
+    <t>SF AN 3</t>
+  </si>
+  <si>
+    <t>SE AN 3</t>
+  </si>
+  <si>
+    <t>9 SF SB 1</t>
+  </si>
+  <si>
+    <t>SF KUT SUR SK</t>
+  </si>
+  <si>
+    <t>9 SF TC 3 Demo</t>
+  </si>
+  <si>
+    <t>SF TC 3 Demo</t>
+  </si>
+  <si>
     <t>ELPAC/ SF TC 3</t>
   </si>
   <si>
-    <t>SF TC 3</t>
-  </si>
-  <si>
-    <t>9 SF TC 3</t>
-  </si>
-  <si>
-    <t>9 SF TC 3 Demo</t>
-  </si>
-  <si>
-    <t>9 SF HF 5</t>
-  </si>
-  <si>
-    <t>9 SF MS 5</t>
-  </si>
-  <si>
-    <t>SF AN 1</t>
-  </si>
-  <si>
-    <t>SF HF 5</t>
-  </si>
-  <si>
     <t>SF MS 5</t>
-  </si>
-  <si>
-    <t>9 SF AN 1</t>
-  </si>
-  <si>
-    <t>SF RTC (ML)</t>
-  </si>
-  <si>
-    <t>SF TC 3 Demo</t>
-  </si>
-  <si>
-    <t>Uke 33</t>
-  </si>
-  <si>
-    <t>Uke 36</t>
-  </si>
-  <si>
-    <t>Møte HR</t>
-  </si>
-  <si>
-    <t>Lofoten</t>
-  </si>
-  <si>
-    <t>Transisjonkurs</t>
-  </si>
-  <si>
-    <t>SF HF 1</t>
-  </si>
-  <si>
-    <t>9 SF RTC AW</t>
-  </si>
-  <si>
-    <t>Uke 37</t>
-  </si>
-  <si>
-    <t>Uke 40</t>
-  </si>
-  <si>
-    <t>A-Lofoten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAST </t>
-  </si>
-  <si>
-    <t>SF TO 2</t>
-  </si>
-  <si>
-    <t>9 SF SB 1</t>
-  </si>
-  <si>
-    <t>SF BR 4</t>
-  </si>
-  <si>
-    <t>9 SE ZV 4</t>
-  </si>
-  <si>
-    <t>SF RTC SUR/1</t>
-  </si>
-  <si>
-    <t>Oppl AP</t>
-  </si>
-  <si>
-    <t>9 SF BR 4</t>
-  </si>
-  <si>
-    <t>9 SF RTC SUR/1</t>
-  </si>
-  <si>
-    <t>eCoach-kurs</t>
-  </si>
-  <si>
-    <t>9 SF EV 4</t>
-  </si>
-  <si>
-    <t>9 SF TO 2</t>
-  </si>
-  <si>
-    <t>9 SF ZV 4</t>
-  </si>
-  <si>
-    <t>SF ZV 4</t>
-  </si>
-  <si>
-    <t>SF EV 4</t>
-  </si>
-  <si>
-    <t>SE ZV 4</t>
-  </si>
-  <si>
-    <t>Uke 38</t>
-  </si>
-  <si>
-    <t>Uke 41</t>
-  </si>
-  <si>
-    <t>9 SF VA 4</t>
-  </si>
-  <si>
-    <t>SF VA 4</t>
-  </si>
-  <si>
-    <t>SF GM 2/4 oppl</t>
-  </si>
-  <si>
-    <t>9 SF GM 2/4</t>
-  </si>
-  <si>
-    <t>SF GM 2/4</t>
-  </si>
-  <si>
-    <t>SF RTC AW</t>
-  </si>
-  <si>
-    <t>9 SE DU 1</t>
-  </si>
-  <si>
-    <t>SF DU 1</t>
-  </si>
-  <si>
-    <t>9 SF AFIS gr. Utd</t>
-  </si>
-  <si>
-    <t>9 SF FL 1</t>
-  </si>
-  <si>
-    <t>SE DU 1</t>
-  </si>
-  <si>
-    <t>Uke 39</t>
-  </si>
-  <si>
-    <t>Uke 42</t>
-  </si>
-  <si>
-    <t>SE BR 4</t>
-  </si>
-  <si>
-    <t>9 SE BR 4</t>
-  </si>
-  <si>
-    <t>SF HD 1</t>
-  </si>
-  <si>
-    <t>9 SE EV 1</t>
-  </si>
-  <si>
-    <t>9 SF HD 1</t>
-  </si>
-  <si>
-    <t>SE AFIS gr. Utd</t>
-  </si>
-  <si>
-    <t>9 SE ZV 5</t>
-  </si>
-  <si>
-    <t>SE ZV 5</t>
-  </si>
-  <si>
-    <t>9 SF RTC 2 AW</t>
-  </si>
-  <si>
-    <t>9 SE AFIS gr. Utd</t>
-  </si>
-  <si>
-    <t>SE EV 1</t>
-  </si>
-  <si>
-    <t>Uke 43</t>
-  </si>
-  <si>
-    <t>Uke 46</t>
-  </si>
-  <si>
-    <t>Vernerunde</t>
-  </si>
-  <si>
-    <t>OPL-samling</t>
-  </si>
-  <si>
-    <t>SF AN 3</t>
-  </si>
-  <si>
-    <t>SF KR 1</t>
-  </si>
-  <si>
-    <t>SE AN 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF MS SUR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE VD SUR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF VD SUR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE MS SUR </t>
-  </si>
-  <si>
-    <t>TVS</t>
-  </si>
-  <si>
-    <t>Uke 44</t>
-  </si>
-  <si>
-    <t>Uke 47</t>
-  </si>
-  <si>
-    <t>SE NA 1</t>
-  </si>
-  <si>
-    <t>SF NA 1</t>
-  </si>
-  <si>
-    <t>Uke 45</t>
-  </si>
-  <si>
-    <t>Uke 48</t>
-  </si>
-  <si>
-    <t>F&amp;P</t>
-  </si>
-  <si>
-    <t>Booking Q1</t>
-  </si>
-  <si>
-    <t>SF RA 1</t>
-  </si>
-  <si>
-    <t>SF KUT SUR OV</t>
-  </si>
-  <si>
-    <t>SF KUT SUR BN</t>
-  </si>
-  <si>
-    <t>Uke 49</t>
-  </si>
-  <si>
-    <t>Uke 52</t>
-  </si>
-  <si>
-    <t>SF KUT SUR SK</t>
-  </si>
-  <si>
-    <t>Uke 50</t>
-  </si>
-  <si>
-    <t>Uke 53</t>
-  </si>
-  <si>
-    <t>Uke 51</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1178,7 +1178,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1320,12 +1320,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF00FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1413,7 +1407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1718,12 +1712,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2097,7 +2085,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="5" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -2126,7 +2114,7 @@
     <col min="28" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2199,7 +2187,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2250,7 +2238,7 @@
       </c>
       <c r="AA2" s="32"/>
     </row>
-    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2301,7 +2289,7 @@
       </c>
       <c r="AA3" s="52"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2352,7 +2340,7 @@
       </c>
       <c r="AA4" s="32"/>
     </row>
-    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -2403,7 +2391,7 @@
       </c>
       <c r="AA5" s="58"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2454,7 +2442,7 @@
       </c>
       <c r="AA6" s="20"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -2505,7 +2493,7 @@
       </c>
       <c r="AA7" s="18"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -2556,7 +2544,7 @@
       </c>
       <c r="AA8" s="28"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -2607,7 +2595,7 @@
       </c>
       <c r="AA9" s="58"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -2658,7 +2646,7 @@
       </c>
       <c r="AA10" s="20"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -2709,7 +2697,7 @@
       </c>
       <c r="AA11" s="52"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -2760,7 +2748,7 @@
       </c>
       <c r="AA12" s="28"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -2811,7 +2799,7 @@
       </c>
       <c r="AA13" s="28"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -2862,7 +2850,7 @@
       </c>
       <c r="AA14" s="58"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -2913,7 +2901,7 @@
       </c>
       <c r="AA15" s="32"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -2960,7 +2948,7 @@
       <c r="Z16" s="21"/>
       <c r="AA16" s="22"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2995,7 +2983,7 @@
       <c r="Z17" s="21"/>
       <c r="AA17" s="22"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -3030,7 +3018,7 @@
       <c r="Z18" s="21"/>
       <c r="AA18" s="22"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -3051,7 +3039,7 @@
       </c>
       <c r="U19" s="34"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -3072,7 +3060,7 @@
       </c>
       <c r="U20" s="58"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -3090,7 +3078,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -3108,7 +3096,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -3181,7 +3169,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3234,7 +3222,7 @@
       </c>
       <c r="AA24" s="20"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -3287,7 +3275,7 @@
       </c>
       <c r="AA25" s="20"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -3340,7 +3328,7 @@
       </c>
       <c r="AA26" s="58"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -3393,7 +3381,7 @@
       </c>
       <c r="AA27" s="18"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
@@ -3446,7 +3434,7 @@
       </c>
       <c r="AA28" s="22"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>26</v>
       </c>
@@ -3499,7 +3487,7 @@
       </c>
       <c r="AA29" s="30"/>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>28</v>
       </c>
@@ -3552,7 +3540,7 @@
       </c>
       <c r="AA30" s="22"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -3605,7 +3593,7 @@
       </c>
       <c r="AA31" s="18"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -3658,7 +3646,7 @@
       </c>
       <c r="AA32" s="58"/>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
@@ -3711,7 +3699,7 @@
       </c>
       <c r="AA33" s="18"/>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -3764,7 +3752,7 @@
       </c>
       <c r="AA34" s="58"/>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>45</v>
       </c>
@@ -3817,7 +3805,7 @@
       </c>
       <c r="AA35" s="28"/>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>48</v>
       </c>
@@ -3870,7 +3858,7 @@
       </c>
       <c r="AA36" s="28"/>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>49</v>
       </c>
@@ -3923,7 +3911,7 @@
       </c>
       <c r="AA37" s="28"/>
     </row>
-    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -3972,7 +3960,7 @@
       <c r="Z38" s="21"/>
       <c r="AA38" s="22"/>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -3993,7 +3981,7 @@
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -4011,7 +3999,7 @@
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>69</v>
       </c>
@@ -4084,7 +4072,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -4137,7 +4125,7 @@
       </c>
       <c r="AA42" s="36"/>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -4190,7 +4178,7 @@
       </c>
       <c r="AA43" s="22"/>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -4243,7 +4231,7 @@
       </c>
       <c r="AA44" s="50"/>
     </row>
-    <row r="45" spans="1:27" ht="15" customHeight="1">
+    <row r="45" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -4296,7 +4284,7 @@
       </c>
       <c r="AA45" s="18"/>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -4349,7 +4337,7 @@
       </c>
       <c r="AA46" s="20"/>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
@@ -4402,7 +4390,7 @@
       </c>
       <c r="AA47" s="22"/>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>28</v>
       </c>
@@ -4455,7 +4443,7 @@
       </c>
       <c r="AA48" s="18"/>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>32</v>
       </c>
@@ -4508,7 +4496,7 @@
       </c>
       <c r="AA49" s="28"/>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
@@ -4561,7 +4549,7 @@
       </c>
       <c r="AA50" s="22"/>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -4609,7 +4597,7 @@
       </c>
       <c r="AA51" s="50"/>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -4657,7 +4645,7 @@
       </c>
       <c r="AA52" s="28"/>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
@@ -4705,7 +4693,7 @@
       </c>
       <c r="AA53" s="20"/>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>48</v>
       </c>
@@ -4753,7 +4741,7 @@
       </c>
       <c r="AA54" s="28"/>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>49</v>
       </c>
@@ -4801,7 +4789,7 @@
       </c>
       <c r="AA55" s="50"/>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -4841,7 +4829,7 @@
       <c r="Z56" s="21"/>
       <c r="AA56" s="22"/>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -4855,7 +4843,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -4869,7 +4857,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -4883,7 +4871,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -5377,7 +5365,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X78"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -5406,7 +5394,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -5474,7 +5462,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -5522,7 +5510,7 @@
       </c>
       <c r="X2" s="20"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -5570,7 +5558,7 @@
       </c>
       <c r="X3" s="20"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -5618,7 +5606,7 @@
       </c>
       <c r="X4" s="20"/>
     </row>
-    <row r="5" spans="1:24" ht="11.25" customHeight="1">
+    <row r="5" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5666,7 +5654,7 @@
       </c>
       <c r="X5" s="20"/>
     </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -5714,7 +5702,7 @@
       </c>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -5762,7 +5750,7 @@
       </c>
       <c r="X7" s="40"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -5810,7 +5798,7 @@
       </c>
       <c r="X8" s="28"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -5858,7 +5846,7 @@
       </c>
       <c r="X9" s="20"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -5906,7 +5894,7 @@
       </c>
       <c r="X10" s="22"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -5954,7 +5942,7 @@
       </c>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -6002,7 +5990,7 @@
       </c>
       <c r="X12" s="28"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -6050,7 +6038,7 @@
       </c>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -6098,7 +6086,7 @@
       </c>
       <c r="X14" s="28"/>
     </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -6146,7 +6134,7 @@
       </c>
       <c r="X15" s="20"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -6186,7 +6174,7 @@
       <c r="W16" s="21"/>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -6210,7 +6198,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -6234,7 +6222,7 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -6258,7 +6246,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>97</v>
       </c>
@@ -6326,7 +6314,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -6374,7 +6362,7 @@
       </c>
       <c r="X21" s="82"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -6422,7 +6410,7 @@
       </c>
       <c r="X22" s="20"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -6470,7 +6458,7 @@
       </c>
       <c r="X23" s="28"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -6518,7 +6506,7 @@
       </c>
       <c r="X24" s="28"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -6566,7 +6554,7 @@
       </c>
       <c r="X25" s="20"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -6614,7 +6602,7 @@
       </c>
       <c r="X26" s="28"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
@@ -6662,7 +6650,7 @@
       </c>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>32</v>
       </c>
@@ -6710,7 +6698,7 @@
       </c>
       <c r="X28" s="26"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>35</v>
       </c>
@@ -6758,7 +6746,7 @@
       </c>
       <c r="X29" s="34"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -6808,7 +6796,7 @@
       </c>
       <c r="X30" s="26"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -6858,7 +6846,7 @@
       </c>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>45</v>
       </c>
@@ -6908,7 +6896,7 @@
       </c>
       <c r="X32" s="34"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -6958,7 +6946,7 @@
       </c>
       <c r="X33" s="34"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>49</v>
       </c>
@@ -7008,7 +6996,7 @@
       </c>
       <c r="X34" s="26"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -7048,7 +7036,7 @@
       </c>
       <c r="X35" s="34"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -7083,7 +7071,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -7106,7 +7094,7 @@
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -7129,12 +7117,12 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="M39" s="7"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>109</v>
       </c>
@@ -7203,7 +7191,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -7252,7 +7240,7 @@
       </c>
       <c r="X41" s="20"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -7300,7 +7288,7 @@
       </c>
       <c r="X42" s="20"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -7348,7 +7336,7 @@
       </c>
       <c r="X43" s="20"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -7396,7 +7384,7 @@
       </c>
       <c r="X44" s="52"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -7444,7 +7432,7 @@
       </c>
       <c r="X45" s="20"/>
     </row>
-    <row r="46" spans="1:24" ht="10.5" customHeight="1">
+    <row r="46" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -7493,7 +7481,7 @@
       </c>
       <c r="X46" s="28"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -7542,7 +7530,7 @@
       </c>
       <c r="X47" s="28"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -7591,7 +7579,7 @@
       </c>
       <c r="X48" s="34"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -7640,7 +7628,7 @@
       </c>
       <c r="X49" s="52"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -7689,7 +7677,7 @@
       </c>
       <c r="X50" s="34"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -7737,7 +7725,7 @@
       </c>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -7785,7 +7773,7 @@
       </c>
       <c r="X52" s="28"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -7833,7 +7821,7 @@
       </c>
       <c r="X53" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -7882,7 +7870,7 @@
       </c>
       <c r="X54" s="18"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -7925,7 +7913,7 @@
       </c>
       <c r="X55" s="34"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
@@ -7962,7 +7950,7 @@
       <c r="W56" s="9"/>
       <c r="X56" s="9"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -7987,7 +7975,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -8001,7 +7989,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -8015,7 +8003,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -8035,7 +8023,7 @@
       <c r="W60" s="9"/>
       <c r="X60" s="9"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -8047,34 +8035,34 @@
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="R62" s="9"/>
     </row>
-    <row r="71" spans="13:13">
+    <row r="71" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="13:13">
+    <row r="72" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M72" s="5"/>
     </row>
-    <row r="73" spans="13:13">
+    <row r="73" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M73" s="5"/>
     </row>
-    <row r="74" spans="13:13">
+    <row r="74" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M74" s="5"/>
     </row>
-    <row r="75" spans="13:13">
+    <row r="75" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M75" s="5"/>
     </row>
-    <row r="76" spans="13:13">
+    <row r="76" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="13:13">
+    <row r="77" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M77" s="5"/>
     </row>
-    <row r="78" spans="13:13">
+    <row r="78" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M78" s="5"/>
     </row>
   </sheetData>
@@ -8558,7 +8546,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X66"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -8588,7 +8576,7 @@
     <col min="27" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
@@ -8656,7 +8644,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -8704,7 +8692,7 @@
       </c>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -8752,7 +8740,7 @@
       </c>
       <c r="X3" s="24"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -8800,7 +8788,7 @@
       </c>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -8848,7 +8836,7 @@
       </c>
       <c r="X5" s="24"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -8896,7 +8884,7 @@
       </c>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -8944,7 +8932,7 @@
       </c>
       <c r="X7" s="18"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -8992,7 +8980,7 @@
       </c>
       <c r="X8" s="26"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -9040,7 +9028,7 @@
       </c>
       <c r="X9" s="18"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -9088,7 +9076,7 @@
       </c>
       <c r="X10" s="26"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -9136,7 +9124,7 @@
       </c>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -9184,7 +9172,7 @@
       </c>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -9232,7 +9220,7 @@
       </c>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -9280,7 +9268,7 @@
       </c>
       <c r="X14" s="24"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -9328,7 +9316,7 @@
       </c>
       <c r="X15" s="24"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -9368,7 +9356,7 @@
       <c r="W16" s="21"/>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="7"/>
@@ -9381,7 +9369,7 @@
       </c>
       <c r="V17" s="18"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="7"/>
@@ -9390,7 +9378,7 @@
       </c>
       <c r="P18" s="18"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="7"/>
@@ -9399,7 +9387,7 @@
       </c>
       <c r="P19" s="24"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="7"/>
@@ -9408,7 +9396,7 @@
       </c>
       <c r="P20" s="24"/>
     </row>
-    <row r="21" spans="1:24" ht="11.25" customHeight="1">
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="7"/>
@@ -9417,7 +9405,7 @@
       </c>
       <c r="P21" s="24"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="7"/>
@@ -9426,17 +9414,17 @@
       </c>
       <c r="P22" s="24"/>
     </row>
-    <row r="23" spans="1:24" ht="11.25" customHeight="1">
+    <row r="23" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:24" ht="11.25" customHeight="1">
+    <row r="24" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>154</v>
       </c>
@@ -9506,7 +9494,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -9552,7 +9540,7 @@
       </c>
       <c r="X26" s="20"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -9598,7 +9586,7 @@
       </c>
       <c r="X27" s="32"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -9644,7 +9632,7 @@
       </c>
       <c r="X28" s="78"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -9690,7 +9678,7 @@
       </c>
       <c r="X29" s="28"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -9736,7 +9724,7 @@
       </c>
       <c r="X30" s="20"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
@@ -9782,7 +9770,7 @@
       </c>
       <c r="X31" s="28"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>28</v>
       </c>
@@ -9828,7 +9816,7 @@
       </c>
       <c r="X32" s="78"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
@@ -9870,7 +9858,7 @@
       </c>
       <c r="X33" s="58"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -9916,7 +9904,7 @@
       </c>
       <c r="X34" s="20"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -9962,7 +9950,7 @@
       </c>
       <c r="X35" s="18"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
@@ -10008,7 +9996,7 @@
       </c>
       <c r="X36" s="58"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>45</v>
       </c>
@@ -10054,7 +10042,7 @@
       </c>
       <c r="X37" s="18"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
@@ -10100,7 +10088,7 @@
       </c>
       <c r="X38" s="28"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>49</v>
       </c>
@@ -10146,7 +10134,7 @@
       </c>
       <c r="X39" s="58"/>
     </row>
-    <row r="40" spans="1:24" ht="11.25" customHeight="1">
+    <row r="40" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
@@ -10188,7 +10176,7 @@
       <c r="W40" s="21"/>
       <c r="X40" s="22"/>
     </row>
-    <row r="41" spans="1:24" ht="11.25" customHeight="1">
+    <row r="41" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -10203,7 +10191,7 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="11.25" customHeight="1">
+    <row r="42" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -10218,7 +10206,7 @@
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="11.25" customHeight="1">
+    <row r="43" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>166</v>
       </c>
@@ -10288,7 +10276,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="11.25" customHeight="1">
+    <row r="44" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -10334,7 +10322,7 @@
       <c r="W44" s="59"/>
       <c r="X44" s="60"/>
     </row>
-    <row r="45" spans="1:24" ht="11.25" customHeight="1">
+    <row r="45" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -10380,7 +10368,7 @@
       <c r="W45" s="59"/>
       <c r="X45" s="60"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -10426,7 +10414,7 @@
       <c r="W46" s="59"/>
       <c r="X46" s="60"/>
     </row>
-    <row r="47" spans="1:24" ht="11.25" customHeight="1">
+    <row r="47" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -10470,7 +10458,7 @@
       <c r="W47" s="59"/>
       <c r="X47" s="60"/>
     </row>
-    <row r="48" spans="1:24" ht="11.25" customHeight="1">
+    <row r="48" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
@@ -10514,7 +10502,7 @@
       <c r="W48" s="59"/>
       <c r="X48" s="60"/>
     </row>
-    <row r="49" spans="1:24" ht="11.25" customHeight="1">
+    <row r="49" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>26</v>
       </c>
@@ -10558,7 +10546,7 @@
       <c r="W49" s="59"/>
       <c r="X49" s="60"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>28</v>
       </c>
@@ -10602,7 +10590,7 @@
       <c r="W50" s="59"/>
       <c r="X50" s="60"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>32</v>
       </c>
@@ -10648,7 +10636,7 @@
       <c r="W51" s="59"/>
       <c r="X51" s="60"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>35</v>
       </c>
@@ -10694,7 +10682,7 @@
       <c r="W52" s="59"/>
       <c r="X52" s="60"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>37</v>
       </c>
@@ -10740,7 +10728,7 @@
       <c r="W53" s="59"/>
       <c r="X53" s="60"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>40</v>
       </c>
@@ -10786,7 +10774,7 @@
       <c r="W54" s="59"/>
       <c r="X54" s="60"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>45</v>
       </c>
@@ -10832,7 +10820,7 @@
       <c r="W55" s="59"/>
       <c r="X55" s="60"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>48</v>
       </c>
@@ -10878,7 +10866,7 @@
       <c r="W56" s="59"/>
       <c r="X56" s="60"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>49</v>
       </c>
@@ -10924,7 +10912,7 @@
       <c r="W57" s="59"/>
       <c r="X57" s="60"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>50</v>
       </c>
@@ -10964,7 +10952,7 @@
       <c r="W58" s="59"/>
       <c r="X58" s="60"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="O59" s="51" t="s">
@@ -10980,7 +10968,7 @@
       </c>
       <c r="T59" s="52"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -10998,7 +10986,7 @@
       </c>
       <c r="P60" s="28"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -11012,7 +11000,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>3</v>
       </c>
@@ -11026,7 +11014,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>4</v>
       </c>
@@ -11034,17 +11022,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -11532,7 +11520,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X62"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -11561,7 +11549,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>178</v>
       </c>
@@ -11629,7 +11617,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -11675,7 +11663,7 @@
       </c>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -11721,7 +11709,7 @@
       </c>
       <c r="X3" s="20"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -11767,7 +11755,7 @@
       </c>
       <c r="X4" s="22"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -11814,7 +11802,7 @@
       </c>
       <c r="X5" s="52"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -11860,7 +11848,7 @@
       </c>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -11906,7 +11894,7 @@
       </c>
       <c r="X7" s="78"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -11952,7 +11940,7 @@
       </c>
       <c r="X8" s="78"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -11998,7 +11986,7 @@
       </c>
       <c r="X9" s="38"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -12044,7 +12032,7 @@
       </c>
       <c r="X10" s="26"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -12090,7 +12078,7 @@
       </c>
       <c r="X11" s="52"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -12136,7 +12124,7 @@
       </c>
       <c r="X12" s="26"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -12182,7 +12170,7 @@
       </c>
       <c r="X13" s="38"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -12228,7 +12216,7 @@
       </c>
       <c r="X14" s="26"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -12274,7 +12262,7 @@
       </c>
       <c r="X15" s="52"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -12314,7 +12302,7 @@
       <c r="W16" s="21"/>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>195</v>
       </c>
@@ -12341,7 +12329,7 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B18" s="17" t="s">
         <v>196</v>
       </c>
@@ -12353,7 +12341,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -12362,7 +12350,7 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -12373,7 +12361,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>197</v>
       </c>
@@ -12441,7 +12429,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -12487,7 +12475,7 @@
       </c>
       <c r="X22" s="36"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -12533,7 +12521,7 @@
       </c>
       <c r="X23" s="32"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -12579,7 +12567,7 @@
       </c>
       <c r="X24" s="22"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -12625,7 +12613,7 @@
       </c>
       <c r="X25" s="38"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -12671,7 +12659,7 @@
       </c>
       <c r="X26" s="20"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -12717,7 +12705,7 @@
       </c>
       <c r="X27" s="26"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -12763,7 +12751,7 @@
       </c>
       <c r="X28" s="38"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -12809,7 +12797,7 @@
       </c>
       <c r="X29" s="20"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -12855,7 +12843,7 @@
       </c>
       <c r="X30" s="20"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -12901,7 +12889,7 @@
       </c>
       <c r="X31" s="52"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -12949,7 +12937,7 @@
       </c>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -12997,7 +12985,7 @@
       </c>
       <c r="X33" s="26"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -13045,7 +13033,7 @@
       </c>
       <c r="X34" s="52"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -13093,7 +13081,7 @@
       </c>
       <c r="X35" s="26"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -13135,7 +13123,7 @@
       </c>
       <c r="X36" s="52"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="4"/>
@@ -13143,7 +13131,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="4"/>
@@ -13151,7 +13139,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="4"/>
@@ -13159,7 +13147,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>212</v>
       </c>
@@ -13229,7 +13217,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -13279,7 +13267,7 @@
       </c>
       <c r="X41" s="36"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -13329,7 +13317,7 @@
       </c>
       <c r="X42" s="22"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -13379,7 +13367,7 @@
       </c>
       <c r="X43" s="22"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -13427,7 +13415,7 @@
       </c>
       <c r="X44" s="58"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -13475,7 +13463,7 @@
       </c>
       <c r="X45" s="20"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -13523,7 +13511,7 @@
       </c>
       <c r="X46" s="20"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -13571,7 +13559,7 @@
       </c>
       <c r="X47" s="42"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -13619,7 +13607,7 @@
       </c>
       <c r="X48" s="32"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -13667,7 +13655,7 @@
       </c>
       <c r="X49" s="20"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -13715,7 +13703,7 @@
       </c>
       <c r="X50" s="20"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -13765,7 +13753,7 @@
       </c>
       <c r="X51" s="20"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -13815,7 +13803,7 @@
       </c>
       <c r="X52" s="58"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -13865,7 +13853,7 @@
       </c>
       <c r="X53" s="58"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -13913,7 +13901,7 @@
       </c>
       <c r="X54" s="32"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -13955,7 +13943,7 @@
       <c r="W55" s="21"/>
       <c r="X55" s="22"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -13985,7 +13973,7 @@
       <c r="W56" s="21"/>
       <c r="X56" s="22"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="8"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -14010,7 +13998,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="8"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -14023,7 +14011,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>1</v>
       </c>
@@ -14048,7 +14036,7 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>2</v>
       </c>
@@ -14062,7 +14050,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>3</v>
       </c>
@@ -14076,7 +14064,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>4</v>
       </c>
@@ -14568,7 +14556,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -14597,7 +14585,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
@@ -14665,7 +14653,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -14713,7 +14701,7 @@
       </c>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -14761,7 +14749,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -14809,7 +14797,7 @@
       </c>
       <c r="X4" s="40"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -14857,7 +14845,7 @@
       </c>
       <c r="X5" s="32"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -14905,7 +14893,7 @@
       </c>
       <c r="X6" s="40"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -14953,7 +14941,7 @@
       </c>
       <c r="X7" s="22"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -15001,7 +14989,7 @@
       </c>
       <c r="X8" s="22"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -15049,7 +15037,7 @@
       </c>
       <c r="X9" s="22"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -15097,7 +15085,7 @@
       </c>
       <c r="X10" s="32"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -15145,7 +15133,7 @@
       </c>
       <c r="X11" s="32"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -15193,7 +15181,7 @@
       </c>
       <c r="X12" s="22"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -15241,7 +15229,7 @@
       </c>
       <c r="X13" s="22"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -15289,7 +15277,7 @@
       </c>
       <c r="X14" s="22"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -15337,7 +15325,7 @@
       </c>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -15381,9 +15369,9 @@
       </c>
       <c r="X16" s="32"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -15451,7 +15439,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -15499,7 +15487,7 @@
       </c>
       <c r="X20" s="32"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -15547,7 +15535,7 @@
       </c>
       <c r="X21" s="32"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -15595,7 +15583,7 @@
       </c>
       <c r="X22" s="32"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -15643,7 +15631,7 @@
       </c>
       <c r="X23" s="32"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -15691,7 +15679,7 @@
       </c>
       <c r="X24" s="32"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -15739,7 +15727,7 @@
       </c>
       <c r="X25" s="32"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -15787,7 +15775,7 @@
       </c>
       <c r="X26" s="22"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -15835,7 +15823,7 @@
       </c>
       <c r="X27" s="22"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -15883,7 +15871,7 @@
       </c>
       <c r="X28" s="32"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -15933,7 +15921,7 @@
       </c>
       <c r="X29" s="32"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -15983,7 +15971,7 @@
       </c>
       <c r="X30" s="32"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -16033,7 +16021,7 @@
       </c>
       <c r="X31" s="22"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -16083,7 +16071,7 @@
       </c>
       <c r="X32" s="32"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -16133,7 +16121,7 @@
       </c>
       <c r="X33" s="22"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -16183,7 +16171,7 @@
       </c>
       <c r="X34" s="32"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -16208,11 +16196,11 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" ht="11.25" customHeight="1">
+    <row r="36" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24" ht="11.25" customHeight="1">
+    <row r="37" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>236</v>
       </c>
@@ -16282,7 +16270,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="11.25" customHeight="1">
+    <row r="38" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -16332,7 +16320,7 @@
       </c>
       <c r="X38" s="32"/>
     </row>
-    <row r="39" spans="1:24" ht="10.5" customHeight="1">
+    <row r="39" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -16382,7 +16370,7 @@
       </c>
       <c r="X39" s="32"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -16432,7 +16420,7 @@
       </c>
       <c r="X40" s="32"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -16480,7 +16468,7 @@
       </c>
       <c r="X41" s="32"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -16528,7 +16516,7 @@
       </c>
       <c r="X42" s="32"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -16576,7 +16564,7 @@
       </c>
       <c r="X43" s="32"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -16624,7 +16612,7 @@
       </c>
       <c r="X44" s="22"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -16672,7 +16660,7 @@
       </c>
       <c r="X45" s="22"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -16720,7 +16708,7 @@
       </c>
       <c r="X46" s="32"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -16768,7 +16756,7 @@
       </c>
       <c r="X47" s="22"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
@@ -16816,7 +16804,7 @@
       </c>
       <c r="X48" s="32"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -16864,7 +16852,7 @@
       </c>
       <c r="X49" s="22"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -16912,7 +16900,7 @@
       </c>
       <c r="X50" s="32"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -16960,7 +16948,7 @@
       </c>
       <c r="X51" s="22"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -17008,7 +16996,7 @@
       </c>
       <c r="X52" s="32"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -17022,7 +17010,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -17038,7 +17026,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -17054,7 +17042,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -17064,15 +17052,15 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -17555,7 +17543,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -17584,7 +17572,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -17652,7 +17640,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -17700,7 +17688,7 @@
       </c>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -17748,7 +17736,7 @@
       </c>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -17796,7 +17784,7 @@
       </c>
       <c r="X4" s="20"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -17844,7 +17832,7 @@
       </c>
       <c r="X5" s="28"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -17892,7 +17880,7 @@
       </c>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -17940,7 +17928,7 @@
       </c>
       <c r="X7" s="22"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -17988,7 +17976,7 @@
       </c>
       <c r="X8" s="22"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -18036,7 +18024,7 @@
       </c>
       <c r="X9" s="32"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -18084,7 +18072,7 @@
       </c>
       <c r="X10" s="20"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -18132,7 +18120,7 @@
       </c>
       <c r="X11" s="20"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -18180,7 +18168,7 @@
       </c>
       <c r="X12" s="32"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -18228,7 +18216,7 @@
       </c>
       <c r="X13" s="32"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -18276,7 +18264,7 @@
       </c>
       <c r="X14" s="20"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -18324,7 +18312,7 @@
       </c>
       <c r="X15" s="32"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -18370,7 +18358,7 @@
       </c>
       <c r="X16" s="28"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -18398,7 +18386,7 @@
       <c r="W17" s="21"/>
       <c r="X17" s="22"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -18426,7 +18414,7 @@
       <c r="W18" s="21"/>
       <c r="X18" s="22"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -18450,7 +18438,7 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -18474,7 +18462,7 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>249</v>
       </c>
@@ -18542,7 +18530,7 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -18590,7 +18578,7 @@
       </c>
       <c r="X22" s="36"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -18638,7 +18626,7 @@
       </c>
       <c r="X23" s="22"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -18670,7 +18658,7 @@
       </c>
       <c r="P24" s="22"/>
       <c r="Q24" s="17" t="s">
-        <v>252</v>
+        <v>343</v>
       </c>
       <c r="R24" s="18"/>
       <c r="S24" s="19" t="s">
@@ -18678,7 +18666,7 @@
       </c>
       <c r="T24" s="20"/>
       <c r="U24" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="V24" s="26"/>
       <c r="W24" s="27" t="s">
@@ -18686,7 +18674,7 @@
       </c>
       <c r="X24" s="28"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -18714,19 +18702,19 @@
         <v>21</v>
       </c>
       <c r="O25" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P25" s="26"/>
       <c r="Q25" s="25" t="s">
-        <v>255</v>
+        <v>341</v>
       </c>
       <c r="R25" s="26"/>
       <c r="S25" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T25" s="26"/>
       <c r="U25" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V25" s="26"/>
       <c r="W25" s="27" t="s">
@@ -18734,7 +18722,7 @@
       </c>
       <c r="X25" s="28"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -18782,7 +18770,7 @@
       </c>
       <c r="X26" s="46"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -18803,18 +18791,18 @@
       </c>
       <c r="I27" s="22"/>
       <c r="J27" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K27" s="20"/>
       <c r="N27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O27" s="19" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P27" s="20"/>
       <c r="Q27" s="19" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R27" s="20"/>
       <c r="S27" s="21" t="s">
@@ -18822,15 +18810,15 @@
       </c>
       <c r="T27" s="22"/>
       <c r="U27" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="V27" s="24"/>
       <c r="W27" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="X27" s="24"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -18878,7 +18866,7 @@
       </c>
       <c r="X28" s="20"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -18926,7 +18914,7 @@
       </c>
       <c r="X29" s="32"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -18947,7 +18935,7 @@
       </c>
       <c r="I30" s="22"/>
       <c r="J30" s="19" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K30" s="20"/>
       <c r="N30" s="6" t="s">
@@ -18958,7 +18946,7 @@
       </c>
       <c r="P30" s="22"/>
       <c r="Q30" s="19" t="s">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="R30" s="20"/>
       <c r="S30" s="21" t="s">
@@ -18966,15 +18954,15 @@
       </c>
       <c r="T30" s="22"/>
       <c r="U30" s="23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="V30" s="24"/>
       <c r="W30" s="23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="X30" s="24"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -19022,7 +19010,7 @@
       </c>
       <c r="X31" s="20"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -19031,7 +19019,7 @@
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="17" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E32" s="18"/>
       <c r="F32" s="19" t="s">
@@ -19070,7 +19058,7 @@
       </c>
       <c r="X32" s="34"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -19106,7 +19094,7 @@
       </c>
       <c r="R33" s="28"/>
       <c r="S33" s="23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T33" s="24"/>
       <c r="U33" s="33" t="s">
@@ -19118,7 +19106,7 @@
       </c>
       <c r="X33" s="34"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -19154,7 +19142,7 @@
       </c>
       <c r="R34" s="28"/>
       <c r="S34" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="T34" s="24"/>
       <c r="U34" s="33" t="s">
@@ -19166,7 +19154,7 @@
       </c>
       <c r="X34" s="34"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -19214,7 +19202,7 @@
       </c>
       <c r="X35" s="32"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -19244,35 +19232,35 @@
         <v>50</v>
       </c>
       <c r="O36" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P36" s="26"/>
       <c r="Q36" s="25" t="s">
-        <v>263</v>
+        <v>342</v>
       </c>
       <c r="R36" s="26"/>
       <c r="S36" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T36" s="26"/>
       <c r="U36" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="V36" s="26"/>
       <c r="W36" s="21"/>
       <c r="X36" s="22"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>1</v>
@@ -19307,7 +19295,7 @@
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>1</v>
@@ -19340,7 +19328,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -19353,7 +19341,7 @@
       </c>
       <c r="E40" s="36"/>
       <c r="F40" s="39" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="35" t="s">
@@ -19386,11 +19374,11 @@
       </c>
       <c r="V40" s="36"/>
       <c r="W40" s="49" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="X40" s="50"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>10</v>
       </c>
@@ -19403,7 +19391,7 @@
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="39" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="21" t="s">
@@ -19440,7 +19428,7 @@
       </c>
       <c r="X41" s="22"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -19488,16 +19476,16 @@
       </c>
       <c r="X42" s="34"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="17" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43" s="31" t="s">
@@ -19505,11 +19493,11 @@
       </c>
       <c r="G43" s="32"/>
       <c r="H43" s="17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I43" s="18"/>
       <c r="J43" s="17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K43" s="18"/>
       <c r="N43" s="1" t="s">
@@ -19520,23 +19508,23 @@
       </c>
       <c r="P43" s="18"/>
       <c r="Q43" s="23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="R43" s="24"/>
       <c r="S43" s="23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T43" s="24"/>
       <c r="U43" s="23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="V43" s="24"/>
       <c r="W43" s="23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="X43" s="24"/>
     </row>
-    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
@@ -19549,7 +19537,7 @@
       </c>
       <c r="E44" s="20"/>
       <c r="F44" s="39" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G44" s="40"/>
       <c r="H44" s="19" t="s">
@@ -19584,7 +19572,7 @@
       </c>
       <c r="X44" s="20"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>26</v>
       </c>
@@ -19632,7 +19620,7 @@
       </c>
       <c r="X45" s="34"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>28</v>
       </c>
@@ -19682,16 +19670,16 @@
       </c>
       <c r="X46" s="28"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E47" s="20"/>
       <c r="F47" s="21" t="s">
@@ -19730,16 +19718,16 @@
       </c>
       <c r="X47" s="34"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="19" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E48" s="20"/>
       <c r="F48" s="21" t="s">
@@ -19778,7 +19766,7 @@
       </c>
       <c r="X48" s="28"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
@@ -19787,11 +19775,11 @@
       </c>
       <c r="C49" s="22"/>
       <c r="D49" s="17" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="19" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G49" s="20"/>
       <c r="H49" s="21" t="s">
@@ -19814,7 +19802,7 @@
       </c>
       <c r="R49" s="28"/>
       <c r="S49" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T49" s="26"/>
       <c r="U49" s="27" t="s">
@@ -19822,11 +19810,11 @@
       </c>
       <c r="V49" s="28"/>
       <c r="W49" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="X49" s="26"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>40</v>
       </c>
@@ -19862,19 +19850,19 @@
       </c>
       <c r="R50" s="20"/>
       <c r="S50" s="17" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="T50" s="18"/>
       <c r="U50" s="17" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="V50" s="18"/>
       <c r="W50" s="17" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>45</v>
       </c>
@@ -19922,7 +19910,7 @@
       </c>
       <c r="X51" s="30"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
@@ -19954,23 +19942,23 @@
       </c>
       <c r="P52" s="18"/>
       <c r="Q52" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="R52" s="24"/>
       <c r="S52" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="T52" s="24"/>
       <c r="U52" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="V52" s="24"/>
       <c r="W52" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="X52" s="24"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>49</v>
       </c>
@@ -19991,7 +19979,7 @@
       </c>
       <c r="I53" s="22"/>
       <c r="J53" s="19" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="K53" s="20"/>
       <c r="N53" s="12" t="s">
@@ -20002,23 +19990,23 @@
       </c>
       <c r="P53" s="18"/>
       <c r="Q53" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R53" s="26"/>
       <c r="S53" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T53" s="26"/>
       <c r="U53" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V53" s="26"/>
       <c r="W53" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X53" s="26"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
@@ -20048,23 +20036,23 @@
       </c>
       <c r="P54" s="18"/>
       <c r="Q54" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="R54" s="26"/>
       <c r="S54" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T54" s="26"/>
       <c r="U54" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="V54" s="26"/>
       <c r="W54" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="X54" s="26"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -20100,7 +20088,7 @@
       </c>
       <c r="X55" s="30"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -20128,7 +20116,7 @@
       <c r="W56" s="21"/>
       <c r="X56" s="22"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -20151,7 +20139,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -20165,7 +20153,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -20179,7 +20167,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -20193,7 +20181,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -20201,22 +20189,22 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="8"/>
     </row>
   </sheetData>
@@ -20710,7 +20698,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X66"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -20740,9 +20728,9 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -20775,7 +20763,7 @@
         <v>46276</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -20808,28 +20796,28 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="C2" s="50"/>
       <c r="D2" s="49" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="E2" s="50"/>
       <c r="F2" s="49" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="G2" s="50"/>
       <c r="H2" s="49" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="I2" s="50"/>
       <c r="J2" s="49" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="K2" s="50"/>
       <c r="N2" s="1" t="s">
@@ -20856,7 +20844,7 @@
       </c>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -20884,19 +20872,19 @@
         <v>10</v>
       </c>
       <c r="O3" s="100" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="P3" s="101"/>
       <c r="Q3" s="100" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="R3" s="101"/>
       <c r="S3" s="100" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="T3" s="101"/>
       <c r="U3" s="100" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="V3" s="101"/>
       <c r="W3" s="21" t="s">
@@ -20904,7 +20892,7 @@
       </c>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -20913,7 +20901,7 @@
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E4" s="26"/>
       <c r="F4" s="21" t="s">
@@ -20921,7 +20909,7 @@
       </c>
       <c r="G4" s="22"/>
       <c r="H4" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I4" s="26"/>
       <c r="J4" s="21" t="s">
@@ -20936,11 +20924,11 @@
       </c>
       <c r="P4" s="22"/>
       <c r="Q4" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="R4" s="50"/>
       <c r="S4" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="T4" s="50"/>
       <c r="U4" s="39" t="s">
@@ -20948,24 +20936,24 @@
       </c>
       <c r="V4" s="40"/>
       <c r="W4" s="17" t="s">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="X4" s="18"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E5" s="26"/>
       <c r="F5" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G5" s="34"/>
       <c r="H5" s="21" t="s">
@@ -20973,34 +20961,34 @@
       </c>
       <c r="I5" s="22"/>
       <c r="J5" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K5" s="26"/>
       <c r="N5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="P5" s="34"/>
       <c r="Q5" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="R5" s="34"/>
       <c r="S5" s="27" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="T5" s="28"/>
       <c r="U5" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="V5" s="18"/>
       <c r="W5" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="X5" s="18"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -21048,7 +21036,7 @@
       </c>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -21057,7 +21045,7 @@
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="19" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="E7" s="20"/>
       <c r="F7" s="21" t="s">
@@ -21076,15 +21064,15 @@
         <v>26</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="P7" s="34"/>
       <c r="Q7" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="R7" s="34"/>
       <c r="S7" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="T7" s="34"/>
       <c r="U7" s="21" t="s">
@@ -21096,7 +21084,7 @@
       </c>
       <c r="X7" s="32"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -21105,7 +21093,7 @@
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="21" t="s">
@@ -21113,7 +21101,7 @@
       </c>
       <c r="G8" s="22"/>
       <c r="H8" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I8" s="26"/>
       <c r="J8" s="21" t="s">
@@ -21128,11 +21116,11 @@
       </c>
       <c r="P8" s="22"/>
       <c r="Q8" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="R8" s="18"/>
       <c r="S8" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="T8" s="34"/>
       <c r="U8" s="21" t="s">
@@ -21144,12 +21132,12 @@
       </c>
       <c r="X8" s="22"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="21" t="s">
@@ -21192,7 +21180,7 @@
       </c>
       <c r="X9" s="52"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -21224,11 +21212,11 @@
       </c>
       <c r="P10" s="20"/>
       <c r="Q10" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="R10" s="18"/>
       <c r="S10" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="T10" s="18"/>
       <c r="U10" s="19" t="s">
@@ -21240,16 +21228,16 @@
       </c>
       <c r="X10" s="20"/>
     </row>
-    <row r="11" spans="1:24" ht="11.25" customHeight="1">
+    <row r="11" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="19" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="E11" s="20"/>
       <c r="F11" s="21" t="s">
@@ -21257,30 +21245,30 @@
       </c>
       <c r="G11" s="22"/>
       <c r="H11" s="19" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K11" s="26"/>
       <c r="N11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O11" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="P11" s="30"/>
       <c r="Q11" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="R11" s="30"/>
       <c r="S11" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="T11" s="30"/>
       <c r="U11" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="V11" s="18"/>
       <c r="W11" s="21" t="s">
@@ -21288,7 +21276,7 @@
       </c>
       <c r="X11" s="22"/>
     </row>
-    <row r="12" spans="1:24" ht="11.25" customHeight="1">
+    <row r="12" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -21320,11 +21308,11 @@
       </c>
       <c r="P12" s="20"/>
       <c r="Q12" s="49" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="R12" s="50"/>
       <c r="S12" s="49" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="T12" s="50"/>
       <c r="U12" s="19" t="s">
@@ -21336,20 +21324,20 @@
       </c>
       <c r="X12" s="20"/>
     </row>
-    <row r="13" spans="1:24" ht="11.25" customHeight="1">
+    <row r="13" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="17" t="s">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="G13" s="28"/>
       <c r="H13" s="21" t="s">
@@ -21357,70 +21345,70 @@
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="K13" s="28"/>
       <c r="N13" s="12" t="s">
         <v>45</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="P13" s="18"/>
       <c r="Q13" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="R13" s="18"/>
       <c r="S13" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="T13" s="18"/>
       <c r="U13" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="V13" s="18"/>
       <c r="W13" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" ht="11.25" customHeight="1">
+    <row r="14" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="C14" s="34"/>
       <c r="D14" s="19" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="E14" s="20"/>
       <c r="F14" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="G14" s="34"/>
       <c r="H14" s="19" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="I14" s="20"/>
       <c r="J14" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K14" s="26"/>
       <c r="N14" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O14" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="R14" s="34"/>
       <c r="S14" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="T14" s="34"/>
       <c r="U14" s="21" t="s">
@@ -21432,47 +21420,47 @@
       </c>
       <c r="X14" s="52"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="19" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="E15" s="20"/>
       <c r="F15" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G15" s="28"/>
       <c r="H15" s="19" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="I15" s="20"/>
       <c r="J15" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K15" s="28"/>
       <c r="N15" s="12" t="s">
         <v>49</v>
       </c>
       <c r="O15" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="P15" s="30"/>
       <c r="Q15" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="R15" s="30"/>
       <c r="S15" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="T15" s="30"/>
       <c r="U15" s="17" t="s">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="V15" s="18"/>
       <c r="W15" s="21" t="s">
@@ -21480,20 +21468,20 @@
       </c>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="19" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G16" s="34"/>
       <c r="H16" s="21" t="s">
@@ -21528,7 +21516,7 @@
       </c>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -21541,11 +21529,11 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="S17" s="27" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="T17" s="28"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -21558,11 +21546,11 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="S18" s="27" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="T18" s="28"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -21575,7 +21563,7 @@
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -21588,9 +21576,9 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -21623,7 +21611,7 @@
         <v>46283</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>1</v>
@@ -21656,12 +21644,12 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="C22" s="50"/>
       <c r="D22" s="35" t="s">
@@ -21704,7 +21692,7 @@
       </c>
       <c r="X22" s="36"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -21717,11 +21705,11 @@
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="G23" s="52"/>
       <c r="H23" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="I23" s="52"/>
       <c r="J23" s="33" t="s">
@@ -21736,7 +21724,7 @@
       </c>
       <c r="P23" s="22"/>
       <c r="Q23" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="R23" s="34"/>
       <c r="S23" s="21" t="s">
@@ -21752,7 +21740,7 @@
       </c>
       <c r="X23" s="22"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -21761,7 +21749,7 @@
       </c>
       <c r="C24" s="22"/>
       <c r="D24" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E24" s="26"/>
       <c r="F24" s="51" t="s">
@@ -21800,35 +21788,35 @@
       </c>
       <c r="X24" s="32"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="G25" s="30"/>
       <c r="H25" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="I25" s="30"/>
       <c r="J25" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="K25" s="30"/>
       <c r="N25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="O25" s="77" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="P25" s="78"/>
       <c r="Q25" s="17" t="s">
@@ -21848,7 +21836,7 @@
       </c>
       <c r="X25" s="18"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -21896,12 +21884,12 @@
       </c>
       <c r="X26" s="20"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="21" t="s">
@@ -21909,11 +21897,11 @@
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="G27" s="28"/>
       <c r="H27" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="I27" s="28"/>
       <c r="J27" s="21" t="s">
@@ -21944,7 +21932,7 @@
       </c>
       <c r="X27" s="32"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -21957,34 +21945,34 @@
       </c>
       <c r="E28" s="52"/>
       <c r="F28" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="G28" s="78"/>
       <c r="H28" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="I28" s="78"/>
       <c r="J28" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="K28" s="78"/>
       <c r="N28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O28" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="P28" s="78"/>
       <c r="Q28" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="R28" s="78"/>
       <c r="S28" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="T28" s="78"/>
       <c r="U28" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="V28" s="78"/>
       <c r="W28" s="21" t="s">
@@ -21992,7 +21980,7 @@
       </c>
       <c r="X28" s="22"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -22001,46 +21989,46 @@
       </c>
       <c r="C29" s="22"/>
       <c r="D29" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="E29" s="34"/>
       <c r="F29" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="G29" s="34"/>
       <c r="H29" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="I29" s="34"/>
       <c r="J29" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="K29" s="34"/>
       <c r="N29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="O29" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="P29" s="18"/>
       <c r="Q29" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="R29" s="18"/>
       <c r="S29" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="T29" s="18"/>
       <c r="U29" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="V29" s="18"/>
       <c r="W29" s="17" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="X29" s="18"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -22057,7 +22045,7 @@
       </c>
       <c r="G30" s="20"/>
       <c r="H30" s="17" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="I30" s="18"/>
       <c r="J30" s="19" t="s">
@@ -22072,7 +22060,7 @@
       </c>
       <c r="P30" s="20"/>
       <c r="Q30" s="37" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="R30" s="38"/>
       <c r="S30" s="19" t="s">
@@ -22088,28 +22076,28 @@
       </c>
       <c r="X30" s="20"/>
     </row>
-    <row r="31" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="31" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="C31" s="52"/>
       <c r="D31" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="E31" s="52"/>
       <c r="F31" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="G31" s="78"/>
       <c r="H31" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="I31" s="78"/>
       <c r="J31" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="K31" s="78"/>
       <c r="L31" s="7"/>
@@ -22118,27 +22106,27 @@
         <v>37</v>
       </c>
       <c r="O31" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="P31" s="78"/>
       <c r="Q31" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="R31" s="78"/>
       <c r="S31" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="T31" s="78"/>
       <c r="U31" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="V31" s="78"/>
       <c r="W31" s="37" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="X31" s="38"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -22155,7 +22143,7 @@
       </c>
       <c r="G32" s="20"/>
       <c r="H32" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I32" s="26"/>
       <c r="J32" s="19" t="s">
@@ -22188,28 +22176,28 @@
       </c>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E33" s="26"/>
       <c r="F33" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G33" s="26"/>
       <c r="H33" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I33" s="26"/>
       <c r="J33" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K33" s="52"/>
       <c r="L33" s="7"/>
@@ -22218,27 +22206,27 @@
         <v>45</v>
       </c>
       <c r="O33" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="P33" s="18"/>
       <c r="Q33" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="T33" s="18"/>
       <c r="U33" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="V33" s="18"/>
       <c r="W33" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -22247,19 +22235,19 @@
       </c>
       <c r="C34" s="52"/>
       <c r="D34" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E34" s="34"/>
       <c r="F34" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G34" s="34"/>
       <c r="H34" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I34" s="34"/>
       <c r="J34" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="K34" s="34"/>
       <c r="L34" s="7"/>
@@ -22268,32 +22256,32 @@
         <v>48</v>
       </c>
       <c r="O34" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="P34" s="34"/>
       <c r="Q34" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="R34" s="34"/>
       <c r="S34" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="T34" s="34"/>
       <c r="U34" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="V34" s="34"/>
       <c r="W34" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="X34" s="18"/>
     </row>
-    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C35" s="28"/>
       <c r="D35" s="21" t="s">
@@ -22301,11 +22289,11 @@
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G35" s="28"/>
       <c r="H35" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I35" s="28"/>
       <c r="J35" s="51" t="s">
@@ -22318,19 +22306,19 @@
         <v>49</v>
       </c>
       <c r="O35" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="P35" s="34"/>
       <c r="Q35" s="17" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="R35" s="18"/>
       <c r="S35" s="17" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="T35" s="18"/>
       <c r="U35" s="17" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="V35" s="18"/>
       <c r="W35" s="17" t="s">
@@ -22338,24 +22326,24 @@
       </c>
       <c r="X35" s="18"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E36" s="26"/>
       <c r="F36" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G36" s="26"/>
       <c r="H36" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I36" s="26"/>
       <c r="J36" s="21" t="s">
@@ -22372,44 +22360,44 @@
       </c>
       <c r="P36" s="22"/>
       <c r="Q36" s="37" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="R36" s="38"/>
       <c r="S36" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="T36" s="34"/>
       <c r="U36" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="V36" s="34"/>
       <c r="W36" s="37" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="X36" s="38"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C37" s="30"/>
       <c r="D37" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="G37" s="30"/>
       <c r="H37" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="I37" s="30"/>
       <c r="J37" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="K37" s="30"/>
       <c r="L37" s="7"/>
@@ -22425,7 +22413,7 @@
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -22450,7 +22438,7 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -22476,9 +22464,9 @@
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>1</v>
@@ -22513,7 +22501,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="1" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>1</v>
@@ -22546,7 +22534,7 @@
         <v>46311</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -22596,16 +22584,16 @@
       </c>
       <c r="X41" s="36"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="C42" s="52"/>
       <c r="D42" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="E42" s="52"/>
       <c r="F42" s="21" t="s">
@@ -22626,15 +22614,15 @@
         <v>10</v>
       </c>
       <c r="O42" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="P42" s="34"/>
       <c r="Q42" s="33" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="R42" s="34"/>
       <c r="S42" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="T42" s="34"/>
       <c r="U42" s="21" t="s">
@@ -22646,16 +22634,16 @@
       </c>
       <c r="X42" s="22"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B43" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="C43" s="78"/>
       <c r="D43" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="E43" s="78"/>
       <c r="F43" s="21" t="s">
@@ -22663,7 +22651,7 @@
       </c>
       <c r="G43" s="22"/>
       <c r="H43" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="I43" s="78"/>
       <c r="J43" s="51" t="s">
@@ -22676,19 +22664,19 @@
         <v>15</v>
       </c>
       <c r="O43" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="P43" s="34"/>
       <c r="Q43" s="33" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="R43" s="34"/>
       <c r="S43" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="T43" s="34"/>
       <c r="U43" s="98" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="V43" s="99"/>
       <c r="W43" s="21" t="s">
@@ -22696,7 +22684,7 @@
       </c>
       <c r="X43" s="22"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -22726,32 +22714,32 @@
         <v>21</v>
       </c>
       <c r="O44" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="P44" s="78"/>
       <c r="Q44" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="R44" s="78"/>
       <c r="S44" s="29" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="T44" s="30"/>
       <c r="U44" s="98" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="V44" s="99"/>
       <c r="W44" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="X44" s="34"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C45" s="28"/>
       <c r="D45" s="19" t="s">
@@ -22763,7 +22751,7 @@
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I45" s="26"/>
       <c r="J45" s="19" t="s">
@@ -22794,16 +22782,16 @@
       </c>
       <c r="X45" s="20"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="C46" s="28"/>
       <c r="D46" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E46" s="28"/>
       <c r="F46" s="21" t="s">
@@ -22811,7 +22799,7 @@
       </c>
       <c r="G46" s="22"/>
       <c r="H46" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I46" s="28"/>
       <c r="J46" s="21" t="s">
@@ -22822,7 +22810,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="P46" s="18"/>
       <c r="Q46" s="17" t="s">
@@ -22842,39 +22830,39 @@
       </c>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B47" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="C47" s="78"/>
       <c r="D47" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="E47" s="78"/>
       <c r="F47" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G47" s="34"/>
       <c r="H47" s="77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="I47" s="78"/>
       <c r="J47" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K47" s="52"/>
       <c r="N47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O47" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="P47" s="78"/>
       <c r="Q47" s="77" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="R47" s="78"/>
       <c r="S47" s="17" t="s">
@@ -22890,28 +22878,28 @@
       </c>
       <c r="X47" s="22"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="C48" s="34"/>
       <c r="D48" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E48" s="26"/>
       <c r="F48" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="G48" s="34"/>
       <c r="H48" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I48" s="28"/>
       <c r="J48" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="K48" s="28"/>
       <c r="N48" s="6" t="s">
@@ -22922,23 +22910,23 @@
       </c>
       <c r="P48" s="22"/>
       <c r="Q48" s="98" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="R48" s="99"/>
       <c r="S48" s="98" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="T48" s="99"/>
       <c r="U48" s="27" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="V48" s="28"/>
       <c r="W48" s="98" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="X48" s="99"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -22955,7 +22943,7 @@
       </c>
       <c r="G49" s="20"/>
       <c r="H49" s="27" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="I49" s="28"/>
       <c r="J49" s="19" t="s">
@@ -22986,28 +22974,28 @@
       </c>
       <c r="X49" s="32"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C50" s="26"/>
       <c r="D50" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E50" s="26"/>
       <c r="F50" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I50" s="26"/>
       <c r="J50" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K50" s="28"/>
       <c r="N50" s="1" t="s">
@@ -23018,32 +23006,32 @@
       </c>
       <c r="P50" s="18"/>
       <c r="Q50" s="98" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="R50" s="99"/>
       <c r="S50" s="98" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="T50" s="99"/>
       <c r="U50" s="27" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="V50" s="28"/>
       <c r="W50" s="98" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="X50" s="99"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C51" s="34"/>
       <c r="D51" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E51" s="28"/>
       <c r="F51" s="19" t="s">
@@ -23051,7 +23039,7 @@
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I51" s="28"/>
       <c r="J51" s="19" t="s">
@@ -23066,15 +23054,15 @@
       </c>
       <c r="P51" s="20"/>
       <c r="Q51" s="17" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="R51" s="18"/>
       <c r="S51" s="17" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="T51" s="18"/>
       <c r="U51" s="27" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="V51" s="28"/>
       <c r="W51" s="19" t="s">
@@ -23082,16 +23070,16 @@
       </c>
       <c r="X51" s="20"/>
     </row>
-    <row r="52" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="52" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="C52" s="30"/>
       <c r="D52" s="29" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="E52" s="30"/>
       <c r="F52" s="51" t="s">
@@ -23103,34 +23091,34 @@
       </c>
       <c r="I52" s="52"/>
       <c r="J52" s="17" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="K52" s="18"/>
       <c r="N52" s="12" t="s">
         <v>45</v>
       </c>
       <c r="O52" s="17" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="P52" s="18"/>
       <c r="Q52" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="R52" s="18"/>
       <c r="S52" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="T52" s="18"/>
       <c r="U52" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="V52" s="18"/>
       <c r="W52" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="X52" s="18"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -23158,7 +23146,7 @@
         <v>48</v>
       </c>
       <c r="O53" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="P53" s="18"/>
       <c r="Q53" s="17" t="s">
@@ -23178,28 +23166,28 @@
       </c>
       <c r="X53" s="18"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C54" s="28"/>
       <c r="D54" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E54" s="28"/>
       <c r="F54" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="G54" s="52"/>
       <c r="H54" s="51" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="I54" s="52"/>
       <c r="J54" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K54" s="28"/>
       <c r="N54" s="12" t="s">
@@ -23222,28 +23210,28 @@
       </c>
       <c r="V54" s="18"/>
       <c r="W54" s="33" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="X54" s="34"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C55" s="26"/>
       <c r="D55" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E55" s="26"/>
       <c r="F55" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G55" s="26"/>
       <c r="H55" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I55" s="26"/>
       <c r="J55" s="21" t="s">
@@ -23274,36 +23262,36 @@
       </c>
       <c r="X55" s="22"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C56" s="30"/>
       <c r="D56" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="I56" s="30"/>
       <c r="J56" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="K56" s="30"/>
       <c r="S56" s="29" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="T56" s="30"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>51</v>
       </c>
@@ -23312,22 +23300,22 @@
       <c r="D57" s="21"/>
       <c r="E57" s="22"/>
       <c r="F57" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="I57" s="30"/>
       <c r="J57" s="29" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="K57" s="30"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>1</v>
       </c>
@@ -23341,7 +23329,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>2</v>
       </c>
@@ -23355,7 +23343,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>3</v>
       </c>
@@ -23370,7 +23358,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>4</v>
       </c>
@@ -23378,13 +23366,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
     </row>
-    <row r="64" spans="1:24" s="4" customFormat="1">
+    <row r="64" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
@@ -23397,7 +23385,7 @@
       <c r="W64" s="5"/>
       <c r="X64" s="5"/>
     </row>
-    <row r="65" spans="14:24" s="4" customFormat="1">
+    <row r="65" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
@@ -23410,7 +23398,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" spans="14:24" s="4" customFormat="1">
+    <row r="66" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
@@ -23913,7 +23901,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X60"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -23943,9 +23931,9 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -23978,7 +23966,7 @@
         <v>46318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -24011,7 +23999,7 @@
         <v>46339</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -24032,7 +24020,7 @@
       </c>
       <c r="I2" s="36"/>
       <c r="J2" s="17" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="K2" s="18"/>
       <c r="N2" s="1" t="s">
@@ -24047,11 +24035,11 @@
       </c>
       <c r="R2" s="36"/>
       <c r="S2" s="35" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="T2" s="36"/>
       <c r="U2" s="35" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="V2" s="36"/>
       <c r="W2" s="35" t="s">
@@ -24059,26 +24047,26 @@
       </c>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="75"/>
       <c r="C3" s="76"/>
       <c r="D3" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E3" s="28"/>
       <c r="F3" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I3" s="34"/>
       <c r="J3" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K3" s="28"/>
       <c r="N3" s="1" t="s">
@@ -24105,26 +24093,26 @@
       </c>
       <c r="X3" s="52"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="75"/>
       <c r="C4" s="76"/>
       <c r="D4" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E4" s="28"/>
       <c r="F4" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I4" s="34"/>
       <c r="J4" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K4" s="28"/>
       <c r="N4" s="1" t="s">
@@ -24151,26 +24139,26 @@
       </c>
       <c r="X4" s="52"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="75"/>
       <c r="C5" s="76"/>
       <c r="D5" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E5" s="28"/>
       <c r="F5" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I5" s="34"/>
       <c r="J5" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K5" s="28"/>
       <c r="N5" s="1" t="s">
@@ -24193,7 +24181,7 @@
       <c r="W5" s="91"/>
       <c r="X5" s="92"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -24241,26 +24229,26 @@
       </c>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="23" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G7" s="34"/>
       <c r="H7" s="91"/>
       <c r="I7" s="92"/>
       <c r="J7" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K7" s="28"/>
       <c r="N7" s="6" t="s">
@@ -24277,34 +24265,34 @@
       </c>
       <c r="T7" s="28"/>
       <c r="U7" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="V7" s="103"/>
       <c r="W7" s="91"/>
       <c r="X7" s="92"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="23" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G8" s="34"/>
       <c r="H8" s="23" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="17" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="7"/>
@@ -24313,11 +24301,11 @@
         <v>28</v>
       </c>
       <c r="O8" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P8" s="50"/>
       <c r="Q8" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="R8" s="50"/>
       <c r="S8" s="27" t="s">
@@ -24325,13 +24313,13 @@
       </c>
       <c r="T8" s="28"/>
       <c r="U8" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="V8" s="103"/>
       <c r="W8" s="91"/>
       <c r="X8" s="92"/>
     </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -24342,15 +24330,15 @@
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G9" s="34"/>
       <c r="H9" s="23" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="I9" s="24"/>
       <c r="J9" s="23" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="K9" s="24"/>
       <c r="L9" s="7"/>
@@ -24359,11 +24347,11 @@
         <v>32</v>
       </c>
       <c r="O9" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P9" s="50"/>
       <c r="Q9" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="R9" s="50"/>
       <c r="S9" s="91"/>
@@ -24373,85 +24361,83 @@
       <c r="W9" s="21"/>
       <c r="X9" s="22"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="104" t="s">
-        <v>323</v>
-      </c>
-      <c r="C10" s="105"/>
-      <c r="D10" s="104" t="s">
-        <v>323</v>
-      </c>
-      <c r="E10" s="105"/>
-      <c r="F10" s="104" t="s">
-        <v>323</v>
-      </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="104" t="s">
-        <v>323</v>
-      </c>
-      <c r="I10" s="105"/>
-      <c r="J10" s="104" t="s">
-        <v>323</v>
-      </c>
-      <c r="K10" s="105"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="K10" s="18"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="6" t="s">
         <v>35</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="P10" s="18"/>
       <c r="Q10" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="R10" s="18"/>
       <c r="S10" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="T10" s="18"/>
       <c r="U10" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="V10" s="18"/>
       <c r="W10" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="X10" s="18"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="104" t="s">
-        <v>326</v>
-      </c>
-      <c r="C11" s="105"/>
-      <c r="D11" s="104" t="s">
-        <v>326</v>
-      </c>
-      <c r="E11" s="105"/>
-      <c r="F11" s="104" t="s">
-        <v>326</v>
-      </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="104" t="s">
-        <v>326</v>
-      </c>
-      <c r="I11" s="105"/>
-      <c r="J11" s="104" t="s">
-        <v>326</v>
-      </c>
-      <c r="K11" s="105"/>
+      <c r="B11" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="I11" s="18"/>
+      <c r="J11" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="K11" s="18"/>
       <c r="N11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="P11" s="18"/>
       <c r="Q11" s="17" t="s">
@@ -24471,35 +24457,35 @@
       </c>
       <c r="X11" s="18"/>
     </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="K12" s="18"/>
       <c r="N12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="P12" s="18"/>
       <c r="Q12" s="17" t="s">
@@ -24519,7 +24505,7 @@
       </c>
       <c r="X12" s="18"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -24528,7 +24514,7 @@
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="19" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="E13" s="20"/>
       <c r="F13" s="17" t="s">
@@ -24547,7 +24533,7 @@
         <v>45</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="P13" s="18"/>
       <c r="Q13" s="17" t="s">
@@ -24567,7 +24553,7 @@
       </c>
       <c r="X13" s="18"/>
     </row>
-    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -24588,7 +24574,7 @@
       </c>
       <c r="I14" s="18"/>
       <c r="J14" s="23" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="K14" s="24"/>
       <c r="N14" s="1" t="s">
@@ -24609,7 +24595,7 @@
       <c r="W14" s="21"/>
       <c r="X14" s="22"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -24645,7 +24631,7 @@
       <c r="W15" s="21"/>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -24677,7 +24663,7 @@
       <c r="W16" s="21"/>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -24698,7 +24684,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -24722,9 +24708,9 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -24757,7 +24743,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -24790,7 +24776,7 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -24838,20 +24824,20 @@
       </c>
       <c r="X20" s="36"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E21" s="28"/>
       <c r="F21" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G21" s="28"/>
       <c r="H21" s="29" t="s">
@@ -24859,7 +24845,7 @@
       </c>
       <c r="I21" s="30"/>
       <c r="J21" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K21" s="28"/>
       <c r="N21" s="1" t="s">
@@ -24886,20 +24872,20 @@
       </c>
       <c r="X21" s="52"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C22" s="28"/>
       <c r="D22" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E22" s="28"/>
       <c r="F22" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G22" s="28"/>
       <c r="H22" s="29" t="s">
@@ -24907,7 +24893,7 @@
       </c>
       <c r="I22" s="30"/>
       <c r="J22" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K22" s="28"/>
       <c r="N22" s="1" t="s">
@@ -24934,26 +24920,26 @@
       </c>
       <c r="X22" s="52"/>
     </row>
-    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E23" s="28"/>
       <c r="F23" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G23" s="28"/>
       <c r="H23" s="21"/>
       <c r="I23" s="22"/>
       <c r="J23" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K23" s="28"/>
       <c r="N23" s="1" t="s">
@@ -24976,7 +24962,7 @@
       </c>
       <c r="X23" s="28"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -25024,12 +25010,12 @@
       </c>
       <c r="X24" s="20"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="29" t="s">
@@ -25037,7 +25023,7 @@
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="83" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="G25" s="84"/>
       <c r="H25" s="91"/>
@@ -25064,26 +25050,26 @@
       </c>
       <c r="X25" s="28"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="75"/>
       <c r="C26" s="76"/>
       <c r="D26" s="19" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="E26" s="20"/>
       <c r="F26" s="19" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="83" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="I26" s="84"/>
       <c r="J26" s="83" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="K26" s="84"/>
       <c r="L26" s="7"/>
@@ -25096,11 +25082,11 @@
       </c>
       <c r="P26" s="28"/>
       <c r="Q26" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="R26" s="18"/>
       <c r="S26" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="T26" s="18"/>
       <c r="U26" s="27" t="s">
@@ -25112,7 +25098,7 @@
       </c>
       <c r="X26" s="28"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -25123,15 +25109,15 @@
       </c>
       <c r="E27" s="30"/>
       <c r="F27" s="83" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="G27" s="84"/>
       <c r="H27" s="83" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="I27" s="84"/>
       <c r="J27" s="83" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="K27" s="84"/>
       <c r="L27" s="7"/>
@@ -25140,48 +25126,48 @@
         <v>32</v>
       </c>
       <c r="O27" s="17" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="P27" s="18"/>
       <c r="Q27" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="R27" s="18"/>
       <c r="S27" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="T27" s="18"/>
       <c r="U27" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="V27" s="18"/>
       <c r="W27" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="G28" s="18"/>
       <c r="H28" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="I28" s="18"/>
       <c r="J28" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="K28" s="18"/>
       <c r="L28" s="7"/>
@@ -25210,28 +25196,28 @@
       </c>
       <c r="X28" s="18"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="E29" s="18"/>
       <c r="F29" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="G29" s="18"/>
       <c r="H29" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="I29" s="18"/>
       <c r="J29" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="K29" s="18"/>
       <c r="L29" s="7"/>
@@ -25260,12 +25246,12 @@
       </c>
       <c r="X29" s="18"/>
     </row>
-    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="17" t="s">
@@ -25290,7 +25276,7 @@
         <v>40</v>
       </c>
       <c r="O30" s="17" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="P30" s="18"/>
       <c r="Q30" s="17" t="s">
@@ -25310,12 +25296,12 @@
       </c>
       <c r="X30" s="18"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="17" t="s">
@@ -25354,16 +25340,16 @@
       </c>
       <c r="V31" s="18"/>
       <c r="W31" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="X31" s="18"/>
     </row>
-    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="C32" s="18"/>
       <c r="D32" s="17" t="s">
@@ -25398,13 +25384,13 @@
       </c>
       <c r="T32" s="18"/>
       <c r="U32" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="V32" s="18"/>
       <c r="W32" s="21"/>
       <c r="X32" s="22"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -25432,25 +25418,25 @@
         <v>49</v>
       </c>
       <c r="O33" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="P33" s="103"/>
       <c r="Q33" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="R33" s="103"/>
       <c r="S33" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="T33" s="103"/>
       <c r="U33" s="21"/>
       <c r="V33" s="22"/>
       <c r="W33" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="X33" s="103"/>
     </row>
-    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -25470,25 +25456,25 @@
         <v>50</v>
       </c>
       <c r="O34" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="P34" s="103"/>
       <c r="Q34" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="R34" s="103"/>
       <c r="S34" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="T34" s="103"/>
       <c r="U34" s="21"/>
       <c r="V34" s="22"/>
       <c r="W34" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="X34" s="103"/>
     </row>
-    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -25509,7 +25495,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -25524,9 +25510,9 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -25561,7 +25547,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="1" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>1</v>
@@ -25594,7 +25580,7 @@
         <v>46353</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -25607,7 +25593,7 @@
       </c>
       <c r="E38" s="36"/>
       <c r="F38" s="35" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
       <c r="G38" s="36"/>
       <c r="H38" s="35" t="s">
@@ -25644,24 +25630,24 @@
       </c>
       <c r="X38" s="36"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="C39" s="18"/>
       <c r="D39" s="17" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="17" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="G39" s="18"/>
       <c r="H39" s="17" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="I39" s="18"/>
       <c r="J39" s="17" t="s">
@@ -25694,7 +25680,7 @@
       </c>
       <c r="X39" s="52"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -25703,7 +25689,7 @@
       </c>
       <c r="C40" s="28"/>
       <c r="D40" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E40" s="50"/>
       <c r="F40" s="27" t="s">
@@ -25742,7 +25728,7 @@
       </c>
       <c r="X40" s="52"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -25788,7 +25774,7 @@
       </c>
       <c r="X41" s="52"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -25836,7 +25822,7 @@
       </c>
       <c r="X42" s="20"/>
     </row>
-    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -25845,15 +25831,15 @@
       </c>
       <c r="C43" s="28"/>
       <c r="D43" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E43" s="50"/>
       <c r="F43" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="G43" s="103"/>
       <c r="H43" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I43" s="50"/>
       <c r="J43" s="17" t="s">
@@ -25884,7 +25870,7 @@
       </c>
       <c r="X43" s="28"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -25893,11 +25879,11 @@
       <c r="D44" s="75"/>
       <c r="E44" s="76"/>
       <c r="F44" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="G44" s="103"/>
       <c r="H44" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I44" s="50"/>
       <c r="J44" s="17" t="s">
@@ -25928,28 +25914,28 @@
       </c>
       <c r="X44" s="28"/>
     </row>
-    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="C45" s="18"/>
       <c r="D45" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="E45" s="18"/>
       <c r="F45" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="G45" s="18"/>
       <c r="H45" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="I45" s="18"/>
       <c r="J45" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="K45" s="18"/>
       <c r="N45" s="6" t="s">
@@ -25974,28 +25960,28 @@
       </c>
       <c r="X45" s="28"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="C46" s="18"/>
       <c r="D46" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="E46" s="18"/>
       <c r="F46" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="G46" s="18"/>
       <c r="H46" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="I46" s="18"/>
       <c r="J46" s="17" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="K46" s="18"/>
       <c r="L46" s="7"/>
@@ -26004,36 +25990,36 @@
         <v>35</v>
       </c>
       <c r="O46" s="17" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="P46" s="18"/>
       <c r="Q46" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="R46" s="18"/>
       <c r="S46" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="T46" s="18"/>
       <c r="U46" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="V46" s="18"/>
       <c r="W46" s="17" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B47" s="83" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="C47" s="84"/>
       <c r="D47" s="83" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="E47" s="84"/>
       <c r="F47" s="27" t="s">
@@ -26074,16 +26060,16 @@
       </c>
       <c r="X47" s="24"/>
     </row>
-    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B48" s="83" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="C48" s="84"/>
       <c r="D48" s="83" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="E48" s="84"/>
       <c r="F48" s="21"/>
@@ -26122,26 +26108,26 @@
       </c>
       <c r="X48" s="24"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B49" s="75"/>
       <c r="C49" s="76"/>
       <c r="D49" s="17" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="17" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="G49" s="18"/>
       <c r="H49" s="17" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="I49" s="18"/>
       <c r="J49" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K49" s="50"/>
       <c r="L49" s="7"/>
@@ -26150,11 +26136,11 @@
         <v>45</v>
       </c>
       <c r="O49" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="P49" s="103"/>
       <c r="Q49" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="R49" s="103"/>
       <c r="S49" s="75"/>
@@ -26166,12 +26152,12 @@
       <c r="W49" s="21"/>
       <c r="X49" s="22"/>
     </row>
-    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="17" t="s">
@@ -26194,32 +26180,32 @@
         <v>48</v>
       </c>
       <c r="O50" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="P50" s="103"/>
       <c r="Q50" s="102" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="R50" s="103"/>
       <c r="S50" s="17" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="T50" s="18"/>
       <c r="U50" s="17" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="V50" s="18"/>
       <c r="W50" s="17" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="C51" s="18"/>
       <c r="D51" s="17" t="s">
@@ -26246,24 +26232,24 @@
       <c r="Q51" s="21"/>
       <c r="R51" s="22"/>
       <c r="S51" s="17" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="T51" s="18"/>
       <c r="U51" s="17" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="V51" s="18"/>
       <c r="W51" s="17" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="X51" s="18"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="C52" s="18"/>
       <c r="D52" s="17" t="s">
@@ -26277,7 +26263,7 @@
       <c r="H52" s="21"/>
       <c r="I52" s="22"/>
       <c r="J52" s="49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K52" s="50"/>
       <c r="N52" s="1" t="s">
@@ -26294,7 +26280,7 @@
       <c r="W52" s="21"/>
       <c r="X52" s="22"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -26308,7 +26294,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -26322,7 +26308,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -26337,7 +26323,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -26345,17 +26331,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -26828,7 +26814,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:Y61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1" style="5" customWidth="1"/>
     <col min="2" max="2" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -26858,10 +26844,10 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
-    <row r="2" spans="2:25">
+    <row r="1" spans="2:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -26894,7 +26880,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -26927,7 +26913,7 @@
         <v>46381</v>
       </c>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
@@ -26973,7 +26959,7 @@
       <c r="X3" s="59"/>
       <c r="Y3" s="60"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
@@ -27009,7 +26995,7 @@
       <c r="X4" s="59"/>
       <c r="Y4" s="60"/>
     </row>
-    <row r="5" spans="2:25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
@@ -27025,10 +27011,10 @@
         <v>31</v>
       </c>
       <c r="H5" s="28"/>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="20"/>
+      <c r="J5" s="40"/>
       <c r="K5" s="27" t="s">
         <v>31</v>
       </c>
@@ -27047,7 +27033,7 @@
       <c r="X5" s="59"/>
       <c r="Y5" s="60"/>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
@@ -27083,7 +27069,7 @@
       <c r="X6" s="59"/>
       <c r="Y6" s="60"/>
     </row>
-    <row r="7" spans="2:25">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
@@ -27129,16 +27115,16 @@
       <c r="X7" s="59"/>
       <c r="Y7" s="60"/>
     </row>
-    <row r="8" spans="2:25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="91"/>
@@ -27163,16 +27149,16 @@
       <c r="X8" s="59"/>
       <c r="Y8" s="60"/>
     </row>
-    <row r="9" spans="2:25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="F9" s="18"/>
       <c r="G9" s="75"/>
@@ -27195,7 +27181,7 @@
       <c r="X9" s="59"/>
       <c r="Y9" s="60"/>
     </row>
-    <row r="10" spans="2:25">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
         <v>32</v>
       </c>
@@ -27229,7 +27215,7 @@
       <c r="X10" s="59"/>
       <c r="Y10" s="60"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
         <v>35</v>
       </c>
@@ -27263,7 +27249,7 @@
       <c r="X11" s="59"/>
       <c r="Y11" s="60"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
@@ -27293,7 +27279,7 @@
       <c r="X12" s="59"/>
       <c r="Y12" s="60"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>40</v>
       </c>
@@ -27305,10 +27291,10 @@
         <v>125</v>
       </c>
       <c r="H13" s="18"/>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="J13" s="20"/>
+      <c r="J13" s="40"/>
       <c r="K13" s="21"/>
       <c r="L13" s="22"/>
       <c r="O13" s="1" t="s">
@@ -27325,7 +27311,7 @@
       <c r="X13" s="59"/>
       <c r="Y13" s="60"/>
     </row>
-    <row r="14" spans="2:25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>45</v>
       </c>
@@ -27363,28 +27349,28 @@
       <c r="X14" s="59"/>
       <c r="Y14" s="60"/>
     </row>
-    <row r="15" spans="2:25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J15" s="18"/>
       <c r="K15" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L15" s="18"/>
       <c r="O15" s="1" t="s">
@@ -27401,7 +27387,7 @@
       <c r="X15" s="59"/>
       <c r="Y15" s="60"/>
     </row>
-    <row r="16" spans="2:25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B16" s="12" t="s">
         <v>49</v>
       </c>
@@ -27429,7 +27415,7 @@
       <c r="X16" s="59"/>
       <c r="Y16" s="60"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
@@ -27457,7 +27443,7 @@
       <c r="X17" s="59"/>
       <c r="Y17" s="60"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -27480,7 +27466,7 @@
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -27492,9 +27478,9 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -27527,7 +27513,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -27560,7 +27546,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
@@ -27606,7 +27592,7 @@
       <c r="X21" s="59"/>
       <c r="Y21" s="60"/>
     </row>
-    <row r="22" spans="2:25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
@@ -27634,7 +27620,7 @@
       <c r="X22" s="59"/>
       <c r="Y22" s="60"/>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
@@ -27666,7 +27652,7 @@
       <c r="X23" s="59"/>
       <c r="Y23" s="60"/>
     </row>
-    <row r="24" spans="2:25">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
@@ -27694,7 +27680,7 @@
       <c r="X24" s="59"/>
       <c r="Y24" s="60"/>
     </row>
-    <row r="25" spans="2:25">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
@@ -27740,7 +27726,7 @@
       <c r="X25" s="59"/>
       <c r="Y25" s="60"/>
     </row>
-    <row r="26" spans="2:25">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
@@ -27768,7 +27754,7 @@
       <c r="X26" s="59"/>
       <c r="Y26" s="60"/>
     </row>
-    <row r="27" spans="2:25">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B27" s="6" t="s">
         <v>28</v>
       </c>
@@ -27798,7 +27784,7 @@
       <c r="X27" s="59"/>
       <c r="Y27" s="60"/>
     </row>
-    <row r="28" spans="2:25">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B28" s="6" t="s">
         <v>32</v>
       </c>
@@ -27832,7 +27818,7 @@
       <c r="X28" s="59"/>
       <c r="Y28" s="60"/>
     </row>
-    <row r="29" spans="2:25">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B29" s="6" t="s">
         <v>35</v>
       </c>
@@ -27860,7 +27846,7 @@
       <c r="X29" s="59"/>
       <c r="Y29" s="60"/>
     </row>
-    <row r="30" spans="2:25">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
@@ -27890,7 +27876,7 @@
       <c r="X30" s="59"/>
       <c r="Y30" s="60"/>
     </row>
-    <row r="31" spans="2:25">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
@@ -27920,7 +27906,7 @@
       <c r="X31" s="59"/>
       <c r="Y31" s="60"/>
     </row>
-    <row r="32" spans="2:25">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B32" s="12" t="s">
         <v>45</v>
       </c>
@@ -27950,7 +27936,7 @@
       <c r="X32" s="59"/>
       <c r="Y32" s="60"/>
     </row>
-    <row r="33" spans="2:25">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>48</v>
       </c>
@@ -27980,7 +27966,7 @@
       <c r="X33" s="59"/>
       <c r="Y33" s="60"/>
     </row>
-    <row r="34" spans="2:25">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B34" s="12" t="s">
         <v>49</v>
       </c>
@@ -28010,7 +27996,7 @@
       <c r="X34" s="59"/>
       <c r="Y34" s="60"/>
     </row>
-    <row r="35" spans="2:25">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -28040,7 +28026,7 @@
       <c r="X35" s="59"/>
       <c r="Y35" s="60"/>
     </row>
-    <row r="36" spans="2:25">
+    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B36" s="5"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -28065,7 +28051,7 @@
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
     </row>
-    <row r="37" spans="2:25">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="5"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -28090,9 +28076,9 @@
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
     </row>
-    <row r="38" spans="2:25">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>
@@ -28137,7 +28123,7 @@
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
     </row>
-    <row r="39" spans="2:25">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
@@ -28174,7 +28160,7 @@
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
     </row>
-    <row r="40" spans="2:25">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
@@ -28201,7 +28187,7 @@
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
     </row>
-    <row r="41" spans="2:25">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
@@ -28228,7 +28214,7 @@
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
     </row>
-    <row r="42" spans="2:25">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>21</v>
       </c>
@@ -28255,7 +28241,7 @@
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
     </row>
-    <row r="43" spans="2:25">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
@@ -28292,7 +28278,7 @@
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
     </row>
-    <row r="44" spans="2:25">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B44" s="6" t="s">
         <v>26</v>
       </c>
@@ -28319,7 +28305,7 @@
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
     </row>
-    <row r="45" spans="2:25">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B45" s="6" t="s">
         <v>28</v>
       </c>
@@ -28346,7 +28332,7 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
     </row>
-    <row r="46" spans="2:25">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B46" s="6" t="s">
         <v>32</v>
       </c>
@@ -28373,7 +28359,7 @@
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
     </row>
-    <row r="47" spans="2:25">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" s="6" t="s">
         <v>35</v>
       </c>
@@ -28400,7 +28386,7 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
     </row>
-    <row r="48" spans="2:25">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>37</v>
       </c>
@@ -28427,7 +28413,7 @@
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
     </row>
-    <row r="49" spans="2:25">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>40</v>
       </c>
@@ -28454,14 +28440,14 @@
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
     </row>
-    <row r="50" spans="2:25">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B50" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C50" s="75"/>
       <c r="D50" s="76"/>
       <c r="E50" s="19" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="F50" s="20"/>
       <c r="G50" s="75"/>
@@ -28483,7 +28469,7 @@
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
     </row>
-    <row r="51" spans="2:25">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
         <v>48</v>
       </c>
@@ -28510,7 +28496,7 @@
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
     </row>
-    <row r="52" spans="2:25">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B52" s="12" t="s">
         <v>49</v>
       </c>
@@ -28537,7 +28523,7 @@
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
     </row>
-    <row r="53" spans="2:25">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>50</v>
       </c>
@@ -28564,7 +28550,7 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
     </row>
-    <row r="54" spans="2:25">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B54" s="5"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -28589,7 +28575,7 @@
       <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
     </row>
-    <row r="55" spans="2:25">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B55" s="5">
         <v>1</v>
       </c>
@@ -28605,7 +28591,7 @@
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="2:25">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B56" s="5">
         <v>2</v>
       </c>
@@ -28619,7 +28605,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:25">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B57" s="8">
         <v>3</v>
       </c>
@@ -28634,7 +28620,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="2:25">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B58" s="5">
         <v>4</v>
       </c>
@@ -28648,7 +28634,7 @@
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="2:25">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="E59" s="5"/>
@@ -28658,7 +28644,7 @@
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="2:25">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="E60" s="5"/>
@@ -28668,7 +28654,7 @@
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="2:25">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
     </row>
@@ -29073,26 +29059,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="294cf202-ea3b-4503-9866-4c6f0069ff97">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001EA62548CDE95149AC1BC8AF3B662818" ma:contentTypeVersion="18" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="6b6114bc50e08fd23ab8a89130bf9f95">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="294cf202-ea3b-4503-9866-4c6f0069ff97" xmlns:ns3="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd29bd8d73cdc406ea9db8e88d30c8e6" ns2:_="" ns3:_="">
     <xsd:import namespace="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
@@ -29341,14 +29307,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="294cf202-ea3b-4503-9866-4c6f0069ff97">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>